--- a/HWA_Lead_Tracker.xlsx
+++ b/HWA_Lead_Tracker.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Leads" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leads" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,25 +429,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P33"/>
+  <dimension ref="A1:O48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="45" customWidth="1" min="10" max="10"/>
-    <col width="40" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="6" customWidth="1" min="13" max="13"/>
-    <col width="7" customWidth="1" min="14" max="14"/>
-    <col width="11" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="42" customWidth="1" min="12" max="12"/>
+    <col width="55" customWidth="1" min="13" max="13"/>
+    <col width="45" customWidth="1" min="14" max="14"/>
+    <col width="45" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -468,67 +467,62 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>IG Username</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>IG Profile Link</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>City</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Phone Type</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Profile Analysis</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Products Needed</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Followed</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>WhatsApp</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Channels</t>
         </is>
       </c>
     </row>
@@ -555,61 +549,50 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>https://www.instagram.com/goldenkyu_bcn/</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>Barcelona</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>+34670425918</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>info@goldenkyu.com</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>goldenkyu.com</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>COMPLETE: IG followed + IG DM + WA + email sent</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
         <is>
           <t>Warm lead - follows mibrointl. FitBoxing/Boxeo/Kickboxing, 3775 followers</t>
         </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P2" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -628,61 +611,54 @@
           <t>Gym/Club</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>@kickbarcelona</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>https://www.instagram.com/kickbarcelona/</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>L'Hospitalet</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>+34635541239</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>kickbarcelona@gmail.com</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>kickbarcelona.com</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>COMPLETE: IG followed + IG DM + email + WA sent (email re-confirmed v4)</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P3" t="n">
-        <v>4</v>
-      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -700,61 +676,54 @@
           <t>School</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>@warriorsbarcelona</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>https://www.instagram.com/warriorsbarcelona/</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>Barcelona</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>+34620953033</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>hola@warriorsbarcelona.com</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>warriorsbarcelona.com</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>COMPLETE: already-following + IG DM + email + WA sent (email re-confirmed v4)</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P4" t="n">
-        <v>4</v>
-      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -779,53 +748,42 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>https://www.instagram.com/kenkyukaidojo/</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>Madrid</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
         <is>
           <t>info@gimnasiokenkyukai.com</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>gimnasiokenkyukai.com</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>COMPLETE: IG followed + IG DM + email sent</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
         <is>
           <t>prestigious martial arts gym in Madrid</t>
         </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -851,53 +809,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>https://www.instagram.com/theacademybcn/</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>Barcelona</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
         <is>
           <t>info@bcnma.com</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>bcnma.com</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>COMPLETE: IG followed + IG DM sent + email sent (phones not on WhatsApp)</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
         <is>
           <t>MMA/BJJ/thai boxing academy in Barcelona</t>
         </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -916,44 +863,45 @@
           <t>Academy</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>@instituto_de_artes_marciales_</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>https://www.instagram.com/instituto_de_artes_marciales_/</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>Madrid</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>info@institutodeartesmarciales.com</t>
-        </is>
-      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
+          <t>info@institutodeartesmarciales.com</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
           <t>COMPLETE: follow=None dm=None email=sent wa=None</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
         <is>
           <t>Instituto de Artes Marciales, Madrid - jiu jitsu</t>
         </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -979,61 +927,50 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>https://www.instagram.com/invictamaa/</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>Porto</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>351910479457</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>info@invictamaa.com</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>invictamaa.com</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>COMPLETE: follow=ok dm=sent email=sent wa={"ok":true,"last":["Hola Invicta Martial Arts! \n\n\n\nwe make c"]}</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
         <is>
           <t>martial arts school in Porto since 2014</t>
         </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P8" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -1053,31 +990,32 @@
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
         <is>
           <t>Porto</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
         <is>
           <t>SKIP: no contact found tonight</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="n">
-        <v>0</v>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>IG handle unverified | Facebook only (legion.combat.porto) - no IG found</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -1096,33 +1034,38 @@
           <t>Gym</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>@nfktrainingcenter</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nfktrainingcenter/</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
         <is>
           <t>nfktrainingcenter.pt</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>SKIP: no contact found tonight</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1147,41 +1090,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>https://www.instagram.com/bjjelitetopteam/</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>Barcelona</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
         <is>
           <t>COMPLETE: follow=ok dm=sent email=None wa=None</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
         <is>
           <t>from IG suggestions</t>
         </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1207,41 +1143,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>https://www.instagram.com/wamai_official/</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>Barcelona</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
         <is>
           <t>COMPLETE: follow=ok dm=sent email=None wa=None</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
         <is>
           <t>from IG suggestions</t>
         </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1267,41 +1196,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>https://www.instagram.com/gripacademy_bjj_crosstraining/</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>Barcelona</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
         <is>
           <t>COMPLETE: follow=ok dm=sent email=None wa=None</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
         <is>
           <t>from IG suggestions</t>
         </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1325,39 +1247,32 @@
           <t>@revolutionmartialartsoficial</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/revolutionmartialartsoficial/</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
         <is>
           <t>COMPLETE: follow=ok dm=sent email=None wa=None</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
         <is>
           <t>from IG suggestions</t>
         </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1383,41 +1298,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>https://www.instagram.com/esport.rogentbcn/</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>Barcelona</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
         <is>
           <t>COMPLETE: follow=ok dm=sent email=None wa=None</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
         <is>
           <t>from IG suggestions</t>
         </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1443,41 +1351,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>https://www.instagram.com/cerdanyolafightclub/</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>Cerdanyola</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
         <is>
           <t>COMPLETE: follow=ok dm=sent email=None wa=None</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
         <is>
           <t>from IG suggestions</t>
         </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1503,41 +1404,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>https://www.instagram.com/troopersboxingstudio/</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>Barcelona</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
         <is>
           <t>COMPLETE: follow=ok dm=sent email=None wa=None</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
         <is>
           <t>from IG suggestions</t>
         </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1563,41 +1457,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>https://www.instagram.com/zonadecombateripollet/</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>Ripollet</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
         <is>
           <t>COMPLETE: follow=ok dm=sent email=None wa=None</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
         <is>
           <t>from IG suggestions</t>
         </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1616,32 +1503,41 @@
           <t>School</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>@dojosakura</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>https://www.instagram.com/dojosakura/</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>Lisboa</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
         <is>
           <t>SKIP: no contact found tonight</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="n">
-        <v>0</v>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>NOTE: IG shows Pampatar, Venezuela location - dojosakura.es may be unrelated. Needs verification before contact.</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -1660,32 +1556,41 @@
           <t>Academy</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>@somosvma</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>https://www.instagram.com/somosvma/</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>Lisboa</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
         <is>
           <t>SKIP: no contact found tonight</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="n">
-        <v>0</v>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>IG handle unverified</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -1709,59 +1614,48 @@
           <t>@ippongear_spain</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr">
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ippongear_spain/</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>34611612163</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
         <is>
           <t>info@ippongear.es</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>ippongear.es</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>COMPLETE: follow=ok dm=sent email=sent wa={"ok":true,"last":["Hola Ippon Gear España! \n\n\n\nHola Ippon G"]}</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
         <is>
           <t>official IJF/IBJJF distributor in Spain - B2B partnership lead</t>
         </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P21" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -1780,56 +1674,57 @@
           <t>Gym</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>@splintersmadrid</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>https://www.instagram.com/splintersmadrid/</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>Madrid</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>34622212369</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
         <is>
           <t>splintersmadrid@gmail.com</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>splintersjiujitsu.com</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>COMPLETE: follow=None dm=None email=sent wa={"ok":true,"last":["Hola Splinters Jiu-Jitsu &amp; MMA! \n\n\n\ngrea"]}</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>BJJ/MMA/kickboxing in central Madrid - WhatsApp-only number</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P22" t="n">
-        <v>2</v>
+          <t>BJJ/MMA/kickboxing in central Madrid - WhatsApp-only number | CONFIRMED via DOJOTAP post: Splinters Madrid BJJ/MMA. Central Madrid (Don Quijote 28).</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -1849,47 +1744,40 @@
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
         <is>
           <t>Madrid</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr">
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
         <is>
           <t>lotusbjjmadrid@hotmail.com</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>bjjmadrid.com</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>COMPLETE: follow=None dm=None email=sent wa=None</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Lotus Club HQ Madrid, multiple sede - sells gear too</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="n">
-        <v>1</v>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Lotus Club HQ Madrid, multiple sede - sells gear too | No IG found on lotusbjj.com or search - email is the channel</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -1909,55 +1797,48 @@
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
         <is>
           <t>Sevilla</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>34625621710</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
         <is>
           <t>info@judosevilla.com</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>judosevilla.com</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>COMPLETE: follow=None dm=None email=sent wa={"ok":true,"last":["Hola Al-Andalus Judo Sevilla! \n\n\n\nwe mak"]}</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>judo club in Sevilla</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P24" t="n">
-        <v>2</v>
+          <t>judo club in Sevilla | No IG found - email info@judosevilla.com is the channel</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -1976,56 +1857,57 @@
           <t>Gym</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>@kalmmafightclub</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
+          <t>https://www.instagram.com/kalmmafightclub/</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t>Madrid</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>34699506391</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
         <is>
           <t>info@kalmmafightclub.com</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>kalmmafightclub.com</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>COMPLETE: follow=None dm=None email=sent wa={"ok":true,"last":["Hola KALMMA Fight Club! \n\n\n\nmartial arts"]}</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
         <is>
           <t>3 centers in Madrid, big tatami, multibrand shop</t>
         </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P25" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -2045,47 +1927,44 @@
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
         <is>
           <t>Madrid</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>34649036805</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
           <t>judokitaro.es</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>COMPLETE: follow=None dm=None email=None wa={"ok":true,"last":["Hola Judo Kitaro! \n\n\n\nwe make custom mar"]}</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>judo school for kids and adults in Madrid</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P26" t="n">
-        <v>1</v>
+          <t>judo school for kids and adults in Madrid | No IG found - phone 649 03 68 05 is the channel</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -2111,57 +1990,50 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
+          <t>https://www.instagram.com/brazilian.fight.lisboa/</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t>Lisboa</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>351910349061</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
         <is>
           <t>brazilian.fight.lisboa@gmail.com</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>brazilianfightlisboa.com</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>COMPLETE: follow=no-btn dm=sent email=sent wa={"ok":true,"last":["Hola Brazilian Fight Lisboa! \n\n\n\nwe make"]}</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr">
         <is>
           <t>JJ academy in Arroios Lisboa since 2019</t>
         </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P27" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -2180,56 +2052,57 @@
           <t>Gym</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>@koteamportugal</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
+          <t>https://www.instagram.com/koteamportugal/</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t>Carcavelos</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>351963919855</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
         <is>
           <t>info@koteam.pt</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>koteam.pt</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>COMPLETE: follow=None dm=None email=sent wa={"ok":true,"last":["Hola K.O. Team Portugal! \n\n\n\nwe produce "]}</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>kickboxing/muay thai/MMA - 14 gyms Lisboa area</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P28" t="n">
-        <v>2</v>
+          <t>kickboxing/muay thai/MMA - 14 gyms Lisboa area | IG handle unverified | EXISTS but tiny (2 followers, 0 posts) - not their real account. Use email info@koteam.pt</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -2255,53 +2128,46 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
+          <t>https://www.instagram.com/team.duramuk/</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
           <t>Lisboa</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>351967734557</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
           <t>teamduramuk.pt</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>COMPLETE: IG followed + IG DM + WA sent (no public email - WhatsApp-only contact)</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>Muay Thai &amp; Kickboxing Lisboa since 2008, founder World Champion, 3044 IG followers. Contact via WhatsApp only.</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P29" t="n">
-        <v>3</v>
+          <t>Muay Thai &amp; Kickboxing Lisboa since 2008, founder World Champion, 3044 IG followers. Contact via WhatsApp only.</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -2320,48 +2186,53 @@
           <t>Academy</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>@fiveelementsjiujitsu</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
+          <t>https://www.instagram.com/fiveelementsjiujitsu/</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
           <t>Lisboa</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>351915267080</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
           <t>fiveelementsjiujitsu.com</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>COMPLETE: follow=None dm=None email=None wa={"ok":true,"last":["Hola Five Elements Academy Jiu-Jitsu! \n\n"]}</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>jiu jitsu academy in Lisboa, 228 ratings</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P30" t="n">
-        <v>1</v>
+          <t>jiu jitsu academy in Lisboa, 228 ratings | IG handle unverified</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -2381,47 +2252,44 @@
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
         <is>
           <t>Lisboa</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>351967599340</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
           <t>gracielisboa.com</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>COMPLETE: follow=None dm=None email=None wa={"ok":true,"last":["Hola Gracie Lisboa! \n\n\n\nmartial arts &amp; s"]}</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>Gracie jiu jitsu Lisboa</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P31" t="n">
-        <v>1</v>
+          <t>Gracie jiu jitsu Lisboa | IG handle unverified | gracielisboa handle = wrong religious account. Real academy IG unknown - use email</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -2441,55 +2309,48 @@
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
         <is>
           <t>Amadora</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>351961320560</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
         <is>
           <t>apko.geral@gmail.com</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>apko.pt</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>COMPLETE: follow=None dm=None email=sent wa={"ok":true,"last":["Hola APKO Okinawa Karate! \n\n\n\nmartial ar"]}</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr">
         <is>
           <t>Okinawa karate association Lisboa and Portalegre</t>
         </is>
-      </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P32" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2508,49 +2369,889 @@
           <t>Gym</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>@lisboafightclub</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
+          <t>https://www.instagram.com/lisboafightclub/</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
           <t>Sacavem</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr">
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
         <is>
           <t>arenaffc@gmail.com</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>lisboafightclub.com</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>COMPLETE: follow=None dm=None email=sent wa=None</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>kickboxing muaythai boxing training center</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="n">
-        <v>1</v>
-      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>kickboxing muaythai boxing training center | IG handle unverified</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>L033</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Spitfire Academy Berlin</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Martial Arts School</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>@spitfiregymberlin</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/spitfiregymberlin/</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>FAILED at 00:43:10: {'follow': None, 'dm': None, 'email': None, 'wa': None}</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>small but real BJJ club</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>L034</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>LAXA BJJ Academy</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Martial Arts School</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>@laxa_bjj_studio</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/laxa_bjj_studio/</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>FAILED at 00:46:51: {'follow': None, 'dm': None, 'email': None, 'wa': None}</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>linktr.ee/laxajiujitsuacademy for contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>L035</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>BJJ Aachen</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Sports Club</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>@bjj_aachen</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bjj_aachen/</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Aachen</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>info@bjjaachen.com</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>FAILED at 00:52:08: {'follow': None, 'dm': None, 'email': 'compose-focus-never-r</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>WARM LEAD - follows mibrointl. Email found on site.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>L036</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Boxe Thai 15</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Association/Club</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>@boxethai15</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/boxethai15/</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Paris 15e</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>contact@boxethai15.com</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>FAILED at 00:56:49: {'follow': None, 'dm': None, 'email': 'compose-focus-never-r</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Paris club - email found</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>L037</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Annecy Fight Club</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Sports team</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>@annecy_fight_club</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/annecy_fight_club/</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Annecy</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>FAILED at 01:00:13: {'follow': None, 'dm': None, 'email': None, 'wa': None}</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>contact in bio highlights - need to check IG story highlights</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>L038</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Accademia Europea Milano</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>@accademia.europea.milano</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/accademia.europea.milano/</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Milano</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>info@accademiaeuropea.net</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>FAILED at 01:05:25: {'follow': None, 'dm': None, 'email': 'compose-focus-never-r</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>BIG multi-discipline gym - since 1989. Email from accademiaeuropea.net</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>L039</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Kick &amp; Punch Milano DownTown</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Sports club</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>@kickandpunch_milano_downtown</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kickandpunch_milano_downtown/</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Milano</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>393914124452</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>HOT LEAD - phone in bio, 6.6K followers, sponsors. WhatsApp target.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>L040</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Haven BJJ Rotterdam</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>BJJ &amp; Grappling Gym</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>@havenbjj</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/havenbjj/</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Rotterdam</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>info@havenbjj.nl</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>FAILED at 01:16:53: {'follow': None, 'dm': None, 'email': 'compose-focus-never-r</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Big Rotterdam gym - contact via havenbjj.nl/links</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>L041</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>10th Planet Jiu-Jitsu Amsterdam</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Martial Arts School</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>@10thplanetjiujitsuamsterdam</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/10thplanetjiujitsuamsterdam/</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>10pjitsamsterdam@gmail.com</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>COMPLETE: IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Famous franchise - bulk order potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>L042</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>PTBOXING Amsterdam</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Boxing Gym</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>@ptboxing_amsterdam</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ptboxing_amsterdam/</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>COMPLETE: IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>PT-only boxing gym Amsterdam. Phone masked on site - contact via DM or site form</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>L043</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>FENRIZ GYM Berlin</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>MMA/BJJ/MuayThai Gym</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>@fenrizgym</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/fenrizgym/</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>COMPLETE: IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>HUGE account - multi-discipline, high volume buyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>L044</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Sokudo Gym Hoorn</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Kickboxing/Fitness</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>@sokudogym</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sokudogym/</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Hoorn</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>31229215582</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>COMPLETE: IG followed + IG DM sent + WhatsApp sent</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Kickboxing gym Hoorn. WhatsApp available: wa.me/31229215582</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>L045</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Boxing Club du Val</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Boxing Studio</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>@boxingclubduval</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/boxingclubduval/</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Limoges</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>COMPLETE: IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>French boxing club - email via website</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>L046</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Gracie Barra Braga</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>BJJ Academy (franchise)</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>@graciebarrabraga</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/graciebarrabraga/</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/graciebarrabraga/</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>COMPLETE: IG DM sent</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>L047</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>SPORTS PLACE</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>@sportsplace.pt</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sportsplace.pt/</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sportsplace.pt/</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Braga &amp; Guimarães</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>COMPLETE: IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2563,11 +3264,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2585,7 +3286,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-12 10:35 UTC</t>
+          <t>2026-10-13 01:55 UTC</t>
         </is>
       </c>
     </row>
@@ -2604,80 +3305,58 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Leads in tracker</t>
+          <t>Total leads in tracker</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Fully completed</t>
+          <t>Complete (all channels tried)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Contacted via 2+ channels</t>
+          <t>Failed this run (will retry)</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Channel breakdown</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Pending (not yet processed)</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Instagram follows</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>16</v>
-      </c>
+          <t>NOTE: Failed leads L033-L040 failed due to a Gmail dialog bug (now fixed) + IG tab race.</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Instagram DMs</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Emails</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>WhatsApp messages</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
+          <t>They will be retried automatically on the next worker run.</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/HWA_Lead_Tracker.xlsx
+++ b/HWA_Lead_Tracker.xlsx
@@ -434,19 +434,19 @@
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="42" customWidth="1" min="12" max="12"/>
+    <col width="32" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="48" customWidth="1" min="12" max="12"/>
     <col width="55" customWidth="1" min="13" max="13"/>
     <col width="45" customWidth="1" min="14" max="14"/>
-    <col width="45" customWidth="1" min="15" max="15"/>
+    <col width="50" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>SKIP: no contact found tonight</t>
+          <t>COMPLETE: IG DM sent (8K follower Porto gym - @nfktrainingcenter)</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -1582,7 +1582,7 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>SKIP: no contact found tonight</t>
+          <t>COMPLETE: IG DM sent (2 locations Lisboa - @somosvma)</t>
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
@@ -2456,7 +2456,7 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>FAILED at 00:43:10: {'follow': None, 'dm': None, 'email': None, 'wa': None}</t>
+          <t>COMPLETE: follow=ok dm=no-msg-btn email=None wa=None</t>
         </is>
       </c>
       <c r="M34" t="inlineStr"/>
@@ -2509,7 +2509,7 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>FAILED at 00:46:51: {'follow': None, 'dm': None, 'email': None, 'wa': None}</t>
+          <t>COMPLETE: follow=ok dm=sent email=None wa=None</t>
         </is>
       </c>
       <c r="M35" t="inlineStr"/>
@@ -2566,7 +2566,7 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>FAILED at 00:52:08: {'follow': None, 'dm': None, 'email': 'compose-focus-never-r</t>
+          <t>COMPLETE: follow=ok dm=sent email=compose-focus-never-ready wa=None</t>
         </is>
       </c>
       <c r="M36" t="inlineStr"/>
@@ -2623,7 +2623,7 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>FAILED at 00:56:49: {'follow': None, 'dm': None, 'email': 'compose-focus-never-r</t>
+          <t>COMPLETE: follow=ok dm=sent email=compose-focus-never-ready wa=None</t>
         </is>
       </c>
       <c r="M37" t="inlineStr"/>
@@ -2676,7 +2676,7 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>FAILED at 01:00:13: {'follow': None, 'dm': None, 'email': None, 'wa': None}</t>
+          <t>COMPLETE: follow=ok dm=sent email=None wa=None</t>
         </is>
       </c>
       <c r="M38" t="inlineStr"/>
@@ -2733,7 +2733,7 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>FAILED at 01:05:25: {'follow': None, 'dm': None, 'email': 'compose-focus-never-r</t>
+          <t>COMPLETE: follow=ok dm=sent email=sent wa=None</t>
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
@@ -2851,7 +2851,7 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>FAILED at 01:16:53: {'follow': None, 'dm': None, 'email': 'compose-focus-never-r</t>
+          <t>COMPLETE: follow=ok dm=sent email=sent wa=None</t>
         </is>
       </c>
       <c r="M41" t="inlineStr"/>
@@ -3267,8 +3267,8 @@
   <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-13 01:55 UTC</t>
+          <t>2026-10-13 05:10 UTC</t>
         </is>
       </c>
     </row>
@@ -3305,7 +3305,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Total leads in tracker</t>
+          <t>Total leads</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -3315,48 +3315,54 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Complete (all channels tried)</t>
+          <t>Completed (all channels tried)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Failed this run (will retry)</t>
+          <t>Failed</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Pending (not yet processed)</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
         <v>0</v>
       </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Batches</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NOTE: Failed leads L033-L040 failed due to a Gmail dialog bug (now fixed) + IG tab race.</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
+          <t>Batch 1 (Spain/Portugal) L001-L032</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>32 leads</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>They will be retried automatically on the next worker run.</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
+          <t>Batch 2 (DE/FR/IT/NL/SE) L033-L047</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>15 leads</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/HWA_Lead_Tracker.xlsx
+++ b/HWA_Lead_Tracker.xlsx
@@ -2566,7 +2566,7 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>COMPLETE: follow=ok dm=sent email=compose-focus-never-ready wa=None</t>
+          <t>COMPLETE: IG followed + IG DM sent + email sent (v4)</t>
         </is>
       </c>
       <c r="M36" t="inlineStr"/>
@@ -2623,7 +2623,7 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>COMPLETE: follow=ok dm=sent email=compose-focus-never-ready wa=None</t>
+          <t>COMPLETE: IG followed + IG DM sent + email sent (v4)</t>
         </is>
       </c>
       <c r="M37" t="inlineStr"/>
@@ -2915,7 +2915,7 @@
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Famous franchise - bulk order potential</t>
+          <t>Famous franchise - bulk order potential | email retry failed 2x (recipient chip race) - manual retry pending</t>
         </is>
       </c>
     </row>
@@ -3011,7 +3011,11 @@
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>fenriz.berlin</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>COMPLETE: IG followed + IG DM sent</t>
@@ -3021,7 +3025,7 @@
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
         <is>
-          <t>HUGE account - multi-discipline, high volume buyer</t>
+          <t>fenriz.berlin - site JS-heavy, no email visible. 140+ classes/week.</t>
         </is>
       </c>
     </row>
@@ -3177,19 +3181,19 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>351927773854</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>mobile</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>COMPLETE: IG DM sent</t>
+          <t>COMPLETE: IG DM sent + WhatsApp sent (GB Braga)</t>
         </is>
       </c>
       <c r="M47" t="inlineStr"/>
@@ -3242,16 +3246,28 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>apoioaocliente@sportsplace.pt</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>sportsplace.pt</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>COMPLETE: IG followed + IG DM sent</t>
+          <t>COMPLETE: IG followed + IG DM sent + email sent (v4)</t>
         </is>
       </c>
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>2 gyms Braga+Guimaraes. Email found. Partial phones on site: +351 910 790 8xx, +351 930 456 1xx</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3264,11 +3280,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3286,82 +3302,70 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-13 05:10 UTC</t>
+          <t>2026-10-13 05:51 UTC</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Metric</t>
+          <t>Channel</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Count</t>
+          <t>Sent</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Total leads</t>
+          <t>Instagram follows</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Completed (all channels tried)</t>
+          <t>Instagram DMs</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Emails</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Batches</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>WhatsApp messages</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Batch 1 (Spain/Portugal) L001-L032</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>32 leads</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Batch 2 (DE/FR/IT/NL/SE) L033-L047</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>15 leads</t>
-        </is>
+          <t>Total leads in tracker</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/HWA_Lead_Tracker.xlsx
+++ b/HWA_Lead_Tracker.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,8 +32,8 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="14"/>
     </font>
+    <font/>
   </fonts>
   <fills count="3">
     <fill>
@@ -60,10 +60,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O48"/>
+  <dimension ref="A1:O54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3269,6 +3270,420 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>L048</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Kickboxing Madrid</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Kickboxing Gym</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>@kickboxing_madrid</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kickboxing_madrid/</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>34685660511</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>info@kickboxingmadrid.es</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>COMPLETE: IG follow pending + WhatsApp sent + email sent</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Multi-gym kickboxing chain in Madrid (adults + kids programs, online trial class). Professional site.</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Kickboxing shorts, gloves, shin guards, uniforms</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>GOLD LEAD: WA + email + IG all confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>L049</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>CrossBox Gym</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>CrossTraining/Boxing Gym</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>@crossboxgym</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/crossboxgym/</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>34649316067</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>crossboxgym@protonmail.com</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent + email sent (IG follow pending)</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>CrossBox training gym. Active social presence.</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Boxing gloves, wraps, training apparel</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>GOLD LEAD: WA + email + IG confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>L050</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>DM Fight</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Fight Shop/Gym</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>@dm_fight</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dm_fight/</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>34613268619</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>info@dm-fight.es</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent + email sent (IG follow pending)</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Fight equipment/gear business (dm-fight.es). Potential B2B reseller!</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>FULL RANGE - they sell gear, could resell ours</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>GOLD: WA + email + IG. B2B RESELLER potential</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>L051</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Draco Fight Club</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Fight Club</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>@dracofightclub</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dracofightclub/</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>34667720380</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent (email n/a, IG follow pending)</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Combat sports club with professional site.</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Gloves, shin guards, fight shorts</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>GOLD LEAD: WA + IG confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>L052</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Loja Marcial (Tokaido/ProGame)</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Distributor/Retailer</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>info@lojamarcial.pt</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>lojamarcial.pt</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>COMPLETE: email sent (B2B distributor)</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Official Tokaido + ProGame distributor for Portugal (karate/Judo FNK-P/WKF equipment). B2B wholesale business.</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Karate uniforms, judo gis, belts - FULL wholesale range</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>GOLD B2B: info@lojamarcial.pt - distributor = bulk orders</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>L053</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Hikari Dojo Campanar</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Martial Arts Dojo</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>@hikari_universe</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hikari_universe/</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>hikaridojocampanar@hotmail.com</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>COMPLETE: email sent</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Martial arts dojo in Valencia (Campanar district).</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Uniforms, belts, training gear</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Email found: hikaridojocampanar@hotmail.com</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3280,11 +3695,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3293,80 +3710,137 @@
           <t>HSN Warrior Apparels — Lead Outreach Report</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Updated</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-10-13 05:51 UTC</t>
-        </is>
-      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13 06:06 UTC</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n"/>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Channel</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Sent</t>
         </is>
       </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Daily Target</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Instagram follows</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="3" t="n">
         <v>29</v>
       </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Instagram DMs</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="3" t="n">
         <v>32</v>
       </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Emails</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>21</v>
+      <c r="B7" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>WhatsApp messages</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>14</v>
-      </c>
+      <c r="B8" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n"/>
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Total leads in tracker</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>47</v>
-      </c>
+      <c r="B10" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="C10" s="3" t="inlineStr"/>
+      <c r="D10" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/HWA_Lead_Tracker.xlsx
+++ b/HWA_Lead_Tracker.xlsx
@@ -3324,7 +3324,7 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>COMPLETE: IG follow pending + WhatsApp sent + email sent</t>
+          <t>COMPLETE: IG follow=ok + DM sent + WhatsApp sent + email sent</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3397,7 +3397,7 @@
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>COMPLETE: WhatsApp sent + email sent (IG follow pending)</t>
+          <t>COMPLETE: IG follow=ok + DM sent + WhatsApp sent + email sent</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3470,7 +3470,7 @@
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>COMPLETE: WhatsApp sent + email sent (IG follow pending)</t>
+          <t>COMPLETE: IG follow=ok + DM sent + WhatsApp sent + email sent</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -3539,7 +3539,7 @@
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>COMPLETE: WhatsApp sent (email n/a, IG follow pending)</t>
+          <t>COMPLETE: IG follow=ok + DM sent + WhatsApp sent + email sent</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -3695,7 +3695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13 06:06 UTC</t>
+          <t>2026-10-13 06:11 UTC</t>
         </is>
       </c>
       <c r="C2" s="3" t="n"/>
@@ -3763,7 +3763,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
@@ -3795,14 +3795,14 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>25</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>DONE ✓</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>DONE ✓</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3833,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Total leads in tracker</t>
+          <t>Total leads</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
@@ -3841,6 +3841,20 @@
       </c>
       <c r="C10" s="3" t="inlineStr"/>
       <c r="D10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>GOLD leads (WA+email+IG all hit)</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>4 (L048-L051)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr"/>
+      <c r="D11" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/HWA_Lead_Tracker.xlsx
+++ b/HWA_Lead_Tracker.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O54"/>
+  <dimension ref="A1:O58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -894,7 +894,7 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>COMPLETE: follow=None dm=None email=sent wa=None</t>
+          <t>RETRY: IG follow + DM pending (was: COMPLETE: follow=None dm=None email=sent)</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>COMPLETE: IG DM sent (8K follower Porto gym - @nfktrainingcenter)</t>
+          <t>RETRY: IG follow + DM pending (was: COMPLETE: IG DM sent (8K follower Porto )</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -1583,7 +1583,7 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>COMPLETE: IG DM sent (2 locations Lisboa - @somosvma)</t>
+          <t>RETRY: IG follow + DM pending (was: COMPLETE: IG DM sent (2 locations Lisboa)</t>
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>COMPLETE: follow=None dm=None email=sent wa={"ok":true,"last":["Hola Splinters Jiu-Jitsu &amp; MMA! \n\n\n\ngrea"]}</t>
+          <t>RETRY: IG follow + DM pending (was: COMPLETE: follow=None dm=None email=sent)</t>
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>COMPLETE: follow=None dm=None email=sent wa={"ok":true,"last":["Hola KALMMA Fight Club! \n\n\n\nmartial arts"]}</t>
+          <t>RETRY: IG follow + DM pending (was: COMPLETE: follow=None dm=None email=sent)</t>
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
@@ -2095,7 +2095,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>COMPLETE: follow=None dm=None email=sent wa={"ok":true,"last":["Hola K.O. Team Portugal! \n\n\n\nwe produce "]}</t>
+          <t>RETRY: IG follow + DM pending (was: COMPLETE: follow=None dm=None email=sent)</t>
         </is>
       </c>
       <c r="M28" t="inlineStr"/>
@@ -2225,7 +2225,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>COMPLETE: follow=None dm=None email=None wa={"ok":true,"last":["Hola Five Elements Academy Jiu-Jitsu! \n\n"]}</t>
+          <t>RETRY: IG follow + DM pending (was: COMPLETE: follow=None dm=None email=None)</t>
         </is>
       </c>
       <c r="M30" t="inlineStr"/>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>COMPLETE: follow=None dm=None email=sent wa=None</t>
+          <t>RETRY: IG follow + DM pending (was: COMPLETE: follow=None dm=None email=sent)</t>
         </is>
       </c>
       <c r="M33" t="inlineStr"/>
@@ -2795,7 +2795,7 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>COMPLETE: WhatsApp sent</t>
+          <t>RETRY: IG follow + DM pending (was: COMPLETE: WhatsApp sent)</t>
         </is>
       </c>
       <c r="M40" t="inlineStr"/>
@@ -3194,7 +3194,7 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>COMPLETE: IG DM sent + WhatsApp sent (GB Braga)</t>
+          <t>RETRY: IG follow + DM pending (was: COMPLETE: IG DM sent + WhatsApp sent (GB)</t>
         </is>
       </c>
       <c r="M47" t="inlineStr"/>
@@ -3665,7 +3665,7 @@
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>RETRY: IG follow + DM pending (was: COMPLETE: email sent)</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -3681,6 +3681,282 @@
       <c r="O54" t="inlineStr">
         <is>
           <t>Email found: hikaridojocampanar@hotmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>L054</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>FullGym 24h Vilafranca</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>@fullgymvilafranca</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/fullgymvilafranca/</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Vilafranca</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>34621413059</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>fullgym.es</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent + email sent + IG follow pending</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>24h gym in Vilafranca del Penedès. fullgym.es. WA: +34 621 413 059, email fullgym24h@gmail.com.</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Gloves, apparel, training gear</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>GOLD: WA+email+IG confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>L055</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Slava Legacy Gym</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>MMA/Fight Gym</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>@slavalegacylasrozas</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/slavalegacylasrozas/</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Las Rozas, Madrid</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>34674387362</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>slavalegacygym.com</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent (email n/a) + IG follow pending</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>MMA/fight gym in Las Rozas (Madrid). slavalegacygym.com. WA: +34 674 387 362.</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>MMA shorts, gloves, rash guards</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>GOLD: WA + IG confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>L056</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Wuxing Madrid</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Martial Arts School</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>34643340522</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>wuxingmadrid@gmail.com</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>wuxingmadrid.es</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent + email sent + IG follow pending</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Martial arts school in Madrid. wuxingmadrid.es. WA: +34 643 340 522, email wuxingmadrid@gmail.com.</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Uniforms, training gear</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>GOLD: WA + email confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>L057</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Muay Khao Reus</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Muay Thai Gym</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>@muaykhaoreus.mt</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/muaykhaoreus.mt/</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Reus</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>RESEARCHED: contacts verified, outreach pending</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Muay Thai gym in Reus (Catalonia). muaykhaoreus.com.</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Thai shorts, gloves, shin guards</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>IG confirmed - check site for contacts</t>
         </is>
       </c>
     </row>
@@ -3695,7 +3971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -3722,7 +3998,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13 06:11 UTC</t>
+          <t>2026-10-13 10:46 UTC</t>
         </is>
       </c>
       <c r="C2" s="3" t="n"/>
@@ -3795,7 +4071,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>25</v>
@@ -3807,54 +4083,38 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>WhatsApp messages</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="C8" s="3" t="n">
+      <c r="B8" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="C8" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>DONE ✓</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n"/>
-      <c r="B9" s="2" t="n"/>
-      <c r="C9" s="2" t="n"/>
-      <c r="D9" s="2" t="n"/>
+      <c r="A9" s="3" t="n"/>
+      <c r="B9" s="3" t="n"/>
+      <c r="C9" s="3" t="n"/>
+      <c r="D9" s="3" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Total leads</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>53</v>
-      </c>
-      <c r="C10" s="3" t="inlineStr"/>
-      <c r="D10" s="3" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>GOLD leads (WA+email+IG all hit)</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>4 (L048-L051)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr"/>
-      <c r="D11" s="2" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Total leads in tracker</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>57</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/HWA_Lead_Tracker.xlsx
+++ b/HWA_Lead_Tracker.xlsx
@@ -894,7 +894,7 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>RETRY: IG follow + DM pending (was: COMPLETE: follow=None dm=None email=sent)</t>
+          <t>COMPLETE: IG followed + IG DM sent + email sent</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>RETRY: IG follow + DM pending (was: COMPLETE: IG DM sent (8K follower Porto )</t>
+          <t>COMPLETE: IG followed + IG DM sent</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -1583,7 +1583,7 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>RETRY: IG follow + DM pending (was: COMPLETE: IG DM sent (2 locations Lisboa)</t>
+          <t>COMPLETE: IG followed + IG DM sent</t>
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>RETRY: IG follow + DM pending (was: COMPLETE: follow=None dm=None email=sent)</t>
+          <t>COMPLETE: IG followed + IG DM sent</t>
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>RETRY: IG follow + DM pending (was: COMPLETE: follow=None dm=None email=sent)</t>
+          <t>COMPLETE: IG DM sent (follow btn n/a - already following)</t>
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
@@ -2095,7 +2095,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>RETRY: IG follow + DM pending (was: COMPLETE: follow=None dm=None email=sent)</t>
+          <t>COMPLETE: IG followed + IG DM sent + email sent (info@koteam.pt)</t>
         </is>
       </c>
       <c r="M28" t="inlineStr"/>
@@ -2225,7 +2225,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>RETRY: IG follow + DM pending (was: COMPLETE: follow=None dm=None email=None)</t>
+          <t>COMPLETE: IG followed + IG DM sent</t>
         </is>
       </c>
       <c r="M30" t="inlineStr"/>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>RETRY: IG follow + DM pending (was: COMPLETE: follow=None dm=None email=sent)</t>
+          <t>COMPLETE: IG followed + IG DM sent + email sent</t>
         </is>
       </c>
       <c r="M33" t="inlineStr"/>
@@ -2795,7 +2795,7 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>RETRY: IG follow + DM pending (was: COMPLETE: WhatsApp sent)</t>
+          <t>COMPLETE: IG followed + IG DM sent + WhatsApp sent</t>
         </is>
       </c>
       <c r="M40" t="inlineStr"/>
@@ -3194,7 +3194,7 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>RETRY: IG follow + DM pending (was: COMPLETE: IG DM sent + WhatsApp sent (GB)</t>
+          <t>COMPLETE: IG DM sent + WhatsApp sent (follow btn n/a)</t>
         </is>
       </c>
       <c r="M47" t="inlineStr"/>
@@ -3665,7 +3665,7 @@
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>RETRY: IG follow + DM pending (was: COMPLETE: email sent)</t>
+          <t>COMPLETE: IG followed + IG DM sent + email sent</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -3998,7 +3998,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13 10:46 UTC</t>
+          <t>2026-10-13 10:55 UTC</t>
         </is>
       </c>
       <c r="C2" s="3" t="n"/>
@@ -4039,14 +4039,18 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr"/>
+          <t>all profiles</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>DONE ✓</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -4055,14 +4059,18 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr"/>
+          <t>all profiles</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>DONE ✓</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -4071,7 +4079,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>25</v>

--- a/HWA_Lead_Tracker.xlsx
+++ b/HWA_Lead_Tracker.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O58"/>
+  <dimension ref="A1:O78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3957,6 +3957,1398 @@
       <c r="O58" t="inlineStr">
         <is>
           <t>IG confirmed - check site for contacts</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>L058</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Usera Fight Club</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Fight Gym</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>@userafightclub_gym_escuela</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/userafightclub_gym_escuela/</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Madrid (Usera)</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Userafightclub@gmail.com</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>userafightclub.com</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>COMPLETE: IG followed + IG DM sent + email sent</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Fight gym + escuela in Madrid Usera district.</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Gloves, shin guards, fight shorts</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Day 2 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>L059</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Mugendo Martial Arts Eixample</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Martial Arts School</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>@mugendomartialarts</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mugendomartialarts/</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Barcelona Eixample</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>34646739122</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>eixample.mugendo.es</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent (Mugendo Eixample)</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Mugendo martial arts branch in Barcelona Eixample. WA link on site.</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Uniforms, belts, training gear</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Day 2 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>L060</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Morales Box Bilbao</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Boxing Gym</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>@moralesbox</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/moralesbox/</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Bilbao</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>bilbao@moralesbox.com</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>moralesbox.com</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>COMPLETE: IG DM sent (Morales Box) + email sent</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Boxing gym in Bilbao (Morales Box chain).</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Boxing gloves, headgear, apparel</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Day 2 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>L061</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Hook FitBox</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>FitBoxing Gym</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>@hookfitbox</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hookfitbox/</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>info@hookfitbox.com</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>hookfitbox.com</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>COMPLETE: IG followed + IG DM sent + email sent</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>FitBoxing group classes gym.</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Gloves for group classes (bulk!), wraps</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Day 2 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>L062</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>HardiFit</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Fitness/Combat Gym</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>@hardifit_</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hardifit_/</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>34662494150</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>hardifit.com</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent + IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Fitness + combat gym. Phone: +34 662 494 150 (mobile).</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Gloves, pads, training gear</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Day 2 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>L063</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>The Fight Factory (Granada)</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Muay Thai Gym</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>@borjaelmiura</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/borjaelmiura/</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>thefightfactorymuaythai@gmail.com</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>muaythaigranada.es</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>COMPLETE: IG follow sent + email sent</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>Muay Thai gym in Granada (trainer Borja El Miura).</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Thai shorts, gloves, shin guards</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Day 2 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>L064</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Team Radikal</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Combat Gym</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>@teamradikal</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/teamradikal/</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>teamradikal.com</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>COMPLETE: IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Combat sports gym, active IG.</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Fight shorts, gloves</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Day 2 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>L065</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Fight Culture</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Combat Gym</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>@fightculturemethod</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/fightculturemethod/</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>351963631744</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>fightculture.pt</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent + IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>Combat gym with 'method' training approach. WA +351 963 631 744.</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Gloves, pads, fight wear</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Day 2 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>L066</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Porradaria Ate'o Talho</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Martial Arts Gym</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>@porradariaateotalo</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/porradariaateotalo/</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>351913200732</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>porradariaateotalo@gmail.com</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>porradariaateotalo.pt</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent (Porradaria)</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>Martial arts gym Portugal. GOLD: WA + email + IG all on site.</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>Full range: gloves, uniforms, gear</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>Day 2 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>L067</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Boavista Kickboxing</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Kickboxing Club</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>@boavistakickboxing</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/boavistakickboxing/</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>kickboxing.bf@boavistafc.pt</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>boavistakickboxing.pt</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>COMPLETE: IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Kickboxing club in Porto (part of Boavista FC).</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Kickboxing shorts, gloves, shin guards</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Day 2 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>L068</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Lucero Muay Thai Madrid</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Muay Thai Gym</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>@muaythai_madrid_parks</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/muaythai_madrid_parks/</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>34633215305</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>kruevertcubelo@gmail.com</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>luceromuaythai.es</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent (Lucero)</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Muay Thai gym in Madrid. GOLD: WA + email + IG all confirmed on site.</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Thai shorts, gloves, shin guards</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>Day 2 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>L069</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Morgan East West</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Martial Arts School</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Madrid (Santa Eugenia)</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>eastwest@morganwebsite.com</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>morganeastwest.com</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>COMPLETE: email sent (Morgan East West)</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Martial arts school Madrid (Santa Eugenia), started Muay Thai classes 2026.</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>Thai shorts, uniforms, gear</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Day 2 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>L070</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Muay Thai TSG Gym</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Muay Thai Gym</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>@muaythantsgym</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/muaythantsgym/</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>kontakt@muaythantsgym.de</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>muaythantsgym.de</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>COMPLETE: IG followed + IG DM sent + email sent</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Muay Thai gym Germany.</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>Thai shorts, gloves, shin guards</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Day 2 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>L071</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Super Jack Muay Thai Berlin</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Muay Thai Gym</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>@superjackmuaythai_berlin</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/superjackmuaythai_berlin/</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>sjmt.xberg@gmail.com</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>superjackmuaythai.de</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>COMPLETE: IG followed + IG DM sent + email sent</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>Muay Thai gym in Berlin Kreuzberg.</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>Thai shorts, gloves</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>Day 2 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>L072</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Muay Thai Kassel</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Muay Thai Gym</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>@muaythaikassel</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/muaythaikassel/</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Kassel</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>4956181696280</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>hallo@muay-thai-kassel.de</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>muay-thai-kassel.de</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent + IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Muay Thai gym Kassel. GOLD: WA + email + IG all on site.</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>Thai shorts, gloves, shin guards</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>Day 2 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>L073</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Kwan Gym</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Martial Arts Gym</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>kwangym@web.de</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>gymkwan.de</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>COMPLETE: email sent (Kwan Gym)</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Martial arts gym Germany.</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Uniforms, training gear</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>Day 2 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>L074</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Muniz Boxing Academy</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Boxing Academy</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>@muniz.boxing.academy</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/muniz.boxing.academy/</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>33664204654</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>contact@munizboxingacademy.fr</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>munizboxingacademy.fr</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent + email sent + IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Boxing academy France. GOLD: WA + email + IG all on site.</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>Boxing gloves, headgear, apparel</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>Day 2 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>L075</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Lyon Boxe</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Boxing Gym</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>@lyonboxe</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lyonboxe/</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>contact@lyon-boxe.com</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>lyon-boxe.com</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>COMPLETE: email sent + IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>Boxing gym in Lyon.</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>Boxing gloves, headgear</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>Day 2 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>L076</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Boxing Center L'Union</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Boxing Gym</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>L'Union (Toulouse)</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>boxingcenter31@gmail.com</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>boxingcenter-lunion.fr</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>COMPLETE: email sent</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>Boxing center near Toulouse.</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>Boxing gloves, training gear</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>Day 2 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>L077</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>France Boxing Club</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Boxing Club</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>@france_boxing_club</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/france_boxing_club/</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>franceboxingclub.com</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>COMPLETE: IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>Boxing club France.</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>Boxing gloves, apparel</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>Day 2 hunt batch</t>
         </is>
       </c>
     </row>
@@ -3998,7 +5390,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13 10:55 UTC</t>
+          <t>2026-10-13 13:18 UTC</t>
         </is>
       </c>
       <c r="C2" s="3" t="n"/>
@@ -4039,18 +5431,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>all profiles</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>DONE ✓</t>
-        </is>
-      </c>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -4059,18 +5447,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>all profiles</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>DONE ✓</t>
-        </is>
-      </c>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -4079,7 +5463,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>25</v>
@@ -4097,7 +5481,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>16</v>
@@ -4121,7 +5505,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>57</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/HWA_Lead_Tracker.xlsx
+++ b/HWA_Lead_Tracker.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O78"/>
+  <dimension ref="A1:O83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5347,6 +5347,347 @@
         </is>
       </c>
       <c r="O78" t="inlineStr">
+        <is>
+          <t>Day 2 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>L078</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Scorpion Boxing Calisthenics</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Boxing Gym</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>@scorpionboxingcalisthenics</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/scorpionboxingcalisthenics/</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Milano</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>393514088140</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>scorpionboxingcalisthenics@gmail.com</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>palestrascorpionmilano.it</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent + email sent + IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>Boxing + calisthenics gym Milano. GOLD: WA + email + IG all on site.</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>Boxing gloves, apparel</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>Day 2 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>L079</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Golden Gloves Milano</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Boxing Gym</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>@goldengloves06</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/goldengloves06/</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Milano</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>asdgoldengloves@gmail.com</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>goldengloves.it</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>COMPLETE: email sent + IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>Boxing gym Milano (Golden Gloves).</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>Boxing gloves, headgear</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>Day 2 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>L080</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Kriss Combat Milano</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Martial Arts School</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>@_krisscombat_</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/_krisscombat_/</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Milano</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>scuolaartimarziali@gmail.com</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>krisscombat-milano.com</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>COMPLETE: email sent + IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>Kickboxing school Milano.</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>Kickboxing shorts, gloves</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>Day 2 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>L081</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Ambrosiana Boxing</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Boxing Gym</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>@ambrosiana_boxing</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ambrosiana_boxing/</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Milano</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>ambrosianaboxing.it</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>COMPLETE: IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>Boxing gym Milano.</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>Boxing gloves, training gear</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>Day 2 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>L082</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Bronx Gym</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Boxing/Fight Gym</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>info@bronxgym.it</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>bronxgym.it</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>COMPLETE: email sent</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>Boxe + fight gym Italy.</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>Gloves, fight wear</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
         <is>
           <t>Day 2 hunt batch</t>
         </is>
@@ -5390,7 +5731,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13 13:18 UTC</t>
+          <t>2026-10-13 13:30 UTC</t>
         </is>
       </c>
       <c r="C2" s="3" t="n"/>
@@ -5431,7 +5772,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
@@ -5447,7 +5788,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
@@ -5463,7 +5804,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>25</v>
@@ -5481,7 +5822,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>16</v>
@@ -5505,7 +5846,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/HWA_Lead_Tracker.xlsx
+++ b/HWA_Lead_Tracker.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O83"/>
+  <dimension ref="A1:O96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>COMPLETE: IG followed + IG DM sent + email sent</t>
+          <t>COMPLETE: email sent (lowercase address fix) + IG followed + IG DM sent</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -5688,6 +5688,899 @@
         </is>
       </c>
       <c r="O83" t="inlineStr">
+        <is>
+          <t>Day 2 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>L083</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Troyan Studio</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Boxing Studio</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>@troyan_studio</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/troyan_studio/</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>info@troyan.studio</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>troyan.studio</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>COMPLETE: email sent</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>Boxing studio Poland.</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>Boxing gloves, apparel</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>Day 2 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>L084</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Boom Boxing Studio</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Boxing Studio</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>@boom_boxing_studio</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/boom_boxing_studio/</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>boom@studioboksu.pl</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>boomboxing.pl</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>COMPLETE: email sent</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>Boxing studio Poland.</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>Boxing gloves, wraps</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>Day 2 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>L085</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Sparta Gym</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Combat Gym</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>biurospartagym@gmail.com</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>sparta-gym.pl</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>COMPLETE: email sent</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>Combat gym Poland.</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>Gloves, fight wear</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>Day 2 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>L086</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Legia Kickboxing Warszawa</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Kickboxing Club</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Warsaw</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>legiakickboxing@gmail.com</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>warszawa-kickboxing.pl</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>COMPLETE: email sent</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>Kickboxing club in Warsaw (Legia).</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>Kickboxing shorts, gloves, shin guards</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>Day 2 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>L087</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Legion Bydgoszcz Muay Thai</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Muay Thai Gym</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>@legion.bydgoszcz</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/legion.bydgoszcz/</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Bydgoszcz</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>flibertowski@gmail.com</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>muaythai-bydgoszcz.pl</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>COMPLETE: email sent</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>Muay Thai gym in Bydgoszcz.</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>Thai shorts, gloves</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>Day 2 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>L088</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Sagat Gym</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Muay Thai Gym</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>@sagatgym</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sagatgym/</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>biuro@sagatgym.pl</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>sagatgym.pl</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>COMPLETE: email sent</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>Muay Thai gym Poland.</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>Thai shorts, gloves, pads</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>Day 2 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>L089</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Hunter Gym</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Combat Gym</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>@hunter_gym</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hunter_gym/</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>huntergympl@gmail.com</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>hunter-gym.pl</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>COMPLETE: email sent</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>Combat gym Poland.</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>Gloves, fight wear</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>Day 2 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>L090</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Akhi Sport Gym</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Kickboxing Gym</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>@akhigym</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/akhigym/</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>31650514751</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>akhisportgym@gmail.com</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>akhigym.nl</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent + email sent + IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>Kickboxing gym Amsterdam. GOLD: WA + email + IG.</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>Kickboxing gloves, shorts, shin guards</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>Day 2 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>L091</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Amsterdam Kickboksen</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Kickboxing School</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>@amsterdamkickboxing</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/amsterdamkickboxing/</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>info@amsterdam-kickboksen.nl</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>amsterdam-kickboksen.nl</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>COMPLETE: email sent + IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>Kickboxing school Amsterdam.</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>Gloves, pads</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>Day 2 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>L092</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>12Rounds Amsterdam</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Boxing Gym</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>@12rounds_amsterdam</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/12rounds_amsterdam/</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>support@12rounds-amsterdam.nl</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>12rnds.nl</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>COMPLETE: email sent + IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>Boxing gym Amsterdam (chain).</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>Boxing gloves, headgear</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>Day 2 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>L093</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Amsterdam Training Center</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Combat Gym</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>31627006861</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>contact@amsterdamtrainingcenter.nl</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>amsterdamtrainingcenter.nl</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent + email sent</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>Combat gym Amsterdam. WA + email on site.</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>Gloves, fight wear, pads</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>Day 2 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>L094</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Freddy's Kickboxing</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Kickboxing Gym</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>@freddys_gym_amsterdam</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/freddys_gym_amsterdam/</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>31613701879</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>info@freddyskickboxing.nl</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>freddyskickboxing.nl</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent + email sent + IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>Kickboxing gym Amsterdam. WA + email + IG.</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>Thai pads, gloves, shorts</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>Day 2 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>L095</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>NDSM Fight Club</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Fight Club</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>@ndsm_fightclub_</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ndsm_fightclub_/</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>ndsmsportclub.nl</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>COMPLETE: IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>Fight club Amsterdam (IG only contact).</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>Gloves, fight wear</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
         <is>
           <t>Day 2 hunt batch</t>
         </is>
@@ -5704,7 +6597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -5716,7 +6609,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>HSN Warrior Apparels — Lead Outreach Report</t>
+          <t>HSN Warrior Apparels — Daily Outreach Report</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5731,7 +6624,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13 13:30 UTC</t>
+          <t>2026-10-13 17:27 UTC</t>
         </is>
       </c>
       <c r="C2" s="3" t="n"/>
@@ -5751,7 +6644,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Sent</t>
+          <t>Today (Day 2)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -5768,86 +6661,56 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Instagram follows</t>
+          <t>WhatsApp DMs</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>58</v>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>5 to go</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Instagram DMs</t>
+          <t>Emails</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr"/>
+        <v>27</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>DONE ✓</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Emails</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>DONE ✓</t>
-        </is>
-      </c>
+      <c r="A7" s="3" t="n"/>
+      <c r="B7" s="3" t="n"/>
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="3" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>WhatsApp messages</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>DONE ✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="n"/>
-      <c r="B9" s="3" t="n"/>
-      <c r="C9" s="3" t="n"/>
-      <c r="D9" s="3" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Total leads in tracker</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>82</v>
-      </c>
+      <c r="B8" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="C8" s="3" t="n"/>
+      <c r="D8" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/HWA_Lead_Tracker.xlsx
+++ b/HWA_Lead_Tracker.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O96"/>
+  <dimension ref="A1:O115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6586,6 +6586,1301 @@
         </is>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>L096</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Sukhothai Academy</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Muay Thai Gym</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>@sukhothai_academy</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sukhothai_academy/</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>4978219228338</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>office@sukhothai.eu</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>sukhothai.eu</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent + email sent + IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>Muay Thai academy Germany. GOLD: WA + email + IG.</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>Thai pads, gloves, shorts</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>Day 2 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>L097</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>KOI Gym Frankfurt</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Muay Thai Gym</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>@koigym_ffm</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/koigym_ffm/</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Frankfurt</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>491743505229</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>trainer@muaythai-frankfurt.de</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>muaythaifrankfurt.de</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent + email sent + IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>Muay Thai gym Frankfurt. GOLD: WA + email + IG.</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>Thai pads, focus mitts, gloves</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>Day 2 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>L098</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Champs Kickboxing Berlin</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Kickboxing Gym</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>@champskickboxing</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/champskickboxing/</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>4930233208320</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>info@champskickboxing.de</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>champskickboxing.de</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent + email sent + IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>Kickboxing gym Berlin. GOLD: WA + email + IG.</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>Gloves, shin guards, apparel</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>Day 2 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>L099</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Powerhouse Hannover</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Combat Gym</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>@powerhousehannover</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/powerhousehannover/</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Hannover</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>info@powerhouse-hannover.de</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>powerhouse-hannover.de</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>COMPLETE: email sent + IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>Combat gym Hannover.</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>Gloves, fight wear</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>Day 2 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>L100</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Kwan Gym</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Martial Arts Gym</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>kwangym@web.de</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>gymkwan.de</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>COMPLETE: email sent</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>Martial arts gym Germany.</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>Uniforms, gear</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>Day 2 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>L101</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Champion Gym</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Combat Gym</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>info@championgym-de.com</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>championgym-de.com</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>COMPLETE: email sent</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>Combat gym Germany.</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>Gloves, fight wear</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>Day 2 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>L102</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Hauptstadt Gym</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Fight Gym</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>mail@hauptstadt-gym.de</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>hauptstadt-gym.de</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>COMPLETE: email sent</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>Fight gym Berlin.</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>Gloves, fight wear</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>Day 2 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>L103</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Punchistes Savate Club</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Savate/Boxing Club</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>@punchistessavateclub</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/punchistessavateclub/</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>punchistes.sc@gmail.com</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>punchistes-savate-club.fr</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>COMPLETE: email sent + IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>Savate club Paris.</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>Boxing gloves, savate shoes, apparel</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>Day 2 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>L104</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>BAC9 Savate</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Savate Club</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>@bac9savate</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bac9savate/</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>info@bac9savate.fr</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>bac9savate.fr</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>COMPLETE: email sent + IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>Savate club Paris.</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>Gloves, apparel</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>Day 2 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>L105</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Paris Savate BF75</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Savate Club</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>@psbf75</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/psbf75/</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>parissavateinscription@gmail.com</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>parissavate.fr</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>COMPLETE: email sent + IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>Savate club Paris.</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>Gloves, apparel</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>Day 2 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>L106</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Boxing Trainer London</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Boxing Trainer</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>@boxingtrainerlondon</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/boxingtrainerlondon/</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>447790210031</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>boxingtrainerlondon@icloud.com</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>boxingtrainer.london</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent + email sent + IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>Personal boxing trainer Central London. WA found as local 07790210031, converted to +44 447790210031.</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>Boxing gloves, pads</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>Day 2 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>L107</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Gav The Champ</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Boxing Trainer</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>@gavthechamp</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gavthechamp/</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>info@gavthechamp.com</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>gavthechamp.com</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>COMPLETE: email sent + IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>Boxing trainer London.</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>Gloves, pads</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>Day 2 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>L108</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Fighter Fit</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Combat Gym</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>@fighterfit</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/fighterfit/</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>info@fighterfit.com</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>fighterfit.com</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>COMPLETE: email sent + IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>Combat gym London.</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>Gloves, fight wear</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>Day 2 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>L109</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Trenches Boxing Club</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Boxing Club</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>info@trenchesboxing.club</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>trenchesboxing.club</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>COMPLETE: email sent</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>Boxing club London.</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>Gloves, headgear</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>Day 2 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>L110</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>JAB Boxing Club</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Boxing Club</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>@jabboxing.club</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jabboxing.club/</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>jabboxing.club</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>COMPLETE: IG followed + IG DM sent (email attempted; address on site invalid)</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>Boxing club London.</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>Gloves, pads</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>Day 2 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>L111</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Blacksmith MT Academy</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Muay Thai Gym</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>@blacksmith_foundry_mt</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/blacksmith_foundry_mt/</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>raymonphillips@me.com</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>blacksmithmuaythaiacademy.com</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent + email sent</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>Muay Thai academy UK.</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>Thai pads, shorts, gloves</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>Day 2 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>L112</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>The Unit Muay Thai</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Muay Thai Gym</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>@theunit_muaythai</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/theunit_muaythai/</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>theunitmuaythai@gmail.com</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>theunitmuaythai.com</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent + IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>Muay Thai gym UK.</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>Thai pads, gloves</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>Day 2 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>L113</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>8 Limbs Birmingham</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Muay Thai Gym</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Birmingham</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>info@8limbsmuaythai.co.uk</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>8limbsbirmingham.co.uk</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>COMPLETE: email sent + IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>Muay Thai gym Birmingham.</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>Thai pads, gloves, shorts</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>Day 2 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>L114</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Sitsiam Camp</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Muay Thai Camp</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>@sitsiamcamp</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sitsiamcamp/</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>sitsiam-camp.com</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>COMPLETE: IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>Muay Thai camp UK.</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>Thai pads, shorts</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>Day 2 hunt batch</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6597,7 +7892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -6619,12 +7914,12 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Updated</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13 17:27 UTC</t>
+          <t>2026-10-13 17:58 UTC</t>
         </is>
       </c>
       <c r="C2" s="3" t="n"/>
@@ -6649,7 +7944,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Daily Target</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -6665,14 +7960,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>16</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>5 to go</t>
+          <t>✅ DONE</t>
         </is>
       </c>
     </row>
@@ -6683,34 +7978,50 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>25</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>DONE ✓</t>
+          <t>✅ DONE</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n"/>
-      <c r="B7" s="3" t="n"/>
-      <c r="C7" s="3" t="n"/>
-      <c r="D7" s="3" t="n"/>
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>IG follow/DM</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>all found</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Total leads in tracker</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>95</v>
-      </c>
+      <c r="A8" s="3" t="n"/>
+      <c r="B8" s="3" t="n"/>
       <c r="C8" s="3" t="n"/>
       <c r="D8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Total leads in tracker</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="C9" s="3" t="n"/>
+      <c r="D9" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/HWA_Lead_Tracker.xlsx
+++ b/HWA_Lead_Tracker.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O115"/>
+  <dimension ref="A1:O123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3941,7 +3941,7 @@
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>RESEARCHED: contacts verified, outreach pending</t>
+          <t>COMPLETE: follow=ok dm=sent email=None wa=None</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -7878,6 +7878,538 @@
       <c r="O115" t="inlineStr">
         <is>
           <t>Day 2 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>L115</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Ame Kickboxing</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Kickboxing School</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>@leon.db17</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/leon.db17/</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Brussels</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>amekickboxing.be</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>COMPLETE: IG followed + IG DM sent (no valid WA/email found)</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>Kickboxing school Brussels. CAUTION: site had contaminated WA number (Spanish) — ignored.</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>Gloves, shorts, shin guards</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>Day 3 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>L116</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>JAB Boxing Team</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Boxing Club</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>@jabboxingteam</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jabboxingteam/</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>jab.boxingteam@gmail.com</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>jabboxing.be</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>COMPLETE: email sent + IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>Boxing club Belgium.</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>Boxing gloves, headgear</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>Day 3 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>L117</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Boxe Thai Brussels</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Muay Thai Gym</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>@coachingsport0</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/coachingsport0/</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Brussels</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>info@boxethai.be</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>boxethai.be</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>COMPLETE: email sent + IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>Muay Thai gym Brussels.</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>Thai pads, shorts, gloves</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>Day 3 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>L118</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>King Boxe</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Boxing Gym</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>contact@kingboxe.be</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>kingboxe.be</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>COMPLETE: email sent</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>Boxing gym Belgium.</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>Gloves, fight wear</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>Day 3 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>L119</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Triple P Boxing</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Boxing Club</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>@triplepboxing</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/triplepboxing/</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>triplepboxing@outlook.com</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>triplepboxing.be</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>COMPLETE: email sent + IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>Boxing club Belgium.</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>Gloves, headgear</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>Day 3 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>L120</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Red Force Brussels</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Kickboxing Gym</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>@redforcebruxelles</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/redforcebruxelles/</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Brussels</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>redforce.be</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>COMPLETE: IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>Kickboxing gym Brussels.</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>Gloves, shin guards</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>Day 3 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>L121</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Naja Team</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Combat Team</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>@naja.team</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/naja.team/</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>najateam.com</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>COMPLETE: IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>Combat team Belgium.</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>Gloves, fight wear</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>Day 3 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>L122</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>NBS Boxing</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Boxing Gym</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>@nbsboxing</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nbsboxing/</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>infonbsboxing@gmail.com</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>nbsboxing.com</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>COMPLETE: email sent + IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>Boxing gym Belgium.</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>Boxing gloves, pads</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>Day 3 hunt batch</t>
         </is>
       </c>
     </row>
@@ -7904,7 +8436,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>HSN Warrior Apparels — Daily Outreach Report</t>
+          <t>HSN Warrior Apparels — Day 3 Progress</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7914,12 +8446,12 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Updated</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13 17:58 UTC</t>
+          <t>2026-10-14 01:29 UTC</t>
         </is>
       </c>
       <c r="C2" s="3" t="n"/>
@@ -7939,7 +8471,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Today (Day 2)</t>
+          <t>Day 3</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -7960,14 +8492,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>16</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>✅ DONE</t>
+          <t>16 to go</t>
         </is>
       </c>
     </row>
@@ -7978,14 +8510,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>25</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>✅ DONE</t>
+          <t>20 to go</t>
         </is>
       </c>
     </row>
@@ -7996,7 +8528,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
@@ -8014,11 +8546,11 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Total leads in tracker</t>
+          <t>Total leads</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="C9" s="3" t="n"/>
       <c r="D9" s="3" t="n"/>

--- a/HWA_Lead_Tracker.xlsx
+++ b/HWA_Lead_Tracker.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O123"/>
+  <dimension ref="A1:O137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8408,6 +8408,960 @@
         </is>
       </c>
       <c r="O123" t="inlineStr">
+        <is>
+          <t>Day 3 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>L123</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Bounce Box Team</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Boxing Team</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>@boxteambounce</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/boxteambounce/</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Vienna</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>info@bounce.at</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>bounce.at</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>COMPLETE: email sent + IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>Boxing team Vienna.</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>Gloves, headgear</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>Day 3 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>L124</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Box Union Favoriten</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Boxing Gym</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>@boxunionfavoriten</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/boxunionfavoriten/</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Vienna</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>boxgym.at</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>COMPLETE: IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>Boxing gym Vienna.</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>Gloves, fight wear</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>Day 3 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>L125</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Kickboxen Wien</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Kickboxing School</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Vienna</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>office@kickboxen.net</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>kickboxen-wien.com</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>COMPLETE: email sent</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>Kickboxing school Vienna.</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>Gloves, shin guards</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>Day 3 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>L126</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Brothers Gym Wien</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Combat Gym</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>@brothers_gym_wien</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/brothers_gym_wien/</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Vienna</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>info@brothersgym.at</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>brothersgym.at</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>COMPLETE: email sent + IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>Combat gym Vienna.</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>Gloves, fight wear</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>Day 3 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>L127</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Boxteam Vienna</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Boxing Team</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>@boxteamvienna</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/boxteamvienna/</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Vienna</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>office@boxteam-vienna.at</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>boxteamvienna.at</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>COMPLETE: email sent + IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>Boxing team Vienna.</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>Gloves, headgear</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>Day 3 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>L128</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Thai Box Gym</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Muay Thai Gym</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>office@thaiboxgym.at</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>thaiboxgym.at</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>COMPLETE: email sent</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>Muay Thai gym Austria.</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>Thai pads, shorts</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>Day 3 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>L129</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Boxschmiede Vienna</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Boxing Gym</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>@boxschmiede_vienna</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/boxschmiede_vienna/</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Vienna</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>office@boxschmiede.wien</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>boxschmiede.wien</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>COMPLETE: email sent + IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>Boxing gym Vienna.</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>Gloves, headgear</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>Day 3 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>L130</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>PT do Bairro</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Kickboxing Gym</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>@ptdobairro</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ptdobairro/</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>351931468801</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>geral@ptdobairro.pt</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>ptdobairro.pt</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent + email sent + IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>Kickboxing gym Portugal. GOLD: WA + email + IG.</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>Gloves, shin guards</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>Day 3 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>L131</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Hammer Box PT</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Boxing Gym</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>hammerboxpt.pt</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>PENDING: WA number truncated on site — needs manual verification</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>Boxing gym Portugal. WA number truncated on site — needs manual check.</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>Gloves, headgear</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>Day 3 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>L132</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Alvaro Campeao</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Boxing/Muay Thai</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>@alvarotdcampeao</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/alvarotdcampeao/</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>351916033601</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>pt.alvarocampeao@gmail.com</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>alvarocampeao.com</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>COMPLETE: email sent + IG followed + IG DM sent (phone NOT on WhatsApp — verified)</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>Boxing/Muay Thai coach Portugal. GOLD: WA + email + IG.</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>Gloves, Thai pads</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>Day 3 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>L133</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Lab Boxing Edgar Marques</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Boxing Gym</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>@edgarmarquescoach</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/edgarmarquescoach/</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>emsports.pt</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>COMPLETE: IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>Boxing coach Portugal.</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>Gloves, pads</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>Day 3 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>L134</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Studio Absoluto JJ</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Jiu-Jitsu Studio</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>@studiofitnessabsoluto</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/studiofitnessabsoluto/</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>351934624841</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>info@studioabsoluto.pt</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>studioabsoluto.pt</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent + email sent + IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>Jiu-Jitsu studio Portugal. GOLD: WA + email + IG.</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>Gis, belts, rash guards</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>Day 3 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>L135</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>AMDKP</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Martial Arts Assoc</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>351911165714</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>assembleia.geral@amdkp.pt</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>amdkp.pt</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent + email sent</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>Martial arts association Portugal. WA + email.</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>Uniforms, belts</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>Day 3 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>L136</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Academia Skills</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Martial Arts Gym</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>@academia.skills</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/academia.skills/</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>treino.na.skills@gmail.com</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>academia-skills.com</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>COMPLETE: email sent + IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>Martial arts gym Portugal.</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>Uniforms, gear</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
         <is>
           <t>Day 3 hunt batch</t>
         </is>
@@ -8451,7 +9405,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-14 01:29 UTC</t>
+          <t>2026-10-14 01:51 UTC</t>
         </is>
       </c>
       <c r="C2" s="3" t="n"/>
@@ -8492,14 +9446,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>16</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>16 to go</t>
+          <t>13 to go</t>
         </is>
       </c>
     </row>
@@ -8510,14 +9464,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>25</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>20 to go</t>
+          <t>9 to go</t>
         </is>
       </c>
     </row>
@@ -8528,7 +9482,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
@@ -8550,7 +9504,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="C9" s="3" t="n"/>
       <c r="D9" s="3" t="n"/>

--- a/HWA_Lead_Tracker.xlsx
+++ b/HWA_Lead_Tracker.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O137"/>
+  <dimension ref="A1:O143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -9362,6 +9362,448 @@
         </is>
       </c>
       <c r="O137" t="inlineStr">
+        <is>
+          <t>Day 3 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>L137</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>AGFA Boxe</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Boxing Club</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>@agfaboxe</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/agfaboxe/</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>contact@agfa-boxe.com</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>agfaboxe.fr</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>COMPLETE: email sent + IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>Boxing club France.</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>Gloves, headgear</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>Day 3 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>L138</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Spirit Academy 74</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Combat Gym</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>@spirit_academy74</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/spirit_academy74/</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>41796061009</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>spiritacademy74@gmail.com</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>spiritacademy74.fr</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent + email sent + IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>Combat gym Switzerland. GOLD: WA + email + IG.</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>Gloves, fight wear</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>Day 3 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>L139</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Beat 35 Studio</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Boxing Studio</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>@beat35studio</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/beat35studio/</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>33672587591</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>hello@beat-35.com</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>beat-35.com</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent + email sent + IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>Boxing studio France. GOLD: WA + email + IG.</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>Gloves, pads</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>Day 3 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>L140</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Fight Center Boxing</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Boxing Gym</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>33783401554</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>fightboxing13@gmail.com</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>fightcenterboxing.fr</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>COMPLETE: email sent (phone NOT on WhatsApp — verified)</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>Boxing gym France. Phone NOT on WhatsApp (verified).</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>Gloves, headgear</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>Day 3 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>L141</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Le Hook Vieux Lille</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>MMA Gym</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>@lehookvieuxlille</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lehookvieuxlille/</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Lille</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>33766685436</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>lehook.fr</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent + IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>MMA gym Lille. WA + IG.</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>MMA shorts, gloves</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>Day 3 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>L142</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Bennies Boxing</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Boxing Gym</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>@benniesboxinggym</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/benniesboxinggym/</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>447961557534</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>benniesboxing@icloud.com</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>benniesboxing.co.uk</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent + email sent + IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>Boxing gym UK. GOLD: WA + email + IG.</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>Gloves, headgear, pads</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
         <is>
           <t>Day 3 hunt batch</t>
         </is>
@@ -9405,7 +9847,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-14 01:51 UTC</t>
+          <t>2026-10-14 02:09 UTC</t>
         </is>
       </c>
       <c r="C2" s="3" t="n"/>
@@ -9446,14 +9888,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>16</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>13 to go</t>
+          <t>9 to go</t>
         </is>
       </c>
     </row>
@@ -9464,14 +9906,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>25</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>9 to go</t>
+          <t>4 to go</t>
         </is>
       </c>
     </row>
@@ -9482,7 +9924,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
@@ -9504,7 +9946,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="C9" s="3" t="n"/>
       <c r="D9" s="3" t="n"/>

--- a/HWA_Lead_Tracker.xlsx
+++ b/HWA_Lead_Tracker.xlsx
@@ -3738,7 +3738,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>COMPLETE: WhatsApp sent + email sent + IG follow pending</t>
+          <t>RESEARCHED: contacts verified, outreach pending</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -9847,7 +9847,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-14 02:09 UTC</t>
+          <t>2026-10-14 05:31 UTC</t>
         </is>
       </c>
       <c r="C2" s="3" t="n"/>

--- a/HWA_Lead_Tracker.xlsx
+++ b/HWA_Lead_Tracker.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O143"/>
+  <dimension ref="A1:O173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>RESEARCHED: contacts verified, outreach pending</t>
+          <t>COMPLETE: follow=ok dm=sent email=None wa={"ok":true,"last":["Hello FullGym 24h Vilafranca! \n\n\n\nwe pro"]}</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -8991,7 +8991,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>PENDING: WA number truncated on site — needs manual verification</t>
+          <t>COMPLETE: follow=None dm=None email=None wa=None</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -9804,6 +9804,2048 @@
         </is>
       </c>
       <c r="O143" t="inlineStr">
+        <is>
+          <t>Day 3 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>L143</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Beat Box Boxing Club</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Boxing Club</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>@beatboxfitnessdublin</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/beatboxfitnessdublin/</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>beatboxboxingclub.com</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>COMPLETE: follow=profile-not-found dm=skipped email=None wa=None</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>Boxing club Dublin.</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>Gloves, pads</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>Day 3 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>L144</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Angels Boxing</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Boxing Club</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>@coach_reg.byrne</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/coach_reg.byrne/</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>353873256588</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>byrnereg43@gmail.com</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>angelsboxing.ie</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent + IG followed + IG DM sent (email dead — verified)</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>Boxing club Dublin. GOLD: WA + email + IG.</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>Gloves, headgear</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>Day 3 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>L145</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Underdog Boxing Gym</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Boxing Gym</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>@underdogboxing</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/underdogboxing/</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>underdogboxingdublin@gmail.com</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>underdogboxinggym.ie</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>COMPLETE: follow=no-btn dm=sent email=sent wa=None</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>Boxing gym Dublin.</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>Gloves, headgear</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>Day 3 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>L146</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Fightr Dublin</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Boxing Gym</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>fightrdublin@gmail.com</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>fightr.ie</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>COMPLETE: follow=None dm=None email=sent wa=None</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>Boxing gym Dublin.</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>Gloves, fight wear</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>Day 3 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>L147</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Glasnevin Boxing Club</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Boxing Club</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>@glasnevin_boxing_club</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/glasnevin_boxing_club/</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>glasnevinboxingclub.ie</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>COMPLETE: follow=no-btn dm=no-composer email=None wa=None</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>Boxing club Dublin.</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>Gloves, headgear</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>Day 3 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>L148</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>CIE Boxing Club</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Boxing Club</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>@cieboxingclub</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cieboxingclub/</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>cieboxingclub@gmail.com</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>cieboxingclub.org</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>COMPLETE: email sent + IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>Boxing club Dublin.</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>Gloves, headgear</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>Day 3 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>L149</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Kickboxing MMA Roma</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Kickboxing Gym</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>info@kickboxingmmaroma.com</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>kickboxingmmaroma.com</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>COMPLETE: email sent</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>Kickboxing/MMA gym Roma.</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>Gloves, shin guards</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>Day 3 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>L150</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Fortitudine Boxe</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Boxing Gym</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>@fortitudoboxe</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/fortitudoboxe/</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>fabriziodife@gmail.com</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>fortitudoboxe.com</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>COMPLETE: email sent + IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>Boxing gym Italy.</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>Gloves, headgear</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>Day 3 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>L151</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Kombatsport Moncalieri</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Kickboxing Gym</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>@kombatsportmoncalieri</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kombatsportmoncalieri/</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>info@kombatsportmoncalieri.it</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>kombatsporttorino.it</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>COMPLETE: email sent + IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>Kickboxing gym Torino.</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>Gloves, fight wear</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>Day 3 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>L152</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Kombat Gym Roma</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Kickboxing Gym</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>info@kombatgymroma.it</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>kombatgymroma.it</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>COMPLETE: email sent</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>Kickboxing gym Roma Centocelle.</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>Gloves, pads</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>Day 3 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>L153</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Bomaye Gym München</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Boxgym</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>@bomayegym_munich</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bomayegym_munich/</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>München</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>491737513627</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>bomayegym.com</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent + IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>Boxgym München. GOLD: WA + IG (site email is placeholder).</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>Gloves, headgear</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>Day 3 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>L154</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Martial Arts Center München</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Martial Arts School</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>München</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>491708890687</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>info@ving-tsun.net</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>martial-arts-center.de</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent + email sent</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>Martial arts school München. WA + email.</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>Gloves, uniforms</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>Day 3 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>L155</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Kimkong Sports</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Boxing/Kickboxing</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr"/>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>mail@kimkongsports.de</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>kimkongsports.de</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>COMPLETE: email sent</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>Boxing/kickboxing gym Germany.</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>Gloves, fight wear</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>Day 3 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>L156</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Trust Gym</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Combat Gym</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>@headcoachayhan</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/headcoachayhan/</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>info@trustgym.de</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>trustgym.de</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>COMPLETE: email sent + IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>Combat gym Germany.</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>Gloves, fight wear</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>Day 3 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>L157</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>NFT Gym München</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Fight Gym</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>@nft_gym</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nft_gym/</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>München</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>nft-gym.de</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>COMPLETE: IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>Fight gym München.</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>Gloves, fight wear</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>Day 3 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>L158</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Crossbox Gym</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Crossbox Gym</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>@crossboxgym</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/crossboxgym/</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>34649316067</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>crossboxgym@protonmail.com</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>crossboxgym.com</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent + email sent + IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>Crossbox gym Spain. GOLD: WA + email + IG.</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>Gloves, fight wear</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>Day 3 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>L159</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Ali Promotions BCN</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Boxing Promotions</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>@alipromotions.bcn</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/alipromotions.bcn/</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>34687075304</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>alipromotions.bcn@gmail.com</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>alipromotions.com</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent + email sent + IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>Boxing promotions Barcelona. GOLD: WA + email + IG.</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>Gloves, fight wear</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>Day 3 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>L160</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Hybrd Academy</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Combat Gym</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr"/>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>34692382544</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>urbansportsclub.com</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent (no other channels)</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>Combat gym (Hybrd Academy, USC venue). WA.</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>Gloves, fight wear</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>Day 3 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>L161</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>CrossFit Diagonal</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Fitness/Crossbox</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>@crossfitdiagonal</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/crossfitdiagonal/</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>crossfit-diagonal.com</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>IG only profile found — no contact channels available</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>CrossFit gym Barcelona.</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>Gloves, apparel</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>Day 3 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>L162</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Rockfit BCN</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Fitness Gym</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>@rockfitbcn</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/rockfitbcn/</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>rockfit.es</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>IG follow/DM failed — profile not found</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>Fitness gym Barcelona.</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>Gloves, apparel</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>Day 3 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>L163</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Armazém Jiu-Jitsu</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Jiu-Jitsu/Muay Thai</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>@armazen.jiujitsu</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/armazen.jiujitsu/</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>351925896645</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>armazenamf@gmail.com</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>armazenjiujitsu.com</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent + email sent + IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>Jiu-Jitsu + Muay Thai Lisboa. GOLD: WA + email + IG.</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>Gis, Thai shorts, gloves</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>Day 3 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>L164</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Fred Motta Muay Thai</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Muay Thai Gym</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>@fredmotta_muaythai</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/fredmotta_muaythai/</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>351968718777</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>fred@fredmotta.pt</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>fredmotta.pt</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent + email sent + IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>Fred Motta Muay Thai Portugal. GOLD: WA + email + IG.</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>Thai pads, shorts, gloves</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>Day 3 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>L165</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Z Fortes Muay Thai</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Muay Thai Gym</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>@zfortesmuaythai</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/zfortesmuaythai/</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>351965577023</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>geral@zfortes.com.pt</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>zfortes.com.pt</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>COMPLETE: WhatsApp sent + email sent + IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>Z Fortes Muay Thai Portugal. GOLD: WA + email + IG.</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>Thai pads, shorts, gloves</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>Day 3 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>L166</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>KO Team</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Combat Team</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr"/>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>info@koteam.pt</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>koteam.pt</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>COMPLETE: email sent</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>Combat team Portugal.</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>Gloves, fight wear</t>
+        </is>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>Day 3 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>L167</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Dinamite Team Lisboa</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Combat Team</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>@dinamite.team</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dinamite.team/</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>dinamite-team.com</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>COMPLETE: IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>Combat team Lisboa.</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>Gloves, fight wear</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>Day 3 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>L168</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Victor Borba MT</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Muay Thai Gym</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>@victor.borbamt</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/victor.borbamt/</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>victorborba@hotmail.com</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>victorborbamt.com</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>COMPLETE: email sent + IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>Victor Borba Muay Thai Portugal.</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>Thai pads, shorts</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>Day 3 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>L169</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Boxing Club Nantais</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Boxing Club</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>@boxingclubnantais</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/boxingclubnantais/</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>boxingclubnantais@gmail.com</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>boxingclubnantais.com</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>COMPLETE: email sent + IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>Boxing club Nantes.</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>Gloves, headgear</t>
+        </is>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>Day 3 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>L170</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Battling Club Bordeaux</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Boxing Club</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>@battlingclubbordeaux</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/battlingclubbordeaux/</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Bordeaux</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>contact@battlingclubbdx.com</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>battlingclubbdx.com</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>COMPLETE: email sent + IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>Boxing club Bordeaux.</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>Gloves, headgear</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>Day 3 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>L171</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Fight'n Fit Bordeaux</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Boxing Gym</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Bordeaux</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>fightnfitbordeaux@gmail.com</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>fightnfitbordeaux.fr</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>COMPLETE: email sent (retry ok)</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>Boxing gym Bordeaux.</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>Gloves, pads</t>
+        </is>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>Day 3 hunt batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>L172</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>École Adam Bordeaux</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Boxing School</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>@ecoleadambordeaux</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ecoleadambordeaux/</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Bordeaux</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>adam-bordeaux.fr</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>COMPLETE: IG followed + IG DM sent</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>Boxing school Bordeaux.</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>Gloves, headgear</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr">
         <is>
           <t>Day 3 hunt batch</t>
         </is>
@@ -9820,7 +11862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -9832,7 +11874,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>HSN Warrior Apparels — Day 3 Progress</t>
+          <t>HSN Warrior Apparels — Day 3 FINAL</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9847,7 +11889,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-14 05:31 UTC</t>
+          <t>2026-10-14 08:16 UTC</t>
         </is>
       </c>
       <c r="C2" s="3" t="n"/>
@@ -9888,14 +11930,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>16</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>9 to go</t>
+          <t>✅ DONE</t>
         </is>
       </c>
     </row>
@@ -9906,14 +11948,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>25</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>4 to go</t>
+          <t>✅ DONE</t>
         </is>
       </c>
     </row>
@@ -9924,7 +11966,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
@@ -9946,10 +11988,24 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>142</v>
+        <v>172</v>
       </c>
       <c r="C9" s="3" t="n"/>
       <c r="D9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Countries</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>ES PT DE FR IT NL PL UK IE BE AT CH</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n"/>
+      <c r="D10" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/HWA_Lead_Tracker.xlsx
+++ b/HWA_Lead_Tracker.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leads" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 4 Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 4 Countries" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -11898,7 +11897,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=no-msg-btn</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
@@ -12020,7 +12019,7 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=no-btn dm=sent</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
@@ -12085,7 +12084,7 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=no-btn dm=sent</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
@@ -12120,16 +12119,8 @@
           <t>Gym/Club</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>@ancora_themes</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/ancora_themes/</t>
-        </is>
-      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr"/>
       <c r="G178" t="inlineStr">
         <is>
@@ -12158,7 +12149,7 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent [IG handle was junk - removed]</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
@@ -12223,7 +12214,7 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
@@ -12288,7 +12279,7 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
@@ -12353,7 +12344,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -12418,7 +12409,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -12548,7 +12539,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -12613,7 +12604,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -12743,7 +12734,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG profile not found | IG profile not found | IG profile not found | IG profile not found | IG profile not found</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -12881,7 +12872,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG profile not found | IG profile not found | IG profile not found | IG profile not found | IG profile not found</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
@@ -12946,7 +12937,7 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
@@ -13011,7 +13002,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -13133,7 +13124,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -13198,7 +13189,7 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
@@ -13377,7 +13368,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
@@ -13499,7 +13490,7 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
@@ -13621,7 +13612,7 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
@@ -13743,7 +13734,7 @@
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG profile not found | IG profile not found | IG profile not found | IG profile not found | IG profile not found</t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
@@ -13808,7 +13799,7 @@
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
@@ -13873,7 +13864,7 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG profile not found | IG profile not found | IG profile not found | IG profile not found | IG profile not found</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
@@ -13995,7 +13986,7 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
@@ -14060,7 +14051,7 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
@@ -14125,7 +14116,7 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
@@ -14190,7 +14181,7 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
@@ -14255,7 +14246,7 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG profile not found | IG profile not found | IG profile not found | IG profile not found | IG profile not found</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
@@ -14320,7 +14311,7 @@
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M212" t="inlineStr">
@@ -14385,7 +14376,7 @@
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M213" t="inlineStr">
@@ -14450,7 +14441,7 @@
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M214" t="inlineStr">
@@ -14515,7 +14506,7 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
@@ -14580,7 +14571,7 @@
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M216" t="inlineStr">
@@ -14645,7 +14636,7 @@
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>FEDERATION - skipped (not a client gym) | IG follow=no-btn dm=sent</t>
         </is>
       </c>
       <c r="M217" t="inlineStr">
@@ -14710,7 +14701,7 @@
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>FEDERATION - skipped (not a client gym) | IG follow=no-btn dm=sent</t>
         </is>
       </c>
       <c r="M218" t="inlineStr">
@@ -14775,7 +14766,7 @@
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>FEDERATION - skipped (not a client gym) | IG follow=no-btn dm=sent</t>
         </is>
       </c>
       <c r="M219" t="inlineStr">
@@ -14840,7 +14831,7 @@
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>FEDERATION - skipped (not a client gym) | IG follow=no-btn dm=sent</t>
         </is>
       </c>
       <c r="M220" t="inlineStr">
@@ -14905,7 +14896,7 @@
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>FEDERATION - skipped (not a client gym)</t>
         </is>
       </c>
       <c r="M221" t="inlineStr">
@@ -14970,7 +14961,7 @@
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>FEDERATION - skipped (not a client gym)</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">
@@ -15035,7 +15026,7 @@
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M223" t="inlineStr">
@@ -15157,7 +15148,7 @@
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M225" t="inlineStr">
@@ -15222,7 +15213,7 @@
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M226" t="inlineStr">
@@ -15344,7 +15335,7 @@
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=clicked dm=no-msg-btn</t>
         </is>
       </c>
       <c r="M228" t="inlineStr">
@@ -15466,7 +15457,7 @@
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>FEDERATION - skipped (not a client gym)</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
@@ -15531,7 +15522,7 @@
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>DUPLICATE SKIPPED (same IG as another lead) | IG follow=no-btn dm=sent</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
@@ -15596,7 +15587,7 @@
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=no-msg-btn</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
@@ -15661,7 +15652,7 @@
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>DUPLICATE SKIPPED (same IG as another lead) | IG follow=no-btn dm=sent</t>
         </is>
       </c>
       <c r="M233" t="inlineStr">
@@ -15726,7 +15717,7 @@
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
@@ -15791,7 +15782,7 @@
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M235" t="inlineStr">
@@ -15856,7 +15847,7 @@
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M236" t="inlineStr">
@@ -15921,7 +15912,7 @@
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG profile not found | IG profile not found</t>
         </is>
       </c>
       <c r="M237" t="inlineStr">
@@ -15986,7 +15977,7 @@
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG profile not found | IG profile not found</t>
         </is>
       </c>
       <c r="M238" t="inlineStr">
@@ -16116,7 +16107,7 @@
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG profile not found | IG profile not found</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
@@ -16181,7 +16172,7 @@
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
@@ -16246,7 +16237,7 @@
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=no-btn dm=sent</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
@@ -16368,7 +16359,7 @@
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG profile not found | IG profile not found</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
@@ -16433,7 +16424,7 @@
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>FEDERATION - skipped (not a client gym)</t>
         </is>
       </c>
       <c r="M245" t="inlineStr">
@@ -16498,7 +16489,7 @@
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>FEDERATION - skipped (not a client gym)</t>
         </is>
       </c>
       <c r="M246" t="inlineStr">
@@ -16563,7 +16554,7 @@
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>DUPLICATE SKIPPED (same IG as another lead) | IG follow=no-btn dm=sent</t>
         </is>
       </c>
       <c r="M247" t="inlineStr">
@@ -16628,7 +16619,7 @@
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>DUPLICATE SKIPPED (same IG as another lead) | IG follow=no-btn dm=sent</t>
         </is>
       </c>
       <c r="M248" t="inlineStr">
@@ -16693,7 +16684,7 @@
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>DUPLICATE SKIPPED (same IG as another lead) | IG follow=no-btn dm=sent</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
@@ -16758,7 +16749,7 @@
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
@@ -16880,7 +16871,7 @@
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M252" t="inlineStr">
@@ -16953,7 +16944,7 @@
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
@@ -17018,7 +17009,7 @@
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
@@ -17091,7 +17082,7 @@
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M255" t="inlineStr">
@@ -17164,7 +17155,7 @@
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
@@ -17286,7 +17277,7 @@
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
@@ -17351,7 +17342,7 @@
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M259" t="inlineStr">
@@ -17416,7 +17407,7 @@
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M260" t="inlineStr">
@@ -17481,7 +17472,7 @@
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=no-btn dm=sent</t>
         </is>
       </c>
       <c r="M261" t="inlineStr">
@@ -17603,7 +17594,7 @@
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M263" t="inlineStr">
@@ -17668,7 +17659,7 @@
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M264" t="inlineStr">
@@ -17733,7 +17724,7 @@
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M265" t="inlineStr">
@@ -17798,7 +17789,7 @@
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M266" t="inlineStr">
@@ -17863,7 +17854,7 @@
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M267" t="inlineStr">
@@ -17936,7 +17927,7 @@
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M268" t="inlineStr">
@@ -18001,7 +17992,7 @@
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M269" t="inlineStr">
@@ -18074,7 +18065,7 @@
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M270" t="inlineStr">
@@ -18139,7 +18130,7 @@
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M271" t="inlineStr">
@@ -18326,7 +18317,7 @@
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=no-btn dm=sent</t>
         </is>
       </c>
       <c r="M274" t="inlineStr">
@@ -18562,7 +18553,7 @@
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>FEDERATION - skipped (not a client gym)</t>
         </is>
       </c>
       <c r="M278" t="inlineStr">
@@ -18627,7 +18618,7 @@
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>FEDERATION - skipped (not a client gym)</t>
         </is>
       </c>
       <c r="M279" t="inlineStr">
@@ -18692,7 +18683,7 @@
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>FEDERATION - skipped (not a client gym)</t>
         </is>
       </c>
       <c r="M280" t="inlineStr">
@@ -18757,7 +18748,7 @@
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>FEDERATION - skipped (not a client gym)</t>
         </is>
       </c>
       <c r="M281" t="inlineStr">
@@ -18822,7 +18813,7 @@
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>FEDERATION - skipped (not a client gym)</t>
         </is>
       </c>
       <c r="M282" t="inlineStr">
@@ -18887,7 +18878,7 @@
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>FEDERATION - skipped (not a client gym)</t>
         </is>
       </c>
       <c r="M283" t="inlineStr">
@@ -18952,7 +18943,7 @@
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M284" t="inlineStr">
@@ -19074,7 +19065,7 @@
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M286" t="inlineStr">
@@ -19139,7 +19130,7 @@
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M287" t="inlineStr">
@@ -19212,7 +19203,7 @@
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M288" t="inlineStr">
@@ -19391,7 +19382,7 @@
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M291" t="inlineStr">
@@ -19456,7 +19447,7 @@
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M292" t="inlineStr">
@@ -19521,7 +19512,7 @@
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M293" t="inlineStr">
@@ -19586,7 +19577,7 @@
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=clicked dm=sent</t>
         </is>
       </c>
       <c r="M294" t="inlineStr">
@@ -19651,7 +19642,7 @@
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>FEDERATION - skipped (not a client gym)</t>
         </is>
       </c>
       <c r="M295" t="inlineStr">
@@ -19716,7 +19707,7 @@
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>FEDERATION - skipped (not a client gym)</t>
         </is>
       </c>
       <c r="M296" t="inlineStr">
@@ -19781,7 +19772,7 @@
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>FEDERATION - skipped (not a client gym)</t>
         </is>
       </c>
       <c r="M297" t="inlineStr">
@@ -19846,7 +19837,7 @@
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>FEDERATION - skipped (not a client gym)</t>
         </is>
       </c>
       <c r="M298" t="inlineStr">
@@ -19968,7 +19959,7 @@
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>FEDERATION - skipped (not a client gym)</t>
         </is>
       </c>
       <c r="M300" t="inlineStr">
@@ -20033,7 +20024,7 @@
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>FEDERATION - skipped (not a client gym)</t>
         </is>
       </c>
       <c r="M301" t="inlineStr">
@@ -20155,7 +20146,7 @@
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>FEDERATION - skipped (not a client gym)</t>
         </is>
       </c>
       <c r="M303" t="inlineStr">
@@ -20277,7 +20268,7 @@
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=clicked dm=sent</t>
         </is>
       </c>
       <c r="M305" t="inlineStr">
@@ -20570,7 +20561,7 @@
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=clicked dm=sent</t>
         </is>
       </c>
       <c r="M310" t="inlineStr">
@@ -20863,7 +20854,7 @@
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=clicked dm=no-msg-btn</t>
         </is>
       </c>
       <c r="M315" t="inlineStr">
@@ -20928,7 +20919,7 @@
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=clicked dm=sent</t>
         </is>
       </c>
       <c r="M316" t="inlineStr">
@@ -20993,7 +20984,7 @@
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=clicked dm=sent</t>
         </is>
       </c>
       <c r="M317" t="inlineStr">
@@ -21058,7 +21049,7 @@
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=clicked dm=sent</t>
         </is>
       </c>
       <c r="M318" t="inlineStr">
@@ -21123,7 +21114,7 @@
       </c>
       <c r="L319" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=clicked dm=sent</t>
         </is>
       </c>
       <c r="M319" t="inlineStr">
@@ -21359,7 +21350,7 @@
       </c>
       <c r="L323" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=clicked dm=sent</t>
         </is>
       </c>
       <c r="M323" t="inlineStr">
@@ -21766,7 +21757,7 @@
       </c>
       <c r="L330" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=clicked dm=no-msg-btn</t>
         </is>
       </c>
       <c r="M330" t="inlineStr">
@@ -21888,7 +21879,7 @@
       </c>
       <c r="L332" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=clicked dm=sent</t>
         </is>
       </c>
       <c r="M332" t="inlineStr">
@@ -21953,7 +21944,7 @@
       </c>
       <c r="L333" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=clicked dm=sent</t>
         </is>
       </c>
       <c r="M333" t="inlineStr">
@@ -22018,7 +22009,7 @@
       </c>
       <c r="L334" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=clicked dm=sent</t>
         </is>
       </c>
       <c r="M334" t="inlineStr">
@@ -22083,7 +22074,7 @@
       </c>
       <c r="L335" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=clicked dm=sent</t>
         </is>
       </c>
       <c r="M335" t="inlineStr">
@@ -22148,7 +22139,7 @@
       </c>
       <c r="L336" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=clicked dm=sent</t>
         </is>
       </c>
       <c r="M336" t="inlineStr">
@@ -22213,7 +22204,7 @@
       </c>
       <c r="L337" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG profile not found</t>
         </is>
       </c>
       <c r="M337" t="inlineStr">
@@ -22343,7 +22334,7 @@
       </c>
       <c r="L339" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=clicked dm=sent</t>
         </is>
       </c>
       <c r="M339" t="inlineStr">
@@ -22465,7 +22456,7 @@
       </c>
       <c r="L341" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=clicked dm=sent</t>
         </is>
       </c>
       <c r="M341" t="inlineStr">
@@ -22530,7 +22521,7 @@
       </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=clicked dm=sent</t>
         </is>
       </c>
       <c r="M342" t="inlineStr">
@@ -22652,7 +22643,7 @@
       </c>
       <c r="L344" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=clicked dm=sent</t>
         </is>
       </c>
       <c r="M344" t="inlineStr">
@@ -22717,7 +22708,7 @@
       </c>
       <c r="L345" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=no-btn dm=sent</t>
         </is>
       </c>
       <c r="M345" t="inlineStr">
@@ -22782,7 +22773,7 @@
       </c>
       <c r="L346" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=clicked dm=sent</t>
         </is>
       </c>
       <c r="M346" t="inlineStr">
@@ -22847,7 +22838,7 @@
       </c>
       <c r="L347" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=clicked dm=sent</t>
         </is>
       </c>
       <c r="M347" t="inlineStr">
@@ -22920,7 +22911,7 @@
       </c>
       <c r="L348" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=clicked dm=sent</t>
         </is>
       </c>
       <c r="M348" t="inlineStr">
@@ -23107,7 +23098,7 @@
       </c>
       <c r="L351" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=clicked dm=sent</t>
         </is>
       </c>
       <c r="M351" t="inlineStr">
@@ -23172,7 +23163,7 @@
       </c>
       <c r="L352" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=clicked dm=sent</t>
         </is>
       </c>
       <c r="M352" t="inlineStr">
@@ -23237,7 +23228,7 @@
       </c>
       <c r="L353" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=clicked dm=sent</t>
         </is>
       </c>
       <c r="M353" t="inlineStr">
@@ -23302,7 +23293,7 @@
       </c>
       <c r="L354" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=clicked dm=sent</t>
         </is>
       </c>
       <c r="M354" t="inlineStr">
@@ -23375,7 +23366,7 @@
       </c>
       <c r="L355" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=clicked dm=sent</t>
         </is>
       </c>
       <c r="M355" t="inlineStr">
@@ -23440,7 +23431,7 @@
       </c>
       <c r="L356" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=clicked dm=sent</t>
         </is>
       </c>
       <c r="M356" t="inlineStr">
@@ -23505,7 +23496,7 @@
       </c>
       <c r="L357" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=clicked dm=sent</t>
         </is>
       </c>
       <c r="M357" t="inlineStr">
@@ -23570,7 +23561,7 @@
       </c>
       <c r="L358" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=clicked dm=sent</t>
         </is>
       </c>
       <c r="M358" t="inlineStr">
@@ -23635,7 +23626,7 @@
       </c>
       <c r="L359" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=clicked dm=sent</t>
         </is>
       </c>
       <c r="M359" t="inlineStr">
@@ -23757,7 +23748,7 @@
       </c>
       <c r="L361" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=clicked dm=sent</t>
         </is>
       </c>
       <c r="M361" t="inlineStr">
@@ -23822,7 +23813,7 @@
       </c>
       <c r="L362" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=clicked dm=no-msg-btn</t>
         </is>
       </c>
       <c r="M362" t="inlineStr">
@@ -23944,7 +23935,7 @@
       </c>
       <c r="L364" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=clicked dm=sent</t>
         </is>
       </c>
       <c r="M364" t="inlineStr">
@@ -24066,7 +24057,7 @@
       </c>
       <c r="L366" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=clicked dm=sent</t>
         </is>
       </c>
       <c r="M366" t="inlineStr">
@@ -24131,7 +24122,7 @@
       </c>
       <c r="L367" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=clicked dm=sent</t>
         </is>
       </c>
       <c r="M367" t="inlineStr">
@@ -24196,7 +24187,7 @@
       </c>
       <c r="L368" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=clicked dm=sent</t>
         </is>
       </c>
       <c r="M368" t="inlineStr">
@@ -24318,7 +24309,7 @@
       </c>
       <c r="L370" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=clicked dm=sent</t>
         </is>
       </c>
       <c r="M370" t="inlineStr">
@@ -24383,7 +24374,7 @@
       </c>
       <c r="L371" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=clicked dm=sent</t>
         </is>
       </c>
       <c r="M371" t="inlineStr">
@@ -24448,7 +24439,7 @@
       </c>
       <c r="L372" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=clicked dm=sent</t>
         </is>
       </c>
       <c r="M372" t="inlineStr">
@@ -24513,7 +24504,7 @@
       </c>
       <c r="L373" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | IG follow=clicked dm=sent</t>
         </is>
       </c>
       <c r="M373" t="inlineStr">
@@ -24543,71 +24534,62 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>HSN Warrior Apparels — Day 4 Overnight Report</t>
+          <t>HSN Warrior Apparels — Day 4 COMPLETE Report</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Updated</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15 01:09 UTC</t>
+          <t>2026-10-15 03:14 UTC</t>
         </is>
       </c>
       <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n"/>
       <c r="B3" s="3" t="n"/>
       <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Metric</t>
+          <t>Channel</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Count</t>
+          <t>Day 4 Total</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Target</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Status</t>
+          <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>New leads found overnight</t>
+          <t>New leads found</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -24615,270 +24597,91 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>150-200</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>✅ DONE</t>
+          <t>target 150-200</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Cold emails sent</t>
+          <t>Emails sent</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>193</v>
+        <v>166</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>150-200</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>✅ DONE</t>
+          <t>waves overnight</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Emails failed (dead addresses)</t>
+          <t>IG follows</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>verified dead</t>
-        </is>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="C7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>IG fallback follow+DM</t>
+          <t>IG DMs sent</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>2</v>
+        <v>108</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>all failed</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>✅ done (2 IG-hunted)</t>
+          <t>unique profiles</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Total leads in tracker</t>
+          <t>Dead IG handles (not found)</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>372</v>
-      </c>
-      <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="3" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>WA numbers collected (pending unban)</t>
+          <t>No DM button (partial)</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>separate sheet</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>✅ in WA_Pending_List.xlsx</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Country</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>New Leads</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Emails Sent</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>32</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>32</v>
-      </c>
-      <c r="C3" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>28</v>
-      </c>
-      <c r="C4" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>22</v>
-      </c>
-      <c r="C5" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Belgium</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>21</v>
-      </c>
-      <c r="C6" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>20</v>
-      </c>
-      <c r="C7" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>18</v>
-      </c>
-      <c r="C8" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Poland</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>16</v>
-      </c>
-      <c r="C9" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>10</v>
-      </c>
-      <c r="C10" t="n">
-        <v>10</v>
+          <t>followed only</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Ireland</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="n">
-        <v>1</v>
-      </c>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Total tracker</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>372</v>
+      </c>
+      <c r="C11" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/HWA_Lead_Tracker.xlsx
+++ b/HWA_Lead_Tracker.xlsx
@@ -9067,7 +9067,7 @@
       </c>
       <c r="L133" s="2" t="inlineStr">
         <is>
-          <t>HOT LEAD (negotiating): picked MMA shorts + MMA tights + JJ gi, asked details. Sent full specs + quantity question 2026-10-15. Awaiting quantities for exact quote + mockup.</t>
+          <t>HOT LEAD (negotiating): picked MMA shorts + MMA tights + JJ gi; 16 Oct 1:16 AM asked 'Do you have any photo to show some examples?' - DRAFT with AI product photos ready, awaiting user send approval</t>
         </is>
       </c>
       <c r="M133" s="2" t="inlineStr">

--- a/HWA_Lead_Tracker.xlsx
+++ b/HWA_Lead_Tracker.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Leads" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Day 5 Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,8 +30,12 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font/>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -39,12 +44,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C00000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFD966"/>
+        <fgColor rgb="001F4E78"/>
       </patternFill>
     </fill>
   </fills>
@@ -60,10 +60,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -432,21 +433,21 @@
   <dimension ref="A1:O581"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
-    <col width="28" customWidth="1" min="11" max="11"/>
-    <col width="42" customWidth="1" min="12" max="12"/>
-    <col width="42" customWidth="1" min="13" max="13"/>
-    <col width="26" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
+    <col width="32" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="50" customWidth="1" min="12" max="12"/>
+    <col width="55" customWidth="1" min="13" max="13"/>
+    <col width="45" customWidth="1" min="14" max="14"/>
+    <col width="50" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -962,7 +963,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>RE-SENT first template via NEW WA number 2026-10-15</t>
+          <t>Follow-up sent 2026-10-16 (reference old pads+gloves chat + free logo branding value). Awaiting reply.</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -1716,7 +1717,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>COMPLETE: IG followed + IG DM sent</t>
+          <t>COMPLETE: IG followed + IG DM sent | WA sent (Day 5 wave)</t>
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
@@ -1899,7 +1900,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>COMPLETE: IG DM sent (follow btn n/a - already following)</t>
+          <t>COMPLETE: IG DM sent (follow btn n/a - already following) | WA sent (Day 5 wave)</t>
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
@@ -2094,7 +2095,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>COMPLETE: IG followed + IG DM sent + email sent (info@koteam.pt)</t>
+          <t>COMPLETE: IG followed + IG DM sent + email sent (info@koteam.pt) | WA sent (Day 5 wave)</t>
         </is>
       </c>
       <c r="M28" t="inlineStr"/>
@@ -2224,7 +2225,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>COMPLETE: IG followed + IG DM sent</t>
+          <t>COMPLETE: IG followed + IG DM sent | WA sent (Day 5 wave)</t>
         </is>
       </c>
       <c r="M30" t="inlineStr"/>
@@ -5137,7 +5138,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>RE-SENT first template via NEW WA number 2026-10-15</t>
+          <t>Follow-up sent 2026-10-16 (fight-team package angle: 2-3 items + exact pricing offer). Awaiting reply.</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -5409,7 +5410,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>RE-SENT first template via NEW WA number 2026-10-15</t>
+          <t>Follow-up sent 2026-10-16 (ultra-short + 'reply yes' micro-commitment). Awaiting reply.</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -9010,77 +9011,77 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+      <c r="A133" t="inlineStr">
         <is>
           <t>L132</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
+      <c r="B133" t="inlineStr">
         <is>
           <t>Alvaro Campeao</t>
         </is>
       </c>
-      <c r="C133" s="2" t="inlineStr">
+      <c r="C133" t="inlineStr">
         <is>
           <t>Boxing/Muay Thai</t>
         </is>
       </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="D133" t="inlineStr">
         <is>
           <t>@alvarotdcampeao</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E133" t="inlineStr">
         <is>
           <t>https://www.instagram.com/alvarotdcampeao/</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F133" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr">
+      <c r="G133" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="H133" t="inlineStr">
         <is>
           <t>351916033601</t>
         </is>
       </c>
-      <c r="I133" s="2" t="inlineStr">
+      <c r="I133" t="inlineStr">
         <is>
           <t>mobile</t>
         </is>
       </c>
-      <c r="J133" s="2" t="inlineStr">
+      <c r="J133" t="inlineStr">
         <is>
           <t>pt.alvarocampeao@gmail.com</t>
         </is>
       </c>
-      <c r="K133" s="2" t="inlineStr">
+      <c r="K133" t="inlineStr">
         <is>
           <t>alvarocampeao.com</t>
         </is>
       </c>
-      <c r="L133" s="2" t="inlineStr">
-        <is>
-          <t>HOT LEAD (negotiating): picked MMA shorts + MMA tights + JJ gi; 16 Oct 1:16 AM asked 'Do you have any photo to show some examples?' - DRAFT with AI product photos ready, awaiting user send approval</t>
-        </is>
-      </c>
-      <c r="M133" s="2" t="inlineStr">
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>HOT LEAD (payment stage): asked Dirham or Euro. Answered: Euro pricing, he pays Dirham via Western Union, we receive local currency. Awaiting his confirmation + logo. Sample EUR 77.40.</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
         <is>
           <t>Boxing/Muay Thai coach Portugal. GOLD: WA + email + IG.</t>
         </is>
       </c>
-      <c r="N133" s="2" t="inlineStr">
+      <c r="N133" t="inlineStr">
         <is>
           <t>Gloves, Thai pads</t>
         </is>
       </c>
-      <c r="O133" s="2" t="inlineStr">
+      <c r="O133" t="inlineStr">
         <is>
           <t>HOT LEAD - Alvaro Campeao, UAE +971504894282. Products: MMA shorts, MMA tights, JJ gi. Next step: quantities -&gt; quote + mockup. Sign-off: company name only.</t>
         </is>
@@ -12148,7 +12149,7 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent [IG handle was junk - removed]</t>
+          <t>COMPLETE: email sent [IG handle was junk - removed] | WA sent (Day 5 wave)</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
@@ -12538,7 +12539,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent | IG follow=ok dm=sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent | WA sent (Day 5 wave)</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -12668,7 +12669,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | WA sent (Day 5 wave)</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -12798,7 +12799,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent</t>
+          <t>COMPLETE: email sent | WA sent (Day 5 wave)</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -12871,7 +12872,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent | IG profile not found | IG profile not found | IG profile not found | IG profile not found | IG profile not found</t>
+          <t>COMPLETE: email sent | IG profile not found | IG profile not found | IG profile not found | IG profile not found | IG profile not found | WA sent (Day 5 wave)</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
@@ -16943,7 +16944,7 @@
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent | IG follow=ok dm=sent</t>
+          <t>COMPLETE: email sent | IG follow=ok dm=sent | WA sent (Day 5 wave)</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
@@ -24568,7 +24569,7 @@
       </c>
       <c r="L374" t="inlineStr">
         <is>
-          <t>EMAIL FAILED: no-gmail-tab - IG fallback</t>
+          <t>EMAIL FAILED: no-gmail-tab - IG fallback | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M374" t="inlineStr">
@@ -24633,7 +24634,7 @@
       </c>
       <c r="L375" t="inlineStr">
         <is>
-          <t>EMAIL FAILED: no-gmail-tab - IG fallback</t>
+          <t>EMAIL FAILED: no-gmail-tab - IG fallback | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M375" t="inlineStr">
@@ -24698,7 +24699,7 @@
       </c>
       <c r="L376" t="inlineStr">
         <is>
-          <t>EMAIL FAILED: no-gmail-tab - IG fallback</t>
+          <t>EMAIL FAILED: no-gmail-tab - IG fallback | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M376" t="inlineStr">
@@ -24763,7 +24764,7 @@
       </c>
       <c r="L377" t="inlineStr">
         <is>
-          <t>EMAIL FAILED: no-gmail-tab - IG fallback</t>
+          <t>EMAIL FAILED: no-gmail-tab - IG fallback | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M377" t="inlineStr">
@@ -24824,7 +24825,7 @@
       </c>
       <c r="L378" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead - email re-hunt needed</t>
+          <t>RESEARCHED: USA lead - email re-hunt needed | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M378" t="inlineStr">
@@ -24889,7 +24890,7 @@
       </c>
       <c r="L379" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave) | IG error: [Errno 32] Broken pipe</t>
         </is>
       </c>
       <c r="M379" t="inlineStr">
@@ -24954,7 +24955,7 @@
       </c>
       <c r="L380" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave) | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M380" t="inlineStr">
@@ -25011,7 +25012,7 @@
       </c>
       <c r="L381" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M381" t="inlineStr">
@@ -25076,7 +25077,7 @@
       </c>
       <c r="L382" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave) | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M382" t="inlineStr">
@@ -25141,7 +25142,7 @@
       </c>
       <c r="L383" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>EMAIL FAILED: recipient-not-registered - IG fallback</t>
         </is>
       </c>
       <c r="M383" t="inlineStr">
@@ -25198,7 +25199,7 @@
       </c>
       <c r="L384" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M384" t="inlineStr">
@@ -25263,7 +25264,7 @@
       </c>
       <c r="L385" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave) | IG not found</t>
         </is>
       </c>
       <c r="M385" t="inlineStr">
@@ -25328,7 +25329,7 @@
       </c>
       <c r="L386" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave) | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M386" t="inlineStr">
@@ -25393,7 +25394,7 @@
       </c>
       <c r="L387" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave) | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M387" t="inlineStr">
@@ -25458,7 +25459,7 @@
       </c>
       <c r="L388" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave) | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M388" t="inlineStr">
@@ -25523,7 +25524,7 @@
       </c>
       <c r="L389" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>EMAIL FAILED: recipient-not-registered - IG fallback</t>
         </is>
       </c>
       <c r="M389" t="inlineStr">
@@ -25588,7 +25589,7 @@
       </c>
       <c r="L390" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave) | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M390" t="inlineStr">
@@ -25653,7 +25654,7 @@
       </c>
       <c r="L391" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M391" t="inlineStr">
@@ -25718,7 +25719,7 @@
       </c>
       <c r="L392" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M392" t="inlineStr">
@@ -25783,7 +25784,7 @@
       </c>
       <c r="L393" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M393" t="inlineStr">
@@ -25848,7 +25849,7 @@
       </c>
       <c r="L394" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M394" t="inlineStr">
@@ -25913,7 +25914,7 @@
       </c>
       <c r="L395" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M395" t="inlineStr">
@@ -25978,7 +25979,7 @@
       </c>
       <c r="L396" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M396" t="inlineStr">
@@ -26043,7 +26044,7 @@
       </c>
       <c r="L397" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M397" t="inlineStr">
@@ -26108,7 +26109,7 @@
       </c>
       <c r="L398" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M398" t="inlineStr">
@@ -26173,7 +26174,7 @@
       </c>
       <c r="L399" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M399" t="inlineStr">
@@ -26238,7 +26239,7 @@
       </c>
       <c r="L400" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M400" t="inlineStr">
@@ -26303,7 +26304,7 @@
       </c>
       <c r="L401" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M401" t="inlineStr">
@@ -26360,7 +26361,7 @@
       </c>
       <c r="L402" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M402" t="inlineStr">
@@ -26425,7 +26426,7 @@
       </c>
       <c r="L403" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>EMAIL FAILED: recipient-not-registered - IG fallback</t>
         </is>
       </c>
       <c r="M403" t="inlineStr">
@@ -26490,7 +26491,7 @@
       </c>
       <c r="L404" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M404" t="inlineStr">
@@ -26547,7 +26548,7 @@
       </c>
       <c r="L405" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M405" t="inlineStr">
@@ -26612,7 +26613,7 @@
       </c>
       <c r="L406" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M406" t="inlineStr">
@@ -26677,7 +26678,7 @@
       </c>
       <c r="L407" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M407" t="inlineStr">
@@ -26734,7 +26735,7 @@
       </c>
       <c r="L408" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>EMAIL FAILED: recipient-not-registered - IG fallback</t>
         </is>
       </c>
       <c r="M408" t="inlineStr">
@@ -26799,7 +26800,7 @@
       </c>
       <c r="L409" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M409" t="inlineStr">
@@ -26856,7 +26857,7 @@
       </c>
       <c r="L410" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M410" t="inlineStr">
@@ -26921,7 +26922,7 @@
       </c>
       <c r="L411" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M411" t="inlineStr">
@@ -26986,7 +26987,7 @@
       </c>
       <c r="L412" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M412" t="inlineStr">
@@ -27051,7 +27052,7 @@
       </c>
       <c r="L413" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M413" t="inlineStr">
@@ -27108,7 +27109,7 @@
       </c>
       <c r="L414" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M414" t="inlineStr">
@@ -27173,7 +27174,7 @@
       </c>
       <c r="L415" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M415" t="inlineStr">
@@ -27238,7 +27239,7 @@
       </c>
       <c r="L416" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M416" t="inlineStr">
@@ -27303,7 +27304,7 @@
       </c>
       <c r="L417" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>EMAIL FAILED: recipient-not-registered - IG fallback</t>
         </is>
       </c>
       <c r="M417" t="inlineStr">
@@ -27368,7 +27369,7 @@
       </c>
       <c r="L418" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M418" t="inlineStr">
@@ -27433,7 +27434,7 @@
       </c>
       <c r="L419" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M419" t="inlineStr">
@@ -27498,7 +27499,7 @@
       </c>
       <c r="L420" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M420" t="inlineStr">
@@ -27563,7 +27564,7 @@
       </c>
       <c r="L421" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M421" t="inlineStr">
@@ -27628,7 +27629,7 @@
       </c>
       <c r="L422" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M422" t="inlineStr">
@@ -27693,7 +27694,7 @@
       </c>
       <c r="L423" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M423" t="inlineStr">
@@ -27758,7 +27759,7 @@
       </c>
       <c r="L424" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M424" t="inlineStr">
@@ -27823,7 +27824,7 @@
       </c>
       <c r="L425" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M425" t="inlineStr">
@@ -27880,7 +27881,7 @@
       </c>
       <c r="L426" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M426" t="inlineStr">
@@ -27937,7 +27938,7 @@
       </c>
       <c r="L427" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M427" t="inlineStr">
@@ -28002,7 +28003,7 @@
       </c>
       <c r="L428" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M428" t="inlineStr">
@@ -28059,7 +28060,7 @@
       </c>
       <c r="L429" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M429" t="inlineStr">
@@ -28124,7 +28125,7 @@
       </c>
       <c r="L430" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M430" t="inlineStr">
@@ -28181,7 +28182,7 @@
       </c>
       <c r="L431" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>EMAIL FAILED: recipient-not-registered - IG fallback</t>
         </is>
       </c>
       <c r="M431" t="inlineStr">
@@ -28246,7 +28247,7 @@
       </c>
       <c r="L432" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M432" t="inlineStr">
@@ -28311,7 +28312,7 @@
       </c>
       <c r="L433" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M433" t="inlineStr">
@@ -28368,7 +28369,7 @@
       </c>
       <c r="L434" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M434" t="inlineStr">
@@ -28433,7 +28434,7 @@
       </c>
       <c r="L435" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M435" t="inlineStr">
@@ -28498,7 +28499,7 @@
       </c>
       <c r="L436" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M436" t="inlineStr">
@@ -28563,7 +28564,7 @@
       </c>
       <c r="L437" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M437" t="inlineStr">
@@ -28628,7 +28629,7 @@
       </c>
       <c r="L438" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M438" t="inlineStr">
@@ -28685,7 +28686,7 @@
       </c>
       <c r="L439" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M439" t="inlineStr">
@@ -28750,7 +28751,7 @@
       </c>
       <c r="L440" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M440" t="inlineStr">
@@ -28815,7 +28816,7 @@
       </c>
       <c r="L441" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M441" t="inlineStr">
@@ -28880,7 +28881,7 @@
       </c>
       <c r="L442" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M442" t="inlineStr">
@@ -28945,7 +28946,7 @@
       </c>
       <c r="L443" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M443" t="inlineStr">
@@ -29010,7 +29011,7 @@
       </c>
       <c r="L444" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M444" t="inlineStr">
@@ -29075,7 +29076,7 @@
       </c>
       <c r="L445" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M445" t="inlineStr">
@@ -29140,7 +29141,7 @@
       </c>
       <c r="L446" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M446" t="inlineStr">
@@ -29205,7 +29206,7 @@
       </c>
       <c r="L447" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M447" t="inlineStr">
@@ -29270,7 +29271,7 @@
       </c>
       <c r="L448" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M448" t="inlineStr">
@@ -29327,7 +29328,7 @@
       </c>
       <c r="L449" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M449" t="inlineStr">
@@ -29392,7 +29393,7 @@
       </c>
       <c r="L450" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M450" t="inlineStr">
@@ -29457,7 +29458,7 @@
       </c>
       <c r="L451" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M451" t="inlineStr">
@@ -29522,7 +29523,7 @@
       </c>
       <c r="L452" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M452" t="inlineStr">
@@ -29579,7 +29580,7 @@
       </c>
       <c r="L453" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M453" t="inlineStr">
@@ -29644,7 +29645,7 @@
       </c>
       <c r="L454" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M454" t="inlineStr">
@@ -29709,7 +29710,7 @@
       </c>
       <c r="L455" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M455" t="inlineStr">
@@ -29774,7 +29775,7 @@
       </c>
       <c r="L456" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M456" t="inlineStr">
@@ -29831,7 +29832,7 @@
       </c>
       <c r="L457" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M457" t="inlineStr">
@@ -29896,7 +29897,7 @@
       </c>
       <c r="L458" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M458" t="inlineStr">
@@ -29953,7 +29954,7 @@
       </c>
       <c r="L459" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M459" t="inlineStr">
@@ -30018,7 +30019,7 @@
       </c>
       <c r="L460" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M460" t="inlineStr">
@@ -30083,7 +30084,7 @@
       </c>
       <c r="L461" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M461" t="inlineStr">
@@ -30148,7 +30149,7 @@
       </c>
       <c r="L462" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M462" t="inlineStr">
@@ -30205,7 +30206,7 @@
       </c>
       <c r="L463" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>EMAIL FAILED: recipient-not-registered - IG fallback</t>
         </is>
       </c>
       <c r="M463" t="inlineStr">
@@ -30270,7 +30271,7 @@
       </c>
       <c r="L464" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M464" t="inlineStr">
@@ -30335,7 +30336,7 @@
       </c>
       <c r="L465" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M465" t="inlineStr">
@@ -30400,7 +30401,7 @@
       </c>
       <c r="L466" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M466" t="inlineStr">
@@ -30465,7 +30466,7 @@
       </c>
       <c r="L467" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M467" t="inlineStr">
@@ -30530,7 +30531,7 @@
       </c>
       <c r="L468" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M468" t="inlineStr">
@@ -30595,7 +30596,7 @@
       </c>
       <c r="L469" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M469" t="inlineStr">
@@ -30660,7 +30661,7 @@
       </c>
       <c r="L470" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M470" t="inlineStr">
@@ -30725,7 +30726,7 @@
       </c>
       <c r="L471" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M471" t="inlineStr">
@@ -30790,7 +30791,7 @@
       </c>
       <c r="L472" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M472" t="inlineStr">
@@ -30855,7 +30856,7 @@
       </c>
       <c r="L473" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>EMAIL FAILED: recipient-not-registered - IG fallback</t>
         </is>
       </c>
       <c r="M473" t="inlineStr">
@@ -30912,7 +30913,7 @@
       </c>
       <c r="L474" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M474" t="inlineStr">
@@ -30969,7 +30970,7 @@
       </c>
       <c r="L475" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M475" t="inlineStr">
@@ -31034,7 +31035,7 @@
       </c>
       <c r="L476" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M476" t="inlineStr">
@@ -31099,7 +31100,7 @@
       </c>
       <c r="L477" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M477" t="inlineStr">
@@ -31164,7 +31165,7 @@
       </c>
       <c r="L478" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M478" t="inlineStr">
@@ -31229,7 +31230,7 @@
       </c>
       <c r="L479" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M479" t="inlineStr">
@@ -31294,7 +31295,7 @@
       </c>
       <c r="L480" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M480" t="inlineStr">
@@ -31359,7 +31360,7 @@
       </c>
       <c r="L481" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M481" t="inlineStr">
@@ -31416,7 +31417,7 @@
       </c>
       <c r="L482" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M482" t="inlineStr">
@@ -31481,7 +31482,7 @@
       </c>
       <c r="L483" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M483" t="inlineStr">
@@ -31546,7 +31547,7 @@
       </c>
       <c r="L484" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M484" t="inlineStr">
@@ -31611,7 +31612,7 @@
       </c>
       <c r="L485" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M485" t="inlineStr">
@@ -31676,7 +31677,7 @@
       </c>
       <c r="L486" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M486" t="inlineStr">
@@ -31733,7 +31734,7 @@
       </c>
       <c r="L487" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M487" t="inlineStr">
@@ -31798,7 +31799,7 @@
       </c>
       <c r="L488" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M488" t="inlineStr">
@@ -31855,7 +31856,7 @@
       </c>
       <c r="L489" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M489" t="inlineStr">
@@ -31920,7 +31921,7 @@
       </c>
       <c r="L490" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M490" t="inlineStr">
@@ -31985,7 +31986,7 @@
       </c>
       <c r="L491" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M491" t="inlineStr">
@@ -32042,7 +32043,7 @@
       </c>
       <c r="L492" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M492" t="inlineStr">
@@ -32160,7 +32161,7 @@
       </c>
       <c r="L494" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M494" t="inlineStr">
@@ -32225,7 +32226,7 @@
       </c>
       <c r="L495" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M495" t="inlineStr">
@@ -32290,7 +32291,7 @@
       </c>
       <c r="L496" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M496" t="inlineStr">
@@ -32355,7 +32356,7 @@
       </c>
       <c r="L497" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M497" t="inlineStr">
@@ -32420,7 +32421,7 @@
       </c>
       <c r="L498" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M498" t="inlineStr">
@@ -32485,7 +32486,7 @@
       </c>
       <c r="L499" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M499" t="inlineStr">
@@ -32550,7 +32551,7 @@
       </c>
       <c r="L500" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M500" t="inlineStr">
@@ -32615,7 +32616,7 @@
       </c>
       <c r="L501" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M501" t="inlineStr">
@@ -32672,7 +32673,7 @@
       </c>
       <c r="L502" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M502" t="inlineStr">
@@ -32729,7 +32730,7 @@
       </c>
       <c r="L503" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M503" t="inlineStr">
@@ -32794,7 +32795,7 @@
       </c>
       <c r="L504" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M504" t="inlineStr">
@@ -32859,7 +32860,7 @@
       </c>
       <c r="L505" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M505" t="inlineStr">
@@ -32924,7 +32925,7 @@
       </c>
       <c r="L506" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M506" t="inlineStr">
@@ -32981,7 +32982,7 @@
       </c>
       <c r="L507" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M507" t="inlineStr">
@@ -33038,7 +33039,7 @@
       </c>
       <c r="L508" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M508" t="inlineStr">
@@ -33095,7 +33096,7 @@
       </c>
       <c r="L509" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M509" t="inlineStr">
@@ -33152,7 +33153,7 @@
       </c>
       <c r="L510" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>EMAIL FAILED: recipient-not-registered - IG fallback</t>
         </is>
       </c>
       <c r="M510" t="inlineStr">
@@ -33217,7 +33218,7 @@
       </c>
       <c r="L511" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M511" t="inlineStr">
@@ -33282,7 +33283,7 @@
       </c>
       <c r="L512" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M512" t="inlineStr">
@@ -33347,7 +33348,7 @@
       </c>
       <c r="L513" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M513" t="inlineStr">
@@ -33412,7 +33413,7 @@
       </c>
       <c r="L514" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M514" t="inlineStr">
@@ -33477,7 +33478,7 @@
       </c>
       <c r="L515" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M515" t="inlineStr">
@@ -33542,7 +33543,7 @@
       </c>
       <c r="L516" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M516" t="inlineStr">
@@ -33607,7 +33608,7 @@
       </c>
       <c r="L517" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M517" t="inlineStr">
@@ -33672,7 +33673,7 @@
       </c>
       <c r="L518" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M518" t="inlineStr">
@@ -33737,7 +33738,7 @@
       </c>
       <c r="L519" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M519" t="inlineStr">
@@ -33794,7 +33795,7 @@
       </c>
       <c r="L520" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M520" t="inlineStr">
@@ -33859,7 +33860,7 @@
       </c>
       <c r="L521" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M521" t="inlineStr">
@@ -33924,7 +33925,7 @@
       </c>
       <c r="L522" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M522" t="inlineStr">
@@ -34050,7 +34051,7 @@
       </c>
       <c r="L524" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M524" t="inlineStr">
@@ -34115,7 +34116,7 @@
       </c>
       <c r="L525" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M525" t="inlineStr">
@@ -34180,7 +34181,7 @@
       </c>
       <c r="L526" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M526" t="inlineStr">
@@ -34245,7 +34246,7 @@
       </c>
       <c r="L527" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M527" t="inlineStr">
@@ -34310,7 +34311,7 @@
       </c>
       <c r="L528" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M528" t="inlineStr">
@@ -34367,7 +34368,7 @@
       </c>
       <c r="L529" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M529" t="inlineStr">
@@ -34436,7 +34437,7 @@
       </c>
       <c r="L530" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M530" t="inlineStr">
@@ -34501,7 +34502,7 @@
       </c>
       <c r="L531" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M531" t="inlineStr">
@@ -34566,7 +34567,7 @@
       </c>
       <c r="L532" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M532" t="inlineStr">
@@ -34631,7 +34632,7 @@
       </c>
       <c r="L533" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M533" t="inlineStr">
@@ -34696,7 +34697,7 @@
       </c>
       <c r="L534" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M534" t="inlineStr">
@@ -34753,7 +34754,7 @@
       </c>
       <c r="L535" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M535" t="inlineStr">
@@ -34818,7 +34819,7 @@
       </c>
       <c r="L536" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M536" t="inlineStr">
@@ -34883,7 +34884,7 @@
       </c>
       <c r="L537" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M537" t="inlineStr">
@@ -34948,7 +34949,7 @@
       </c>
       <c r="L538" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>EMAIL FAILED: recipient-not-registered - IG fallback</t>
         </is>
       </c>
       <c r="M538" t="inlineStr">
@@ -35005,7 +35006,7 @@
       </c>
       <c r="L539" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M539" t="inlineStr">
@@ -35070,7 +35071,7 @@
       </c>
       <c r="L540" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M540" t="inlineStr">
@@ -35135,7 +35136,7 @@
       </c>
       <c r="L541" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M541" t="inlineStr">
@@ -35200,7 +35201,7 @@
       </c>
       <c r="L542" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M542" t="inlineStr">
@@ -35265,7 +35266,7 @@
       </c>
       <c r="L543" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>EMAIL FAILED: recipient-not-registered - IG fallback</t>
         </is>
       </c>
       <c r="M543" t="inlineStr">
@@ -35322,7 +35323,7 @@
       </c>
       <c r="L544" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M544" t="inlineStr">
@@ -35387,7 +35388,7 @@
       </c>
       <c r="L545" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M545" t="inlineStr">
@@ -35444,7 +35445,7 @@
       </c>
       <c r="L546" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M546" t="inlineStr">
@@ -35509,7 +35510,7 @@
       </c>
       <c r="L547" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M547" t="inlineStr">
@@ -35574,7 +35575,7 @@
       </c>
       <c r="L548" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M548" t="inlineStr">
@@ -35631,7 +35632,7 @@
       </c>
       <c r="L549" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M549" t="inlineStr">
@@ -35696,7 +35697,7 @@
       </c>
       <c r="L550" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M550" t="inlineStr">
@@ -35761,7 +35762,7 @@
       </c>
       <c r="L551" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M551" t="inlineStr">
@@ -35826,7 +35827,7 @@
       </c>
       <c r="L552" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M552" t="inlineStr">
@@ -35891,7 +35892,7 @@
       </c>
       <c r="L553" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>EMAIL FAILED: recipient-not-registered - IG fallback</t>
         </is>
       </c>
       <c r="M553" t="inlineStr">
@@ -35956,7 +35957,7 @@
       </c>
       <c r="L554" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M554" t="inlineStr">
@@ -36021,7 +36022,7 @@
       </c>
       <c r="L555" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M555" t="inlineStr">
@@ -36086,7 +36087,7 @@
       </c>
       <c r="L556" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M556" t="inlineStr">
@@ -36151,7 +36152,7 @@
       </c>
       <c r="L557" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M557" t="inlineStr">
@@ -36216,7 +36217,7 @@
       </c>
       <c r="L558" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M558" t="inlineStr">
@@ -36281,7 +36282,7 @@
       </c>
       <c r="L559" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M559" t="inlineStr">
@@ -36346,7 +36347,7 @@
       </c>
       <c r="L560" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M560" t="inlineStr">
@@ -36411,7 +36412,7 @@
       </c>
       <c r="L561" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M561" t="inlineStr">
@@ -36476,7 +36477,7 @@
       </c>
       <c r="L562" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M562" t="inlineStr">
@@ -36533,7 +36534,7 @@
       </c>
       <c r="L563" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M563" t="inlineStr">
@@ -36602,7 +36603,7 @@
       </c>
       <c r="L564" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M564" t="inlineStr">
@@ -36667,7 +36668,7 @@
       </c>
       <c r="L565" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M565" t="inlineStr">
@@ -36732,7 +36733,7 @@
       </c>
       <c r="L566" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M566" t="inlineStr">
@@ -36797,7 +36798,7 @@
       </c>
       <c r="L567" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M567" t="inlineStr">
@@ -36862,7 +36863,7 @@
       </c>
       <c r="L568" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M568" t="inlineStr">
@@ -36927,7 +36928,7 @@
       </c>
       <c r="L569" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M569" t="inlineStr">
@@ -36992,7 +36993,7 @@
       </c>
       <c r="L570" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>EMAIL FAILED: recipient-not-registered - IG fallback</t>
         </is>
       </c>
       <c r="M570" t="inlineStr">
@@ -37057,7 +37058,7 @@
       </c>
       <c r="L571" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M571" t="inlineStr">
@@ -37122,7 +37123,7 @@
       </c>
       <c r="L572" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M572" t="inlineStr">
@@ -37179,7 +37180,7 @@
       </c>
       <c r="L573" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M573" t="inlineStr">
@@ -37244,7 +37245,7 @@
       </c>
       <c r="L574" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M574" t="inlineStr">
@@ -37301,7 +37302,7 @@
       </c>
       <c r="L575" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M575" t="inlineStr">
@@ -37419,7 +37420,7 @@
       </c>
       <c r="L577" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M577" t="inlineStr">
@@ -37484,7 +37485,7 @@
       </c>
       <c r="L578" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M578" t="inlineStr">
@@ -37541,7 +37542,7 @@
       </c>
       <c r="L579" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M579" t="inlineStr">
@@ -37606,7 +37607,7 @@
       </c>
       <c r="L580" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>COMPLETE: email sent (Day 5 USA wave)</t>
         </is>
       </c>
       <c r="M580" t="inlineStr">
@@ -37671,7 +37672,7 @@
       </c>
       <c r="L581" t="inlineStr">
         <is>
-          <t>RESEARCHED: USA lead, outreach pending</t>
+          <t>EMAIL FAILED: recipient-not-registered - IG fallback</t>
         </is>
       </c>
       <c r="M581" t="inlineStr">
@@ -37687,6 +37688,170 @@
       <c r="O581" t="inlineStr">
         <is>
           <t>Day 5 USA batch</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>HSN Warrior Apparels - Day 5 USA Campaign</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-17 23:36 UTC</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n"/>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>USA leads found</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>208</v>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>target 200 - EXCEEDED</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>USA emails sent</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>186</v>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>186 OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Dead emails verified</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>14 bounced - removed</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>USA IG follow+DM</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>50 in current wave</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>EU WA sends today</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>10/10 sent</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Total leads</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>580</v>
+      </c>
+      <c r="C10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>HOT LEADS</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Alvaro Campeao - sample deal closing</t>
         </is>
       </c>
     </row>

--- a/HWA_Lead_Tracker.xlsx
+++ b/HWA_Lead_Tracker.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Leads" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Day 5 Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leads" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 5 Final" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="L391" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent (Day 5 USA wave)</t>
+          <t>COMPLETE: email sent (Day 5 USA wave) | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M391" t="inlineStr">
@@ -25719,7 +25719,7 @@
       </c>
       <c r="L392" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent (Day 5 USA wave)</t>
+          <t>COMPLETE: email sent (Day 5 USA wave) | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M392" t="inlineStr">
@@ -25784,7 +25784,7 @@
       </c>
       <c r="L393" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent (Day 5 USA wave)</t>
+          <t>COMPLETE: email sent (Day 5 USA wave) | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M393" t="inlineStr">
@@ -25849,7 +25849,7 @@
       </c>
       <c r="L394" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent (Day 5 USA wave)</t>
+          <t>COMPLETE: email sent (Day 5 USA wave) | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M394" t="inlineStr">
@@ -25914,7 +25914,7 @@
       </c>
       <c r="L395" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent (Day 5 USA wave)</t>
+          <t>COMPLETE: email sent (Day 5 USA wave) | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M395" t="inlineStr">
@@ -25979,7 +25979,7 @@
       </c>
       <c r="L396" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent (Day 5 USA wave)</t>
+          <t>COMPLETE: email sent (Day 5 USA wave) | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M396" t="inlineStr">
@@ -26044,7 +26044,7 @@
       </c>
       <c r="L397" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent (Day 5 USA wave)</t>
+          <t>COMPLETE: email sent (Day 5 USA wave) | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M397" t="inlineStr">
@@ -26109,7 +26109,7 @@
       </c>
       <c r="L398" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent (Day 5 USA wave)</t>
+          <t>COMPLETE: email sent (Day 5 USA wave) | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M398" t="inlineStr">
@@ -26174,7 +26174,7 @@
       </c>
       <c r="L399" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent (Day 5 USA wave)</t>
+          <t>COMPLETE: email sent (Day 5 USA wave) | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M399" t="inlineStr">
@@ -26239,7 +26239,7 @@
       </c>
       <c r="L400" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent (Day 5 USA wave)</t>
+          <t>COMPLETE: email sent (Day 5 USA wave) | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M400" t="inlineStr">
@@ -26304,7 +26304,7 @@
       </c>
       <c r="L401" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent (Day 5 USA wave)</t>
+          <t>COMPLETE: email sent (Day 5 USA wave) | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M401" t="inlineStr">
@@ -26491,7 +26491,7 @@
       </c>
       <c r="L404" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent (Day 5 USA wave)</t>
+          <t>COMPLETE: email sent (Day 5 USA wave) | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M404" t="inlineStr">
@@ -26613,7 +26613,7 @@
       </c>
       <c r="L406" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent (Day 5 USA wave)</t>
+          <t>COMPLETE: email sent (Day 5 USA wave) | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M406" t="inlineStr">
@@ -26678,7 +26678,7 @@
       </c>
       <c r="L407" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent (Day 5 USA wave)</t>
+          <t>COMPLETE: email sent (Day 5 USA wave) | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M407" t="inlineStr">
@@ -26800,7 +26800,7 @@
       </c>
       <c r="L409" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent (Day 5 USA wave)</t>
+          <t>COMPLETE: email sent (Day 5 USA wave) | IG not found</t>
         </is>
       </c>
       <c r="M409" t="inlineStr">
@@ -26922,7 +26922,7 @@
       </c>
       <c r="L411" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent (Day 5 USA wave)</t>
+          <t>COMPLETE: email sent (Day 5 USA wave) | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M411" t="inlineStr">
@@ -26987,7 +26987,7 @@
       </c>
       <c r="L412" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent (Day 5 USA wave)</t>
+          <t>COMPLETE: email sent (Day 5 USA wave) | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M412" t="inlineStr">
@@ -27052,7 +27052,7 @@
       </c>
       <c r="L413" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent (Day 5 USA wave)</t>
+          <t>COMPLETE: email sent (Day 5 USA wave) | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M413" t="inlineStr">
@@ -27174,7 +27174,7 @@
       </c>
       <c r="L415" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent (Day 5 USA wave)</t>
+          <t>COMPLETE: email sent (Day 5 USA wave) | IG follow=no-btn dm=sent</t>
         </is>
       </c>
       <c r="M415" t="inlineStr">
@@ -27239,7 +27239,7 @@
       </c>
       <c r="L416" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent (Day 5 USA wave)</t>
+          <t>COMPLETE: email sent (Day 5 USA wave) | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M416" t="inlineStr">
@@ -27369,7 +27369,7 @@
       </c>
       <c r="L418" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent (Day 5 USA wave)</t>
+          <t>COMPLETE: email sent (Day 5 USA wave) | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M418" t="inlineStr">
@@ -27434,7 +27434,7 @@
       </c>
       <c r="L419" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent (Day 5 USA wave)</t>
+          <t>COMPLETE: email sent (Day 5 USA wave) | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M419" t="inlineStr">
@@ -27499,7 +27499,7 @@
       </c>
       <c r="L420" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent (Day 5 USA wave)</t>
+          <t>COMPLETE: email sent (Day 5 USA wave) | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M420" t="inlineStr">
@@ -27564,7 +27564,7 @@
       </c>
       <c r="L421" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent (Day 5 USA wave)</t>
+          <t>COMPLETE: email sent (Day 5 USA wave) | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M421" t="inlineStr">
@@ -27629,7 +27629,7 @@
       </c>
       <c r="L422" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent (Day 5 USA wave)</t>
+          <t>COMPLETE: email sent (Day 5 USA wave) | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M422" t="inlineStr">
@@ -27694,7 +27694,7 @@
       </c>
       <c r="L423" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent (Day 5 USA wave)</t>
+          <t>COMPLETE: email sent (Day 5 USA wave) | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M423" t="inlineStr">
@@ -27759,7 +27759,7 @@
       </c>
       <c r="L424" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent (Day 5 USA wave)</t>
+          <t>COMPLETE: email sent (Day 5 USA wave) | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M424" t="inlineStr">
@@ -27824,7 +27824,7 @@
       </c>
       <c r="L425" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent (Day 5 USA wave)</t>
+          <t>COMPLETE: email sent (Day 5 USA wave) | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M425" t="inlineStr">
@@ -28003,7 +28003,7 @@
       </c>
       <c r="L428" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent (Day 5 USA wave)</t>
+          <t>COMPLETE: email sent (Day 5 USA wave) | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M428" t="inlineStr">
@@ -28125,7 +28125,7 @@
       </c>
       <c r="L430" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent (Day 5 USA wave)</t>
+          <t>COMPLETE: email sent (Day 5 USA wave) | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M430" t="inlineStr">
@@ -28247,7 +28247,7 @@
       </c>
       <c r="L432" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent (Day 5 USA wave)</t>
+          <t>COMPLETE: email sent (Day 5 USA wave) | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M432" t="inlineStr">
@@ -28312,7 +28312,7 @@
       </c>
       <c r="L433" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent (Day 5 USA wave)</t>
+          <t>COMPLETE: email sent (Day 5 USA wave) | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M433" t="inlineStr">
@@ -28434,7 +28434,7 @@
       </c>
       <c r="L435" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent (Day 5 USA wave)</t>
+          <t>COMPLETE: email sent (Day 5 USA wave) | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M435" t="inlineStr">
@@ -28499,7 +28499,7 @@
       </c>
       <c r="L436" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent (Day 5 USA wave)</t>
+          <t>COMPLETE: email sent (Day 5 USA wave) | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M436" t="inlineStr">
@@ -28564,7 +28564,7 @@
       </c>
       <c r="L437" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent (Day 5 USA wave)</t>
+          <t>COMPLETE: email sent (Day 5 USA wave) | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M437" t="inlineStr">
@@ -28629,7 +28629,7 @@
       </c>
       <c r="L438" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent (Day 5 USA wave)</t>
+          <t>COMPLETE: email sent (Day 5 USA wave) | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M438" t="inlineStr">
@@ -28751,7 +28751,7 @@
       </c>
       <c r="L440" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent (Day 5 USA wave)</t>
+          <t>COMPLETE: email sent (Day 5 USA wave) | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M440" t="inlineStr">
@@ -28816,7 +28816,7 @@
       </c>
       <c r="L441" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent (Day 5 USA wave)</t>
+          <t>COMPLETE: email sent (Day 5 USA wave) | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M441" t="inlineStr">
@@ -28881,7 +28881,7 @@
       </c>
       <c r="L442" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent (Day 5 USA wave)</t>
+          <t>COMPLETE: email sent (Day 5 USA wave) | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M442" t="inlineStr">
@@ -28946,7 +28946,7 @@
       </c>
       <c r="L443" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent (Day 5 USA wave)</t>
+          <t>COMPLETE: email sent (Day 5 USA wave) | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M443" t="inlineStr">
@@ -29011,7 +29011,7 @@
       </c>
       <c r="L444" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent (Day 5 USA wave)</t>
+          <t>COMPLETE: email sent (Day 5 USA wave) | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M444" t="inlineStr">
@@ -29076,7 +29076,7 @@
       </c>
       <c r="L445" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent (Day 5 USA wave)</t>
+          <t>COMPLETE: email sent (Day 5 USA wave) | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M445" t="inlineStr">
@@ -29141,7 +29141,7 @@
       </c>
       <c r="L446" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent (Day 5 USA wave)</t>
+          <t>COMPLETE: email sent (Day 5 USA wave) | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M446" t="inlineStr">
@@ -37702,18 +37702,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>HSN Warrior Apparels - Day 5 USA Campaign</t>
+          <t>HSN Warrior Apparels — Day 5 COMPLETE Report</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -37727,7 +37727,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-17 23:36 UTC</t>
+          <t>2026-10-18 00:07 UTC</t>
         </is>
       </c>
       <c r="C2" s="3" t="n"/>
@@ -37740,7 +37740,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Metric</t>
+          <t>Channel</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -37750,7 +37750,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Details</t>
         </is>
       </c>
     </row>
@@ -37765,7 +37765,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>target 200 - EXCEEDED</t>
+          <t>target 200 — EXCEEDED</t>
         </is>
       </c>
     </row>
@@ -37780,14 +37780,14 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>186 OK</t>
+          <t>wave completed</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Dead emails verified</t>
+          <t>Dead emails removed</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
@@ -37795,7 +37795,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>14 bounced - removed</t>
+          <t>verified bounces</t>
         </is>
       </c>
     </row>
@@ -37806,18 +37806,18 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>50 in current wave</t>
+          <t>48 sent, 2 not found</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>EU WA sends today</t>
+          <t>EU WA sends (best 10)</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
@@ -37825,7 +37825,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>10/10 sent</t>
+          <t>all Spain/PT/DE mobiles</t>
         </is>
       </c>
     </row>
@@ -37838,20 +37838,31 @@
       <c r="B10" s="3" t="n">
         <v>580</v>
       </c>
-      <c r="C10" s="3" t="inlineStr"/>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>580+ pipeline</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>HOT LEADS</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Alvaro Campeao - sample deal closing</t>
+      <c r="A11" s="3" t="n"/>
+      <c r="B11" s="3" t="n"/>
+      <c r="C11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>HOT LEAD</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Alvaro Campeao (UAE)</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Sample deal: EUR 77.40, awaiting logo + payment confirm</t>
         </is>
       </c>
     </row>

--- a/HWA_Lead_Tracker.xlsx
+++ b/HWA_Lead_Tracker.xlsx
@@ -1,16 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leads" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 5 Final" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Leads" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$O$581</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -18,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,13 +31,14 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
+      <sz val="13"/>
     </font>
-    <font/>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -44,7 +47,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
+        <fgColor rgb="001F4E4F"/>
+        <bgColor rgb="001F4E4F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE8A3"/>
+        <bgColor rgb="00FFE8A3"/>
       </patternFill>
     </fill>
   </fills>
@@ -62,9 +72,11 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -434,20 +446,20 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="32" customWidth="1" min="10" max="10"/>
-    <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="50" customWidth="1" min="12" max="12"/>
-    <col width="55" customWidth="1" min="13" max="13"/>
-    <col width="45" customWidth="1" min="14" max="14"/>
-    <col width="50" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="46" customWidth="1" min="12" max="12"/>
+    <col width="40" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="36" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9011,77 +9023,77 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>L132</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
         <is>
           <t>Alvaro Campeao</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr">
+      <c r="C133" s="2" t="inlineStr">
         <is>
           <t>Boxing/Muay Thai</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr">
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>@alvarotdcampeao</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>https://www.instagram.com/alvarotdcampeao/</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>351916033601</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr">
+      <c r="I133" s="2" t="inlineStr">
         <is>
           <t>mobile</t>
         </is>
       </c>
-      <c r="J133" t="inlineStr">
+      <c r="J133" s="2" t="inlineStr">
         <is>
           <t>pt.alvarocampeao@gmail.com</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr">
+      <c r="K133" s="2" t="inlineStr">
         <is>
           <t>alvarocampeao.com</t>
         </is>
       </c>
-      <c r="L133" t="inlineStr">
+      <c r="L133" s="2" t="inlineStr">
         <is>
           <t>HOT LEAD (payment stage): asked Dirham or Euro. Answered: Euro pricing, he pays Dirham via Western Union, we receive local currency. Awaiting his confirmation + logo. Sample EUR 77.40.</t>
         </is>
       </c>
-      <c r="M133" t="inlineStr">
+      <c r="M133" s="2" t="inlineStr">
         <is>
           <t>Boxing/Muay Thai coach Portugal. GOLD: WA + email + IG.</t>
         </is>
       </c>
-      <c r="N133" t="inlineStr">
+      <c r="N133" s="2" t="inlineStr">
         <is>
           <t>Gloves, Thai pads</t>
         </is>
       </c>
-      <c r="O133" t="inlineStr">
+      <c r="O133" s="2" t="inlineStr">
         <is>
           <t>HOT LEAD - Alvaro Campeao, UAE +971504894282. Products: MMA shorts, MMA tights, JJ gi. Next step: quantities -&gt; quote + mockup. Sign-off: company name only.</t>
         </is>
@@ -24569,7 +24581,7 @@
       </c>
       <c r="L374" t="inlineStr">
         <is>
-          <t>EMAIL FAILED: no-gmail-tab - IG fallback | IG follow=ok dm=sent</t>
+          <t>COMPLETE: email sent (Day 5 USA wave retry) | | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M374" t="inlineStr">
@@ -24634,7 +24646,7 @@
       </c>
       <c r="L375" t="inlineStr">
         <is>
-          <t>EMAIL FAILED: no-gmail-tab - IG fallback | IG follow=ok dm=sent</t>
+          <t>COMPLETE: email sent (Day 5 USA wave retry) | | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M375" t="inlineStr">
@@ -24699,7 +24711,7 @@
       </c>
       <c r="L376" t="inlineStr">
         <is>
-          <t>EMAIL FAILED: no-gmail-tab - IG fallback | IG follow=ok dm=sent</t>
+          <t>COMPLETE: email sent (Day 5 USA wave retry) | | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M376" t="inlineStr">
@@ -24764,7 +24776,7 @@
       </c>
       <c r="L377" t="inlineStr">
         <is>
-          <t>EMAIL FAILED: no-gmail-tab - IG fallback | IG follow=ok dm=sent</t>
+          <t>COMPLETE: email sent (Day 5 USA wave retry) | | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M377" t="inlineStr">
@@ -24890,7 +24902,7 @@
       </c>
       <c r="L379" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent (Day 5 USA wave) | IG error: [Errno 32] Broken pipe</t>
+          <t>COMPLETE: email sent (Day 5 USA wave) | IG error: [Errno 32] Broken pipe | IG follow=no-btn dm=sent</t>
         </is>
       </c>
       <c r="M379" t="inlineStr">
@@ -25142,7 +25154,7 @@
       </c>
       <c r="L383" t="inlineStr">
         <is>
-          <t>EMAIL FAILED: recipient-not-registered - IG fallback</t>
+          <t>EMAIL FAILED: recipient-not-registered - IG fallback | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M383" t="inlineStr">
@@ -25264,7 +25276,7 @@
       </c>
       <c r="L385" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent (Day 5 USA wave) | IG not found</t>
+          <t>COMPLETE: email sent (Day 5 USA wave) | IG not found | IG profile not found</t>
         </is>
       </c>
       <c r="M385" t="inlineStr">
@@ -25524,7 +25536,7 @@
       </c>
       <c r="L389" t="inlineStr">
         <is>
-          <t>EMAIL FAILED: recipient-not-registered - IG fallback</t>
+          <t>EMAIL FAILED: recipient-not-registered - IG fallback | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M389" t="inlineStr">
@@ -26426,7 +26438,7 @@
       </c>
       <c r="L403" t="inlineStr">
         <is>
-          <t>EMAIL FAILED: recipient-not-registered - IG fallback</t>
+          <t>EMAIL FAILED: recipient-not-registered - IG fallback | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M403" t="inlineStr">
@@ -26800,7 +26812,7 @@
       </c>
       <c r="L409" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent (Day 5 USA wave) | IG not found</t>
+          <t>COMPLETE: email sent (Day 5 USA wave) | IG not found | IG profile not found</t>
         </is>
       </c>
       <c r="M409" t="inlineStr">
@@ -27304,7 +27316,7 @@
       </c>
       <c r="L417" t="inlineStr">
         <is>
-          <t>EMAIL FAILED: recipient-not-registered - IG fallback</t>
+          <t>EMAIL FAILED: recipient-not-registered - IG fallback | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M417" t="inlineStr">
@@ -29206,7 +29218,7 @@
       </c>
       <c r="L447" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent (Day 5 USA wave)</t>
+          <t>COMPLETE: email sent (Day 5 USA wave) | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M447" t="inlineStr">
@@ -29271,7 +29283,7 @@
       </c>
       <c r="L448" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent (Day 5 USA wave)</t>
+          <t>COMPLETE: email sent (Day 5 USA wave) | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M448" t="inlineStr">
@@ -29393,7 +29405,7 @@
       </c>
       <c r="L450" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent (Day 5 USA wave)</t>
+          <t>COMPLETE: email sent (Day 5 USA wave) | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M450" t="inlineStr">
@@ -29458,7 +29470,7 @@
       </c>
       <c r="L451" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent (Day 5 USA wave)</t>
+          <t>COMPLETE: email sent (Day 5 USA wave) | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M451" t="inlineStr">
@@ -29523,7 +29535,7 @@
       </c>
       <c r="L452" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent (Day 5 USA wave)</t>
+          <t>COMPLETE: email sent (Day 5 USA wave) | IG profile not found</t>
         </is>
       </c>
       <c r="M452" t="inlineStr">
@@ -29645,7 +29657,7 @@
       </c>
       <c r="L454" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent (Day 5 USA wave)</t>
+          <t>COMPLETE: email sent (Day 5 USA wave) | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M454" t="inlineStr">
@@ -29710,7 +29722,7 @@
       </c>
       <c r="L455" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent (Day 5 USA wave)</t>
+          <t>COMPLETE: email sent (Day 5 USA wave) | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M455" t="inlineStr">
@@ -29775,7 +29787,7 @@
       </c>
       <c r="L456" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent (Day 5 USA wave)</t>
+          <t>COMPLETE: email sent (Day 5 USA wave) | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M456" t="inlineStr">
@@ -29897,7 +29909,7 @@
       </c>
       <c r="L458" t="inlineStr">
         <is>
-          <t>COMPLETE: email sent (Day 5 USA wave)</t>
+          <t>COMPLETE: email sent (Day 5 USA wave) | IG follow=ok dm=sent</t>
         </is>
       </c>
       <c r="M458" t="inlineStr">
@@ -37692,6 +37704,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:O581"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -37702,168 +37715,76 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>HSN Warrior Apparels — Day 5 COMPLETE Report</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Updated</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-18 00:07 UTC</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="n"/>
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>HSN Warrior Apparels — Lead Tracker Summary</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n"/>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Generated (UTC):</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-10-18 01:09</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Channel</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Details</t>
-        </is>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Total leads:</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>580</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>USA leads found</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>USA batch:</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>208</v>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>target 200 — EXCEEDED</t>
-        </is>
-      </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>USA emails sent</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>186</v>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>wave completed</t>
-        </is>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>USA emails sent:</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>190</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Dead emails removed</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>verified bounces</t>
-        </is>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>USA IG follow/DM done:</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>66</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>USA IG follow+DM</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>53</v>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>48 sent, 2 not found</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>EU WA sends (best 10)</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>all Spain/PT/DE mobiles</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Total leads</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>580</v>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>580+ pipeline</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="n"/>
-      <c r="B11" s="3" t="n"/>
-      <c r="C11" s="3" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>HOT LEAD</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Alvaro Campeao (UAE)</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Sample deal: EUR 77.40, awaiting logo + payment confirm</t>
-        </is>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>HOT leads:</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/HWA_Lead_Tracker.xlsx
+++ b/HWA_Lead_Tracker.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$O$680</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$O$780</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O680"/>
+  <dimension ref="A1:O780"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -43451,8 +43451,6132 @@
         </is>
       </c>
     </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>L693</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>Boxe Le Torri ASD</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr"/>
+      <c r="E681" t="inlineStr"/>
+      <c r="F681" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="G681" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="H681" t="inlineStr"/>
+      <c r="I681" t="inlineStr"/>
+      <c r="J681" t="inlineStr">
+        <is>
+          <t>info@boxeletorri.it</t>
+        </is>
+      </c>
+      <c r="K681" t="inlineStr">
+        <is>
+          <t>aicsbologna.it</t>
+        </is>
+      </c>
+      <c r="L681" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M681" t="inlineStr">
+        <is>
+          <t>Found via search: palestra boxe Bologna contatti email</t>
+        </is>
+      </c>
+      <c r="N681" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O681" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>L694</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>Bolognina Boxe</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr"/>
+      <c r="E682" t="inlineStr"/>
+      <c r="F682" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="G682" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="H682" t="inlineStr"/>
+      <c r="I682" t="inlineStr"/>
+      <c r="J682" t="inlineStr">
+        <is>
+          <t>info@aksado.com</t>
+        </is>
+      </c>
+      <c r="K682" t="inlineStr">
+        <is>
+          <t>komania.it</t>
+        </is>
+      </c>
+      <c r="L682" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M682" t="inlineStr">
+        <is>
+          <t>Found via search: palestra boxe Bologna contatti email</t>
+        </is>
+      </c>
+      <c r="N682" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O682" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>L695</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>Boxing Club Bologna</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr"/>
+      <c r="E683" t="inlineStr"/>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="G683" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="H683" t="inlineStr"/>
+      <c r="I683" t="inlineStr"/>
+      <c r="J683" t="inlineStr">
+        <is>
+          <t>alessandro77bar@libero.it</t>
+        </is>
+      </c>
+      <c r="K683" t="inlineStr">
+        <is>
+          <t>boxingclubbologna.it</t>
+        </is>
+      </c>
+      <c r="L683" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M683" t="inlineStr">
+        <is>
+          <t>Found via search: palestra boxe Bologna contatti email</t>
+        </is>
+      </c>
+      <c r="N683" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O683" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>L696</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>Brooklyn Fitboxing</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr"/>
+      <c r="E684" t="inlineStr"/>
+      <c r="F684" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="G684" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="H684" t="inlineStr"/>
+      <c r="I684" t="inlineStr"/>
+      <c r="J684" t="inlineStr">
+        <is>
+          <t>viamazzini@brooklynfitboxing.com</t>
+        </is>
+      </c>
+      <c r="K684" t="inlineStr">
+        <is>
+          <t>brooklynfitboxing.com</t>
+        </is>
+      </c>
+      <c r="L684" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M684" t="inlineStr">
+        <is>
+          <t>Found via search: palestra boxe Bologna contatti email</t>
+        </is>
+      </c>
+      <c r="N684" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O684" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>L697</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>Siam Boxing</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr"/>
+      <c r="E685" t="inlineStr"/>
+      <c r="F685" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="G685" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="H685" t="inlineStr"/>
+      <c r="I685" t="inlineStr"/>
+      <c r="J685" t="inlineStr">
+        <is>
+          <t>info@siam-boxing.com</t>
+        </is>
+      </c>
+      <c r="K685" t="inlineStr">
+        <is>
+          <t>siam-boxing.com</t>
+        </is>
+      </c>
+      <c r="L685" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M685" t="inlineStr">
+        <is>
+          <t>Found via search: palestra boxe Bologna contatti email</t>
+        </is>
+      </c>
+      <c r="N685" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O685" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>L698</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>Unknown Gym</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr"/>
+      <c r="E686" t="inlineStr"/>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>Firenze</t>
+        </is>
+      </c>
+      <c r="G686" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="H686" t="inlineStr"/>
+      <c r="I686" t="inlineStr"/>
+      <c r="J686" t="inlineStr">
+        <is>
+          <t>info@kodokan01.it</t>
+        </is>
+      </c>
+      <c r="K686" t="inlineStr">
+        <is>
+          <t>kodokan01.it</t>
+        </is>
+      </c>
+      <c r="L686" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M686" t="inlineStr">
+        <is>
+          <t>Found via search: muay thai Firenze palestra email</t>
+        </is>
+      </c>
+      <c r="N686" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O686" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>L699</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>AMTF Amateur Muay Thai Firenze</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr"/>
+      <c r="E687" t="inlineStr"/>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>Firenze</t>
+        </is>
+      </c>
+      <c r="G687" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="H687" t="inlineStr"/>
+      <c r="I687" t="inlineStr"/>
+      <c r="J687" t="inlineStr">
+        <is>
+          <t>info@muaythaifirenze.com</t>
+        </is>
+      </c>
+      <c r="K687" t="inlineStr">
+        <is>
+          <t>100ma.it</t>
+        </is>
+      </c>
+      <c r="L687" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M687" t="inlineStr">
+        <is>
+          <t>Found via search: muay thai Firenze palestra email</t>
+        </is>
+      </c>
+      <c r="N687" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O687" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>L700</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>Fight Club Palestra Muay Thai Firenze</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr"/>
+      <c r="E688" t="inlineStr"/>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>Firenze</t>
+        </is>
+      </c>
+      <c r="G688" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="H688" t="inlineStr"/>
+      <c r="I688" t="inlineStr"/>
+      <c r="J688" t="inlineStr">
+        <is>
+          <t>fightclubxboxing@pec.it</t>
+        </is>
+      </c>
+      <c r="K688" t="inlineStr">
+        <is>
+          <t>fightclubworld.com</t>
+        </is>
+      </c>
+      <c r="L688" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M688" t="inlineStr">
+        <is>
+          <t>Found via search: muay thai Firenze palestra email</t>
+        </is>
+      </c>
+      <c r="N688" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O688" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>L701</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>Muay Thai</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr"/>
+      <c r="E689" t="inlineStr"/>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>Firenze</t>
+        </is>
+      </c>
+      <c r="G689" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="H689" t="inlineStr"/>
+      <c r="I689" t="inlineStr"/>
+      <c r="J689" t="inlineStr">
+        <is>
+          <t>connect@haraclub.com</t>
+        </is>
+      </c>
+      <c r="K689" t="inlineStr">
+        <is>
+          <t>haraclub.com</t>
+        </is>
+      </c>
+      <c r="L689" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M689" t="inlineStr">
+        <is>
+          <t>Found via search: muay thai Firenze palestra email</t>
+        </is>
+      </c>
+      <c r="N689" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O689" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>L702</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>Unknown Gym</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr"/>
+      <c r="E690" t="inlineStr"/>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>Genova</t>
+        </is>
+      </c>
+      <c r="G690" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="H690" t="inlineStr"/>
+      <c r="I690" t="inlineStr"/>
+      <c r="J690" t="inlineStr">
+        <is>
+          <t>esempio@ilmiosito.com</t>
+        </is>
+      </c>
+      <c r="K690" t="inlineStr">
+        <is>
+          <t>ballatoremma.com</t>
+        </is>
+      </c>
+      <c r="L690" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M690" t="inlineStr">
+        <is>
+          <t>Found via search: MMA Genova palestra contatti email</t>
+        </is>
+      </c>
+      <c r="N690" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O690" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>L703</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>Palestra Genova</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr"/>
+      <c r="E691" t="inlineStr"/>
+      <c r="F691" t="inlineStr">
+        <is>
+          <t>Genova</t>
+        </is>
+      </c>
+      <c r="G691" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="H691" t="inlineStr"/>
+      <c r="I691" t="inlineStr"/>
+      <c r="J691" t="inlineStr">
+        <is>
+          <t>info@teammomogenova.it</t>
+        </is>
+      </c>
+      <c r="K691" t="inlineStr">
+        <is>
+          <t>teammomogenova.it</t>
+        </is>
+      </c>
+      <c r="L691" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M691" t="inlineStr">
+        <is>
+          <t>Found via search: MMA Genova palestra contatti email</t>
+        </is>
+      </c>
+      <c r="N691" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O691" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>L704</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>Body and Dream Kombat</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr"/>
+      <c r="E692" t="inlineStr"/>
+      <c r="F692" t="inlineStr">
+        <is>
+          <t>Genova</t>
+        </is>
+      </c>
+      <c r="G692" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="H692" t="inlineStr"/>
+      <c r="I692" t="inlineStr"/>
+      <c r="J692" t="inlineStr">
+        <is>
+          <t>info@ssdmtt.it</t>
+        </is>
+      </c>
+      <c r="K692" t="inlineStr">
+        <is>
+          <t>bodyanddream.it</t>
+        </is>
+      </c>
+      <c r="L692" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M692" t="inlineStr">
+        <is>
+          <t>Found via search: MMA Genova palestra contatti email</t>
+        </is>
+      </c>
+      <c r="N692" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O692" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>L705</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>Unknown Gym</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr"/>
+      <c r="E693" t="inlineStr"/>
+      <c r="F693" t="inlineStr">
+        <is>
+          <t>Genova</t>
+        </is>
+      </c>
+      <c r="G693" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="H693" t="inlineStr"/>
+      <c r="I693" t="inlineStr"/>
+      <c r="J693" t="inlineStr">
+        <is>
+          <t>kbc@boxegenova.com</t>
+        </is>
+      </c>
+      <c r="K693" t="inlineStr">
+        <is>
+          <t>boxegenova.com</t>
+        </is>
+      </c>
+      <c r="L693" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M693" t="inlineStr">
+        <is>
+          <t>Found via search: MMA Genova palestra contatti email</t>
+        </is>
+      </c>
+      <c r="N693" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O693" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>L706</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>MMA Ragazzi</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr"/>
+      <c r="E694" t="inlineStr"/>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t>Genova</t>
+        </is>
+      </c>
+      <c r="G694" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="H694" t="inlineStr"/>
+      <c r="I694" t="inlineStr"/>
+      <c r="J694" t="inlineStr">
+        <is>
+          <t>info@fightback.it</t>
+        </is>
+      </c>
+      <c r="K694" t="inlineStr">
+        <is>
+          <t>fightback.it</t>
+        </is>
+      </c>
+      <c r="L694" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M694" t="inlineStr">
+        <is>
+          <t>Found via search: MMA Genova palestra contatti email</t>
+        </is>
+      </c>
+      <c r="N694" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O694" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>L707</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>Accademia Pugilistica Portoghese, Bari, Pugil</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr"/>
+      <c r="E695" t="inlineStr"/>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>Bari</t>
+        </is>
+      </c>
+      <c r="G695" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="H695" t="inlineStr"/>
+      <c r="I695" t="inlineStr"/>
+      <c r="J695" t="inlineStr">
+        <is>
+          <t>info@boxeportoghese.it</t>
+        </is>
+      </c>
+      <c r="K695" t="inlineStr">
+        <is>
+          <t>boxeportoghese.it</t>
+        </is>
+      </c>
+      <c r="L695" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M695" t="inlineStr">
+        <is>
+          <t>Found via search: pugilato Bari palestra contatti email</t>
+        </is>
+      </c>
+      <c r="N695" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O695" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>L708</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>CSC Bari</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>@cscbari</t>
+        </is>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cscbari/</t>
+        </is>
+      </c>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>Bari</t>
+        </is>
+      </c>
+      <c r="G696" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="H696" t="inlineStr"/>
+      <c r="I696" t="inlineStr"/>
+      <c r="J696" t="inlineStr">
+        <is>
+          <t>info@cscbari.com</t>
+        </is>
+      </c>
+      <c r="K696" t="inlineStr">
+        <is>
+          <t>cscbari.com</t>
+        </is>
+      </c>
+      <c r="L696" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8 | IG profile not found (Day 8 batch)</t>
+        </is>
+      </c>
+      <c r="M696" t="inlineStr">
+        <is>
+          <t>Found via search: pugilato Bari palestra contatti email</t>
+        </is>
+      </c>
+      <c r="N696" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O696" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>L709</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>Puglia-Basilicata</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr"/>
+      <c r="E697" t="inlineStr"/>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>Bari</t>
+        </is>
+      </c>
+      <c r="G697" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="H697" t="inlineStr"/>
+      <c r="I697" t="inlineStr"/>
+      <c r="J697" t="inlineStr">
+        <is>
+          <t>puglia.basilicata@fpi.it</t>
+        </is>
+      </c>
+      <c r="K697" t="inlineStr">
+        <is>
+          <t>fpi.it</t>
+        </is>
+      </c>
+      <c r="L697" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M697" t="inlineStr">
+        <is>
+          <t>Found via search: pugilato Bari palestra contatti email</t>
+        </is>
+      </c>
+      <c r="N697" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O697" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>L710</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>Sporting Club Bari</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr"/>
+      <c r="E698" t="inlineStr"/>
+      <c r="F698" t="inlineStr">
+        <is>
+          <t>Bari</t>
+        </is>
+      </c>
+      <c r="G698" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="H698" t="inlineStr"/>
+      <c r="I698" t="inlineStr"/>
+      <c r="J698" t="inlineStr">
+        <is>
+          <t>francescodangelo1908@pec.it</t>
+        </is>
+      </c>
+      <c r="K698" t="inlineStr">
+        <is>
+          <t>sportingclubbari.it</t>
+        </is>
+      </c>
+      <c r="L698" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M698" t="inlineStr">
+        <is>
+          <t>Found via search: pugilato Bari palestra contatti email</t>
+        </is>
+      </c>
+      <c r="N698" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O698" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>L711</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>Kick Boxing Bari: scopri i corsi Gotham</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr"/>
+      <c r="E699" t="inlineStr"/>
+      <c r="F699" t="inlineStr">
+        <is>
+          <t>Bari</t>
+        </is>
+      </c>
+      <c r="G699" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="H699" t="inlineStr"/>
+      <c r="I699" t="inlineStr"/>
+      <c r="J699" t="inlineStr">
+        <is>
+          <t>info@gothamgymbari.it</t>
+        </is>
+      </c>
+      <c r="K699" t="inlineStr">
+        <is>
+          <t>gothamgymbari.it</t>
+        </is>
+      </c>
+      <c r="L699" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M699" t="inlineStr">
+        <is>
+          <t>Found via search: pugilato Bari palestra contatti email</t>
+        </is>
+      </c>
+      <c r="N699" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O699" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>L712</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>Metaclub</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr"/>
+      <c r="E700" t="inlineStr"/>
+      <c r="F700" t="inlineStr">
+        <is>
+          <t>Bari</t>
+        </is>
+      </c>
+      <c r="G700" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="H700" t="inlineStr"/>
+      <c r="I700" t="inlineStr"/>
+      <c r="J700" t="inlineStr">
+        <is>
+          <t>info@metaclub.fit</t>
+        </is>
+      </c>
+      <c r="K700" t="inlineStr">
+        <is>
+          <t>metaclub.fit</t>
+        </is>
+      </c>
+      <c r="L700" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M700" t="inlineStr">
+        <is>
+          <t>Found via search: pugilato Bari palestra contatti email</t>
+        </is>
+      </c>
+      <c r="N700" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O700" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>L713</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>Kickboxing</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr"/>
+      <c r="E701" t="inlineStr"/>
+      <c r="F701" t="inlineStr">
+        <is>
+          <t>Padova</t>
+        </is>
+      </c>
+      <c r="G701" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="H701" t="inlineStr"/>
+      <c r="I701" t="inlineStr"/>
+      <c r="J701" t="inlineStr">
+        <is>
+          <t>info@cfcpadova.it</t>
+        </is>
+      </c>
+      <c r="K701" t="inlineStr">
+        <is>
+          <t>cfcpadova.it</t>
+        </is>
+      </c>
+      <c r="L701" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M701" t="inlineStr">
+        <is>
+          <t>Found via search: kickboxing Padova palestra contatti email</t>
+        </is>
+      </c>
+      <c r="N701" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O701" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>L714</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>Corsi di KickBoxing</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr"/>
+      <c r="E702" t="inlineStr"/>
+      <c r="F702" t="inlineStr">
+        <is>
+          <t>Padova</t>
+        </is>
+      </c>
+      <c r="G702" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="H702" t="inlineStr"/>
+      <c r="I702" t="inlineStr"/>
+      <c r="J702" t="inlineStr">
+        <is>
+          <t>segreteria@sdmteam.it</t>
+        </is>
+      </c>
+      <c r="K702" t="inlineStr">
+        <is>
+          <t>sdmteam.it</t>
+        </is>
+      </c>
+      <c r="L702" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M702" t="inlineStr">
+        <is>
+          <t>Found via search: kickboxing Padova palestra contatti email</t>
+        </is>
+      </c>
+      <c r="N702" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O702" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>L715</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>Brooklyn Fitboxing</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr"/>
+      <c r="E703" t="inlineStr"/>
+      <c r="F703" t="inlineStr">
+        <is>
+          <t>Padova</t>
+        </is>
+      </c>
+      <c r="G703" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="H703" t="inlineStr"/>
+      <c r="I703" t="inlineStr"/>
+      <c r="J703" t="inlineStr">
+        <is>
+          <t>padova@brooklynfitboxing.com</t>
+        </is>
+      </c>
+      <c r="K703" t="inlineStr">
+        <is>
+          <t>brooklynfitboxing.com</t>
+        </is>
+      </c>
+      <c r="L703" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M703" t="inlineStr">
+        <is>
+          <t>Found via search: kickboxing Padova palestra contatti email</t>
+        </is>
+      </c>
+      <c r="N703" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O703" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>L716</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>Padova Top Team: La Palestra ad Abano Terme d</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr"/>
+      <c r="E704" t="inlineStr"/>
+      <c r="F704" t="inlineStr">
+        <is>
+          <t>Padova</t>
+        </is>
+      </c>
+      <c r="G704" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="H704" t="inlineStr"/>
+      <c r="I704" t="inlineStr"/>
+      <c r="J704" t="inlineStr">
+        <is>
+          <t>info@padovatopteam.it</t>
+        </is>
+      </c>
+      <c r="K704" t="inlineStr">
+        <is>
+          <t>padovatopteam.it</t>
+        </is>
+      </c>
+      <c r="L704" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M704" t="inlineStr">
+        <is>
+          <t>Found via search: kickboxing Padova palestra contatti email</t>
+        </is>
+      </c>
+      <c r="N704" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O704" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>L717</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>Unknown Gym</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr"/>
+      <c r="E705" t="inlineStr"/>
+      <c r="F705" t="inlineStr">
+        <is>
+          <t>Padova</t>
+        </is>
+      </c>
+      <c r="G705" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="H705" t="inlineStr"/>
+      <c r="I705" t="inlineStr"/>
+      <c r="J705" t="inlineStr">
+        <is>
+          <t>info@my-club.it</t>
+        </is>
+      </c>
+      <c r="K705" t="inlineStr">
+        <is>
+          <t>my-club.it</t>
+        </is>
+      </c>
+      <c r="L705" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M705" t="inlineStr">
+        <is>
+          <t>Found via search: kickboxing Padova palestra contatti email</t>
+        </is>
+      </c>
+      <c r="N705" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O705" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>L718</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>Corso e lezioni di Fit Boxe a Padova</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr"/>
+      <c r="E706" t="inlineStr"/>
+      <c r="F706" t="inlineStr">
+        <is>
+          <t>Padova</t>
+        </is>
+      </c>
+      <c r="G706" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="H706" t="inlineStr"/>
+      <c r="I706" t="inlineStr"/>
+      <c r="J706" t="inlineStr">
+        <is>
+          <t>segreteria@gymup-city.it</t>
+        </is>
+      </c>
+      <c r="K706" t="inlineStr">
+        <is>
+          <t>gymup-city.it</t>
+        </is>
+      </c>
+      <c r="L706" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M706" t="inlineStr">
+        <is>
+          <t>Found via search: kickboxing Padova palestra contatti email</t>
+        </is>
+      </c>
+      <c r="N706" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O706" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>L719</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr"/>
+      <c r="E707" t="inlineStr"/>
+      <c r="F707" t="inlineStr">
+        <is>
+          <t>Padova</t>
+        </is>
+      </c>
+      <c r="G707" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="H707" t="inlineStr"/>
+      <c r="I707" t="inlineStr"/>
+      <c r="J707" t="inlineStr">
+        <is>
+          <t>walter@dragoblu.com</t>
+        </is>
+      </c>
+      <c r="K707" t="inlineStr">
+        <is>
+          <t>dragoblu.com</t>
+        </is>
+      </c>
+      <c r="L707" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M707" t="inlineStr">
+        <is>
+          <t>Found via search: kickboxing Padova palestra contatti email</t>
+        </is>
+      </c>
+      <c r="N707" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O707" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>L720</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>Palestra di boxe a Verona</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr"/>
+      <c r="E708" t="inlineStr"/>
+      <c r="F708" t="inlineStr">
+        <is>
+          <t>Verona</t>
+        </is>
+      </c>
+      <c r="G708" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="H708" t="inlineStr"/>
+      <c r="I708" t="inlineStr"/>
+      <c r="J708" t="inlineStr">
+        <is>
+          <t>info@sperifightclub.com</t>
+        </is>
+      </c>
+      <c r="K708" t="inlineStr">
+        <is>
+          <t>sperifightclub.com</t>
+        </is>
+      </c>
+      <c r="L708" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M708" t="inlineStr">
+        <is>
+          <t>Found via search: boxe Verona palestra contatti email</t>
+        </is>
+      </c>
+      <c r="N708" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O708" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>L721</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>Unknown Gym</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr"/>
+      <c r="E709" t="inlineStr"/>
+      <c r="F709" t="inlineStr">
+        <is>
+          <t>Verona</t>
+        </is>
+      </c>
+      <c r="G709" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="H709" t="inlineStr"/>
+      <c r="I709" t="inlineStr"/>
+      <c r="J709" t="inlineStr">
+        <is>
+          <t>veronaboxingfighters@libero.it</t>
+        </is>
+      </c>
+      <c r="K709" t="inlineStr">
+        <is>
+          <t>veronaboxingfighters.it</t>
+        </is>
+      </c>
+      <c r="L709" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M709" t="inlineStr">
+        <is>
+          <t>Found via search: boxe Verona palestra contatti email</t>
+        </is>
+      </c>
+      <c r="N709" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O709" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>L722</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>Brooklyn Fitboxing</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr"/>
+      <c r="E710" t="inlineStr"/>
+      <c r="F710" t="inlineStr">
+        <is>
+          <t>Verona</t>
+        </is>
+      </c>
+      <c r="G710" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="H710" t="inlineStr"/>
+      <c r="I710" t="inlineStr"/>
+      <c r="J710" t="inlineStr">
+        <is>
+          <t>verona@brooklynfitboxing.com</t>
+        </is>
+      </c>
+      <c r="K710" t="inlineStr">
+        <is>
+          <t>brooklynfitboxing.com</t>
+        </is>
+      </c>
+      <c r="L710" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M710" t="inlineStr">
+        <is>
+          <t>Found via search: boxe Verona palestra contatti email</t>
+        </is>
+      </c>
+      <c r="N710" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O710" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>L723</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>Gym Boxe</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr"/>
+      <c r="E711" t="inlineStr"/>
+      <c r="F711" t="inlineStr">
+        <is>
+          <t>Verona</t>
+        </is>
+      </c>
+      <c r="G711" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="H711" t="inlineStr"/>
+      <c r="I711" t="inlineStr"/>
+      <c r="J711" t="inlineStr">
+        <is>
+          <t>urukai-nic@libero.it</t>
+        </is>
+      </c>
+      <c r="K711" t="inlineStr">
+        <is>
+          <t>tempiodeglielfi.it</t>
+        </is>
+      </c>
+      <c r="L711" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M711" t="inlineStr">
+        <is>
+          <t>Found via search: boxe Verona palestra contatti email</t>
+        </is>
+      </c>
+      <c r="N711" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O711" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>L724</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>Sport da combattimento Centro Forma Evolution</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr"/>
+      <c r="E712" t="inlineStr"/>
+      <c r="F712" t="inlineStr">
+        <is>
+          <t>Verona</t>
+        </is>
+      </c>
+      <c r="G712" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="H712" t="inlineStr"/>
+      <c r="I712" t="inlineStr"/>
+      <c r="J712" t="inlineStr">
+        <is>
+          <t>info@centroformaevolution.it</t>
+        </is>
+      </c>
+      <c r="K712" t="inlineStr">
+        <is>
+          <t>centroformaevolution.it</t>
+        </is>
+      </c>
+      <c r="L712" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M712" t="inlineStr">
+        <is>
+          <t>Found via search: boxe Verona palestra contatti email</t>
+        </is>
+      </c>
+      <c r="N712" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O712" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>L725</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>CUS VERONA A.S.D.</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr"/>
+      <c r="E713" t="inlineStr"/>
+      <c r="F713" t="inlineStr">
+        <is>
+          <t>Verona</t>
+        </is>
+      </c>
+      <c r="G713" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="H713" t="inlineStr"/>
+      <c r="I713" t="inlineStr"/>
+      <c r="J713" t="inlineStr">
+        <is>
+          <t>combat@cusverona.it</t>
+        </is>
+      </c>
+      <c r="K713" t="inlineStr">
+        <is>
+          <t>servizi.cusverona.it</t>
+        </is>
+      </c>
+      <c r="L713" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M713" t="inlineStr">
+        <is>
+          <t>Found via search: boxe Verona palestra contatti email</t>
+        </is>
+      </c>
+      <c r="N713" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O713" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>L726</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>Nr.1 für Fitnessboxen</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr"/>
+      <c r="E714" t="inlineStr"/>
+      <c r="F714" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="G714" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H714" t="inlineStr"/>
+      <c r="I714" t="inlineStr"/>
+      <c r="J714" t="inlineStr">
+        <is>
+          <t>boxacademystuttgart@web.de</t>
+        </is>
+      </c>
+      <c r="K714" t="inlineStr">
+        <is>
+          <t>boxacademystuttgart.de</t>
+        </is>
+      </c>
+      <c r="L714" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M714" t="inlineStr">
+        <is>
+          <t>Found via search: Boxgym Stuttgart Kontakt E-Mail</t>
+        </is>
+      </c>
+      <c r="N714" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O714" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>L727</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>Boxen Stuttgart West</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr"/>
+      <c r="E715" t="inlineStr"/>
+      <c r="F715" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="G715" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H715" t="inlineStr"/>
+      <c r="I715" t="inlineStr"/>
+      <c r="J715" t="inlineStr">
+        <is>
+          <t>info@boxen-stuttgart-west.de</t>
+        </is>
+      </c>
+      <c r="K715" t="inlineStr">
+        <is>
+          <t>boxen-stuttgart-west.de</t>
+        </is>
+      </c>
+      <c r="L715" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M715" t="inlineStr">
+        <is>
+          <t>Found via search: Boxgym Stuttgart Kontakt E-Mail</t>
+        </is>
+      </c>
+      <c r="N715" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O715" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>L728</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>Vfk Germania 1890 Stuttgart e.V.</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr"/>
+      <c r="E716" t="inlineStr"/>
+      <c r="F716" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="G716" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H716" t="inlineStr"/>
+      <c r="I716" t="inlineStr"/>
+      <c r="J716" t="inlineStr">
+        <is>
+          <t>info@boxen-stuttgart.dpoint.eu</t>
+        </is>
+      </c>
+      <c r="K716" t="inlineStr">
+        <is>
+          <t>stadtleben.de</t>
+        </is>
+      </c>
+      <c r="L716" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M716" t="inlineStr">
+        <is>
+          <t>Found via search: Boxgym Stuttgart Kontakt E-Mail</t>
+        </is>
+      </c>
+      <c r="N716" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O716" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>L729</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>Unknown Gym</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr"/>
+      <c r="E717" t="inlineStr"/>
+      <c r="F717" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="G717" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H717" t="inlineStr"/>
+      <c r="I717" t="inlineStr"/>
+      <c r="J717" t="inlineStr">
+        <is>
+          <t>info@sturmboxing.de</t>
+        </is>
+      </c>
+      <c r="K717" t="inlineStr">
+        <is>
+          <t>sturmboxing.de</t>
+        </is>
+      </c>
+      <c r="L717" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M717" t="inlineStr">
+        <is>
+          <t>Found via search: Boxgym Stuttgart Kontakt E-Mail</t>
+        </is>
+      </c>
+      <c r="N717" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O717" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>L730</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>Boxing: Im Boxring Stuttgart</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr"/>
+      <c r="E718" t="inlineStr"/>
+      <c r="F718" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="G718" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H718" t="inlineStr"/>
+      <c r="I718" t="inlineStr"/>
+      <c r="J718" t="inlineStr">
+        <is>
+          <t>unisport@uni-hohenheim.de</t>
+        </is>
+      </c>
+      <c r="K718" t="inlineStr">
+        <is>
+          <t>unisport.uni-hohenheim.de</t>
+        </is>
+      </c>
+      <c r="L718" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M718" t="inlineStr">
+        <is>
+          <t>Found via search: Boxgym Stuttgart Kontakt E-Mail</t>
+        </is>
+      </c>
+      <c r="N718" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O718" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>L731</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>Dragon Gym Kampfkunstschule in Stuttgart</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr"/>
+      <c r="E719" t="inlineStr"/>
+      <c r="F719" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="G719" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H719" t="inlineStr"/>
+      <c r="I719" t="inlineStr"/>
+      <c r="J719" t="inlineStr">
+        <is>
+          <t>stuttgart@dragongym.de</t>
+        </is>
+      </c>
+      <c r="K719" t="inlineStr">
+        <is>
+          <t>dragongym.de</t>
+        </is>
+      </c>
+      <c r="L719" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M719" t="inlineStr">
+        <is>
+          <t>Found via search: Boxgym Stuttgart Kontakt E-Mail</t>
+        </is>
+      </c>
+      <c r="N719" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O719" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>L732</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>UFD GYM Düsseldorf</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr"/>
+      <c r="E720" t="inlineStr"/>
+      <c r="F720" t="inlineStr">
+        <is>
+          <t>Düsseldorf</t>
+        </is>
+      </c>
+      <c r="G720" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H720" t="inlineStr"/>
+      <c r="I720" t="inlineStr"/>
+      <c r="J720" t="inlineStr">
+        <is>
+          <t>info@ufd-gym.de</t>
+        </is>
+      </c>
+      <c r="K720" t="inlineStr">
+        <is>
+          <t>ufd-gym.de</t>
+        </is>
+      </c>
+      <c r="L720" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M720" t="inlineStr">
+        <is>
+          <t>Found via search: MMA Gym Düsseldorf Kontakt email</t>
+        </is>
+      </c>
+      <c r="N720" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O720" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>L733</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>Unknown Gym</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr"/>
+      <c r="E721" t="inlineStr"/>
+      <c r="F721" t="inlineStr">
+        <is>
+          <t>Düsseldorf</t>
+        </is>
+      </c>
+      <c r="G721" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H721" t="inlineStr"/>
+      <c r="I721" t="inlineStr"/>
+      <c r="J721" t="inlineStr">
+        <is>
+          <t>info@mfa-gym.de</t>
+        </is>
+      </c>
+      <c r="K721" t="inlineStr">
+        <is>
+          <t>mfa-gym.de</t>
+        </is>
+      </c>
+      <c r="L721" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M721" t="inlineStr">
+        <is>
+          <t>Found via search: MMA Gym Düsseldorf Kontakt email</t>
+        </is>
+      </c>
+      <c r="N721" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O721" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>L734</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>MMA</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr"/>
+      <c r="E722" t="inlineStr"/>
+      <c r="F722" t="inlineStr">
+        <is>
+          <t>Düsseldorf</t>
+        </is>
+      </c>
+      <c r="G722" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H722" t="inlineStr"/>
+      <c r="I722" t="inlineStr"/>
+      <c r="J722" t="inlineStr">
+        <is>
+          <t>duesseldorf@red-tiger-club.de</t>
+        </is>
+      </c>
+      <c r="K722" t="inlineStr">
+        <is>
+          <t>red-tiger-club.de</t>
+        </is>
+      </c>
+      <c r="L722" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M722" t="inlineStr">
+        <is>
+          <t>Found via search: MMA Gym Düsseldorf Kontakt email</t>
+        </is>
+      </c>
+      <c r="N722" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O722" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>L735</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>Unknown Gym</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr"/>
+      <c r="E723" t="inlineStr"/>
+      <c r="F723" t="inlineStr">
+        <is>
+          <t>Dresden</t>
+        </is>
+      </c>
+      <c r="G723" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H723" t="inlineStr"/>
+      <c r="I723" t="inlineStr"/>
+      <c r="J723" t="inlineStr">
+        <is>
+          <t>info@boxklubdresden.de</t>
+        </is>
+      </c>
+      <c r="K723" t="inlineStr">
+        <is>
+          <t>boxklubdresden.de</t>
+        </is>
+      </c>
+      <c r="L723" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M723" t="inlineStr">
+        <is>
+          <t>Found via search: Boxschule Dresden Kontakt E-Mail</t>
+        </is>
+      </c>
+      <c r="N723" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O723" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>L736</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>Kampfsport Akademie Dresden</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr"/>
+      <c r="E724" t="inlineStr"/>
+      <c r="F724" t="inlineStr">
+        <is>
+          <t>Dresden</t>
+        </is>
+      </c>
+      <c r="G724" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H724" t="inlineStr"/>
+      <c r="I724" t="inlineStr"/>
+      <c r="J724" t="inlineStr">
+        <is>
+          <t>service@taofit.de</t>
+        </is>
+      </c>
+      <c r="K724" t="inlineStr">
+        <is>
+          <t>kampfsport-akademie.de</t>
+        </is>
+      </c>
+      <c r="L724" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M724" t="inlineStr">
+        <is>
+          <t>Found via search: Boxschule Dresden Kontakt E-Mail</t>
+        </is>
+      </c>
+      <c r="N724" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O724" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>L737</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>Kampfsportzentrum Dresden: Kontakt und FAQ</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr"/>
+      <c r="E725" t="inlineStr"/>
+      <c r="F725" t="inlineStr">
+        <is>
+          <t>Dresden</t>
+        </is>
+      </c>
+      <c r="G725" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H725" t="inlineStr"/>
+      <c r="I725" t="inlineStr"/>
+      <c r="J725" t="inlineStr">
+        <is>
+          <t>info@kampfsportzentrum-dresden.de</t>
+        </is>
+      </c>
+      <c r="K725" t="inlineStr">
+        <is>
+          <t>kampfsportzentrum-dresden.de</t>
+        </is>
+      </c>
+      <c r="L725" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M725" t="inlineStr">
+        <is>
+          <t>Found via search: Boxschule Dresden Kontakt E-Mail</t>
+        </is>
+      </c>
+      <c r="N725" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O725" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>L738</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>Fitboxen Dresden</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr"/>
+      <c r="E726" t="inlineStr"/>
+      <c r="F726" t="inlineStr">
+        <is>
+          <t>Dresden</t>
+        </is>
+      </c>
+      <c r="G726" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H726" t="inlineStr"/>
+      <c r="I726" t="inlineStr"/>
+      <c r="J726" t="inlineStr">
+        <is>
+          <t>info@fitboxen-dresden.de</t>
+        </is>
+      </c>
+      <c r="K726" t="inlineStr">
+        <is>
+          <t>fitboxen-dresden.de</t>
+        </is>
+      </c>
+      <c r="L726" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M726" t="inlineStr">
+        <is>
+          <t>Found via search: Boxschule Dresden Kontakt E-Mail</t>
+        </is>
+      </c>
+      <c r="N726" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O726" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>L739</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>Boxring Dresden e.V. in Dresden</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr"/>
+      <c r="E727" t="inlineStr"/>
+      <c r="F727" t="inlineStr">
+        <is>
+          <t>Dresden</t>
+        </is>
+      </c>
+      <c r="G727" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H727" t="inlineStr"/>
+      <c r="I727" t="inlineStr"/>
+      <c r="J727" t="inlineStr">
+        <is>
+          <t>info@boxring-dresden.de</t>
+        </is>
+      </c>
+      <c r="K727" t="inlineStr">
+        <is>
+          <t>diebestenderstadt.de</t>
+        </is>
+      </c>
+      <c r="L727" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M727" t="inlineStr">
+        <is>
+          <t>Found via search: Boxschule Dresden Kontakt E-Mail</t>
+        </is>
+      </c>
+      <c r="N727" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O727" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>L740</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>Home of Sports Elbflorenz</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr"/>
+      <c r="E728" t="inlineStr"/>
+      <c r="F728" t="inlineStr">
+        <is>
+          <t>Dresden</t>
+        </is>
+      </c>
+      <c r="G728" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H728" t="inlineStr"/>
+      <c r="I728" t="inlineStr"/>
+      <c r="J728" t="inlineStr">
+        <is>
+          <t>info@home-of-sports.studio</t>
+        </is>
+      </c>
+      <c r="K728" t="inlineStr">
+        <is>
+          <t>kampfsport-finder.de</t>
+        </is>
+      </c>
+      <c r="L728" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M728" t="inlineStr">
+        <is>
+          <t>Found via search: Boxschule Dresden Kontakt E-Mail</t>
+        </is>
+      </c>
+      <c r="N728" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O728" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>L741</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>Kampfsport &amp; Selbstverteidigung in Dresden</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr"/>
+      <c r="E729" t="inlineStr"/>
+      <c r="F729" t="inlineStr">
+        <is>
+          <t>Dresden</t>
+        </is>
+      </c>
+      <c r="G729" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H729" t="inlineStr"/>
+      <c r="I729" t="inlineStr"/>
+      <c r="J729" t="inlineStr">
+        <is>
+          <t>buero@traininghoch3.de</t>
+        </is>
+      </c>
+      <c r="K729" t="inlineStr">
+        <is>
+          <t>traininghoch3.de</t>
+        </is>
+      </c>
+      <c r="L729" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M729" t="inlineStr">
+        <is>
+          <t>Found via search: Boxschule Dresden Kontakt E-Mail</t>
+        </is>
+      </c>
+      <c r="N729" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O729" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>L742</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>I.S- Double Touch GYM Dresden e.V.</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr"/>
+      <c r="E730" t="inlineStr"/>
+      <c r="F730" t="inlineStr">
+        <is>
+          <t>Dresden</t>
+        </is>
+      </c>
+      <c r="G730" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H730" t="inlineStr"/>
+      <c r="I730" t="inlineStr"/>
+      <c r="J730" t="inlineStr">
+        <is>
+          <t>info@k1-boxen.de</t>
+        </is>
+      </c>
+      <c r="K730" t="inlineStr">
+        <is>
+          <t>kampfsport-finder.de</t>
+        </is>
+      </c>
+      <c r="L730" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M730" t="inlineStr">
+        <is>
+          <t>Found via search: Boxschule Dresden Kontakt E-Mail</t>
+        </is>
+      </c>
+      <c r="N730" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O730" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>L743</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>Unknown Gym</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr"/>
+      <c r="E731" t="inlineStr"/>
+      <c r="F731" t="inlineStr">
+        <is>
+          <t>Leipzig</t>
+        </is>
+      </c>
+      <c r="G731" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H731" t="inlineStr"/>
+      <c r="I731" t="inlineStr"/>
+      <c r="J731" t="inlineStr">
+        <is>
+          <t>info@kickboxen-in-leipzig.de</t>
+        </is>
+      </c>
+      <c r="K731" t="inlineStr">
+        <is>
+          <t>kickboxen-in-leipzig.de</t>
+        </is>
+      </c>
+      <c r="L731" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M731" t="inlineStr">
+        <is>
+          <t>Found via search: Kickboxen Leipzig Verein Kontakt email</t>
+        </is>
+      </c>
+      <c r="N731" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O731" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>L744</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>Kickboxen Training</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr"/>
+      <c r="E732" t="inlineStr"/>
+      <c r="F732" t="inlineStr">
+        <is>
+          <t>Leipzig</t>
+        </is>
+      </c>
+      <c r="G732" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H732" t="inlineStr"/>
+      <c r="I732" t="inlineStr"/>
+      <c r="J732" t="inlineStr">
+        <is>
+          <t>kickboxen@boxring-atlas.de</t>
+        </is>
+      </c>
+      <c r="K732" t="inlineStr">
+        <is>
+          <t>boxring-atlas.de</t>
+        </is>
+      </c>
+      <c r="L732" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M732" t="inlineStr">
+        <is>
+          <t>Found via search: Kickboxen Leipzig Verein Kontakt email</t>
+        </is>
+      </c>
+      <c r="N732" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O732" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>L745</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>Kickboxen</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr"/>
+      <c r="E733" t="inlineStr"/>
+      <c r="F733" t="inlineStr">
+        <is>
+          <t>Leipzig</t>
+        </is>
+      </c>
+      <c r="G733" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H733" t="inlineStr"/>
+      <c r="I733" t="inlineStr"/>
+      <c r="J733" t="inlineStr">
+        <is>
+          <t>info@seiwakai-leipzig.de</t>
+        </is>
+      </c>
+      <c r="K733" t="inlineStr">
+        <is>
+          <t>seiwakai-leipzig.de</t>
+        </is>
+      </c>
+      <c r="L733" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M733" t="inlineStr">
+        <is>
+          <t>Found via search: Kickboxen Leipzig Verein Kontakt email</t>
+        </is>
+      </c>
+      <c r="N733" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O733" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>L746</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>Effektives Kickboxen in Leipzig</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>@prisma_empowerment</t>
+        </is>
+      </c>
+      <c r="E734" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/prisma_empowerment/</t>
+        </is>
+      </c>
+      <c r="F734" t="inlineStr">
+        <is>
+          <t>Leipzig</t>
+        </is>
+      </c>
+      <c r="G734" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H734" t="inlineStr"/>
+      <c r="I734" t="inlineStr"/>
+      <c r="J734" t="inlineStr">
+        <is>
+          <t>info@prisma-empowerment.com</t>
+        </is>
+      </c>
+      <c r="K734" t="inlineStr">
+        <is>
+          <t>prismadojo.com</t>
+        </is>
+      </c>
+      <c r="L734" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8 | IG profile not found (Day 8 batch)</t>
+        </is>
+      </c>
+      <c r="M734" t="inlineStr">
+        <is>
+          <t>Found via search: Kickboxen Leipzig Verein Kontakt email</t>
+        </is>
+      </c>
+      <c r="N734" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O734" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>L747</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>Karateverein Bushido Leipzig e.V.</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr"/>
+      <c r="E735" t="inlineStr"/>
+      <c r="F735" t="inlineStr">
+        <is>
+          <t>Leipzig</t>
+        </is>
+      </c>
+      <c r="G735" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H735" t="inlineStr"/>
+      <c r="I735" t="inlineStr"/>
+      <c r="J735" t="inlineStr">
+        <is>
+          <t>youne@bushido-leipzig.de</t>
+        </is>
+      </c>
+      <c r="K735" t="inlineStr">
+        <is>
+          <t>leipzig.de</t>
+        </is>
+      </c>
+      <c r="L735" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M735" t="inlineStr">
+        <is>
+          <t>Found via search: Kickboxen Leipzig Verein Kontakt email</t>
+        </is>
+      </c>
+      <c r="N735" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O735" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>L748</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>Boxzentrum-Nuernberg</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr"/>
+      <c r="E736" t="inlineStr"/>
+      <c r="F736" t="inlineStr">
+        <is>
+          <t>Nürnberg</t>
+        </is>
+      </c>
+      <c r="G736" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H736" t="inlineStr"/>
+      <c r="I736" t="inlineStr"/>
+      <c r="J736" t="inlineStr">
+        <is>
+          <t>info@boxzentrumnuernberg.com</t>
+        </is>
+      </c>
+      <c r="K736" t="inlineStr">
+        <is>
+          <t>boxzentrumnuernberg.com</t>
+        </is>
+      </c>
+      <c r="L736" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M736" t="inlineStr">
+        <is>
+          <t>Found via search: Boxgym Nürnberg Kontakt E-Mail</t>
+        </is>
+      </c>
+      <c r="N736" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O736" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>L749</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>Kontakt Boxclub Almaz Nürnberg</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr"/>
+      <c r="E737" t="inlineStr"/>
+      <c r="F737" t="inlineStr">
+        <is>
+          <t>Nürnberg</t>
+        </is>
+      </c>
+      <c r="G737" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H737" t="inlineStr"/>
+      <c r="I737" t="inlineStr"/>
+      <c r="J737" t="inlineStr">
+        <is>
+          <t>info@boxclub-nuernberg.de</t>
+        </is>
+      </c>
+      <c r="K737" t="inlineStr">
+        <is>
+          <t>boxclub-nuernberg.de</t>
+        </is>
+      </c>
+      <c r="L737" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M737" t="inlineStr">
+        <is>
+          <t>Found via search: Boxgym Nürnberg Kontakt E-Mail</t>
+        </is>
+      </c>
+      <c r="N737" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O737" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>L750</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>Phoenix Boxing</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr"/>
+      <c r="E738" t="inlineStr"/>
+      <c r="F738" t="inlineStr">
+        <is>
+          <t>Nürnberg</t>
+        </is>
+      </c>
+      <c r="G738" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H738" t="inlineStr"/>
+      <c r="I738" t="inlineStr"/>
+      <c r="J738" t="inlineStr">
+        <is>
+          <t>info@phoenixboxing.de</t>
+        </is>
+      </c>
+      <c r="K738" t="inlineStr">
+        <is>
+          <t>phoenixboxing.de</t>
+        </is>
+      </c>
+      <c r="L738" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M738" t="inlineStr">
+        <is>
+          <t>Found via search: Boxgym Nürnberg Kontakt E-Mail</t>
+        </is>
+      </c>
+      <c r="N738" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O738" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>L751</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>Boxsportverein Olympia Nürnberg</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr"/>
+      <c r="E739" t="inlineStr"/>
+      <c r="F739" t="inlineStr">
+        <is>
+          <t>Nürnberg</t>
+        </is>
+      </c>
+      <c r="G739" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H739" t="inlineStr"/>
+      <c r="I739" t="inlineStr"/>
+      <c r="J739" t="inlineStr">
+        <is>
+          <t>info@olympia-nuernberg.de</t>
+        </is>
+      </c>
+      <c r="K739" t="inlineStr">
+        <is>
+          <t>boxen-nuernberg.de</t>
+        </is>
+      </c>
+      <c r="L739" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M739" t="inlineStr">
+        <is>
+          <t>Found via search: Boxgym Nürnberg Kontakt E-Mail</t>
+        </is>
+      </c>
+      <c r="N739" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O739" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>L752</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr"/>
+      <c r="E740" t="inlineStr"/>
+      <c r="F740" t="inlineStr">
+        <is>
+          <t>Nürnberg</t>
+        </is>
+      </c>
+      <c r="G740" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H740" t="inlineStr"/>
+      <c r="I740" t="inlineStr"/>
+      <c r="J740" t="inlineStr">
+        <is>
+          <t>info@thegym-nuernberg.de</t>
+        </is>
+      </c>
+      <c r="K740" t="inlineStr">
+        <is>
+          <t>thegym-nuernberg.de</t>
+        </is>
+      </c>
+      <c r="L740" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M740" t="inlineStr">
+        <is>
+          <t>Found via search: Boxgym Nürnberg Kontakt E-Mail</t>
+        </is>
+      </c>
+      <c r="N740" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O740" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>L753</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>Unknown Gym</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr"/>
+      <c r="E741" t="inlineStr"/>
+      <c r="F741" t="inlineStr">
+        <is>
+          <t>Nürnberg</t>
+        </is>
+      </c>
+      <c r="G741" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H741" t="inlineStr"/>
+      <c r="I741" t="inlineStr"/>
+      <c r="J741" t="inlineStr">
+        <is>
+          <t>boxenstop-nbg@t-online.de</t>
+        </is>
+      </c>
+      <c r="K741" t="inlineStr">
+        <is>
+          <t>boxenstop-nbg.de</t>
+        </is>
+      </c>
+      <c r="L741" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M741" t="inlineStr">
+        <is>
+          <t>Found via search: Boxgym Nürnberg Kontakt E-Mail</t>
+        </is>
+      </c>
+      <c r="N741" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O741" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>L754</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>Unknown Gym</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr"/>
+      <c r="E742" t="inlineStr"/>
+      <c r="F742" t="inlineStr">
+        <is>
+          <t>Nürnberg</t>
+        </is>
+      </c>
+      <c r="G742" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H742" t="inlineStr"/>
+      <c r="I742" t="inlineStr"/>
+      <c r="J742" t="inlineStr">
+        <is>
+          <t>mail@box-club-fcn.de</t>
+        </is>
+      </c>
+      <c r="K742" t="inlineStr">
+        <is>
+          <t>box-club-fcn.de</t>
+        </is>
+      </c>
+      <c r="L742" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M742" t="inlineStr">
+        <is>
+          <t>Found via search: Boxgym Nürnberg Kontakt E-Mail</t>
+        </is>
+      </c>
+      <c r="N742" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O742" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>L755</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>Unknown Gym</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr"/>
+      <c r="E743" t="inlineStr"/>
+      <c r="F743" t="inlineStr">
+        <is>
+          <t>Hannover</t>
+        </is>
+      </c>
+      <c r="G743" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H743" t="inlineStr"/>
+      <c r="I743" t="inlineStr"/>
+      <c r="J743" t="inlineStr">
+        <is>
+          <t>info@kingsgym-hannover.de</t>
+        </is>
+      </c>
+      <c r="K743" t="inlineStr">
+        <is>
+          <t>kingsgym-hannover.de</t>
+        </is>
+      </c>
+      <c r="L743" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M743" t="inlineStr">
+        <is>
+          <t>Found via search: Muay Thai Gym Hannover Kontakt email</t>
+        </is>
+      </c>
+      <c r="N743" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O743" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>L756</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>Lee Gym</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr"/>
+      <c r="E744" t="inlineStr"/>
+      <c r="F744" t="inlineStr">
+        <is>
+          <t>Hannover</t>
+        </is>
+      </c>
+      <c r="G744" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H744" t="inlineStr"/>
+      <c r="I744" t="inlineStr"/>
+      <c r="J744" t="inlineStr">
+        <is>
+          <t>info@lee-gym.de</t>
+        </is>
+      </c>
+      <c r="K744" t="inlineStr">
+        <is>
+          <t>epassi.de</t>
+        </is>
+      </c>
+      <c r="L744" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M744" t="inlineStr">
+        <is>
+          <t>Found via search: Muay Thai Gym Hannover Kontakt email</t>
+        </is>
+      </c>
+      <c r="N744" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O744" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>L757</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>Mixed Martial Arts</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr"/>
+      <c r="E745" t="inlineStr"/>
+      <c r="F745" t="inlineStr">
+        <is>
+          <t>Münster</t>
+        </is>
+      </c>
+      <c r="G745" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H745" t="inlineStr"/>
+      <c r="I745" t="inlineStr"/>
+      <c r="J745" t="inlineStr">
+        <is>
+          <t>info@sticksandstones-ms.de</t>
+        </is>
+      </c>
+      <c r="K745" t="inlineStr">
+        <is>
+          <t>sticksandstones-ms.de</t>
+        </is>
+      </c>
+      <c r="L745" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M745" t="inlineStr">
+        <is>
+          <t>Found via search: MMA Gym Münster Kontakt email</t>
+        </is>
+      </c>
+      <c r="N745" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O745" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>L758</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>Kickboxen, Thaiboxen, Boxen, Karate, MMA, Rin</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr"/>
+      <c r="E746" t="inlineStr"/>
+      <c r="F746" t="inlineStr">
+        <is>
+          <t>Münster</t>
+        </is>
+      </c>
+      <c r="G746" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H746" t="inlineStr"/>
+      <c r="I746" t="inlineStr"/>
+      <c r="J746" t="inlineStr">
+        <is>
+          <t>info@ufa-ms.de</t>
+        </is>
+      </c>
+      <c r="K746" t="inlineStr">
+        <is>
+          <t>ufa-ms.de</t>
+        </is>
+      </c>
+      <c r="L746" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M746" t="inlineStr">
+        <is>
+          <t>Found via search: MMA Gym Münster Kontakt email</t>
+        </is>
+      </c>
+      <c r="N746" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O746" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>L759</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>Unknown Gym</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr"/>
+      <c r="E747" t="inlineStr"/>
+      <c r="F747" t="inlineStr">
+        <is>
+          <t>Groningen</t>
+        </is>
+      </c>
+      <c r="G747" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="H747" t="inlineStr"/>
+      <c r="I747" t="inlineStr"/>
+      <c r="J747" t="inlineStr">
+        <is>
+          <t>contact@fightacademygroningen.nl</t>
+        </is>
+      </c>
+      <c r="K747" t="inlineStr">
+        <is>
+          <t>fightacademygroningen.nl</t>
+        </is>
+      </c>
+      <c r="L747" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M747" t="inlineStr">
+        <is>
+          <t>Found via search: muay thai Groningen contact email</t>
+        </is>
+      </c>
+      <c r="N747" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O747" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>L760</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>Muay Thai Groningen, Assen &amp; Veendam</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr"/>
+      <c r="E748" t="inlineStr"/>
+      <c r="F748" t="inlineStr">
+        <is>
+          <t>Groningen</t>
+        </is>
+      </c>
+      <c r="G748" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="H748" t="inlineStr"/>
+      <c r="I748" t="inlineStr"/>
+      <c r="J748" t="inlineStr">
+        <is>
+          <t>info@pauloboer.nl</t>
+        </is>
+      </c>
+      <c r="K748" t="inlineStr">
+        <is>
+          <t>pauloboer.nl</t>
+        </is>
+      </c>
+      <c r="L748" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M748" t="inlineStr">
+        <is>
+          <t>Found via search: muay thai Groningen contact email</t>
+        </is>
+      </c>
+      <c r="N748" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O748" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>L761</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>Unknown Gym</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr"/>
+      <c r="E749" t="inlineStr"/>
+      <c r="F749" t="inlineStr">
+        <is>
+          <t>Groningen</t>
+        </is>
+      </c>
+      <c r="G749" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="H749" t="inlineStr"/>
+      <c r="I749" t="inlineStr"/>
+      <c r="J749" t="inlineStr">
+        <is>
+          <t>info@kickboxinggroningen.nl</t>
+        </is>
+      </c>
+      <c r="K749" t="inlineStr">
+        <is>
+          <t>vechtsportengroningen.nl</t>
+        </is>
+      </c>
+      <c r="L749" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M749" t="inlineStr">
+        <is>
+          <t>Found via search: muay thai Groningen contact email</t>
+        </is>
+      </c>
+      <c r="N749" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O749" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>L762</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>Kung Fu / Wushu vereniging Bao Trieu / Blijd</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr"/>
+      <c r="E750" t="inlineStr"/>
+      <c r="F750" t="inlineStr">
+        <is>
+          <t>Groningen</t>
+        </is>
+      </c>
+      <c r="G750" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="H750" t="inlineStr"/>
+      <c r="I750" t="inlineStr"/>
+      <c r="J750" t="inlineStr">
+        <is>
+          <t>info@baotrieu.com</t>
+        </is>
+      </c>
+      <c r="K750" t="inlineStr">
+        <is>
+          <t>sport050.nl</t>
+        </is>
+      </c>
+      <c r="L750" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M750" t="inlineStr">
+        <is>
+          <t>Found via search: muay thai Groningen contact email</t>
+        </is>
+      </c>
+      <c r="N750" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O750" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>L763</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>Unknown Gym</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr"/>
+      <c r="E751" t="inlineStr"/>
+      <c r="F751" t="inlineStr">
+        <is>
+          <t>Groningen</t>
+        </is>
+      </c>
+      <c r="G751" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="H751" t="inlineStr"/>
+      <c r="I751" t="inlineStr"/>
+      <c r="J751" t="inlineStr">
+        <is>
+          <t>info@renshu-fights.nl</t>
+        </is>
+      </c>
+      <c r="K751" t="inlineStr">
+        <is>
+          <t>renshu-fights.nl</t>
+        </is>
+      </c>
+      <c r="L751" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M751" t="inlineStr">
+        <is>
+          <t>Found via search: muay thai Groningen contact email</t>
+        </is>
+      </c>
+      <c r="N751" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O751" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>L764</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>SUPERPRO SPORTCENTER</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr"/>
+      <c r="E752" t="inlineStr"/>
+      <c r="F752" t="inlineStr">
+        <is>
+          <t>Groningen</t>
+        </is>
+      </c>
+      <c r="G752" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="H752" t="inlineStr"/>
+      <c r="I752" t="inlineStr"/>
+      <c r="J752" t="inlineStr">
+        <is>
+          <t>info@superprosportcenter.com</t>
+        </is>
+      </c>
+      <c r="K752" t="inlineStr">
+        <is>
+          <t>superprosportcenter.com</t>
+        </is>
+      </c>
+      <c r="L752" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M752" t="inlineStr">
+        <is>
+          <t>Found via search: muay thai Groningen contact email</t>
+        </is>
+      </c>
+      <c r="N752" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O752" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>L765</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>Contact Muay-Thai Gym Enschede</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr"/>
+      <c r="E753" t="inlineStr"/>
+      <c r="F753" t="inlineStr">
+        <is>
+          <t>Groningen</t>
+        </is>
+      </c>
+      <c r="G753" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="H753" t="inlineStr"/>
+      <c r="I753" t="inlineStr"/>
+      <c r="J753" t="inlineStr">
+        <is>
+          <t>info@muaythaigym.nl</t>
+        </is>
+      </c>
+      <c r="K753" t="inlineStr">
+        <is>
+          <t>muaythaigym.nl</t>
+        </is>
+      </c>
+      <c r="L753" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M753" t="inlineStr">
+        <is>
+          <t>Found via search: muay thai Groningen contact email</t>
+        </is>
+      </c>
+      <c r="N753" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O753" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>L766</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>Brooklyn Fitboxing</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr"/>
+      <c r="E754" t="inlineStr"/>
+      <c r="F754" t="inlineStr">
+        <is>
+          <t>Zaragoza</t>
+        </is>
+      </c>
+      <c r="G754" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H754" t="inlineStr"/>
+      <c r="I754" t="inlineStr"/>
+      <c r="J754" t="inlineStr">
+        <is>
+          <t>zaragozacentro@brooklynfitboxing.com</t>
+        </is>
+      </c>
+      <c r="K754" t="inlineStr">
+        <is>
+          <t>brooklynfitboxing.com</t>
+        </is>
+      </c>
+      <c r="L754" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M754" t="inlineStr">
+        <is>
+          <t>Found via search: boxeo Zaragoza gimnasio contacto email</t>
+        </is>
+      </c>
+      <c r="N754" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O754" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>L767</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>Boxeo: clases en Zaragoza</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr"/>
+      <c r="E755" t="inlineStr"/>
+      <c r="F755" t="inlineStr">
+        <is>
+          <t>Zaragoza</t>
+        </is>
+      </c>
+      <c r="G755" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H755" t="inlineStr"/>
+      <c r="I755" t="inlineStr"/>
+      <c r="J755" t="inlineStr">
+        <is>
+          <t>info@sabah.es</t>
+        </is>
+      </c>
+      <c r="K755" t="inlineStr">
+        <is>
+          <t>sabah.es</t>
+        </is>
+      </c>
+      <c r="L755" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M755" t="inlineStr">
+        <is>
+          <t>Found via search: boxeo Zaragoza gimnasio contacto email</t>
+        </is>
+      </c>
+      <c r="N755" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O755" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>L768</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>Unknown Gym</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr"/>
+      <c r="E756" t="inlineStr"/>
+      <c r="F756" t="inlineStr">
+        <is>
+          <t>Zaragoza</t>
+        </is>
+      </c>
+      <c r="G756" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H756" t="inlineStr"/>
+      <c r="I756" t="inlineStr"/>
+      <c r="J756" t="inlineStr">
+        <is>
+          <t>hola@gallarbox.es</t>
+        </is>
+      </c>
+      <c r="K756" t="inlineStr">
+        <is>
+          <t>gallarbox.es</t>
+        </is>
+      </c>
+      <c r="L756" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M756" t="inlineStr">
+        <is>
+          <t>Found via search: boxeo Zaragoza gimnasio contacto email</t>
+        </is>
+      </c>
+      <c r="N756" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O756" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>L769</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>Boxeo en Zaragoza</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr"/>
+      <c r="E757" t="inlineStr"/>
+      <c r="F757" t="inlineStr">
+        <is>
+          <t>Zaragoza</t>
+        </is>
+      </c>
+      <c r="G757" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H757" t="inlineStr"/>
+      <c r="I757" t="inlineStr"/>
+      <c r="J757" t="inlineStr">
+        <is>
+          <t>info@stadiumvenecia.com</t>
+        </is>
+      </c>
+      <c r="K757" t="inlineStr">
+        <is>
+          <t>stadiumvenecia.com</t>
+        </is>
+      </c>
+      <c r="L757" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M757" t="inlineStr">
+        <is>
+          <t>Found via search: boxeo Zaragoza gimnasio contacto email</t>
+        </is>
+      </c>
+      <c r="N757" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O757" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>L770</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>Boxeo Zaragoza</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr"/>
+      <c r="E758" t="inlineStr"/>
+      <c r="F758" t="inlineStr">
+        <is>
+          <t>Zaragoza</t>
+        </is>
+      </c>
+      <c r="G758" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H758" t="inlineStr"/>
+      <c r="I758" t="inlineStr"/>
+      <c r="J758" t="inlineStr">
+        <is>
+          <t>gimnasio@karatekan.es</t>
+        </is>
+      </c>
+      <c r="K758" t="inlineStr">
+        <is>
+          <t>karatekan.es</t>
+        </is>
+      </c>
+      <c r="L758" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M758" t="inlineStr">
+        <is>
+          <t>Found via search: boxeo Zaragoza gimnasio contacto email</t>
+        </is>
+      </c>
+      <c r="N758" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O758" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>L771</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>Gimasio Almozara Zaragoza Kyokushin Mantente</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D759" t="inlineStr"/>
+      <c r="E759" t="inlineStr"/>
+      <c r="F759" t="inlineStr">
+        <is>
+          <t>Zaragoza</t>
+        </is>
+      </c>
+      <c r="G759" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H759" t="inlineStr"/>
+      <c r="I759" t="inlineStr"/>
+      <c r="J759" t="inlineStr">
+        <is>
+          <t>info@gimnasioalmozara.com</t>
+        </is>
+      </c>
+      <c r="K759" t="inlineStr">
+        <is>
+          <t>gimnasioalmozara.com</t>
+        </is>
+      </c>
+      <c r="L759" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M759" t="inlineStr">
+        <is>
+          <t>Found via search: boxeo Zaragoza gimnasio contacto email</t>
+        </is>
+      </c>
+      <c r="N759" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O759" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>L772</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>Academias de BJJ y MMA en Malaga</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D760" t="inlineStr"/>
+      <c r="E760" t="inlineStr"/>
+      <c r="F760" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="G760" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H760" t="inlineStr"/>
+      <c r="I760" t="inlineStr"/>
+      <c r="J760" t="inlineStr">
+        <is>
+          <t>javier@artesuave.es</t>
+        </is>
+      </c>
+      <c r="K760" t="inlineStr">
+        <is>
+          <t>fightsol.com</t>
+        </is>
+      </c>
+      <c r="L760" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M760" t="inlineStr">
+        <is>
+          <t>Found via search: MMA Málaga gimnasio email contacto</t>
+        </is>
+      </c>
+      <c r="N760" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O760" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>L773</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>ON AIR Málaga Soho</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D761" t="inlineStr"/>
+      <c r="E761" t="inlineStr"/>
+      <c r="F761" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="G761" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H761" t="inlineStr"/>
+      <c r="I761" t="inlineStr"/>
+      <c r="J761" t="inlineStr">
+        <is>
+          <t>malagasoho@onair-fitness.es</t>
+        </is>
+      </c>
+      <c r="K761" t="inlineStr">
+        <is>
+          <t>onairfitness.es</t>
+        </is>
+      </c>
+      <c r="L761" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M761" t="inlineStr">
+        <is>
+          <t>Found via search: MMA Málaga gimnasio email contacto</t>
+        </is>
+      </c>
+      <c r="N761" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O761" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>L774</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>Gimnasio de Muay Thai y MMA en Marbella</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D762" t="inlineStr"/>
+      <c r="E762" t="inlineStr"/>
+      <c r="F762" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="G762" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H762" t="inlineStr"/>
+      <c r="I762" t="inlineStr"/>
+      <c r="J762" t="inlineStr">
+        <is>
+          <t>info@baankaimuay.com</t>
+        </is>
+      </c>
+      <c r="K762" t="inlineStr">
+        <is>
+          <t>baankaimuay.com</t>
+        </is>
+      </c>
+      <c r="L762" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M762" t="inlineStr">
+        <is>
+          <t>Found via search: MMA Málaga gimnasio email contacto</t>
+        </is>
+      </c>
+      <c r="N762" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O762" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>L775</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>Contact Murcia MMA</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D763" t="inlineStr"/>
+      <c r="E763" t="inlineStr"/>
+      <c r="F763" t="inlineStr">
+        <is>
+          <t>Murcia</t>
+        </is>
+      </c>
+      <c r="G763" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H763" t="inlineStr"/>
+      <c r="I763" t="inlineStr"/>
+      <c r="J763" t="inlineStr">
+        <is>
+          <t>info@contactmurcia.com</t>
+        </is>
+      </c>
+      <c r="K763" t="inlineStr">
+        <is>
+          <t>contactmurcia.com</t>
+        </is>
+      </c>
+      <c r="L763" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M763" t="inlineStr">
+        <is>
+          <t>Found via search: kickboxing Murcia gimnasio contacto</t>
+        </is>
+      </c>
+      <c r="N763" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O763" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>L776</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>Brooklyn Fitboxing</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D764" t="inlineStr"/>
+      <c r="E764" t="inlineStr"/>
+      <c r="F764" t="inlineStr">
+        <is>
+          <t>Murcia</t>
+        </is>
+      </c>
+      <c r="G764" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H764" t="inlineStr"/>
+      <c r="I764" t="inlineStr"/>
+      <c r="J764" t="inlineStr">
+        <is>
+          <t>murcia@brooklynfitboxing.com</t>
+        </is>
+      </c>
+      <c r="K764" t="inlineStr">
+        <is>
+          <t>brooklynfitboxing.com</t>
+        </is>
+      </c>
+      <c r="L764" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M764" t="inlineStr">
+        <is>
+          <t>Found via search: kickboxing Murcia gimnasio contacto</t>
+        </is>
+      </c>
+      <c r="N764" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O764" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>L777</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>Artes Marciales</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D765" t="inlineStr"/>
+      <c r="E765" t="inlineStr"/>
+      <c r="F765" t="inlineStr">
+        <is>
+          <t>Murcia</t>
+        </is>
+      </c>
+      <c r="G765" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H765" t="inlineStr"/>
+      <c r="I765" t="inlineStr"/>
+      <c r="J765" t="inlineStr">
+        <is>
+          <t>info@dragonsclubgimnasio.com</t>
+        </is>
+      </c>
+      <c r="K765" t="inlineStr">
+        <is>
+          <t>dragonsclubgimnasio.com</t>
+        </is>
+      </c>
+      <c r="L765" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M765" t="inlineStr">
+        <is>
+          <t>Found via search: kickboxing Murcia gimnasio contacto</t>
+        </is>
+      </c>
+      <c r="N765" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O765" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>L778</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>Contacto Alicante</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D766" t="inlineStr"/>
+      <c r="E766" t="inlineStr"/>
+      <c r="F766" t="inlineStr">
+        <is>
+          <t>Alicante</t>
+        </is>
+      </c>
+      <c r="G766" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H766" t="inlineStr"/>
+      <c r="I766" t="inlineStr"/>
+      <c r="J766" t="inlineStr">
+        <is>
+          <t>info@fightland.es</t>
+        </is>
+      </c>
+      <c r="K766" t="inlineStr">
+        <is>
+          <t>fightland.es</t>
+        </is>
+      </c>
+      <c r="L766" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M766" t="inlineStr">
+        <is>
+          <t>Found via search: boxing gym Alicante contacto email</t>
+        </is>
+      </c>
+      <c r="N766" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O766" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>L779</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>Brooklyn Fitboxing</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D767" t="inlineStr"/>
+      <c r="E767" t="inlineStr"/>
+      <c r="F767" t="inlineStr">
+        <is>
+          <t>Alicante</t>
+        </is>
+      </c>
+      <c r="G767" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H767" t="inlineStr"/>
+      <c r="I767" t="inlineStr"/>
+      <c r="J767" t="inlineStr">
+        <is>
+          <t>alicantepau1@brooklynfitboxing.com</t>
+        </is>
+      </c>
+      <c r="K767" t="inlineStr">
+        <is>
+          <t>brooklynfitboxing.com</t>
+        </is>
+      </c>
+      <c r="L767" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M767" t="inlineStr">
+        <is>
+          <t>Found via search: boxing gym Alicante contacto email</t>
+        </is>
+      </c>
+      <c r="N767" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O767" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>L780</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>Boxing Box</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D768" t="inlineStr"/>
+      <c r="E768" t="inlineStr"/>
+      <c r="F768" t="inlineStr">
+        <is>
+          <t>Alicante</t>
+        </is>
+      </c>
+      <c r="G768" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H768" t="inlineStr"/>
+      <c r="I768" t="inlineStr"/>
+      <c r="J768" t="inlineStr">
+        <is>
+          <t>info@arenaalicante.com</t>
+        </is>
+      </c>
+      <c r="K768" t="inlineStr">
+        <is>
+          <t>arenaalicante.com</t>
+        </is>
+      </c>
+      <c r="L768" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M768" t="inlineStr">
+        <is>
+          <t>Found via search: boxing gym Alicante contacto email</t>
+        </is>
+      </c>
+      <c r="N768" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O768" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>L781</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>¿Dónde boxeo?</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>@feboxeo</t>
+        </is>
+      </c>
+      <c r="E769" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/feboxeo/</t>
+        </is>
+      </c>
+      <c r="F769" t="inlineStr">
+        <is>
+          <t>Alicante</t>
+        </is>
+      </c>
+      <c r="G769" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H769" t="inlineStr"/>
+      <c r="I769" t="inlineStr"/>
+      <c r="J769" t="inlineStr">
+        <is>
+          <t>info@academinalegiovii.com</t>
+        </is>
+      </c>
+      <c r="K769" t="inlineStr">
+        <is>
+          <t>feboxeo.es</t>
+        </is>
+      </c>
+      <c r="L769" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8 | IG profile not found (Day 8 batch)</t>
+        </is>
+      </c>
+      <c r="M769" t="inlineStr">
+        <is>
+          <t>Found via search: boxing gym Alicante contacto email</t>
+        </is>
+      </c>
+      <c r="N769" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O769" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>L782</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>Club de Boxeo, Alicante: Horario, Precio y Op</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D770" t="inlineStr"/>
+      <c r="E770" t="inlineStr"/>
+      <c r="F770" t="inlineStr">
+        <is>
+          <t>Alicante</t>
+        </is>
+      </c>
+      <c r="G770" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H770" t="inlineStr"/>
+      <c r="I770" t="inlineStr"/>
+      <c r="J770" t="inlineStr">
+        <is>
+          <t>info@sgowellness.com</t>
+        </is>
+      </c>
+      <c r="K770" t="inlineStr">
+        <is>
+          <t>gimnasios.fitness</t>
+        </is>
+      </c>
+      <c r="L770" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M770" t="inlineStr">
+        <is>
+          <t>Found via search: boxing gym Alicante contacto email</t>
+        </is>
+      </c>
+      <c r="N770" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O770" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>L783</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>Gimnasio MTXS, Alicante</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D771" t="inlineStr"/>
+      <c r="E771" t="inlineStr"/>
+      <c r="F771" t="inlineStr">
+        <is>
+          <t>Alicante</t>
+        </is>
+      </c>
+      <c r="G771" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H771" t="inlineStr"/>
+      <c r="I771" t="inlineStr"/>
+      <c r="J771" t="inlineStr">
+        <is>
+          <t>info@gimnasio-mtxs.com</t>
+        </is>
+      </c>
+      <c r="K771" t="inlineStr">
+        <is>
+          <t>app.fitual.com</t>
+        </is>
+      </c>
+      <c r="L771" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M771" t="inlineStr">
+        <is>
+          <t>Found via search: boxing gym Alicante contacto email</t>
+        </is>
+      </c>
+      <c r="N771" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O771" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>L784</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>CLUBS ALACANT</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D772" t="inlineStr"/>
+      <c r="E772" t="inlineStr"/>
+      <c r="F772" t="inlineStr">
+        <is>
+          <t>Alicante</t>
+        </is>
+      </c>
+      <c r="G772" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H772" t="inlineStr"/>
+      <c r="I772" t="inlineStr"/>
+      <c r="J772" t="inlineStr">
+        <is>
+          <t>fboxcv@fboxcv.com</t>
+        </is>
+      </c>
+      <c r="K772" t="inlineStr">
+        <is>
+          <t>fboxcv.com</t>
+        </is>
+      </c>
+      <c r="L772" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M772" t="inlineStr">
+        <is>
+          <t>Found via search: boxing gym Alicante contacto email</t>
+        </is>
+      </c>
+      <c r="N772" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O772" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>L785</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>Brooklyn Fitboxing</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D773" t="inlineStr"/>
+      <c r="E773" t="inlineStr"/>
+      <c r="F773" t="inlineStr">
+        <is>
+          <t>Vigo</t>
+        </is>
+      </c>
+      <c r="G773" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H773" t="inlineStr"/>
+      <c r="I773" t="inlineStr"/>
+      <c r="J773" t="inlineStr">
+        <is>
+          <t>vigocentro@brooklynfitboxing.com</t>
+        </is>
+      </c>
+      <c r="K773" t="inlineStr">
+        <is>
+          <t>brooklynfitboxing.com</t>
+        </is>
+      </c>
+      <c r="L773" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M773" t="inlineStr">
+        <is>
+          <t>Found via search: boxeo Vigo gimnasio contacto email</t>
+        </is>
+      </c>
+      <c r="N773" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O773" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>L786</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>Clases De Boxeo, Taekwondo Y Entrenamiento Pe</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D774" t="inlineStr"/>
+      <c r="E774" t="inlineStr"/>
+      <c r="F774" t="inlineStr">
+        <is>
+          <t>Vigo</t>
+        </is>
+      </c>
+      <c r="G774" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H774" t="inlineStr"/>
+      <c r="I774" t="inlineStr"/>
+      <c r="J774" t="inlineStr">
+        <is>
+          <t>hola@inlegatum.com</t>
+        </is>
+      </c>
+      <c r="K774" t="inlineStr">
+        <is>
+          <t>inlegatum.com</t>
+        </is>
+      </c>
+      <c r="L774" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M774" t="inlineStr">
+        <is>
+          <t>Found via search: boxeo Vigo gimnasio contacto email</t>
+        </is>
+      </c>
+      <c r="N774" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O774" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>L787</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>Club de boxeo</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D775" t="inlineStr"/>
+      <c r="E775" t="inlineStr"/>
+      <c r="F775" t="inlineStr">
+        <is>
+          <t>Vigo</t>
+        </is>
+      </c>
+      <c r="G775" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H775" t="inlineStr"/>
+      <c r="I775" t="inlineStr"/>
+      <c r="J775" t="inlineStr">
+        <is>
+          <t>info@gimnasioarenalvigo.es</t>
+        </is>
+      </c>
+      <c r="K775" t="inlineStr">
+        <is>
+          <t>gimnasioarenalvigo.es</t>
+        </is>
+      </c>
+      <c r="L775" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M775" t="inlineStr">
+        <is>
+          <t>Found via search: boxeo Vigo gimnasio contacto email</t>
+        </is>
+      </c>
+      <c r="N775" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O775" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>L788</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>Boxeo</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D776" t="inlineStr"/>
+      <c r="E776" t="inlineStr"/>
+      <c r="F776" t="inlineStr">
+        <is>
+          <t>Vigo</t>
+        </is>
+      </c>
+      <c r="G776" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H776" t="inlineStr"/>
+      <c r="I776" t="inlineStr"/>
+      <c r="J776" t="inlineStr">
+        <is>
+          <t>info@coliseumvigo.com</t>
+        </is>
+      </c>
+      <c r="K776" t="inlineStr">
+        <is>
+          <t>coliseumvigo.com</t>
+        </is>
+      </c>
+      <c r="L776" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M776" t="inlineStr">
+        <is>
+          <t>Found via search: boxeo Vigo gimnasio contacto email</t>
+        </is>
+      </c>
+      <c r="N776" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O776" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>L789</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>Florida Gym, Vigo: Horario, Precio y Opinione</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D777" t="inlineStr"/>
+      <c r="E777" t="inlineStr"/>
+      <c r="F777" t="inlineStr">
+        <is>
+          <t>Vigo</t>
+        </is>
+      </c>
+      <c r="G777" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H777" t="inlineStr"/>
+      <c r="I777" t="inlineStr"/>
+      <c r="J777" t="inlineStr">
+        <is>
+          <t>info@floridagym.es</t>
+        </is>
+      </c>
+      <c r="K777" t="inlineStr">
+        <is>
+          <t>gimnasios.fitness</t>
+        </is>
+      </c>
+      <c r="L777" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M777" t="inlineStr">
+        <is>
+          <t>Found via search: boxeo Vigo gimnasio contacto email</t>
+        </is>
+      </c>
+      <c r="N777" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O777" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>L790</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>¿Dónde boxeo?</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D778" t="inlineStr"/>
+      <c r="E778" t="inlineStr"/>
+      <c r="F778" t="inlineStr">
+        <is>
+          <t>Vigo</t>
+        </is>
+      </c>
+      <c r="G778" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H778" t="inlineStr"/>
+      <c r="I778" t="inlineStr"/>
+      <c r="J778" t="inlineStr">
+        <is>
+          <t>admin@laviejaescuelagym.com</t>
+        </is>
+      </c>
+      <c r="K778" t="inlineStr">
+        <is>
+          <t>feboxeo.es</t>
+        </is>
+      </c>
+      <c r="L778" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M778" t="inlineStr">
+        <is>
+          <t>Found via search: boxeo Vigo gimnasio contacto email</t>
+        </is>
+      </c>
+      <c r="N778" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O778" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>L791</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>Contactos</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D779" t="inlineStr"/>
+      <c r="E779" t="inlineStr"/>
+      <c r="F779" t="inlineStr">
+        <is>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="G779" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="H779" t="inlineStr"/>
+      <c r="I779" t="inlineStr"/>
+      <c r="J779" t="inlineStr">
+        <is>
+          <t>geral@bragaopenboxing.com</t>
+        </is>
+      </c>
+      <c r="K779" t="inlineStr">
+        <is>
+          <t>bragaopenboxing.com</t>
+        </is>
+      </c>
+      <c r="L779" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M779" t="inlineStr">
+        <is>
+          <t>Found via search: academia boxe Braga contacto email</t>
+        </is>
+      </c>
+      <c r="N779" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O779" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>L792</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>Flexgym</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>Gym/Club</t>
+        </is>
+      </c>
+      <c r="D780" t="inlineStr"/>
+      <c r="E780" t="inlineStr"/>
+      <c r="F780" t="inlineStr">
+        <is>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="G780" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="H780" t="inlineStr"/>
+      <c r="I780" t="inlineStr"/>
+      <c r="J780" t="inlineStr">
+        <is>
+          <t>geral@flexgym.pt</t>
+        </is>
+      </c>
+      <c r="K780" t="inlineStr">
+        <is>
+          <t>badgie.es</t>
+        </is>
+      </c>
+      <c r="L780" t="inlineStr">
+        <is>
+          <t>HUNTED Day 8</t>
+        </is>
+      </c>
+      <c r="M780" t="inlineStr">
+        <is>
+          <t>Found via search: academia boxe Braga contacto email</t>
+        </is>
+      </c>
+      <c r="N780" t="inlineStr">
+        <is>
+          <t>Martial arts gear, uniforms</t>
+        </is>
+      </c>
+      <c r="O780" t="inlineStr">
+        <is>
+          <t>Hunted Day 8 (2026-10-21)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O680"/>
+  <autoFilter ref="A1:O780"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -43481,7 +49605,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-21 00:50</t>
+          <t>2026-10-21 01:06</t>
         </is>
       </c>
     </row>
@@ -43492,7 +49616,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>679</v>
+        <v>779</v>
       </c>
     </row>
     <row r="5">

--- a/HWA_Lead_Tracker.xlsx
+++ b/HWA_Lead_Tracker.xlsx
@@ -8,11 +8,9 @@
   </bookViews>
   <sheets>
     <sheet name="Leads" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Scrape Report" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$O$780</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -20,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,11 +29,6 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="13"/>
     </font>
   </fonts>
   <fills count="3">
@@ -47,8 +40,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E4F"/>
-        <bgColor rgb="001F4E4F"/>
+        <fgColor rgb="001F4E78"/>
       </patternFill>
     </fill>
   </fills>
@@ -64,12 +56,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,24 +424,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O780"/>
+  <dimension ref="A1:O951"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="34" customWidth="1" min="10" max="10"/>
-    <col width="28" customWidth="1" min="11" max="11"/>
-    <col width="46" customWidth="1" min="12" max="12"/>
-    <col width="40" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="36" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -49575,8 +49564,8642 @@
         </is>
       </c>
     </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>L780</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>Wutian BJJ &amp; Kickboxing in Isle of Dogs</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>Martial arts club</t>
+        </is>
+      </c>
+      <c r="D781" t="inlineStr"/>
+      <c r="E781" t="inlineStr"/>
+      <c r="F781" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G781" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H781" t="inlineStr">
+        <is>
+          <t>442081583986</t>
+        </is>
+      </c>
+      <c r="I781" t="inlineStr"/>
+      <c r="J781" t="inlineStr">
+        <is>
+          <t>info@wutianmartialart.com</t>
+        </is>
+      </c>
+      <c r="K781" t="inlineStr">
+        <is>
+          <t>http://www.wutianmartialart.com/</t>
+        </is>
+      </c>
+      <c r="L781" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M781" t="inlineStr"/>
+      <c r="N781" t="inlineStr"/>
+      <c r="O781" t="inlineStr"/>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>L781</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>Xen-Do Martial Arts</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D782" t="inlineStr"/>
+      <c r="E782" t="inlineStr"/>
+      <c r="F782" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G782" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H782" t="inlineStr">
+        <is>
+          <t>442074873807</t>
+        </is>
+      </c>
+      <c r="I782" t="inlineStr"/>
+      <c r="J782" t="inlineStr"/>
+      <c r="K782" t="inlineStr">
+        <is>
+          <t>https://www.xen-do.com/</t>
+        </is>
+      </c>
+      <c r="L782" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M782" t="inlineStr"/>
+      <c r="N782" t="inlineStr"/>
+      <c r="O782" t="inlineStr"/>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>L782</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>London Fight Factory</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D783" t="inlineStr"/>
+      <c r="E783" t="inlineStr"/>
+      <c r="F783" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G783" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H783" t="inlineStr">
+        <is>
+          <t>447944574046</t>
+        </is>
+      </c>
+      <c r="I783" t="inlineStr"/>
+      <c r="J783" t="inlineStr">
+        <is>
+          <t>info@londonfightfactory.com</t>
+        </is>
+      </c>
+      <c r="K783" t="inlineStr">
+        <is>
+          <t>http://www.londonfightfactory.com/</t>
+        </is>
+      </c>
+      <c r="L783" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M783" t="inlineStr"/>
+      <c r="N783" t="inlineStr"/>
+      <c r="O783" t="inlineStr"/>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>L783</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>Fightzone London</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D784" t="inlineStr"/>
+      <c r="E784" t="inlineStr"/>
+      <c r="F784" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G784" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H784" t="inlineStr">
+        <is>
+          <t>442077293907</t>
+        </is>
+      </c>
+      <c r="I784" t="inlineStr"/>
+      <c r="J784" t="inlineStr">
+        <is>
+          <t>fightzonelondon@gmail.com</t>
+        </is>
+      </c>
+      <c r="K784" t="inlineStr">
+        <is>
+          <t>http://fightzonelondon.co.uk/</t>
+        </is>
+      </c>
+      <c r="L784" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M784" t="inlineStr"/>
+      <c r="N784" t="inlineStr"/>
+      <c r="O784" t="inlineStr"/>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>L784</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>AVALON Mixed Martial Arts Academy - MMA, BJJ, Wing Chun</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D785" t="inlineStr"/>
+      <c r="E785" t="inlineStr"/>
+      <c r="F785" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G785" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H785" t="inlineStr">
+        <is>
+          <t>447976855259</t>
+        </is>
+      </c>
+      <c r="I785" t="inlineStr"/>
+      <c r="J785" t="inlineStr"/>
+      <c r="K785" t="inlineStr">
+        <is>
+          <t>http://www.mmagymlondon.com/</t>
+        </is>
+      </c>
+      <c r="L785" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M785" t="inlineStr"/>
+      <c r="N785" t="inlineStr"/>
+      <c r="O785" t="inlineStr"/>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>L785</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>Ryu-Kai Martial Arts</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>Kickboxing school</t>
+        </is>
+      </c>
+      <c r="D786" t="inlineStr"/>
+      <c r="E786" t="inlineStr"/>
+      <c r="F786" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G786" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H786" t="inlineStr">
+        <is>
+          <t>442033369040</t>
+        </is>
+      </c>
+      <c r="I786" t="inlineStr"/>
+      <c r="J786" t="inlineStr">
+        <is>
+          <t>admin@ryu-kai.com</t>
+        </is>
+      </c>
+      <c r="K786" t="inlineStr">
+        <is>
+          <t>https://www.ryu-kai.com/</t>
+        </is>
+      </c>
+      <c r="L786" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M786" t="inlineStr"/>
+      <c r="N786" t="inlineStr"/>
+      <c r="O786" t="inlineStr"/>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>L786</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>London Fight Academy</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>Martial arts club</t>
+        </is>
+      </c>
+      <c r="D787" t="inlineStr"/>
+      <c r="E787" t="inlineStr"/>
+      <c r="F787" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G787" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H787" t="inlineStr">
+        <is>
+          <t>442088232323</t>
+        </is>
+      </c>
+      <c r="I787" t="inlineStr"/>
+      <c r="J787" t="inlineStr">
+        <is>
+          <t>info@londonfightacademy.com</t>
+        </is>
+      </c>
+      <c r="K787" t="inlineStr">
+        <is>
+          <t>http://www.londonfightacademy.com/</t>
+        </is>
+      </c>
+      <c r="L787" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M787" t="inlineStr"/>
+      <c r="N787" t="inlineStr"/>
+      <c r="O787" t="inlineStr"/>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>L787</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>Elite Martial Arts Academy</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D788" t="inlineStr"/>
+      <c r="E788" t="inlineStr"/>
+      <c r="F788" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G788" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H788" t="inlineStr">
+        <is>
+          <t>447516916432</t>
+        </is>
+      </c>
+      <c r="I788" t="inlineStr"/>
+      <c r="J788" t="inlineStr">
+        <is>
+          <t>elite-maa@outlook.com</t>
+        </is>
+      </c>
+      <c r="K788" t="inlineStr">
+        <is>
+          <t>https://elitemartial-arts.com/</t>
+        </is>
+      </c>
+      <c r="L788" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M788" t="inlineStr"/>
+      <c r="N788" t="inlineStr"/>
+      <c r="O788" t="inlineStr"/>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>L788</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>Legacy Martial Arts London</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>Martial arts club</t>
+        </is>
+      </c>
+      <c r="D789" t="inlineStr"/>
+      <c r="E789" t="inlineStr"/>
+      <c r="F789" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G789" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H789" t="inlineStr">
+        <is>
+          <t>447857948554</t>
+        </is>
+      </c>
+      <c r="I789" t="inlineStr"/>
+      <c r="J789" t="inlineStr">
+        <is>
+          <t>info@legacymartialartslondon.co.uk</t>
+        </is>
+      </c>
+      <c r="K789" t="inlineStr">
+        <is>
+          <t>https://www.legacymartialartslondon.co.uk/</t>
+        </is>
+      </c>
+      <c r="L789" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M789" t="inlineStr"/>
+      <c r="N789" t="inlineStr"/>
+      <c r="O789" t="inlineStr"/>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>L789</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>Tokei Martial Arts and Fitness Centre</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D790" t="inlineStr"/>
+      <c r="E790" t="inlineStr"/>
+      <c r="F790" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G790" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H790" t="inlineStr">
+        <is>
+          <t>442074035979</t>
+        </is>
+      </c>
+      <c r="I790" t="inlineStr"/>
+      <c r="J790" t="inlineStr"/>
+      <c r="K790" t="inlineStr">
+        <is>
+          <t>http://www.tokeicentre.org/</t>
+        </is>
+      </c>
+      <c r="L790" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M790" t="inlineStr"/>
+      <c r="N790" t="inlineStr"/>
+      <c r="O790" t="inlineStr"/>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>L790</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>KO Combat Academy</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>Martial arts club</t>
+        </is>
+      </c>
+      <c r="D791" t="inlineStr"/>
+      <c r="E791" t="inlineStr"/>
+      <c r="F791" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G791" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H791" t="inlineStr">
+        <is>
+          <t>442072659693</t>
+        </is>
+      </c>
+      <c r="I791" t="inlineStr"/>
+      <c r="J791" t="inlineStr">
+        <is>
+          <t>info@kocombatacademy.com</t>
+        </is>
+      </c>
+      <c r="K791" t="inlineStr">
+        <is>
+          <t>https://www.kocombatacademy.com/</t>
+        </is>
+      </c>
+      <c r="L791" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M791" t="inlineStr"/>
+      <c r="N791" t="inlineStr"/>
+      <c r="O791" t="inlineStr"/>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>L791</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>The Martial Arts Place</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D792" t="inlineStr"/>
+      <c r="E792" t="inlineStr"/>
+      <c r="F792" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G792" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H792" t="inlineStr">
+        <is>
+          <t>442072540332</t>
+        </is>
+      </c>
+      <c r="I792" t="inlineStr"/>
+      <c r="J792" t="inlineStr"/>
+      <c r="K792" t="inlineStr">
+        <is>
+          <t>http://www.themartialartsplace.com/</t>
+        </is>
+      </c>
+      <c r="L792" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M792" t="inlineStr"/>
+      <c r="N792" t="inlineStr"/>
+      <c r="O792" t="inlineStr"/>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>L792</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>Islington Martial Arts</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D793" t="inlineStr"/>
+      <c r="E793" t="inlineStr"/>
+      <c r="F793" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G793" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H793" t="inlineStr">
+        <is>
+          <t>447503554872</t>
+        </is>
+      </c>
+      <c r="I793" t="inlineStr"/>
+      <c r="J793" t="inlineStr"/>
+      <c r="K793" t="inlineStr">
+        <is>
+          <t>https://islingtonmartialarts.com/</t>
+        </is>
+      </c>
+      <c r="L793" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M793" t="inlineStr"/>
+      <c r="N793" t="inlineStr"/>
+      <c r="O793" t="inlineStr"/>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>L793</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>The London Jiu Jitsu Centre</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D794" t="inlineStr"/>
+      <c r="E794" t="inlineStr"/>
+      <c r="F794" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G794" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H794" t="inlineStr">
+        <is>
+          <t>447591492052</t>
+        </is>
+      </c>
+      <c r="I794" t="inlineStr"/>
+      <c r="J794" t="inlineStr">
+        <is>
+          <t>admin@londonjiujitsucentre.com</t>
+        </is>
+      </c>
+      <c r="K794" t="inlineStr">
+        <is>
+          <t>https://www.londonjiujitsucentre.com/</t>
+        </is>
+      </c>
+      <c r="L794" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M794" t="inlineStr"/>
+      <c r="N794" t="inlineStr"/>
+      <c r="O794" t="inlineStr"/>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>L794</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>Xen-Do Martial Arts</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D795" t="inlineStr"/>
+      <c r="E795" t="inlineStr"/>
+      <c r="F795" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G795" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H795" t="inlineStr">
+        <is>
+          <t>442078134293</t>
+        </is>
+      </c>
+      <c r="I795" t="inlineStr"/>
+      <c r="J795" t="inlineStr"/>
+      <c r="K795" t="inlineStr">
+        <is>
+          <t>https://www.xen-do.com/</t>
+        </is>
+      </c>
+      <c r="L795" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M795" t="inlineStr"/>
+      <c r="N795" t="inlineStr"/>
+      <c r="O795" t="inlineStr"/>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>L795</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>Fight City Gym - Moorgate</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D796" t="inlineStr"/>
+      <c r="E796" t="inlineStr"/>
+      <c r="F796" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G796" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H796" t="inlineStr">
+        <is>
+          <t>442070436032</t>
+        </is>
+      </c>
+      <c r="I796" t="inlineStr"/>
+      <c r="J796" t="inlineStr"/>
+      <c r="K796" t="inlineStr">
+        <is>
+          <t>https://fightcitygym.co.uk/locations/moorgate/?utm_source=go</t>
+        </is>
+      </c>
+      <c r="L796" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M796" t="inlineStr"/>
+      <c r="N796" t="inlineStr"/>
+      <c r="O796" t="inlineStr"/>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>L796</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>The Budokwai</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D797" t="inlineStr"/>
+      <c r="E797" t="inlineStr"/>
+      <c r="F797" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G797" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H797" t="inlineStr">
+        <is>
+          <t>442073701000</t>
+        </is>
+      </c>
+      <c r="I797" t="inlineStr"/>
+      <c r="J797" t="inlineStr">
+        <is>
+          <t>office@budokwai.co.uk</t>
+        </is>
+      </c>
+      <c r="K797" t="inlineStr">
+        <is>
+          <t>http://budokwai.co.uk/</t>
+        </is>
+      </c>
+      <c r="L797" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M797" t="inlineStr"/>
+      <c r="N797" t="inlineStr"/>
+      <c r="O797" t="inlineStr"/>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>L797</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>Bruce Lee's Jeet Kune Do with JKD London (Sifu Lak Loi)</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D798" t="inlineStr"/>
+      <c r="E798" t="inlineStr"/>
+      <c r="F798" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G798" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H798" t="inlineStr">
+        <is>
+          <t>447438308367</t>
+        </is>
+      </c>
+      <c r="I798" t="inlineStr"/>
+      <c r="J798" t="inlineStr"/>
+      <c r="K798" t="inlineStr">
+        <is>
+          <t>http://www.jkdlondon.com/</t>
+        </is>
+      </c>
+      <c r="L798" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M798" t="inlineStr"/>
+      <c r="N798" t="inlineStr"/>
+      <c r="O798" t="inlineStr"/>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>L798</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>Koryo Taekwondo Academy London</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>Taekwondo school</t>
+        </is>
+      </c>
+      <c r="D799" t="inlineStr"/>
+      <c r="E799" t="inlineStr"/>
+      <c r="F799" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G799" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H799" t="inlineStr">
+        <is>
+          <t>447910061481</t>
+        </is>
+      </c>
+      <c r="I799" t="inlineStr"/>
+      <c r="J799" t="inlineStr"/>
+      <c r="K799" t="inlineStr">
+        <is>
+          <t>https://koryo.co.uk/</t>
+        </is>
+      </c>
+      <c r="L799" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M799" t="inlineStr"/>
+      <c r="N799" t="inlineStr"/>
+      <c r="O799" t="inlineStr"/>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>L799</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>Wing Tsun London - Victoria</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D800" t="inlineStr"/>
+      <c r="E800" t="inlineStr"/>
+      <c r="F800" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G800" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H800" t="inlineStr"/>
+      <c r="I800" t="inlineStr"/>
+      <c r="J800" t="inlineStr">
+        <is>
+          <t>info@wingtsun-london.com</t>
+        </is>
+      </c>
+      <c r="K800" t="inlineStr">
+        <is>
+          <t>http://wingtsun-london.com/</t>
+        </is>
+      </c>
+      <c r="L800" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M800" t="inlineStr"/>
+      <c r="N800" t="inlineStr"/>
+      <c r="O800" t="inlineStr"/>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>L800</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>London Grapple</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D801" t="inlineStr"/>
+      <c r="E801" t="inlineStr"/>
+      <c r="F801" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G801" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H801" t="inlineStr">
+        <is>
+          <t>442037717955</t>
+        </is>
+      </c>
+      <c r="I801" t="inlineStr"/>
+      <c r="J801" t="inlineStr">
+        <is>
+          <t>info@londongrapple.co.uk</t>
+        </is>
+      </c>
+      <c r="K801" t="inlineStr">
+        <is>
+          <t>https://londongrapple.co.uk/</t>
+        </is>
+      </c>
+      <c r="L801" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M801" t="inlineStr"/>
+      <c r="N801" t="inlineStr"/>
+      <c r="O801" t="inlineStr"/>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>L801</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>The Gentle Arts School</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D802" t="inlineStr"/>
+      <c r="E802" t="inlineStr"/>
+      <c r="F802" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G802" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H802" t="inlineStr">
+        <is>
+          <t>447360334349</t>
+        </is>
+      </c>
+      <c r="I802" t="inlineStr"/>
+      <c r="J802" t="inlineStr">
+        <is>
+          <t>rayder@thegentleartschool.co.uk</t>
+        </is>
+      </c>
+      <c r="K802" t="inlineStr">
+        <is>
+          <t>https://www.thegentleartsschool.co.uk/</t>
+        </is>
+      </c>
+      <c r="L802" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M802" t="inlineStr"/>
+      <c r="N802" t="inlineStr"/>
+      <c r="O802" t="inlineStr"/>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>L802</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>Leo Wing Chun Chinese Kung Fu</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D803" t="inlineStr"/>
+      <c r="E803" t="inlineStr"/>
+      <c r="F803" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G803" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H803" t="inlineStr">
+        <is>
+          <t>447887427765</t>
+        </is>
+      </c>
+      <c r="I803" t="inlineStr"/>
+      <c r="J803" t="inlineStr">
+        <is>
+          <t>info@chinesekungfu.co.uk</t>
+        </is>
+      </c>
+      <c r="K803" t="inlineStr">
+        <is>
+          <t>http://www.chinesekungfu.co.uk/</t>
+        </is>
+      </c>
+      <c r="L803" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M803" t="inlineStr"/>
+      <c r="N803" t="inlineStr"/>
+      <c r="O803" t="inlineStr"/>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>L803</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meiji Martial Arts (Temple Fortune Dojo) / Kickboxing / Jiu </t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>Martial arts club</t>
+        </is>
+      </c>
+      <c r="D804" t="inlineStr"/>
+      <c r="E804" t="inlineStr"/>
+      <c r="F804" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G804" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H804" t="inlineStr">
+        <is>
+          <t>442075865880</t>
+        </is>
+      </c>
+      <c r="I804" t="inlineStr"/>
+      <c r="J804" t="inlineStr"/>
+      <c r="K804" t="inlineStr">
+        <is>
+          <t>https://meijimartialarts.co.uk/</t>
+        </is>
+      </c>
+      <c r="L804" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M804" t="inlineStr"/>
+      <c r="N804" t="inlineStr"/>
+      <c r="O804" t="inlineStr"/>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>L804</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>Shorinji Kempo - London Self Defence Martial Art</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D805" t="inlineStr"/>
+      <c r="E805" t="inlineStr"/>
+      <c r="F805" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G805" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H805" t="inlineStr">
+        <is>
+          <t>447713482314</t>
+        </is>
+      </c>
+      <c r="I805" t="inlineStr"/>
+      <c r="J805" t="inlineStr"/>
+      <c r="K805" t="inlineStr">
+        <is>
+          <t>http://www.bskfmayfairbranch.com/</t>
+        </is>
+      </c>
+      <c r="L805" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M805" t="inlineStr"/>
+      <c r="N805" t="inlineStr"/>
+      <c r="O805" t="inlineStr"/>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>L805</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>Diesel Gym London</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D806" t="inlineStr"/>
+      <c r="E806" t="inlineStr"/>
+      <c r="F806" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G806" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H806" t="inlineStr">
+        <is>
+          <t>447765243012</t>
+        </is>
+      </c>
+      <c r="I806" t="inlineStr"/>
+      <c r="J806" t="inlineStr"/>
+      <c r="K806" t="inlineStr">
+        <is>
+          <t>http://www.dieselgym.co.uk/</t>
+        </is>
+      </c>
+      <c r="L806" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M806" t="inlineStr"/>
+      <c r="N806" t="inlineStr"/>
+      <c r="O806" t="inlineStr"/>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>L806</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>London Combat MMA Academy</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D807" t="inlineStr"/>
+      <c r="E807" t="inlineStr"/>
+      <c r="F807" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G807" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H807" t="inlineStr">
+        <is>
+          <t>447930824601</t>
+        </is>
+      </c>
+      <c r="I807" t="inlineStr"/>
+      <c r="J807" t="inlineStr">
+        <is>
+          <t>londoncombat@gmail.com</t>
+        </is>
+      </c>
+      <c r="K807" t="inlineStr">
+        <is>
+          <t>http://www.londoncombatmma.co.uk/</t>
+        </is>
+      </c>
+      <c r="L807" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M807" t="inlineStr"/>
+      <c r="N807" t="inlineStr"/>
+      <c r="O807" t="inlineStr"/>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>L807</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>JAPAN SHOTOKAN KARATE LONDON</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>Karate school</t>
+        </is>
+      </c>
+      <c r="D808" t="inlineStr"/>
+      <c r="E808" t="inlineStr"/>
+      <c r="F808" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G808" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H808" t="inlineStr"/>
+      <c r="I808" t="inlineStr"/>
+      <c r="J808" t="inlineStr"/>
+      <c r="K808" t="inlineStr">
+        <is>
+          <t>http://shotokankaratelondon.co.uk/</t>
+        </is>
+      </c>
+      <c r="L808" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M808" t="inlineStr"/>
+      <c r="N808" t="inlineStr"/>
+      <c r="O808" t="inlineStr"/>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>L808</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>Kung Fu Zone</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D809" t="inlineStr"/>
+      <c r="E809" t="inlineStr"/>
+      <c r="F809" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G809" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H809" t="inlineStr"/>
+      <c r="I809" t="inlineStr"/>
+      <c r="J809" t="inlineStr">
+        <is>
+          <t>info@kungfuzone.co.uk</t>
+        </is>
+      </c>
+      <c r="K809" t="inlineStr">
+        <is>
+          <t>http://www.kungfuzone.co.uk/</t>
+        </is>
+      </c>
+      <c r="L809" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M809" t="inlineStr"/>
+      <c r="N809" t="inlineStr"/>
+      <c r="O809" t="inlineStr"/>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>L809</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>TEAM SHARK CLAPHAM JUNCTION Martial Arts Academy. Muay Thai.</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D810" t="inlineStr"/>
+      <c r="E810" t="inlineStr"/>
+      <c r="F810" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G810" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H810" t="inlineStr">
+        <is>
+          <t>447949029157</t>
+        </is>
+      </c>
+      <c r="I810" t="inlineStr"/>
+      <c r="J810" t="inlineStr"/>
+      <c r="K810" t="inlineStr">
+        <is>
+          <t>https://teamshark-martial-arts.com/</t>
+        </is>
+      </c>
+      <c r="L810" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M810" t="inlineStr"/>
+      <c r="N810" t="inlineStr"/>
+      <c r="O810" t="inlineStr"/>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>L810</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>Xen-Do Martial Arts</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>Martial arts club</t>
+        </is>
+      </c>
+      <c r="D811" t="inlineStr"/>
+      <c r="E811" t="inlineStr"/>
+      <c r="F811" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G811" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H811" t="inlineStr">
+        <is>
+          <t>442077230206</t>
+        </is>
+      </c>
+      <c r="I811" t="inlineStr"/>
+      <c r="J811" t="inlineStr"/>
+      <c r="K811" t="inlineStr">
+        <is>
+          <t>https://www.xen-do.com/</t>
+        </is>
+      </c>
+      <c r="L811" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M811" t="inlineStr"/>
+      <c r="N811" t="inlineStr"/>
+      <c r="O811" t="inlineStr"/>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>L811</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>Daigaku Karate Kai (University of Westminster Karate Club)</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>Karate school</t>
+        </is>
+      </c>
+      <c r="D812" t="inlineStr"/>
+      <c r="E812" t="inlineStr"/>
+      <c r="F812" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G812" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H812" t="inlineStr">
+        <is>
+          <t>447976411901</t>
+        </is>
+      </c>
+      <c r="I812" t="inlineStr"/>
+      <c r="J812" t="inlineStr">
+        <is>
+          <t>info@goju-karate.co.uk</t>
+        </is>
+      </c>
+      <c r="K812" t="inlineStr">
+        <is>
+          <t>http://www.goju-karate.co.uk/</t>
+        </is>
+      </c>
+      <c r="L812" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M812" t="inlineStr"/>
+      <c r="N812" t="inlineStr"/>
+      <c r="O812" t="inlineStr"/>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>L812</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>Sanda Kickboxing Academy London</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>Kickboxing school</t>
+        </is>
+      </c>
+      <c r="D813" t="inlineStr"/>
+      <c r="E813" t="inlineStr"/>
+      <c r="F813" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G813" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H813" t="inlineStr">
+        <is>
+          <t>447920056974</t>
+        </is>
+      </c>
+      <c r="I813" t="inlineStr"/>
+      <c r="J813" t="inlineStr">
+        <is>
+          <t>info@sandakickboxingacademy.co.uk</t>
+        </is>
+      </c>
+      <c r="K813" t="inlineStr">
+        <is>
+          <t>https://www.sandakickboxingacademy.co.uk/</t>
+        </is>
+      </c>
+      <c r="L813" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M813" t="inlineStr"/>
+      <c r="N813" t="inlineStr"/>
+      <c r="O813" t="inlineStr"/>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>L813</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>Qwan Ki Do &amp; Tai Chi - Martial Arts Club</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>Martial arts club</t>
+        </is>
+      </c>
+      <c r="D814" t="inlineStr"/>
+      <c r="E814" t="inlineStr"/>
+      <c r="F814" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G814" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H814" t="inlineStr">
+        <is>
+          <t>447737825087</t>
+        </is>
+      </c>
+      <c r="I814" t="inlineStr"/>
+      <c r="J814" t="inlineStr">
+        <is>
+          <t>info@qwankido.co.uk</t>
+        </is>
+      </c>
+      <c r="K814" t="inlineStr">
+        <is>
+          <t>http://qwankido.co.uk/</t>
+        </is>
+      </c>
+      <c r="L814" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M814" t="inlineStr"/>
+      <c r="N814" t="inlineStr"/>
+      <c r="O814" t="inlineStr"/>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>L814</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>Bujinkan Central London Dojo</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D815" t="inlineStr"/>
+      <c r="E815" t="inlineStr"/>
+      <c r="F815" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G815" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H815" t="inlineStr"/>
+      <c r="I815" t="inlineStr"/>
+      <c r="J815" t="inlineStr"/>
+      <c r="K815" t="inlineStr">
+        <is>
+          <t>http://www.bujinkanlondon.org/</t>
+        </is>
+      </c>
+      <c r="L815" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M815" t="inlineStr"/>
+      <c r="N815" t="inlineStr"/>
+      <c r="O815" t="inlineStr"/>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>L815</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>Karoon Taekwondo Academy</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D816" t="inlineStr"/>
+      <c r="E816" t="inlineStr"/>
+      <c r="F816" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G816" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H816" t="inlineStr">
+        <is>
+          <t>447903570600</t>
+        </is>
+      </c>
+      <c r="I816" t="inlineStr"/>
+      <c r="J816" t="inlineStr"/>
+      <c r="K816" t="inlineStr">
+        <is>
+          <t>https://www.mastersammy.com/taekwondo-old-street/</t>
+        </is>
+      </c>
+      <c r="L816" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M816" t="inlineStr"/>
+      <c r="N816" t="inlineStr"/>
+      <c r="O816" t="inlineStr"/>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>L816</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>STARTA Brazilian Jiu-Jitsu London</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D817" t="inlineStr"/>
+      <c r="E817" t="inlineStr"/>
+      <c r="F817" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G817" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H817" t="inlineStr">
+        <is>
+          <t>447564434982</t>
+        </is>
+      </c>
+      <c r="I817" t="inlineStr"/>
+      <c r="J817" t="inlineStr">
+        <is>
+          <t>info@mysite.com</t>
+        </is>
+      </c>
+      <c r="K817" t="inlineStr">
+        <is>
+          <t>http://www.startabjj.co.uk/</t>
+        </is>
+      </c>
+      <c r="L817" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M817" t="inlineStr"/>
+      <c r="N817" t="inlineStr"/>
+      <c r="O817" t="inlineStr"/>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>L817</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>London Taekwondo Academy Ltd</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D818" t="inlineStr"/>
+      <c r="E818" t="inlineStr"/>
+      <c r="F818" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G818" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H818" t="inlineStr">
+        <is>
+          <t>447857967855</t>
+        </is>
+      </c>
+      <c r="I818" t="inlineStr"/>
+      <c r="J818" t="inlineStr"/>
+      <c r="K818" t="inlineStr"/>
+      <c r="L818" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M818" t="inlineStr"/>
+      <c r="N818" t="inlineStr"/>
+      <c r="O818" t="inlineStr"/>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>L818</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>New Cross Martial Arts</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>Martial arts</t>
+        </is>
+      </c>
+      <c r="D819" t="inlineStr"/>
+      <c r="E819" t="inlineStr"/>
+      <c r="F819" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G819" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H819" t="inlineStr">
+        <is>
+          <t>447821679058</t>
+        </is>
+      </c>
+      <c r="I819" t="inlineStr"/>
+      <c r="J819" t="inlineStr">
+        <is>
+          <t>neil@newcrossmartialarts.com</t>
+        </is>
+      </c>
+      <c r="K819" t="inlineStr">
+        <is>
+          <t>https://britishjudocouncil.org/club-details/130</t>
+        </is>
+      </c>
+      <c r="L819" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M819" t="inlineStr"/>
+      <c r="N819" t="inlineStr"/>
+      <c r="O819" t="inlineStr"/>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>L819</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>Gurumu Taekwondo - Olympic Martial Arts</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D820" t="inlineStr"/>
+      <c r="E820" t="inlineStr"/>
+      <c r="F820" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G820" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H820" t="inlineStr">
+        <is>
+          <t>447931709140</t>
+        </is>
+      </c>
+      <c r="I820" t="inlineStr"/>
+      <c r="J820" t="inlineStr"/>
+      <c r="K820" t="inlineStr">
+        <is>
+          <t>http://www.gurumutaekwondo.co.uk/</t>
+        </is>
+      </c>
+      <c r="L820" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M820" t="inlineStr"/>
+      <c r="N820" t="inlineStr"/>
+      <c r="O820" t="inlineStr"/>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>L820</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>Bromley Martial Arts Academy (Black Belt School)</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D821" t="inlineStr"/>
+      <c r="E821" t="inlineStr"/>
+      <c r="F821" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G821" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H821" t="inlineStr">
+        <is>
+          <t>447720218455</t>
+        </is>
+      </c>
+      <c r="I821" t="inlineStr"/>
+      <c r="J821" t="inlineStr"/>
+      <c r="K821" t="inlineStr">
+        <is>
+          <t>https://bromleymartialarts.co.uk/</t>
+        </is>
+      </c>
+      <c r="L821" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M821" t="inlineStr"/>
+      <c r="N821" t="inlineStr"/>
+      <c r="O821" t="inlineStr"/>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>L821</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>Shaolin Temple UK</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>Buddhist temple</t>
+        </is>
+      </c>
+      <c r="D822" t="inlineStr"/>
+      <c r="E822" t="inlineStr"/>
+      <c r="F822" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G822" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H822" t="inlineStr">
+        <is>
+          <t>442076878333</t>
+        </is>
+      </c>
+      <c r="I822" t="inlineStr"/>
+      <c r="J822" t="inlineStr">
+        <is>
+          <t>info@shaolintempleuk.org</t>
+        </is>
+      </c>
+      <c r="K822" t="inlineStr">
+        <is>
+          <t>http://www.shaolintempleuk.org/</t>
+        </is>
+      </c>
+      <c r="L822" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M822" t="inlineStr"/>
+      <c r="N822" t="inlineStr"/>
+      <c r="O822" t="inlineStr"/>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>L822</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>Forrer Martial Arts Academy</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D823" t="inlineStr"/>
+      <c r="E823" t="inlineStr"/>
+      <c r="F823" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G823" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H823" t="inlineStr"/>
+      <c r="I823" t="inlineStr"/>
+      <c r="J823" t="inlineStr">
+        <is>
+          <t>contact@forrermartialartsacademy.com</t>
+        </is>
+      </c>
+      <c r="K823" t="inlineStr">
+        <is>
+          <t>http://forrermartialartsacademy.com/</t>
+        </is>
+      </c>
+      <c r="L823" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M823" t="inlineStr"/>
+      <c r="N823" t="inlineStr"/>
+      <c r="O823" t="inlineStr"/>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>L823</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>SBL London Academy</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D824" t="inlineStr"/>
+      <c r="E824" t="inlineStr"/>
+      <c r="F824" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G824" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H824" t="inlineStr">
+        <is>
+          <t>447723009164</t>
+        </is>
+      </c>
+      <c r="I824" t="inlineStr"/>
+      <c r="J824" t="inlineStr"/>
+      <c r="K824" t="inlineStr">
+        <is>
+          <t>http://www.silatopencircle.com/</t>
+        </is>
+      </c>
+      <c r="L824" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M824" t="inlineStr"/>
+      <c r="N824" t="inlineStr"/>
+      <c r="O824" t="inlineStr"/>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>L824</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>East London Shorinji Kempo</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>Martial arts club</t>
+        </is>
+      </c>
+      <c r="D825" t="inlineStr"/>
+      <c r="E825" t="inlineStr"/>
+      <c r="F825" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G825" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H825" t="inlineStr">
+        <is>
+          <t>442081232824</t>
+        </is>
+      </c>
+      <c r="I825" t="inlineStr"/>
+      <c r="J825" t="inlineStr"/>
+      <c r="K825" t="inlineStr">
+        <is>
+          <t>http://www.eastlondonkempo.co.uk/</t>
+        </is>
+      </c>
+      <c r="L825" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M825" t="inlineStr"/>
+      <c r="N825" t="inlineStr"/>
+      <c r="O825" t="inlineStr"/>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>L825</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>Boado Academy of Martial Arts BAMA</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D826" t="inlineStr"/>
+      <c r="E826" t="inlineStr"/>
+      <c r="F826" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G826" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H826" t="inlineStr">
+        <is>
+          <t>447751813956</t>
+        </is>
+      </c>
+      <c r="I826" t="inlineStr"/>
+      <c r="J826" t="inlineStr">
+        <is>
+          <t>chrisboado@hotmail.com</t>
+        </is>
+      </c>
+      <c r="K826" t="inlineStr">
+        <is>
+          <t>https://bamalondon.co.uk/</t>
+        </is>
+      </c>
+      <c r="L826" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M826" t="inlineStr"/>
+      <c r="N826" t="inlineStr"/>
+      <c r="O826" t="inlineStr"/>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>L826</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>Peak Performance Taekwondo Academy - Olympic Martial arts ce</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>Martial arts club</t>
+        </is>
+      </c>
+      <c r="D827" t="inlineStr"/>
+      <c r="E827" t="inlineStr"/>
+      <c r="F827" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G827" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H827" t="inlineStr">
+        <is>
+          <t>447961534525</t>
+        </is>
+      </c>
+      <c r="I827" t="inlineStr"/>
+      <c r="J827" t="inlineStr">
+        <is>
+          <t>info@peakperformancetkd.co.uk</t>
+        </is>
+      </c>
+      <c r="K827" t="inlineStr">
+        <is>
+          <t>http://www.peakperformancetkd.co.uk/</t>
+        </is>
+      </c>
+      <c r="L827" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M827" t="inlineStr"/>
+      <c r="N827" t="inlineStr"/>
+      <c r="O827" t="inlineStr"/>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>L827</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>Jeffrey Alexander School of Martial Arts (JASMA)</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D828" t="inlineStr"/>
+      <c r="E828" t="inlineStr"/>
+      <c r="F828" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G828" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H828" t="inlineStr">
+        <is>
+          <t>447909914567</t>
+        </is>
+      </c>
+      <c r="I828" t="inlineStr"/>
+      <c r="J828" t="inlineStr"/>
+      <c r="K828" t="inlineStr">
+        <is>
+          <t>http://jasma.org.uk/</t>
+        </is>
+      </c>
+      <c r="L828" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M828" t="inlineStr"/>
+      <c r="N828" t="inlineStr"/>
+      <c r="O828" t="inlineStr"/>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>L828</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>Westminster Shotokan Karate Club</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>Karate school</t>
+        </is>
+      </c>
+      <c r="D829" t="inlineStr"/>
+      <c r="E829" t="inlineStr"/>
+      <c r="F829" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G829" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H829" t="inlineStr">
+        <is>
+          <t>447956593184</t>
+        </is>
+      </c>
+      <c r="I829" t="inlineStr"/>
+      <c r="J829" t="inlineStr"/>
+      <c r="K829" t="inlineStr">
+        <is>
+          <t>http://wskc-jka.co.uk/</t>
+        </is>
+      </c>
+      <c r="L829" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M829" t="inlineStr"/>
+      <c r="N829" t="inlineStr"/>
+      <c r="O829" t="inlineStr"/>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>L829</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>Sanjuro Martial Arts</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>Martial arts club</t>
+        </is>
+      </c>
+      <c r="D830" t="inlineStr"/>
+      <c r="E830" t="inlineStr"/>
+      <c r="F830" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G830" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H830" t="inlineStr">
+        <is>
+          <t>447779249469</t>
+        </is>
+      </c>
+      <c r="I830" t="inlineStr"/>
+      <c r="J830" t="inlineStr">
+        <is>
+          <t>anita@sanjurotrainingsystems.com</t>
+        </is>
+      </c>
+      <c r="K830" t="inlineStr">
+        <is>
+          <t>http://www.sanjuromartialarts.com/</t>
+        </is>
+      </c>
+      <c r="L830" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M830" t="inlineStr"/>
+      <c r="N830" t="inlineStr"/>
+      <c r="O830" t="inlineStr"/>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>L830</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>Docklands Kyokushinkai Karate Club</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D831" t="inlineStr"/>
+      <c r="E831" t="inlineStr"/>
+      <c r="F831" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G831" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H831" t="inlineStr">
+        <is>
+          <t>447801406639</t>
+        </is>
+      </c>
+      <c r="I831" t="inlineStr"/>
+      <c r="J831" t="inlineStr">
+        <is>
+          <t>kem.resh@outlook.com</t>
+        </is>
+      </c>
+      <c r="K831" t="inlineStr">
+        <is>
+          <t>https://www.docklandsdojo.co.uk/</t>
+        </is>
+      </c>
+      <c r="L831" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M831" t="inlineStr"/>
+      <c r="N831" t="inlineStr"/>
+      <c r="O831" t="inlineStr"/>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>L831</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>MD Martial Arts Academy</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D832" t="inlineStr"/>
+      <c r="E832" t="inlineStr"/>
+      <c r="F832" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G832" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H832" t="inlineStr">
+        <is>
+          <t>447960599125</t>
+        </is>
+      </c>
+      <c r="I832" t="inlineStr"/>
+      <c r="J832" t="inlineStr">
+        <is>
+          <t>sifumarcdavis@gmail.com</t>
+        </is>
+      </c>
+      <c r="K832" t="inlineStr">
+        <is>
+          <t>http://sifumarcdavis.com/</t>
+        </is>
+      </c>
+      <c r="L832" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M832" t="inlineStr"/>
+      <c r="N832" t="inlineStr"/>
+      <c r="O832" t="inlineStr"/>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>L832</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>Tactical Thai Sword London</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D833" t="inlineStr"/>
+      <c r="E833" t="inlineStr"/>
+      <c r="F833" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G833" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H833" t="inlineStr">
+        <is>
+          <t>447837643316</t>
+        </is>
+      </c>
+      <c r="I833" t="inlineStr"/>
+      <c r="J833" t="inlineStr"/>
+      <c r="K833" t="inlineStr">
+        <is>
+          <t>https://tacticalthaiswordlondon.co.uk/</t>
+        </is>
+      </c>
+      <c r="L833" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M833" t="inlineStr"/>
+      <c r="N833" t="inlineStr"/>
+      <c r="O833" t="inlineStr"/>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>L833</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>Stoa Grappling</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>Jujitsu school</t>
+        </is>
+      </c>
+      <c r="D834" t="inlineStr"/>
+      <c r="E834" t="inlineStr"/>
+      <c r="F834" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G834" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H834" t="inlineStr">
+        <is>
+          <t>447540841820</t>
+        </is>
+      </c>
+      <c r="I834" t="inlineStr"/>
+      <c r="J834" t="inlineStr">
+        <is>
+          <t>info@stoagrappling.com</t>
+        </is>
+      </c>
+      <c r="K834" t="inlineStr">
+        <is>
+          <t>https://stoagrappling.com/</t>
+        </is>
+      </c>
+      <c r="L834" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M834" t="inlineStr"/>
+      <c r="N834" t="inlineStr"/>
+      <c r="O834" t="inlineStr"/>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>L834</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>Roger Gracie Brazilian Jiu Jitsu Academy HQ</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D835" t="inlineStr"/>
+      <c r="E835" t="inlineStr"/>
+      <c r="F835" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G835" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H835" t="inlineStr">
+        <is>
+          <t>442087410231</t>
+        </is>
+      </c>
+      <c r="I835" t="inlineStr"/>
+      <c r="J835" t="inlineStr">
+        <is>
+          <t>academy@rogergracie.com</t>
+        </is>
+      </c>
+      <c r="K835" t="inlineStr">
+        <is>
+          <t>http://rogergracie.com/</t>
+        </is>
+      </c>
+      <c r="L835" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M835" t="inlineStr"/>
+      <c r="N835" t="inlineStr"/>
+      <c r="O835" t="inlineStr"/>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>L835</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>Roger Gracie Euston</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>Jujitsu school</t>
+        </is>
+      </c>
+      <c r="D836" t="inlineStr"/>
+      <c r="E836" t="inlineStr"/>
+      <c r="F836" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G836" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H836" t="inlineStr">
+        <is>
+          <t>447365331358</t>
+        </is>
+      </c>
+      <c r="I836" t="inlineStr"/>
+      <c r="J836" t="inlineStr">
+        <is>
+          <t>contact@rogergracieeuston.com</t>
+        </is>
+      </c>
+      <c r="K836" t="inlineStr">
+        <is>
+          <t>https://rogergracieeuston.com/</t>
+        </is>
+      </c>
+      <c r="L836" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M836" t="inlineStr"/>
+      <c r="N836" t="inlineStr"/>
+      <c r="O836" t="inlineStr"/>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>L836</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>Carlson Gracie London</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D837" t="inlineStr"/>
+      <c r="E837" t="inlineStr"/>
+      <c r="F837" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G837" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H837" t="inlineStr">
+        <is>
+          <t>447518111170</t>
+        </is>
+      </c>
+      <c r="I837" t="inlineStr"/>
+      <c r="J837" t="inlineStr">
+        <is>
+          <t>info@bjjlondon.com</t>
+        </is>
+      </c>
+      <c r="K837" t="inlineStr">
+        <is>
+          <t>http://www.bjjlondon.com/</t>
+        </is>
+      </c>
+      <c r="L837" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M837" t="inlineStr"/>
+      <c r="N837" t="inlineStr"/>
+      <c r="O837" t="inlineStr"/>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>L837</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>BALANCE BRAZILIAN JIU JITSU ACADEMY</t>
+        </is>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D838" t="inlineStr"/>
+      <c r="E838" t="inlineStr"/>
+      <c r="F838" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G838" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H838" t="inlineStr">
+        <is>
+          <t>447360542667</t>
+        </is>
+      </c>
+      <c r="I838" t="inlineStr"/>
+      <c r="J838" t="inlineStr">
+        <is>
+          <t>info@balancebjj.co.uk</t>
+        </is>
+      </c>
+      <c r="K838" t="inlineStr">
+        <is>
+          <t>http://www.balancebjj.co.uk/</t>
+        </is>
+      </c>
+      <c r="L838" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M838" t="inlineStr"/>
+      <c r="N838" t="inlineStr"/>
+      <c r="O838" t="inlineStr"/>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>L838</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>Alliance Jiu Jitsu London</t>
+        </is>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D839" t="inlineStr"/>
+      <c r="E839" t="inlineStr"/>
+      <c r="F839" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G839" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H839" t="inlineStr">
+        <is>
+          <t>442080791044</t>
+        </is>
+      </c>
+      <c r="I839" t="inlineStr"/>
+      <c r="J839" t="inlineStr">
+        <is>
+          <t>hello@alliancejjlondon.com</t>
+        </is>
+      </c>
+      <c r="K839" t="inlineStr">
+        <is>
+          <t>https://alliancejjlondon.com/</t>
+        </is>
+      </c>
+      <c r="L839" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M839" t="inlineStr"/>
+      <c r="N839" t="inlineStr"/>
+      <c r="O839" t="inlineStr"/>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>L839</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>Kodokan Academy of Brazilian Jiu Jitsu - BJJ School London</t>
+        </is>
+      </c>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>Martial arts club</t>
+        </is>
+      </c>
+      <c r="D840" t="inlineStr"/>
+      <c r="E840" t="inlineStr"/>
+      <c r="F840" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G840" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H840" t="inlineStr">
+        <is>
+          <t>447834230066</t>
+        </is>
+      </c>
+      <c r="I840" t="inlineStr"/>
+      <c r="J840" t="inlineStr">
+        <is>
+          <t>sensei@thekodokan.com</t>
+        </is>
+      </c>
+      <c r="K840" t="inlineStr">
+        <is>
+          <t>http://www.thekodokan.com/</t>
+        </is>
+      </c>
+      <c r="L840" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M840" t="inlineStr"/>
+      <c r="N840" t="inlineStr"/>
+      <c r="O840" t="inlineStr"/>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>L840</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>BJJ ART UK - Brazilian Jiu Jitsu</t>
+        </is>
+      </c>
+      <c r="C841" t="inlineStr">
+        <is>
+          <t>Martial arts club</t>
+        </is>
+      </c>
+      <c r="D841" t="inlineStr"/>
+      <c r="E841" t="inlineStr"/>
+      <c r="F841" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G841" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H841" t="inlineStr">
+        <is>
+          <t>447565132401</t>
+        </is>
+      </c>
+      <c r="I841" t="inlineStr"/>
+      <c r="J841" t="inlineStr">
+        <is>
+          <t>bjj4all.ltd@gmail.com</t>
+        </is>
+      </c>
+      <c r="K841" t="inlineStr">
+        <is>
+          <t>https://bjj-art.com/</t>
+        </is>
+      </c>
+      <c r="L841" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M841" t="inlineStr"/>
+      <c r="N841" t="inlineStr"/>
+      <c r="O841" t="inlineStr"/>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>L841</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>Putney Jiu Jitsu - 5* BJJ Gym in South West London</t>
+        </is>
+      </c>
+      <c r="C842" t="inlineStr">
+        <is>
+          <t>Jujitsu school</t>
+        </is>
+      </c>
+      <c r="D842" t="inlineStr"/>
+      <c r="E842" t="inlineStr"/>
+      <c r="F842" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G842" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H842" t="inlineStr">
+        <is>
+          <t>447716222602</t>
+        </is>
+      </c>
+      <c r="I842" t="inlineStr"/>
+      <c r="J842" t="inlineStr">
+        <is>
+          <t>info@putneybjj.com</t>
+        </is>
+      </c>
+      <c r="K842" t="inlineStr">
+        <is>
+          <t>http://www.putneybjj.com/</t>
+        </is>
+      </c>
+      <c r="L842" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M842" t="inlineStr"/>
+      <c r="N842" t="inlineStr"/>
+      <c r="O842" t="inlineStr"/>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>L842</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>BJJ Dojo</t>
+        </is>
+      </c>
+      <c r="C843" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D843" t="inlineStr"/>
+      <c r="E843" t="inlineStr"/>
+      <c r="F843" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G843" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H843" t="inlineStr">
+        <is>
+          <t>447841764210</t>
+        </is>
+      </c>
+      <c r="I843" t="inlineStr"/>
+      <c r="J843" t="inlineStr">
+        <is>
+          <t>info@bjjhouse.co.uk</t>
+        </is>
+      </c>
+      <c r="K843" t="inlineStr">
+        <is>
+          <t>https://bjjhouse.uk/</t>
+        </is>
+      </c>
+      <c r="L843" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M843" t="inlineStr"/>
+      <c r="N843" t="inlineStr"/>
+      <c r="O843" t="inlineStr"/>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>L843</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>Luciano Cristovam BJJ Academy</t>
+        </is>
+      </c>
+      <c r="C844" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D844" t="inlineStr"/>
+      <c r="E844" t="inlineStr"/>
+      <c r="F844" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G844" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H844" t="inlineStr">
+        <is>
+          <t>447498471113</t>
+        </is>
+      </c>
+      <c r="I844" t="inlineStr"/>
+      <c r="J844" t="inlineStr"/>
+      <c r="K844" t="inlineStr">
+        <is>
+          <t>http://lucianocristovam.com/</t>
+        </is>
+      </c>
+      <c r="L844" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M844" t="inlineStr"/>
+      <c r="N844" t="inlineStr"/>
+      <c r="O844" t="inlineStr"/>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>L844</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>Gracie Barra Oval</t>
+        </is>
+      </c>
+      <c r="C845" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D845" t="inlineStr"/>
+      <c r="E845" t="inlineStr"/>
+      <c r="F845" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G845" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H845" t="inlineStr">
+        <is>
+          <t>447734463932</t>
+        </is>
+      </c>
+      <c r="I845" t="inlineStr"/>
+      <c r="J845" t="inlineStr">
+        <is>
+          <t>info@graciebarraoval.com</t>
+        </is>
+      </c>
+      <c r="K845" t="inlineStr">
+        <is>
+          <t>https://www.graciebarraoval.com/</t>
+        </is>
+      </c>
+      <c r="L845" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M845" t="inlineStr"/>
+      <c r="N845" t="inlineStr"/>
+      <c r="O845" t="inlineStr"/>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>L845</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>Carlson Gracie Jiu Jitsu Gym Clapham</t>
+        </is>
+      </c>
+      <c r="C846" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D846" t="inlineStr"/>
+      <c r="E846" t="inlineStr"/>
+      <c r="F846" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G846" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H846" t="inlineStr"/>
+      <c r="I846" t="inlineStr"/>
+      <c r="J846" t="inlineStr">
+        <is>
+          <t>martinfootbjj@gmail.com</t>
+        </is>
+      </c>
+      <c r="K846" t="inlineStr">
+        <is>
+          <t>http://www.bjjsouthlondon.com/</t>
+        </is>
+      </c>
+      <c r="L846" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M846" t="inlineStr"/>
+      <c r="N846" t="inlineStr"/>
+      <c r="O846" t="inlineStr"/>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>L846</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>ARMA Jiu Jitsu Club</t>
+        </is>
+      </c>
+      <c r="C847" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D847" t="inlineStr"/>
+      <c r="E847" t="inlineStr"/>
+      <c r="F847" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G847" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H847" t="inlineStr">
+        <is>
+          <t>442081290847</t>
+        </is>
+      </c>
+      <c r="I847" t="inlineStr"/>
+      <c r="J847" t="inlineStr">
+        <is>
+          <t>info@armabjj.com</t>
+        </is>
+      </c>
+      <c r="K847" t="inlineStr">
+        <is>
+          <t>https://www.armabjj.com/?utm_source=google&amp;utm_medium=organi</t>
+        </is>
+      </c>
+      <c r="L847" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M847" t="inlineStr"/>
+      <c r="N847" t="inlineStr"/>
+      <c r="O847" t="inlineStr"/>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>L847</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>Cantagalo JiuJitsu London</t>
+        </is>
+      </c>
+      <c r="C848" t="inlineStr">
+        <is>
+          <t>Martial arts club</t>
+        </is>
+      </c>
+      <c r="D848" t="inlineStr"/>
+      <c r="E848" t="inlineStr"/>
+      <c r="F848" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G848" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H848" t="inlineStr">
+        <is>
+          <t>447902491656</t>
+        </is>
+      </c>
+      <c r="I848" t="inlineStr"/>
+      <c r="J848" t="inlineStr">
+        <is>
+          <t>cantagalojiujitsulondon@gmail.com</t>
+        </is>
+      </c>
+      <c r="K848" t="inlineStr">
+        <is>
+          <t>https://cantagalobjj.com/</t>
+        </is>
+      </c>
+      <c r="L848" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M848" t="inlineStr"/>
+      <c r="N848" t="inlineStr"/>
+      <c r="O848" t="inlineStr"/>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>L848</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>Grapple Zone Brazilian Jiu Jitsu, Waterloo</t>
+        </is>
+      </c>
+      <c r="C849" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D849" t="inlineStr"/>
+      <c r="E849" t="inlineStr"/>
+      <c r="F849" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G849" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H849" t="inlineStr">
+        <is>
+          <t>447496636266</t>
+        </is>
+      </c>
+      <c r="I849" t="inlineStr"/>
+      <c r="J849" t="inlineStr">
+        <is>
+          <t>admin@grapplezone.co.uk</t>
+        </is>
+      </c>
+      <c r="K849" t="inlineStr">
+        <is>
+          <t>https://www.grapplezone.co.uk/</t>
+        </is>
+      </c>
+      <c r="L849" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M849" t="inlineStr"/>
+      <c r="N849" t="inlineStr"/>
+      <c r="O849" t="inlineStr"/>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>L849</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>10th Planet Jiu Jitsu London</t>
+        </is>
+      </c>
+      <c r="C850" t="inlineStr">
+        <is>
+          <t>Martial arts club</t>
+        </is>
+      </c>
+      <c r="D850" t="inlineStr"/>
+      <c r="E850" t="inlineStr"/>
+      <c r="F850" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G850" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H850" t="inlineStr">
+        <is>
+          <t>447984973337</t>
+        </is>
+      </c>
+      <c r="I850" t="inlineStr"/>
+      <c r="J850" t="inlineStr"/>
+      <c r="K850" t="inlineStr">
+        <is>
+          <t>http://www.10thplanetjjlondon.com/</t>
+        </is>
+      </c>
+      <c r="L850" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M850" t="inlineStr"/>
+      <c r="N850" t="inlineStr"/>
+      <c r="O850" t="inlineStr"/>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>L850</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>Wave Brazilian Jiu Jitsu</t>
+        </is>
+      </c>
+      <c r="C851" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D851" t="inlineStr"/>
+      <c r="E851" t="inlineStr"/>
+      <c r="F851" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G851" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H851" t="inlineStr">
+        <is>
+          <t>442080128355</t>
+        </is>
+      </c>
+      <c r="I851" t="inlineStr"/>
+      <c r="J851" t="inlineStr">
+        <is>
+          <t>info@wavebjj.co</t>
+        </is>
+      </c>
+      <c r="K851" t="inlineStr">
+        <is>
+          <t>http://www.bjjwestlondon.com/</t>
+        </is>
+      </c>
+      <c r="L851" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M851" t="inlineStr"/>
+      <c r="N851" t="inlineStr"/>
+      <c r="O851" t="inlineStr"/>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>L851</t>
+        </is>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>Los Banditos Submission Grappling Club</t>
+        </is>
+      </c>
+      <c r="C852" t="inlineStr">
+        <is>
+          <t>Jujitsu school</t>
+        </is>
+      </c>
+      <c r="D852" t="inlineStr"/>
+      <c r="E852" t="inlineStr"/>
+      <c r="F852" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G852" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H852" t="inlineStr"/>
+      <c r="I852" t="inlineStr"/>
+      <c r="J852" t="inlineStr"/>
+      <c r="K852" t="inlineStr">
+        <is>
+          <t>https://losbanditos.club/</t>
+        </is>
+      </c>
+      <c r="L852" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M852" t="inlineStr"/>
+      <c r="N852" t="inlineStr"/>
+      <c r="O852" t="inlineStr"/>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>L852</t>
+        </is>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>PURE JIUJITSU</t>
+        </is>
+      </c>
+      <c r="C853" t="inlineStr">
+        <is>
+          <t>Martial arts club</t>
+        </is>
+      </c>
+      <c r="D853" t="inlineStr"/>
+      <c r="E853" t="inlineStr"/>
+      <c r="F853" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G853" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H853" t="inlineStr">
+        <is>
+          <t>447521420733</t>
+        </is>
+      </c>
+      <c r="I853" t="inlineStr"/>
+      <c r="J853" t="inlineStr">
+        <is>
+          <t>info@purejiujitsu.com</t>
+        </is>
+      </c>
+      <c r="K853" t="inlineStr">
+        <is>
+          <t>http://www.purejiujitsu.com/</t>
+        </is>
+      </c>
+      <c r="L853" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M853" t="inlineStr"/>
+      <c r="N853" t="inlineStr"/>
+      <c r="O853" t="inlineStr"/>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>L853</t>
+        </is>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>London Ju Jitsu - Elephant and Castle</t>
+        </is>
+      </c>
+      <c r="C854" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D854" t="inlineStr"/>
+      <c r="E854" t="inlineStr"/>
+      <c r="F854" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G854" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H854" t="inlineStr">
+        <is>
+          <t>447903190978</t>
+        </is>
+      </c>
+      <c r="I854" t="inlineStr"/>
+      <c r="J854" t="inlineStr">
+        <is>
+          <t>info@londonjujitsu.com</t>
+        </is>
+      </c>
+      <c r="K854" t="inlineStr">
+        <is>
+          <t>http://www.londonjujitsu.com/</t>
+        </is>
+      </c>
+      <c r="L854" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M854" t="inlineStr"/>
+      <c r="N854" t="inlineStr"/>
+      <c r="O854" t="inlineStr"/>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>L854</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>Manchester Karate - Missing Link in Manchester</t>
+        </is>
+      </c>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D855" t="inlineStr"/>
+      <c r="E855" t="inlineStr"/>
+      <c r="F855" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G855" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H855" t="inlineStr">
+        <is>
+          <t>447539946777</t>
+        </is>
+      </c>
+      <c r="I855" t="inlineStr"/>
+      <c r="J855" t="inlineStr">
+        <is>
+          <t>manchester@missinglink-martialarts.uk</t>
+        </is>
+      </c>
+      <c r="K855" t="inlineStr">
+        <is>
+          <t>http://www.missinglink-martialarts.uk/</t>
+        </is>
+      </c>
+      <c r="L855" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M855" t="inlineStr"/>
+      <c r="N855" t="inlineStr"/>
+      <c r="O855" t="inlineStr"/>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>L855</t>
+        </is>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>SBG Manchester Mixed Martial Arts and Brazilian Jiu Jitsu</t>
+        </is>
+      </c>
+      <c r="C856" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D856" t="inlineStr"/>
+      <c r="E856" t="inlineStr"/>
+      <c r="F856" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G856" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H856" t="inlineStr"/>
+      <c r="I856" t="inlineStr"/>
+      <c r="J856" t="inlineStr">
+        <is>
+          <t>info@sbgmanchester.com</t>
+        </is>
+      </c>
+      <c r="K856" t="inlineStr">
+        <is>
+          <t>http://www.sbgmanchester.com/</t>
+        </is>
+      </c>
+      <c r="L856" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M856" t="inlineStr"/>
+      <c r="N856" t="inlineStr"/>
+      <c r="O856" t="inlineStr"/>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>L856</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>Fighting Fit Manchester</t>
+        </is>
+      </c>
+      <c r="C857" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D857" t="inlineStr"/>
+      <c r="E857" t="inlineStr"/>
+      <c r="F857" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G857" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H857" t="inlineStr">
+        <is>
+          <t>447385187483</t>
+        </is>
+      </c>
+      <c r="I857" t="inlineStr"/>
+      <c r="J857" t="inlineStr">
+        <is>
+          <t>gym@fightingfitmanchester.co.uk</t>
+        </is>
+      </c>
+      <c r="K857" t="inlineStr">
+        <is>
+          <t>http://www.fightingfitmanchester.com/</t>
+        </is>
+      </c>
+      <c r="L857" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M857" t="inlineStr"/>
+      <c r="N857" t="inlineStr"/>
+      <c r="O857" t="inlineStr"/>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>L857</t>
+        </is>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>Shaolin Kung Fu - Gao Can Mun Nam Pai Chuan</t>
+        </is>
+      </c>
+      <c r="C858" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D858" t="inlineStr"/>
+      <c r="E858" t="inlineStr"/>
+      <c r="F858" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G858" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H858" t="inlineStr">
+        <is>
+          <t>447887776132</t>
+        </is>
+      </c>
+      <c r="I858" t="inlineStr"/>
+      <c r="J858" t="inlineStr">
+        <is>
+          <t>manchestershaolinnpc@gmail.com</t>
+        </is>
+      </c>
+      <c r="K858" t="inlineStr">
+        <is>
+          <t>http://www.manchesterkungfu.co.uk/</t>
+        </is>
+      </c>
+      <c r="L858" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M858" t="inlineStr"/>
+      <c r="N858" t="inlineStr"/>
+      <c r="O858" t="inlineStr"/>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>L858</t>
+        </is>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>Didsbury Black Belt Academy</t>
+        </is>
+      </c>
+      <c r="C859" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D859" t="inlineStr"/>
+      <c r="E859" t="inlineStr"/>
+      <c r="F859" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G859" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H859" t="inlineStr">
+        <is>
+          <t>441614457733</t>
+        </is>
+      </c>
+      <c r="I859" t="inlineStr"/>
+      <c r="J859" t="inlineStr"/>
+      <c r="K859" t="inlineStr">
+        <is>
+          <t>http://www.didsburybba.com/</t>
+        </is>
+      </c>
+      <c r="L859" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M859" t="inlineStr"/>
+      <c r="N859" t="inlineStr"/>
+      <c r="O859" t="inlineStr"/>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>L859</t>
+        </is>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>Union Academy Manchester - BJJ and Kickboxing Academy</t>
+        </is>
+      </c>
+      <c r="C860" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D860" t="inlineStr"/>
+      <c r="E860" t="inlineStr"/>
+      <c r="F860" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G860" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H860" t="inlineStr">
+        <is>
+          <t>442088168382</t>
+        </is>
+      </c>
+      <c r="I860" t="inlineStr"/>
+      <c r="J860" t="inlineStr"/>
+      <c r="K860" t="inlineStr">
+        <is>
+          <t>http://www.unionacademy.co.uk/</t>
+        </is>
+      </c>
+      <c r="L860" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M860" t="inlineStr"/>
+      <c r="N860" t="inlineStr"/>
+      <c r="O860" t="inlineStr"/>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>L860</t>
+        </is>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>Solid MMA Manchester</t>
+        </is>
+      </c>
+      <c r="C861" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D861" t="inlineStr"/>
+      <c r="E861" t="inlineStr"/>
+      <c r="F861" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G861" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H861" t="inlineStr">
+        <is>
+          <t>447543619474</t>
+        </is>
+      </c>
+      <c r="I861" t="inlineStr"/>
+      <c r="J861" t="inlineStr">
+        <is>
+          <t>info@solidmmamanchester.co.uk</t>
+        </is>
+      </c>
+      <c r="K861" t="inlineStr">
+        <is>
+          <t>https://www.solidmmamanchester.co.uk/</t>
+        </is>
+      </c>
+      <c r="L861" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M861" t="inlineStr"/>
+      <c r="N861" t="inlineStr"/>
+      <c r="O861" t="inlineStr"/>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>L861</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>K.M.M.A. Freestyle Martial Arts Academy</t>
+        </is>
+      </c>
+      <c r="C862" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D862" t="inlineStr"/>
+      <c r="E862" t="inlineStr"/>
+      <c r="F862" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G862" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H862" t="inlineStr">
+        <is>
+          <t>447961914054</t>
+        </is>
+      </c>
+      <c r="I862" t="inlineStr"/>
+      <c r="J862" t="inlineStr">
+        <is>
+          <t>kmmafreestyle.info@gmail.com</t>
+        </is>
+      </c>
+      <c r="K862" t="inlineStr">
+        <is>
+          <t>https://www.kmma-freestyle.co.uk/</t>
+        </is>
+      </c>
+      <c r="L862" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M862" t="inlineStr"/>
+      <c r="N862" t="inlineStr"/>
+      <c r="O862" t="inlineStr"/>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>L862</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>Predators MMA and BJJ Academy Manchester</t>
+        </is>
+      </c>
+      <c r="C863" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="D863" t="inlineStr"/>
+      <c r="E863" t="inlineStr"/>
+      <c r="F863" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G863" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H863" t="inlineStr">
+        <is>
+          <t>447897313488</t>
+        </is>
+      </c>
+      <c r="I863" t="inlineStr"/>
+      <c r="J863" t="inlineStr">
+        <is>
+          <t>predatorsmmagym@gmail.com</t>
+        </is>
+      </c>
+      <c r="K863" t="inlineStr">
+        <is>
+          <t>http://www.manchester-mma.com/</t>
+        </is>
+      </c>
+      <c r="L863" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M863" t="inlineStr"/>
+      <c r="N863" t="inlineStr"/>
+      <c r="O863" t="inlineStr"/>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>L863</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>Ip Man Wing Chun Kung Fu Manchester</t>
+        </is>
+      </c>
+      <c r="C864" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D864" t="inlineStr"/>
+      <c r="E864" t="inlineStr"/>
+      <c r="F864" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G864" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H864" t="inlineStr">
+        <is>
+          <t>447593913883</t>
+        </is>
+      </c>
+      <c r="I864" t="inlineStr"/>
+      <c r="J864" t="inlineStr"/>
+      <c r="K864" t="inlineStr">
+        <is>
+          <t>http://www.wingchunkuen.org/</t>
+        </is>
+      </c>
+      <c r="L864" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M864" t="inlineStr"/>
+      <c r="N864" t="inlineStr"/>
+      <c r="O864" t="inlineStr"/>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>L864</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>Advanced Basics MMA Gym Manchester</t>
+        </is>
+      </c>
+      <c r="C865" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D865" t="inlineStr"/>
+      <c r="E865" t="inlineStr"/>
+      <c r="F865" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G865" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H865" t="inlineStr">
+        <is>
+          <t>447856969170</t>
+        </is>
+      </c>
+      <c r="I865" t="inlineStr"/>
+      <c r="J865" t="inlineStr"/>
+      <c r="K865" t="inlineStr">
+        <is>
+          <t>http://www.advancedbasics.co.uk/</t>
+        </is>
+      </c>
+      <c r="L865" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M865" t="inlineStr"/>
+      <c r="N865" t="inlineStr"/>
+      <c r="O865" t="inlineStr"/>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>L865</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>Henshall Brazilian jiu jitsu</t>
+        </is>
+      </c>
+      <c r="C866" t="inlineStr">
+        <is>
+          <t>Martial arts club</t>
+        </is>
+      </c>
+      <c r="D866" t="inlineStr"/>
+      <c r="E866" t="inlineStr"/>
+      <c r="F866" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G866" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H866" t="inlineStr">
+        <is>
+          <t>447475938425</t>
+        </is>
+      </c>
+      <c r="I866" t="inlineStr"/>
+      <c r="J866" t="inlineStr"/>
+      <c r="K866" t="inlineStr">
+        <is>
+          <t>http://www.manchesterbrazilianjiujitsu.co.uk/</t>
+        </is>
+      </c>
+      <c r="L866" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M866" t="inlineStr"/>
+      <c r="N866" t="inlineStr"/>
+      <c r="O866" t="inlineStr"/>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>L866</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>Mo's Martial Arts Centre</t>
+        </is>
+      </c>
+      <c r="C867" t="inlineStr">
+        <is>
+          <t>Martial arts club</t>
+        </is>
+      </c>
+      <c r="D867" t="inlineStr"/>
+      <c r="E867" t="inlineStr"/>
+      <c r="F867" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G867" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H867" t="inlineStr">
+        <is>
+          <t>447811575614</t>
+        </is>
+      </c>
+      <c r="I867" t="inlineStr"/>
+      <c r="J867" t="inlineStr"/>
+      <c r="K867" t="inlineStr"/>
+      <c r="L867" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M867" t="inlineStr"/>
+      <c r="N867" t="inlineStr"/>
+      <c r="O867" t="inlineStr"/>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>L867</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>North Manchester Family Martial Arts Centre (Prestwich)</t>
+        </is>
+      </c>
+      <c r="C868" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D868" t="inlineStr"/>
+      <c r="E868" t="inlineStr"/>
+      <c r="F868" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G868" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H868" t="inlineStr">
+        <is>
+          <t>447811006469</t>
+        </is>
+      </c>
+      <c r="I868" t="inlineStr"/>
+      <c r="J868" t="inlineStr">
+        <is>
+          <t>fmacnorthmanchester@gmail.com</t>
+        </is>
+      </c>
+      <c r="K868" t="inlineStr">
+        <is>
+          <t>http://www.northmanchesterfamilymartialarts.co.uk/</t>
+        </is>
+      </c>
+      <c r="L868" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M868" t="inlineStr"/>
+      <c r="N868" t="inlineStr"/>
+      <c r="O868" t="inlineStr"/>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>L868</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>STRETFORD MARTIAL ARTS</t>
+        </is>
+      </c>
+      <c r="C869" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D869" t="inlineStr"/>
+      <c r="E869" t="inlineStr"/>
+      <c r="F869" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G869" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H869" t="inlineStr">
+        <is>
+          <t>447591214756</t>
+        </is>
+      </c>
+      <c r="I869" t="inlineStr"/>
+      <c r="J869" t="inlineStr">
+        <is>
+          <t>stretfordmartialarts@gmail.com</t>
+        </is>
+      </c>
+      <c r="K869" t="inlineStr">
+        <is>
+          <t>http://www.stretfordmartialarts.com/</t>
+        </is>
+      </c>
+      <c r="L869" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M869" t="inlineStr"/>
+      <c r="N869" t="inlineStr"/>
+      <c r="O869" t="inlineStr"/>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>L869</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>Krav Maga Manchester FEKM</t>
+        </is>
+      </c>
+      <c r="C870" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D870" t="inlineStr"/>
+      <c r="E870" t="inlineStr"/>
+      <c r="F870" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G870" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H870" t="inlineStr">
+        <is>
+          <t>447519038169</t>
+        </is>
+      </c>
+      <c r="I870" t="inlineStr"/>
+      <c r="J870" t="inlineStr"/>
+      <c r="K870" t="inlineStr">
+        <is>
+          <t>http://www.manchester-kravmaga.com/</t>
+        </is>
+      </c>
+      <c r="L870" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M870" t="inlineStr"/>
+      <c r="N870" t="inlineStr"/>
+      <c r="O870" t="inlineStr"/>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>L870</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>Franks Team Sports Club - MMA - BOXING - BJJ - Fitness</t>
+        </is>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D871" t="inlineStr"/>
+      <c r="E871" t="inlineStr"/>
+      <c r="F871" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G871" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H871" t="inlineStr">
+        <is>
+          <t>447713499484</t>
+        </is>
+      </c>
+      <c r="I871" t="inlineStr"/>
+      <c r="J871" t="inlineStr"/>
+      <c r="K871" t="inlineStr">
+        <is>
+          <t>http://www.franksteam.co.uk/</t>
+        </is>
+      </c>
+      <c r="L871" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M871" t="inlineStr"/>
+      <c r="N871" t="inlineStr"/>
+      <c r="O871" t="inlineStr"/>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>L871</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>Manchester School of Arms Hema Club</t>
+        </is>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D872" t="inlineStr"/>
+      <c r="E872" t="inlineStr"/>
+      <c r="F872" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G872" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H872" t="inlineStr"/>
+      <c r="I872" t="inlineStr"/>
+      <c r="J872" t="inlineStr">
+        <is>
+          <t>manchesterschoolofarms@gmail.com</t>
+        </is>
+      </c>
+      <c r="K872" t="inlineStr">
+        <is>
+          <t>https://manchesterschoolofarms.com/</t>
+        </is>
+      </c>
+      <c r="L872" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M872" t="inlineStr"/>
+      <c r="N872" t="inlineStr"/>
+      <c r="O872" t="inlineStr"/>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>L872</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>Wayfarer Academy®</t>
+        </is>
+      </c>
+      <c r="C873" t="inlineStr">
+        <is>
+          <t>Martial arts club</t>
+        </is>
+      </c>
+      <c r="D873" t="inlineStr"/>
+      <c r="E873" t="inlineStr"/>
+      <c r="F873" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G873" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H873" t="inlineStr">
+        <is>
+          <t>447700148142</t>
+        </is>
+      </c>
+      <c r="I873" t="inlineStr"/>
+      <c r="J873" t="inlineStr"/>
+      <c r="K873" t="inlineStr">
+        <is>
+          <t>https://www.wayfareracademy.com/</t>
+        </is>
+      </c>
+      <c r="L873" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M873" t="inlineStr"/>
+      <c r="N873" t="inlineStr"/>
+      <c r="O873" t="inlineStr"/>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>L873</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>Mantkd Taekwondo Academy</t>
+        </is>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>Taekwondo school</t>
+        </is>
+      </c>
+      <c r="D874" t="inlineStr"/>
+      <c r="E874" t="inlineStr"/>
+      <c r="F874" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G874" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H874" t="inlineStr">
+        <is>
+          <t>447946650820</t>
+        </is>
+      </c>
+      <c r="I874" t="inlineStr"/>
+      <c r="J874" t="inlineStr">
+        <is>
+          <t>info@mantkd.co.uk</t>
+        </is>
+      </c>
+      <c r="K874" t="inlineStr">
+        <is>
+          <t>http://www.mantkd.co.uk/</t>
+        </is>
+      </c>
+      <c r="L874" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M874" t="inlineStr"/>
+      <c r="N874" t="inlineStr"/>
+      <c r="O874" t="inlineStr"/>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>L874</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>Salford Mixed Martial Arts</t>
+        </is>
+      </c>
+      <c r="C875" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D875" t="inlineStr"/>
+      <c r="E875" t="inlineStr"/>
+      <c r="F875" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G875" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H875" t="inlineStr">
+        <is>
+          <t>441617430028</t>
+        </is>
+      </c>
+      <c r="I875" t="inlineStr"/>
+      <c r="J875" t="inlineStr"/>
+      <c r="K875" t="inlineStr">
+        <is>
+          <t>http://www.salfordmma.com/</t>
+        </is>
+      </c>
+      <c r="L875" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M875" t="inlineStr"/>
+      <c r="N875" t="inlineStr"/>
+      <c r="O875" t="inlineStr"/>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>L875</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>Chi mo martial art Centre</t>
+        </is>
+      </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D876" t="inlineStr"/>
+      <c r="E876" t="inlineStr"/>
+      <c r="F876" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G876" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H876" t="inlineStr">
+        <is>
+          <t>447847888828</t>
+        </is>
+      </c>
+      <c r="I876" t="inlineStr"/>
+      <c r="J876" t="inlineStr"/>
+      <c r="K876" t="inlineStr">
+        <is>
+          <t>https://m.facebook.com/chimokungfu/</t>
+        </is>
+      </c>
+      <c r="L876" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M876" t="inlineStr"/>
+      <c r="N876" t="inlineStr"/>
+      <c r="O876" t="inlineStr"/>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>L876</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>AK Academy of Martial Arts</t>
+        </is>
+      </c>
+      <c r="C877" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D877" t="inlineStr"/>
+      <c r="E877" t="inlineStr"/>
+      <c r="F877" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G877" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H877" t="inlineStr">
+        <is>
+          <t>447932592556</t>
+        </is>
+      </c>
+      <c r="I877" t="inlineStr"/>
+      <c r="J877" t="inlineStr"/>
+      <c r="K877" t="inlineStr">
+        <is>
+          <t>https://akacademyofmartialarts.com/</t>
+        </is>
+      </c>
+      <c r="L877" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M877" t="inlineStr"/>
+      <c r="N877" t="inlineStr"/>
+      <c r="O877" t="inlineStr"/>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>L877</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>Manchester Taekwondo Warriors</t>
+        </is>
+      </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>Taekwondo school</t>
+        </is>
+      </c>
+      <c r="D878" t="inlineStr"/>
+      <c r="E878" t="inlineStr"/>
+      <c r="F878" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G878" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H878" t="inlineStr"/>
+      <c r="I878" t="inlineStr"/>
+      <c r="J878" t="inlineStr"/>
+      <c r="K878" t="inlineStr">
+        <is>
+          <t>http://manchestertaekwondo.com/</t>
+        </is>
+      </c>
+      <c r="L878" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M878" t="inlineStr"/>
+      <c r="N878" t="inlineStr"/>
+      <c r="O878" t="inlineStr"/>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>L878</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>Master A Muay Thai</t>
+        </is>
+      </c>
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>Muay Thai boxing gym</t>
+        </is>
+      </c>
+      <c r="D879" t="inlineStr"/>
+      <c r="E879" t="inlineStr"/>
+      <c r="F879" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G879" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H879" t="inlineStr">
+        <is>
+          <t>447791040637</t>
+        </is>
+      </c>
+      <c r="I879" t="inlineStr"/>
+      <c r="J879" t="inlineStr"/>
+      <c r="K879" t="inlineStr">
+        <is>
+          <t>http://www.masteramuaythaipro.com/</t>
+        </is>
+      </c>
+      <c r="L879" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M879" t="inlineStr"/>
+      <c r="N879" t="inlineStr"/>
+      <c r="O879" t="inlineStr"/>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>L879</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>Roger Gracie BJJ Academy Salford in Manchester</t>
+        </is>
+      </c>
+      <c r="C880" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D880" t="inlineStr"/>
+      <c r="E880" t="inlineStr"/>
+      <c r="F880" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G880" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H880" t="inlineStr">
+        <is>
+          <t>447506746662</t>
+        </is>
+      </c>
+      <c r="I880" t="inlineStr"/>
+      <c r="J880" t="inlineStr">
+        <is>
+          <t>info@rgasalford.co.uk</t>
+        </is>
+      </c>
+      <c r="K880" t="inlineStr">
+        <is>
+          <t>https://rgasalford.co.uk/?utm_source=google&amp;utm_medium=organ</t>
+        </is>
+      </c>
+      <c r="L880" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M880" t="inlineStr"/>
+      <c r="N880" t="inlineStr"/>
+      <c r="O880" t="inlineStr"/>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>L880</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>AP TAEKWONDO ACADEMY - Gorton</t>
+        </is>
+      </c>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>Martial arts club</t>
+        </is>
+      </c>
+      <c r="D881" t="inlineStr"/>
+      <c r="E881" t="inlineStr"/>
+      <c r="F881" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G881" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H881" t="inlineStr">
+        <is>
+          <t>447743991146</t>
+        </is>
+      </c>
+      <c r="I881" t="inlineStr"/>
+      <c r="J881" t="inlineStr"/>
+      <c r="K881" t="inlineStr">
+        <is>
+          <t>http://www.aptaekwondoacademy.co.uk/</t>
+        </is>
+      </c>
+      <c r="L881" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M881" t="inlineStr"/>
+      <c r="N881" t="inlineStr"/>
+      <c r="O881" t="inlineStr"/>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>L881</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>Chorlton Jujitsu (The Ikiyōyō Dojo)</t>
+        </is>
+      </c>
+      <c r="C882" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D882" t="inlineStr"/>
+      <c r="E882" t="inlineStr"/>
+      <c r="F882" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G882" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H882" t="inlineStr"/>
+      <c r="I882" t="inlineStr"/>
+      <c r="J882" t="inlineStr"/>
+      <c r="K882" t="inlineStr">
+        <is>
+          <t>http://www.chorltonjujitsu.org.uk/</t>
+        </is>
+      </c>
+      <c r="L882" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M882" t="inlineStr"/>
+      <c r="N882" t="inlineStr"/>
+      <c r="O882" t="inlineStr"/>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>L882</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>MMU Jiu Jitsu</t>
+        </is>
+      </c>
+      <c r="C883" t="inlineStr">
+        <is>
+          <t>Jujitsu school</t>
+        </is>
+      </c>
+      <c r="D883" t="inlineStr"/>
+      <c r="E883" t="inlineStr"/>
+      <c r="F883" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G883" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H883" t="inlineStr">
+        <is>
+          <t>441612476447</t>
+        </is>
+      </c>
+      <c r="I883" t="inlineStr"/>
+      <c r="J883" t="inlineStr"/>
+      <c r="K883" t="inlineStr">
+        <is>
+          <t>https://www.mmu.ac.uk/sport/find-a-sport/jiu-jitsu</t>
+        </is>
+      </c>
+      <c r="L883" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M883" t="inlineStr"/>
+      <c r="N883" t="inlineStr"/>
+      <c r="O883" t="inlineStr"/>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>L883</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>Bee-Safe Manchester</t>
+        </is>
+      </c>
+      <c r="C884" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D884" t="inlineStr"/>
+      <c r="E884" t="inlineStr"/>
+      <c r="F884" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G884" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H884" t="inlineStr">
+        <is>
+          <t>447525441949</t>
+        </is>
+      </c>
+      <c r="I884" t="inlineStr"/>
+      <c r="J884" t="inlineStr">
+        <is>
+          <t>beesafemanchester@gmail.com</t>
+        </is>
+      </c>
+      <c r="K884" t="inlineStr">
+        <is>
+          <t>http://www.beesafemanchester.co.uk/</t>
+        </is>
+      </c>
+      <c r="L884" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M884" t="inlineStr"/>
+      <c r="N884" t="inlineStr"/>
+      <c r="O884" t="inlineStr"/>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>L884</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>Red Tiger Karate - Old Trafford</t>
+        </is>
+      </c>
+      <c r="C885" t="inlineStr">
+        <is>
+          <t>Karate club</t>
+        </is>
+      </c>
+      <c r="D885" t="inlineStr"/>
+      <c r="E885" t="inlineStr"/>
+      <c r="F885" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G885" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H885" t="inlineStr">
+        <is>
+          <t>447825446825</t>
+        </is>
+      </c>
+      <c r="I885" t="inlineStr"/>
+      <c r="J885" t="inlineStr">
+        <is>
+          <t>info@redtigerkarateclub.co.uk</t>
+        </is>
+      </c>
+      <c r="K885" t="inlineStr">
+        <is>
+          <t>https://www.redtigerkarateclub.co.uk/classes/old-trafford?ut</t>
+        </is>
+      </c>
+      <c r="L885" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M885" t="inlineStr"/>
+      <c r="N885" t="inlineStr"/>
+      <c r="O885" t="inlineStr"/>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>L885</t>
+        </is>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>Temple Kickboxing Didsbury</t>
+        </is>
+      </c>
+      <c r="C886" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D886" t="inlineStr"/>
+      <c r="E886" t="inlineStr"/>
+      <c r="F886" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G886" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H886" t="inlineStr">
+        <is>
+          <t>447838355221</t>
+        </is>
+      </c>
+      <c r="I886" t="inlineStr"/>
+      <c r="J886" t="inlineStr"/>
+      <c r="K886" t="inlineStr">
+        <is>
+          <t>https://clubs.templemanchester.co.uk/didsbury</t>
+        </is>
+      </c>
+      <c r="L886" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M886" t="inlineStr"/>
+      <c r="N886" t="inlineStr"/>
+      <c r="O886" t="inlineStr"/>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>L886</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>Stealth BJJ - Manchester Brazilian Jiu Jitsu</t>
+        </is>
+      </c>
+      <c r="C887" t="inlineStr">
+        <is>
+          <t>Jujitsu school</t>
+        </is>
+      </c>
+      <c r="D887" t="inlineStr"/>
+      <c r="E887" t="inlineStr"/>
+      <c r="F887" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G887" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H887" t="inlineStr">
+        <is>
+          <t>447903644928</t>
+        </is>
+      </c>
+      <c r="I887" t="inlineStr"/>
+      <c r="J887" t="inlineStr">
+        <is>
+          <t>info@stealthbjj.com</t>
+        </is>
+      </c>
+      <c r="K887" t="inlineStr">
+        <is>
+          <t>http://www.stealthbjj.com/</t>
+        </is>
+      </c>
+      <c r="L887" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M887" t="inlineStr"/>
+      <c r="N887" t="inlineStr"/>
+      <c r="O887" t="inlineStr"/>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>L887</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>Shaolin Kung Fu - Manchester South Central</t>
+        </is>
+      </c>
+      <c r="C888" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D888" t="inlineStr"/>
+      <c r="E888" t="inlineStr"/>
+      <c r="F888" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G888" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H888" t="inlineStr"/>
+      <c r="I888" t="inlineStr"/>
+      <c r="J888" t="inlineStr">
+        <is>
+          <t>enquiries@shahrokh.org</t>
+        </is>
+      </c>
+      <c r="K888" t="inlineStr">
+        <is>
+          <t>http://www.shahrokh.org/</t>
+        </is>
+      </c>
+      <c r="L888" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M888" t="inlineStr"/>
+      <c r="N888" t="inlineStr"/>
+      <c r="O888" t="inlineStr"/>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>L888</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>J M Taekwondo</t>
+        </is>
+      </c>
+      <c r="C889" t="inlineStr">
+        <is>
+          <t>Taekwondo school</t>
+        </is>
+      </c>
+      <c r="D889" t="inlineStr"/>
+      <c r="E889" t="inlineStr"/>
+      <c r="F889" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G889" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H889" t="inlineStr">
+        <is>
+          <t>447738497319</t>
+        </is>
+      </c>
+      <c r="I889" t="inlineStr"/>
+      <c r="J889" t="inlineStr">
+        <is>
+          <t>matt@pixelspread.com</t>
+        </is>
+      </c>
+      <c r="K889" t="inlineStr">
+        <is>
+          <t>https://jm-taekwondo.co.uk/</t>
+        </is>
+      </c>
+      <c r="L889" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M889" t="inlineStr"/>
+      <c r="N889" t="inlineStr"/>
+      <c r="O889" t="inlineStr"/>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>L889</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>Sharman Taekwon-Do</t>
+        </is>
+      </c>
+      <c r="C890" t="inlineStr">
+        <is>
+          <t>Taekwondo school</t>
+        </is>
+      </c>
+      <c r="D890" t="inlineStr"/>
+      <c r="E890" t="inlineStr"/>
+      <c r="F890" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G890" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H890" t="inlineStr">
+        <is>
+          <t>447511767186</t>
+        </is>
+      </c>
+      <c r="I890" t="inlineStr"/>
+      <c r="J890" t="inlineStr">
+        <is>
+          <t>haohao.jiang+designer@strikingly.com</t>
+        </is>
+      </c>
+      <c r="K890" t="inlineStr">
+        <is>
+          <t>https://www.sharmantkd.org.uk/</t>
+        </is>
+      </c>
+      <c r="L890" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M890" t="inlineStr"/>
+      <c r="N890" t="inlineStr"/>
+      <c r="O890" t="inlineStr"/>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>L890</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>Manchester Aikido</t>
+        </is>
+      </c>
+      <c r="C891" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D891" t="inlineStr"/>
+      <c r="E891" t="inlineStr"/>
+      <c r="F891" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G891" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H891" t="inlineStr"/>
+      <c r="I891" t="inlineStr"/>
+      <c r="J891" t="inlineStr">
+        <is>
+          <t>manchesteraikido@gmail.com</t>
+        </is>
+      </c>
+      <c r="K891" t="inlineStr">
+        <is>
+          <t>http://www.manchesteraikido.com/</t>
+        </is>
+      </c>
+      <c r="L891" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M891" t="inlineStr"/>
+      <c r="N891" t="inlineStr"/>
+      <c r="O891" t="inlineStr"/>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>L891</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>Tai Chi Kung Fu Centre</t>
+        </is>
+      </c>
+      <c r="C892" t="inlineStr">
+        <is>
+          <t>Tai chi school</t>
+        </is>
+      </c>
+      <c r="D892" t="inlineStr"/>
+      <c r="E892" t="inlineStr"/>
+      <c r="F892" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G892" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H892" t="inlineStr">
+        <is>
+          <t>447765922725</t>
+        </is>
+      </c>
+      <c r="I892" t="inlineStr"/>
+      <c r="J892" t="inlineStr">
+        <is>
+          <t>tckfc.info@gmail.com</t>
+        </is>
+      </c>
+      <c r="K892" t="inlineStr">
+        <is>
+          <t>http://www.taichikungfucentre.com/</t>
+        </is>
+      </c>
+      <c r="L892" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M892" t="inlineStr"/>
+      <c r="N892" t="inlineStr"/>
+      <c r="O892" t="inlineStr"/>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>L892</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>Lishi Tai Chi Classes in Manchester</t>
+        </is>
+      </c>
+      <c r="C893" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D893" t="inlineStr"/>
+      <c r="E893" t="inlineStr"/>
+      <c r="F893" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G893" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H893" t="inlineStr">
+        <is>
+          <t>447761882289</t>
+        </is>
+      </c>
+      <c r="I893" t="inlineStr"/>
+      <c r="J893" t="inlineStr"/>
+      <c r="K893" t="inlineStr">
+        <is>
+          <t>http://www.lishi.org/manchester</t>
+        </is>
+      </c>
+      <c r="L893" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M893" t="inlineStr"/>
+      <c r="N893" t="inlineStr"/>
+      <c r="O893" t="inlineStr"/>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>L893</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>British Taekwondo</t>
+        </is>
+      </c>
+      <c r="C894" t="inlineStr">
+        <is>
+          <t>Taekwondo school</t>
+        </is>
+      </c>
+      <c r="D894" t="inlineStr"/>
+      <c r="E894" t="inlineStr"/>
+      <c r="F894" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G894" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H894" t="inlineStr">
+        <is>
+          <t>441616975330</t>
+        </is>
+      </c>
+      <c r="I894" t="inlineStr"/>
+      <c r="J894" t="inlineStr">
+        <is>
+          <t>membership.services@britishtaekwondo.org</t>
+        </is>
+      </c>
+      <c r="K894" t="inlineStr">
+        <is>
+          <t>https://www.britishtaekwondo.org.uk/</t>
+        </is>
+      </c>
+      <c r="L894" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M894" t="inlineStr"/>
+      <c r="N894" t="inlineStr"/>
+      <c r="O894" t="inlineStr"/>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>L894</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>Salford Martial Arts</t>
+        </is>
+      </c>
+      <c r="C895" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D895" t="inlineStr"/>
+      <c r="E895" t="inlineStr"/>
+      <c r="F895" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G895" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H895" t="inlineStr">
+        <is>
+          <t>447799424337</t>
+        </is>
+      </c>
+      <c r="I895" t="inlineStr"/>
+      <c r="J895" t="inlineStr"/>
+      <c r="K895" t="inlineStr">
+        <is>
+          <t>https://salfordmartialarts.co.uk/</t>
+        </is>
+      </c>
+      <c r="L895" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M895" t="inlineStr"/>
+      <c r="N895" t="inlineStr"/>
+      <c r="O895" t="inlineStr"/>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>L895</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>Jason Baird's Black Belt Academy</t>
+        </is>
+      </c>
+      <c r="C896" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D896" t="inlineStr"/>
+      <c r="E896" t="inlineStr"/>
+      <c r="F896" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G896" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H896" t="inlineStr">
+        <is>
+          <t>447949066244</t>
+        </is>
+      </c>
+      <c r="I896" t="inlineStr"/>
+      <c r="J896" t="inlineStr"/>
+      <c r="K896" t="inlineStr">
+        <is>
+          <t>http://www.kickboxwithus.co.uk/</t>
+        </is>
+      </c>
+      <c r="L896" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M896" t="inlineStr"/>
+      <c r="N896" t="inlineStr"/>
+      <c r="O896" t="inlineStr"/>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>L896</t>
+        </is>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>Trident Taekwon-Do Academy</t>
+        </is>
+      </c>
+      <c r="C897" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D897" t="inlineStr"/>
+      <c r="E897" t="inlineStr"/>
+      <c r="F897" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G897" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H897" t="inlineStr">
+        <is>
+          <t>447974649015</t>
+        </is>
+      </c>
+      <c r="I897" t="inlineStr"/>
+      <c r="J897" t="inlineStr">
+        <is>
+          <t>hello@tridenttkdmanchester.co.uk</t>
+        </is>
+      </c>
+      <c r="K897" t="inlineStr">
+        <is>
+          <t>http://www.tridenttkdmanchester.co.uk/</t>
+        </is>
+      </c>
+      <c r="L897" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M897" t="inlineStr"/>
+      <c r="N897" t="inlineStr"/>
+      <c r="O897" t="inlineStr"/>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>L897</t>
+        </is>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>Openshaw Shukokai Karate Club. East Manchester Leisure Centr</t>
+        </is>
+      </c>
+      <c r="C898" t="inlineStr">
+        <is>
+          <t>Karate club</t>
+        </is>
+      </c>
+      <c r="D898" t="inlineStr"/>
+      <c r="E898" t="inlineStr"/>
+      <c r="F898" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G898" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H898" t="inlineStr">
+        <is>
+          <t>447799827017</t>
+        </is>
+      </c>
+      <c r="I898" t="inlineStr"/>
+      <c r="J898" t="inlineStr"/>
+      <c r="K898" t="inlineStr">
+        <is>
+          <t>http://openshaw-shukokai.co.uk/</t>
+        </is>
+      </c>
+      <c r="L898" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M898" t="inlineStr"/>
+      <c r="N898" t="inlineStr"/>
+      <c r="O898" t="inlineStr"/>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>L898</t>
+        </is>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>Cobra Martial Arts Association</t>
+        </is>
+      </c>
+      <c r="C899" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D899" t="inlineStr"/>
+      <c r="E899" t="inlineStr"/>
+      <c r="F899" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G899" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H899" t="inlineStr">
+        <is>
+          <t>447909673894</t>
+        </is>
+      </c>
+      <c r="I899" t="inlineStr"/>
+      <c r="J899" t="inlineStr">
+        <is>
+          <t>cmaauk@hotmail.com</t>
+        </is>
+      </c>
+      <c r="K899" t="inlineStr">
+        <is>
+          <t>http://www.cmaauk.com/</t>
+        </is>
+      </c>
+      <c r="L899" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M899" t="inlineStr"/>
+      <c r="N899" t="inlineStr"/>
+      <c r="O899" t="inlineStr"/>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>L899</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>Family Martial Arts Centres - Urmston</t>
+        </is>
+      </c>
+      <c r="C900" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D900" t="inlineStr"/>
+      <c r="E900" t="inlineStr"/>
+      <c r="F900" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G900" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H900" t="inlineStr">
+        <is>
+          <t>447801498677</t>
+        </is>
+      </c>
+      <c r="I900" t="inlineStr"/>
+      <c r="J900" t="inlineStr">
+        <is>
+          <t>urmstonfmac@outlook.com</t>
+        </is>
+      </c>
+      <c r="K900" t="inlineStr">
+        <is>
+          <t>https://www.familymartialartscentres.com/our-centres/urmston</t>
+        </is>
+      </c>
+      <c r="L900" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M900" t="inlineStr"/>
+      <c r="N900" t="inlineStr"/>
+      <c r="O900" t="inlineStr"/>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>L900</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>Valour JiuJitsu Manchester</t>
+        </is>
+      </c>
+      <c r="C901" t="inlineStr">
+        <is>
+          <t>Sports school</t>
+        </is>
+      </c>
+      <c r="D901" t="inlineStr"/>
+      <c r="E901" t="inlineStr"/>
+      <c r="F901" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G901" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H901" t="inlineStr">
+        <is>
+          <t>447843304308</t>
+        </is>
+      </c>
+      <c r="I901" t="inlineStr"/>
+      <c r="J901" t="inlineStr">
+        <is>
+          <t>valourbjj@proton.me</t>
+        </is>
+      </c>
+      <c r="K901" t="inlineStr">
+        <is>
+          <t>https://valourjiujitsumanchester.co.uk/</t>
+        </is>
+      </c>
+      <c r="L901" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M901" t="inlineStr"/>
+      <c r="N901" t="inlineStr"/>
+      <c r="O901" t="inlineStr"/>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>L901</t>
+        </is>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>Family Martial Arts Centres Swinton</t>
+        </is>
+      </c>
+      <c r="C902" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D902" t="inlineStr"/>
+      <c r="E902" t="inlineStr"/>
+      <c r="F902" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G902" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H902" t="inlineStr">
+        <is>
+          <t>441617284449</t>
+        </is>
+      </c>
+      <c r="I902" t="inlineStr"/>
+      <c r="J902" t="inlineStr">
+        <is>
+          <t>info@familymartialartscentres.com</t>
+        </is>
+      </c>
+      <c r="K902" t="inlineStr">
+        <is>
+          <t>http://www.familymartialartscentres.com/</t>
+        </is>
+      </c>
+      <c r="L902" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M902" t="inlineStr"/>
+      <c r="N902" t="inlineStr"/>
+      <c r="O902" t="inlineStr"/>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>L902</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>Family Karate Clubs</t>
+        </is>
+      </c>
+      <c r="C903" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D903" t="inlineStr"/>
+      <c r="E903" t="inlineStr"/>
+      <c r="F903" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G903" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H903" t="inlineStr"/>
+      <c r="I903" t="inlineStr"/>
+      <c r="J903" t="inlineStr"/>
+      <c r="K903" t="inlineStr">
+        <is>
+          <t>http://www.familykarateclubs.co.uk/</t>
+        </is>
+      </c>
+      <c r="L903" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M903" t="inlineStr"/>
+      <c r="N903" t="inlineStr"/>
+      <c r="O903" t="inlineStr"/>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>L903</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>Athena Muay Thai</t>
+        </is>
+      </c>
+      <c r="C904" t="inlineStr">
+        <is>
+          <t>Muay Thai boxing gym</t>
+        </is>
+      </c>
+      <c r="D904" t="inlineStr"/>
+      <c r="E904" t="inlineStr"/>
+      <c r="F904" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G904" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H904" t="inlineStr">
+        <is>
+          <t>447930511659</t>
+        </is>
+      </c>
+      <c r="I904" t="inlineStr"/>
+      <c r="J904" t="inlineStr">
+        <is>
+          <t>athenamtb@gmail.com</t>
+        </is>
+      </c>
+      <c r="K904" t="inlineStr">
+        <is>
+          <t>https://athenamuaythai.com/</t>
+        </is>
+      </c>
+      <c r="L904" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M904" t="inlineStr"/>
+      <c r="N904" t="inlineStr"/>
+      <c r="O904" t="inlineStr"/>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>L904</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>Gym 72</t>
+        </is>
+      </c>
+      <c r="C905" t="inlineStr">
+        <is>
+          <t>Personal trainer</t>
+        </is>
+      </c>
+      <c r="D905" t="inlineStr"/>
+      <c r="E905" t="inlineStr"/>
+      <c r="F905" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G905" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H905" t="inlineStr">
+        <is>
+          <t>441612360686</t>
+        </is>
+      </c>
+      <c r="I905" t="inlineStr"/>
+      <c r="J905" t="inlineStr">
+        <is>
+          <t>info@gym72.co.uk</t>
+        </is>
+      </c>
+      <c r="K905" t="inlineStr">
+        <is>
+          <t>http://www.gym72.co.uk/</t>
+        </is>
+      </c>
+      <c r="L905" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M905" t="inlineStr"/>
+      <c r="N905" t="inlineStr"/>
+      <c r="O905" t="inlineStr"/>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>L905</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>Fight Factory Manchester</t>
+        </is>
+      </c>
+      <c r="C906" t="inlineStr">
+        <is>
+          <t>Boxing gym</t>
+        </is>
+      </c>
+      <c r="D906" t="inlineStr"/>
+      <c r="E906" t="inlineStr"/>
+      <c r="F906" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G906" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H906" t="inlineStr">
+        <is>
+          <t>447746661931</t>
+        </is>
+      </c>
+      <c r="I906" t="inlineStr"/>
+      <c r="J906" t="inlineStr">
+        <is>
+          <t>your@email.com</t>
+        </is>
+      </c>
+      <c r="K906" t="inlineStr">
+        <is>
+          <t>https://fightfactorymanchester.com/</t>
+        </is>
+      </c>
+      <c r="L906" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M906" t="inlineStr"/>
+      <c r="N906" t="inlineStr"/>
+      <c r="O906" t="inlineStr"/>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>L906</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>GZ Boxing Academy</t>
+        </is>
+      </c>
+      <c r="C907" t="inlineStr">
+        <is>
+          <t>Boxing club</t>
+        </is>
+      </c>
+      <c r="D907" t="inlineStr"/>
+      <c r="E907" t="inlineStr"/>
+      <c r="F907" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G907" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H907" t="inlineStr">
+        <is>
+          <t>447776437440</t>
+        </is>
+      </c>
+      <c r="I907" t="inlineStr"/>
+      <c r="J907" t="inlineStr"/>
+      <c r="K907" t="inlineStr"/>
+      <c r="L907" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M907" t="inlineStr"/>
+      <c r="N907" t="inlineStr"/>
+      <c r="O907" t="inlineStr"/>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>L907</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>Moss Side Boxing &amp; Athletics Association</t>
+        </is>
+      </c>
+      <c r="C908" t="inlineStr">
+        <is>
+          <t>Boxing gym</t>
+        </is>
+      </c>
+      <c r="D908" t="inlineStr"/>
+      <c r="E908" t="inlineStr"/>
+      <c r="F908" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G908" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H908" t="inlineStr">
+        <is>
+          <t>441612278708</t>
+        </is>
+      </c>
+      <c r="I908" t="inlineStr"/>
+      <c r="J908" t="inlineStr"/>
+      <c r="K908" t="inlineStr">
+        <is>
+          <t>http://www.mosssideboxing.co.uk/</t>
+        </is>
+      </c>
+      <c r="L908" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M908" t="inlineStr"/>
+      <c r="N908" t="inlineStr"/>
+      <c r="O908" t="inlineStr"/>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>L908</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>ST JOHN'S AMATEUR BOXING CLUB</t>
+        </is>
+      </c>
+      <c r="C909" t="inlineStr">
+        <is>
+          <t>Boxing club</t>
+        </is>
+      </c>
+      <c r="D909" t="inlineStr"/>
+      <c r="E909" t="inlineStr"/>
+      <c r="F909" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G909" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H909" t="inlineStr"/>
+      <c r="I909" t="inlineStr"/>
+      <c r="J909" t="inlineStr">
+        <is>
+          <t>andyjohnrea@gmail.com</t>
+        </is>
+      </c>
+      <c r="K909" t="inlineStr">
+        <is>
+          <t>http://www.chorltonboxing.com/</t>
+        </is>
+      </c>
+      <c r="L909" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M909" t="inlineStr"/>
+      <c r="N909" t="inlineStr"/>
+      <c r="O909" t="inlineStr"/>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>L909</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>Arnies Boxing Gym</t>
+        </is>
+      </c>
+      <c r="C910" t="inlineStr">
+        <is>
+          <t>Boxing gym</t>
+        </is>
+      </c>
+      <c r="D910" t="inlineStr"/>
+      <c r="E910" t="inlineStr"/>
+      <c r="F910" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G910" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H910" t="inlineStr">
+        <is>
+          <t>447951246860</t>
+        </is>
+      </c>
+      <c r="I910" t="inlineStr"/>
+      <c r="J910" t="inlineStr"/>
+      <c r="K910" t="inlineStr">
+        <is>
+          <t>https://arniesboxinggym.com/</t>
+        </is>
+      </c>
+      <c r="L910" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M910" t="inlineStr"/>
+      <c r="N910" t="inlineStr"/>
+      <c r="O910" t="inlineStr"/>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>L910</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>Fit2Fight</t>
+        </is>
+      </c>
+      <c r="C911" t="inlineStr">
+        <is>
+          <t>Boxing club</t>
+        </is>
+      </c>
+      <c r="D911" t="inlineStr"/>
+      <c r="E911" t="inlineStr"/>
+      <c r="F911" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G911" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H911" t="inlineStr">
+        <is>
+          <t>443300888974</t>
+        </is>
+      </c>
+      <c r="I911" t="inlineStr"/>
+      <c r="J911" t="inlineStr">
+        <is>
+          <t>info@fit2fightgym.co.uk</t>
+        </is>
+      </c>
+      <c r="K911" t="inlineStr">
+        <is>
+          <t>https://fit2fightgym.co.uk/</t>
+        </is>
+      </c>
+      <c r="L911" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M911" t="inlineStr"/>
+      <c r="N911" t="inlineStr"/>
+      <c r="O911" t="inlineStr"/>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>L911</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>Collyhurst and Moston Lads Club</t>
+        </is>
+      </c>
+      <c r="C912" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="D912" t="inlineStr"/>
+      <c r="E912" t="inlineStr"/>
+      <c r="F912" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G912" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H912" t="inlineStr">
+        <is>
+          <t>441616835046</t>
+        </is>
+      </c>
+      <c r="I912" t="inlineStr"/>
+      <c r="J912" t="inlineStr"/>
+      <c r="K912" t="inlineStr"/>
+      <c r="L912" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M912" t="inlineStr"/>
+      <c r="N912" t="inlineStr"/>
+      <c r="O912" t="inlineStr"/>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>L912</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>Collyhurst and Moston ABC</t>
+        </is>
+      </c>
+      <c r="C913" t="inlineStr">
+        <is>
+          <t>Boxing club</t>
+        </is>
+      </c>
+      <c r="D913" t="inlineStr"/>
+      <c r="E913" t="inlineStr"/>
+      <c r="F913" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G913" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H913" t="inlineStr">
+        <is>
+          <t>447832983843</t>
+        </is>
+      </c>
+      <c r="I913" t="inlineStr"/>
+      <c r="J913" t="inlineStr"/>
+      <c r="K913" t="inlineStr">
+        <is>
+          <t>https://www.collyhurstandmostonboxing.co.uk/</t>
+        </is>
+      </c>
+      <c r="L913" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M913" t="inlineStr"/>
+      <c r="N913" t="inlineStr"/>
+      <c r="O913" t="inlineStr"/>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>L913</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>Paulino’s Boxing</t>
+        </is>
+      </c>
+      <c r="C914" t="inlineStr">
+        <is>
+          <t>Boxing gym</t>
+        </is>
+      </c>
+      <c r="D914" t="inlineStr"/>
+      <c r="E914" t="inlineStr"/>
+      <c r="F914" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G914" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H914" t="inlineStr">
+        <is>
+          <t>447510947761</t>
+        </is>
+      </c>
+      <c r="I914" t="inlineStr"/>
+      <c r="J914" t="inlineStr"/>
+      <c r="K914" t="inlineStr">
+        <is>
+          <t>http://paulinosboxing.com/</t>
+        </is>
+      </c>
+      <c r="L914" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M914" t="inlineStr"/>
+      <c r="N914" t="inlineStr"/>
+      <c r="O914" t="inlineStr"/>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>L914</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>FRANK'S</t>
+        </is>
+      </c>
+      <c r="C915" t="inlineStr">
+        <is>
+          <t>Fitness center</t>
+        </is>
+      </c>
+      <c r="D915" t="inlineStr"/>
+      <c r="E915" t="inlineStr"/>
+      <c r="F915" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G915" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H915" t="inlineStr">
+        <is>
+          <t>447467435330</t>
+        </is>
+      </c>
+      <c r="I915" t="inlineStr"/>
+      <c r="J915" t="inlineStr">
+        <is>
+          <t>frank@frankwellness.co.uk</t>
+        </is>
+      </c>
+      <c r="K915" t="inlineStr">
+        <is>
+          <t>https://franksflow.co.uk/</t>
+        </is>
+      </c>
+      <c r="L915" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M915" t="inlineStr"/>
+      <c r="N915" t="inlineStr"/>
+      <c r="O915" t="inlineStr"/>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>L915</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>Moss Side Fire Station Boxing Club</t>
+        </is>
+      </c>
+      <c r="C916" t="inlineStr">
+        <is>
+          <t>Boxing club</t>
+        </is>
+      </c>
+      <c r="D916" t="inlineStr"/>
+      <c r="E916" t="inlineStr"/>
+      <c r="F916" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G916" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H916" t="inlineStr">
+        <is>
+          <t>441616085215</t>
+        </is>
+      </c>
+      <c r="I916" t="inlineStr"/>
+      <c r="J916" t="inlineStr">
+        <is>
+          <t>mosssidefirestationboxingclub@gmail.com</t>
+        </is>
+      </c>
+      <c r="K916" t="inlineStr">
+        <is>
+          <t>https://www.mosssidefirebox.co.uk/</t>
+        </is>
+      </c>
+      <c r="L916" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M916" t="inlineStr"/>
+      <c r="N916" t="inlineStr"/>
+      <c r="O916" t="inlineStr"/>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>L916</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>OnPoint Boxing Club</t>
+        </is>
+      </c>
+      <c r="C917" t="inlineStr">
+        <is>
+          <t>Boxing gym</t>
+        </is>
+      </c>
+      <c r="D917" t="inlineStr"/>
+      <c r="E917" t="inlineStr"/>
+      <c r="F917" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G917" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H917" t="inlineStr">
+        <is>
+          <t>447944838529</t>
+        </is>
+      </c>
+      <c r="I917" t="inlineStr"/>
+      <c r="J917" t="inlineStr"/>
+      <c r="K917" t="inlineStr"/>
+      <c r="L917" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M917" t="inlineStr"/>
+      <c r="N917" t="inlineStr"/>
+      <c r="O917" t="inlineStr"/>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>L917</t>
+        </is>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>Oliver's Gym</t>
+        </is>
+      </c>
+      <c r="C918" t="inlineStr">
+        <is>
+          <t>Boxing gym</t>
+        </is>
+      </c>
+      <c r="D918" t="inlineStr"/>
+      <c r="E918" t="inlineStr"/>
+      <c r="F918" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G918" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H918" t="inlineStr">
+        <is>
+          <t>447757623229</t>
+        </is>
+      </c>
+      <c r="I918" t="inlineStr"/>
+      <c r="J918" t="inlineStr"/>
+      <c r="K918" t="inlineStr"/>
+      <c r="L918" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M918" t="inlineStr"/>
+      <c r="N918" t="inlineStr"/>
+      <c r="O918" t="inlineStr"/>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>L918</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>Manchester M31 Boxing Academy</t>
+        </is>
+      </c>
+      <c r="C919" t="inlineStr">
+        <is>
+          <t>Sports complex</t>
+        </is>
+      </c>
+      <c r="D919" t="inlineStr"/>
+      <c r="E919" t="inlineStr"/>
+      <c r="F919" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G919" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H919" t="inlineStr"/>
+      <c r="I919" t="inlineStr"/>
+      <c r="J919" t="inlineStr"/>
+      <c r="K919" t="inlineStr">
+        <is>
+          <t>http://www.m31boxingacademy.wordpress.com/</t>
+        </is>
+      </c>
+      <c r="L919" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M919" t="inlineStr"/>
+      <c r="N919" t="inlineStr"/>
+      <c r="O919" t="inlineStr"/>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>L919</t>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>Kickboxing</t>
+        </is>
+      </c>
+      <c r="C920" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="D920" t="inlineStr"/>
+      <c r="E920" t="inlineStr"/>
+      <c r="F920" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G920" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H920" t="inlineStr">
+        <is>
+          <t>447774723839</t>
+        </is>
+      </c>
+      <c r="I920" t="inlineStr"/>
+      <c r="J920" t="inlineStr">
+        <is>
+          <t>chris.nwckb@gmail.com</t>
+        </is>
+      </c>
+      <c r="K920" t="inlineStr">
+        <is>
+          <t>http://www.nwckb.co.uk/</t>
+        </is>
+      </c>
+      <c r="L920" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M920" t="inlineStr"/>
+      <c r="N920" t="inlineStr"/>
+      <c r="O920" t="inlineStr"/>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>L920</t>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>Fighting Fit Elite Performance Centre</t>
+        </is>
+      </c>
+      <c r="C921" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="D921" t="inlineStr"/>
+      <c r="E921" t="inlineStr"/>
+      <c r="F921" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G921" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H921" t="inlineStr">
+        <is>
+          <t>447951219442</t>
+        </is>
+      </c>
+      <c r="I921" t="inlineStr"/>
+      <c r="J921" t="inlineStr"/>
+      <c r="K921" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/p/FightingFit-Elite-Performance-Cen</t>
+        </is>
+      </c>
+      <c r="L921" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M921" t="inlineStr"/>
+      <c r="N921" t="inlineStr"/>
+      <c r="O921" t="inlineStr"/>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>L921</t>
+        </is>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>Jimmy Egan’s Boxing Academy</t>
+        </is>
+      </c>
+      <c r="C922" t="inlineStr">
+        <is>
+          <t>Boxing gym</t>
+        </is>
+      </c>
+      <c r="D922" t="inlineStr"/>
+      <c r="E922" t="inlineStr"/>
+      <c r="F922" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G922" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H922" t="inlineStr">
+        <is>
+          <t>447886035030</t>
+        </is>
+      </c>
+      <c r="I922" t="inlineStr"/>
+      <c r="J922" t="inlineStr">
+        <is>
+          <t>jimmyegansboxingacademycic@outlook.com</t>
+        </is>
+      </c>
+      <c r="K922" t="inlineStr">
+        <is>
+          <t>https://jimmyegansboxingacademy.co.uk/</t>
+        </is>
+      </c>
+      <c r="L922" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M922" t="inlineStr"/>
+      <c r="N922" t="inlineStr"/>
+      <c r="O922" t="inlineStr"/>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>L922</t>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>M27 Boxing and Fitness</t>
+        </is>
+      </c>
+      <c r="C923" t="inlineStr">
+        <is>
+          <t>Boxing gym</t>
+        </is>
+      </c>
+      <c r="D923" t="inlineStr"/>
+      <c r="E923" t="inlineStr"/>
+      <c r="F923" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G923" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H923" t="inlineStr">
+        <is>
+          <t>441615665798</t>
+        </is>
+      </c>
+      <c r="I923" t="inlineStr"/>
+      <c r="J923" t="inlineStr"/>
+      <c r="K923" t="inlineStr">
+        <is>
+          <t>http://www.m27boxingandfitness.com/</t>
+        </is>
+      </c>
+      <c r="L923" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M923" t="inlineStr"/>
+      <c r="N923" t="inlineStr"/>
+      <c r="O923" t="inlineStr"/>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>L923</t>
+        </is>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>Barton Athletic Club</t>
+        </is>
+      </c>
+      <c r="C924" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="D924" t="inlineStr"/>
+      <c r="E924" t="inlineStr"/>
+      <c r="F924" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G924" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H924" t="inlineStr">
+        <is>
+          <t>441617078124</t>
+        </is>
+      </c>
+      <c r="I924" t="inlineStr"/>
+      <c r="J924" t="inlineStr"/>
+      <c r="K924" t="inlineStr"/>
+      <c r="L924" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M924" t="inlineStr"/>
+      <c r="N924" t="inlineStr"/>
+      <c r="O924" t="inlineStr"/>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>L924</t>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>Urban Reform</t>
+        </is>
+      </c>
+      <c r="C925" t="inlineStr">
+        <is>
+          <t>Fitness center</t>
+        </is>
+      </c>
+      <c r="D925" t="inlineStr"/>
+      <c r="E925" t="inlineStr"/>
+      <c r="F925" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G925" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H925" t="inlineStr">
+        <is>
+          <t>447854868113</t>
+        </is>
+      </c>
+      <c r="I925" t="inlineStr"/>
+      <c r="J925" t="inlineStr">
+        <is>
+          <t>urbanreformfit@gmail.com</t>
+        </is>
+      </c>
+      <c r="K925" t="inlineStr">
+        <is>
+          <t>http://www.urbanreformfit.co.uk/</t>
+        </is>
+      </c>
+      <c r="L925" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M925" t="inlineStr"/>
+      <c r="N925" t="inlineStr"/>
+      <c r="O925" t="inlineStr"/>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>L925</t>
+        </is>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>The Yard Boxing Gym</t>
+        </is>
+      </c>
+      <c r="C926" t="inlineStr">
+        <is>
+          <t>Boxing gym</t>
+        </is>
+      </c>
+      <c r="D926" t="inlineStr"/>
+      <c r="E926" t="inlineStr"/>
+      <c r="F926" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G926" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H926" t="inlineStr">
+        <is>
+          <t>447562648802</t>
+        </is>
+      </c>
+      <c r="I926" t="inlineStr"/>
+      <c r="J926" t="inlineStr"/>
+      <c r="K926" t="inlineStr"/>
+      <c r="L926" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M926" t="inlineStr"/>
+      <c r="N926" t="inlineStr"/>
+      <c r="O926" t="inlineStr"/>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>L926</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>Manchester Top Team</t>
+        </is>
+      </c>
+      <c r="C927" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="D927" t="inlineStr"/>
+      <c r="E927" t="inlineStr"/>
+      <c r="F927" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G927" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H927" t="inlineStr">
+        <is>
+          <t>447863877959</t>
+        </is>
+      </c>
+      <c r="I927" t="inlineStr"/>
+      <c r="J927" t="inlineStr">
+        <is>
+          <t>contact@manchestertopteam.com</t>
+        </is>
+      </c>
+      <c r="K927" t="inlineStr">
+        <is>
+          <t>http://manchestertopteam.com/</t>
+        </is>
+      </c>
+      <c r="L927" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M927" t="inlineStr"/>
+      <c r="N927" t="inlineStr"/>
+      <c r="O927" t="inlineStr"/>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>L927</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>Salford City Boxing Academy (Dorvy)</t>
+        </is>
+      </c>
+      <c r="C928" t="inlineStr">
+        <is>
+          <t>Boxing gym</t>
+        </is>
+      </c>
+      <c r="D928" t="inlineStr"/>
+      <c r="E928" t="inlineStr"/>
+      <c r="F928" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G928" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H928" t="inlineStr">
+        <is>
+          <t>447748567595</t>
+        </is>
+      </c>
+      <c r="I928" t="inlineStr"/>
+      <c r="J928" t="inlineStr"/>
+      <c r="K928" t="inlineStr">
+        <is>
+          <t>http://salfordcityboxingacademy.wordpress.com/</t>
+        </is>
+      </c>
+      <c r="L928" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M928" t="inlineStr"/>
+      <c r="N928" t="inlineStr"/>
+      <c r="O928" t="inlineStr"/>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>L928</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>The Olympus Projects</t>
+        </is>
+      </c>
+      <c r="C929" t="inlineStr">
+        <is>
+          <t>Fitness center</t>
+        </is>
+      </c>
+      <c r="D929" t="inlineStr"/>
+      <c r="E929" t="inlineStr"/>
+      <c r="F929" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G929" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H929" t="inlineStr">
+        <is>
+          <t>441615472679</t>
+        </is>
+      </c>
+      <c r="I929" t="inlineStr"/>
+      <c r="J929" t="inlineStr">
+        <is>
+          <t>train@theolympusprojects.com</t>
+        </is>
+      </c>
+      <c r="K929" t="inlineStr">
+        <is>
+          <t>https://www.theolympusprojects.com/</t>
+        </is>
+      </c>
+      <c r="L929" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M929" t="inlineStr"/>
+      <c r="N929" t="inlineStr"/>
+      <c r="O929" t="inlineStr"/>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>L929</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>Health Lab</t>
+        </is>
+      </c>
+      <c r="C930" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="D930" t="inlineStr"/>
+      <c r="E930" t="inlineStr"/>
+      <c r="F930" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G930" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H930" t="inlineStr">
+        <is>
+          <t>447554299598</t>
+        </is>
+      </c>
+      <c r="I930" t="inlineStr"/>
+      <c r="J930" t="inlineStr"/>
+      <c r="K930" t="inlineStr"/>
+      <c r="L930" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M930" t="inlineStr"/>
+      <c r="N930" t="inlineStr"/>
+      <c r="O930" t="inlineStr"/>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>L930</t>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>SubZone Fight Academy</t>
+        </is>
+      </c>
+      <c r="C931" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="D931" t="inlineStr"/>
+      <c r="E931" t="inlineStr"/>
+      <c r="F931" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G931" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H931" t="inlineStr"/>
+      <c r="I931" t="inlineStr"/>
+      <c r="J931" t="inlineStr">
+        <is>
+          <t>you@email.com</t>
+        </is>
+      </c>
+      <c r="K931" t="inlineStr">
+        <is>
+          <t>https://www.matr-bjj.com/locations/manchester/subzone-fight-</t>
+        </is>
+      </c>
+      <c r="L931" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M931" t="inlineStr"/>
+      <c r="N931" t="inlineStr"/>
+      <c r="O931" t="inlineStr"/>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>L931</t>
+        </is>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>Salford Striking Academy</t>
+        </is>
+      </c>
+      <c r="C932" t="inlineStr">
+        <is>
+          <t>Muay Thai boxing gym</t>
+        </is>
+      </c>
+      <c r="D932" t="inlineStr"/>
+      <c r="E932" t="inlineStr"/>
+      <c r="F932" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G932" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H932" t="inlineStr">
+        <is>
+          <t>447890869960</t>
+        </is>
+      </c>
+      <c r="I932" t="inlineStr"/>
+      <c r="J932" t="inlineStr"/>
+      <c r="K932" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Salfordstrikingacademy/?ref=bookmar</t>
+        </is>
+      </c>
+      <c r="L932" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M932" t="inlineStr"/>
+      <c r="N932" t="inlineStr"/>
+      <c r="O932" t="inlineStr"/>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>L932</t>
+        </is>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>Urmston Boxing Club</t>
+        </is>
+      </c>
+      <c r="C933" t="inlineStr">
+        <is>
+          <t>Sports school</t>
+        </is>
+      </c>
+      <c r="D933" t="inlineStr"/>
+      <c r="E933" t="inlineStr"/>
+      <c r="F933" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G933" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H933" t="inlineStr">
+        <is>
+          <t>447759383081</t>
+        </is>
+      </c>
+      <c r="I933" t="inlineStr"/>
+      <c r="J933" t="inlineStr"/>
+      <c r="K933" t="inlineStr"/>
+      <c r="L933" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M933" t="inlineStr"/>
+      <c r="N933" t="inlineStr"/>
+      <c r="O933" t="inlineStr"/>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>L933</t>
+        </is>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>Delaneys gym</t>
+        </is>
+      </c>
+      <c r="C934" t="inlineStr">
+        <is>
+          <t>Boxing gym</t>
+        </is>
+      </c>
+      <c r="D934" t="inlineStr"/>
+      <c r="E934" t="inlineStr"/>
+      <c r="F934" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G934" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H934" t="inlineStr">
+        <is>
+          <t>447927127256</t>
+        </is>
+      </c>
+      <c r="I934" t="inlineStr"/>
+      <c r="J934" t="inlineStr"/>
+      <c r="K934" t="inlineStr"/>
+      <c r="L934" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M934" t="inlineStr"/>
+      <c r="N934" t="inlineStr"/>
+      <c r="O934" t="inlineStr"/>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>L934</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>ROC BoxFit</t>
+        </is>
+      </c>
+      <c r="C935" t="inlineStr">
+        <is>
+          <t>Personal trainer</t>
+        </is>
+      </c>
+      <c r="D935" t="inlineStr">
+        <is>
+          <t>roconnor1978</t>
+        </is>
+      </c>
+      <c r="E935" t="inlineStr"/>
+      <c r="F935" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G935" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H935" t="inlineStr">
+        <is>
+          <t>447833257747</t>
+        </is>
+      </c>
+      <c r="I935" t="inlineStr"/>
+      <c r="J935" t="inlineStr"/>
+      <c r="K935" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/roconnor1978/</t>
+        </is>
+      </c>
+      <c r="L935" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M935" t="inlineStr"/>
+      <c r="N935" t="inlineStr"/>
+      <c r="O935" t="inlineStr"/>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>L935</t>
+        </is>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>Manchester Fighters Academy</t>
+        </is>
+      </c>
+      <c r="C936" t="inlineStr">
+        <is>
+          <t>Muay Thai boxing gym</t>
+        </is>
+      </c>
+      <c r="D936" t="inlineStr"/>
+      <c r="E936" t="inlineStr"/>
+      <c r="F936" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G936" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H936" t="inlineStr">
+        <is>
+          <t>447770583190</t>
+        </is>
+      </c>
+      <c r="I936" t="inlineStr"/>
+      <c r="J936" t="inlineStr"/>
+      <c r="K936" t="inlineStr">
+        <is>
+          <t>https://manchesterfightersacademy.wordpress.com/</t>
+        </is>
+      </c>
+      <c r="L936" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M936" t="inlineStr"/>
+      <c r="N936" t="inlineStr"/>
+      <c r="O936" t="inlineStr"/>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>L936</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>Wickstead Muay Thai</t>
+        </is>
+      </c>
+      <c r="C937" t="inlineStr">
+        <is>
+          <t>Muay Thai boxing gym</t>
+        </is>
+      </c>
+      <c r="D937" t="inlineStr"/>
+      <c r="E937" t="inlineStr"/>
+      <c r="F937" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G937" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H937" t="inlineStr">
+        <is>
+          <t>447500584846</t>
+        </is>
+      </c>
+      <c r="I937" t="inlineStr"/>
+      <c r="J937" t="inlineStr"/>
+      <c r="K937" t="inlineStr"/>
+      <c r="L937" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M937" t="inlineStr"/>
+      <c r="N937" t="inlineStr"/>
+      <c r="O937" t="inlineStr"/>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>L937</t>
+        </is>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>Bells Gym</t>
+        </is>
+      </c>
+      <c r="C938" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="D938" t="inlineStr"/>
+      <c r="E938" t="inlineStr"/>
+      <c r="F938" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G938" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H938" t="inlineStr"/>
+      <c r="I938" t="inlineStr"/>
+      <c r="J938" t="inlineStr">
+        <is>
+          <t>info@bellsgym.co.uk</t>
+        </is>
+      </c>
+      <c r="K938" t="inlineStr">
+        <is>
+          <t>http://www.bellsgym.co.uk/</t>
+        </is>
+      </c>
+      <c r="L938" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M938" t="inlineStr"/>
+      <c r="N938" t="inlineStr"/>
+      <c r="O938" t="inlineStr"/>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>L938</t>
+        </is>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>Hive Jiu Jitsu</t>
+        </is>
+      </c>
+      <c r="C939" t="inlineStr">
+        <is>
+          <t>Martial arts club</t>
+        </is>
+      </c>
+      <c r="D939" t="inlineStr"/>
+      <c r="E939" t="inlineStr"/>
+      <c r="F939" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G939" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H939" t="inlineStr">
+        <is>
+          <t>447476927426</t>
+        </is>
+      </c>
+      <c r="I939" t="inlineStr"/>
+      <c r="J939" t="inlineStr"/>
+      <c r="K939" t="inlineStr">
+        <is>
+          <t>http://hivejiujitsu.co.uk/</t>
+        </is>
+      </c>
+      <c r="L939" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M939" t="inlineStr"/>
+      <c r="N939" t="inlineStr"/>
+      <c r="O939" t="inlineStr"/>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>L939</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>3rothers Gym- Mixed Martial Arts and Fitness Gym</t>
+        </is>
+      </c>
+      <c r="C940" t="inlineStr">
+        <is>
+          <t>Martial arts club</t>
+        </is>
+      </c>
+      <c r="D940" t="inlineStr"/>
+      <c r="E940" t="inlineStr"/>
+      <c r="F940" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G940" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H940" t="inlineStr">
+        <is>
+          <t>447496555708</t>
+        </is>
+      </c>
+      <c r="I940" t="inlineStr"/>
+      <c r="J940" t="inlineStr">
+        <is>
+          <t>3rothersgym@gmail.com</t>
+        </is>
+      </c>
+      <c r="K940" t="inlineStr">
+        <is>
+          <t>http://3rothersgym.com/</t>
+        </is>
+      </c>
+      <c r="L940" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M940" t="inlineStr"/>
+      <c r="N940" t="inlineStr"/>
+      <c r="O940" t="inlineStr"/>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>L940</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>ONE MMA Academy Manchester</t>
+        </is>
+      </c>
+      <c r="C941" t="inlineStr">
+        <is>
+          <t>Martial arts club</t>
+        </is>
+      </c>
+      <c r="D941" t="inlineStr"/>
+      <c r="E941" t="inlineStr"/>
+      <c r="F941" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G941" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H941" t="inlineStr">
+        <is>
+          <t>447398896732</t>
+        </is>
+      </c>
+      <c r="I941" t="inlineStr"/>
+      <c r="J941" t="inlineStr"/>
+      <c r="K941" t="inlineStr">
+        <is>
+          <t>https://onemma.co.uk/</t>
+        </is>
+      </c>
+      <c r="L941" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M941" t="inlineStr"/>
+      <c r="N941" t="inlineStr"/>
+      <c r="O941" t="inlineStr"/>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>L941</t>
+        </is>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>TKO Gym Manchester</t>
+        </is>
+      </c>
+      <c r="C942" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="D942" t="inlineStr"/>
+      <c r="E942" t="inlineStr"/>
+      <c r="F942" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G942" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H942" t="inlineStr">
+        <is>
+          <t>447448573150</t>
+        </is>
+      </c>
+      <c r="I942" t="inlineStr"/>
+      <c r="J942" t="inlineStr">
+        <is>
+          <t>support@webador.com</t>
+        </is>
+      </c>
+      <c r="K942" t="inlineStr">
+        <is>
+          <t>http://tko-gym.com/</t>
+        </is>
+      </c>
+      <c r="L942" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M942" t="inlineStr"/>
+      <c r="N942" t="inlineStr"/>
+      <c r="O942" t="inlineStr"/>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>L942</t>
+        </is>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>Viva MMA BJJ &amp; Kickboxing</t>
+        </is>
+      </c>
+      <c r="C943" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D943" t="inlineStr"/>
+      <c r="E943" t="inlineStr"/>
+      <c r="F943" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G943" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H943" t="inlineStr">
+        <is>
+          <t>441613123100</t>
+        </is>
+      </c>
+      <c r="I943" t="inlineStr"/>
+      <c r="J943" t="inlineStr"/>
+      <c r="K943" t="inlineStr">
+        <is>
+          <t>https://www.vivacombatathletics.co.uk/</t>
+        </is>
+      </c>
+      <c r="L943" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M943" t="inlineStr"/>
+      <c r="N943" t="inlineStr"/>
+      <c r="O943" t="inlineStr"/>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>L943</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>Academia BJJ Lifestyle UK</t>
+        </is>
+      </c>
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>Martial arts club</t>
+        </is>
+      </c>
+      <c r="D944" t="inlineStr"/>
+      <c r="E944" t="inlineStr"/>
+      <c r="F944" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G944" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H944" t="inlineStr">
+        <is>
+          <t>447549966379</t>
+        </is>
+      </c>
+      <c r="I944" t="inlineStr"/>
+      <c r="J944" t="inlineStr"/>
+      <c r="K944" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Lucio-Sergio-BJJ-Manchester-5556503</t>
+        </is>
+      </c>
+      <c r="L944" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M944" t="inlineStr"/>
+      <c r="N944" t="inlineStr"/>
+      <c r="O944" t="inlineStr"/>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>L944</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>Phoenix Muay Thai Boxing</t>
+        </is>
+      </c>
+      <c r="C945" t="inlineStr">
+        <is>
+          <t>Muay Thai boxing gym</t>
+        </is>
+      </c>
+      <c r="D945" t="inlineStr"/>
+      <c r="E945" t="inlineStr"/>
+      <c r="F945" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G945" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H945" t="inlineStr">
+        <is>
+          <t>447973697683</t>
+        </is>
+      </c>
+      <c r="I945" t="inlineStr"/>
+      <c r="J945" t="inlineStr">
+        <is>
+          <t>train@phoenixmuaythai.co.uk</t>
+        </is>
+      </c>
+      <c r="K945" t="inlineStr">
+        <is>
+          <t>http://www.phoenixmuaythai.co.uk/</t>
+        </is>
+      </c>
+      <c r="L945" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M945" t="inlineStr"/>
+      <c r="N945" t="inlineStr"/>
+      <c r="O945" t="inlineStr"/>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>L945</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>Factory BJJ - Brazilian Jiu Jitsu</t>
+        </is>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D946" t="inlineStr"/>
+      <c r="E946" t="inlineStr"/>
+      <c r="F946" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G946" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H946" t="inlineStr">
+        <is>
+          <t>441613008795</t>
+        </is>
+      </c>
+      <c r="I946" t="inlineStr"/>
+      <c r="J946" t="inlineStr">
+        <is>
+          <t>admin@factorybjj.com</t>
+        </is>
+      </c>
+      <c r="K946" t="inlineStr">
+        <is>
+          <t>http://factorybjj.com/</t>
+        </is>
+      </c>
+      <c r="L946" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M946" t="inlineStr"/>
+      <c r="N946" t="inlineStr"/>
+      <c r="O946" t="inlineStr"/>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>L946</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>12 Gauge MMA</t>
+        </is>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="D947" t="inlineStr"/>
+      <c r="E947" t="inlineStr"/>
+      <c r="F947" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G947" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H947" t="inlineStr">
+        <is>
+          <t>441614949191</t>
+        </is>
+      </c>
+      <c r="I947" t="inlineStr"/>
+      <c r="J947" t="inlineStr">
+        <is>
+          <t>info@12gaugemma.com</t>
+        </is>
+      </c>
+      <c r="K947" t="inlineStr">
+        <is>
+          <t>http://www.12gaugemma.com/</t>
+        </is>
+      </c>
+      <c r="L947" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M947" t="inlineStr"/>
+      <c r="N947" t="inlineStr"/>
+      <c r="O947" t="inlineStr"/>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>L947</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>Adrenaline Combatives</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>Self defense school</t>
+        </is>
+      </c>
+      <c r="D948" t="inlineStr"/>
+      <c r="E948" t="inlineStr"/>
+      <c r="F948" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G948" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H948" t="inlineStr">
+        <is>
+          <t>447555486603</t>
+        </is>
+      </c>
+      <c r="I948" t="inlineStr"/>
+      <c r="J948" t="inlineStr"/>
+      <c r="K948" t="inlineStr">
+        <is>
+          <t>http://www.adrenalinecombatives.com/</t>
+        </is>
+      </c>
+      <c r="L948" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M948" t="inlineStr"/>
+      <c r="N948" t="inlineStr"/>
+      <c r="O948" t="inlineStr"/>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>L948</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>Black Tiger Martial Arts</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>Martial arts club</t>
+        </is>
+      </c>
+      <c r="D949" t="inlineStr"/>
+      <c r="E949" t="inlineStr"/>
+      <c r="F949" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G949" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H949" t="inlineStr">
+        <is>
+          <t>447760543735</t>
+        </is>
+      </c>
+      <c r="I949" t="inlineStr"/>
+      <c r="J949" t="inlineStr">
+        <is>
+          <t>blacktigerkarate@hotmail.com</t>
+        </is>
+      </c>
+      <c r="K949" t="inlineStr">
+        <is>
+          <t>https://www.blacktigerma.com/</t>
+        </is>
+      </c>
+      <c r="L949" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M949" t="inlineStr"/>
+      <c r="N949" t="inlineStr"/>
+      <c r="O949" t="inlineStr"/>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>L949</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>Manchester Martial Arts &amp; Gym Supply</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>Sporting goods store</t>
+        </is>
+      </c>
+      <c r="D950" t="inlineStr"/>
+      <c r="E950" t="inlineStr"/>
+      <c r="F950" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G950" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H950" t="inlineStr">
+        <is>
+          <t>441616378110</t>
+        </is>
+      </c>
+      <c r="I950" t="inlineStr"/>
+      <c r="J950" t="inlineStr"/>
+      <c r="K950" t="inlineStr">
+        <is>
+          <t>https://manchestermartialarts.co.uk/</t>
+        </is>
+      </c>
+      <c r="L950" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M950" t="inlineStr"/>
+      <c r="N950" t="inlineStr"/>
+      <c r="O950" t="inlineStr"/>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>L950</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>Matratz BJJ</t>
+        </is>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>Martial arts club</t>
+        </is>
+      </c>
+      <c r="D951" t="inlineStr"/>
+      <c r="E951" t="inlineStr"/>
+      <c r="F951" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="G951" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H951" t="inlineStr">
+        <is>
+          <t>447715549105</t>
+        </is>
+      </c>
+      <c r="I951" t="inlineStr"/>
+      <c r="J951" t="inlineStr">
+        <is>
+          <t>ashley@matratzbjj.com</t>
+        </is>
+      </c>
+      <c r="K951" t="inlineStr">
+        <is>
+          <t>https://www.matratzbjj.com/?utm_source=google&amp;utm_medium=wix</t>
+        </is>
+      </c>
+      <c r="L951" t="inlineStr">
+        <is>
+          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="M951" t="inlineStr"/>
+      <c r="N951" t="inlineStr"/>
+      <c r="O951" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O780"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -49587,76 +58210,34 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>HSN Warrior Apparels — Lead Tracker Summary</t>
-        </is>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>gmaps daily scrape - 2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>New leads today</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>171</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated (UTC):</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-10-21 01:06</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Total leads:</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>779</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>USA batch:</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>USA emails sent:</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>USA IG follow/DM done:</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>HOT leads:</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0</v>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>950</v>
       </c>
     </row>
   </sheetData>

--- a/HWA_Lead_Tracker.xlsx
+++ b/HWA_Lead_Tracker.xlsx
@@ -49567,7 +49567,7 @@
     <row r="781">
       <c r="A781" t="inlineStr">
         <is>
-          <t>L780</t>
+          <t>L793</t>
         </is>
       </c>
       <c r="B781" t="inlineStr">
@@ -49594,7 +49594,7 @@
       </c>
       <c r="H781" t="inlineStr">
         <is>
-          <t>442081583986</t>
+          <t>+442081583986</t>
         </is>
       </c>
       <c r="I781" t="inlineStr"/>
@@ -49620,7 +49620,7 @@
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t>L781</t>
+          <t>L794</t>
         </is>
       </c>
       <c r="B782" t="inlineStr">
@@ -49647,7 +49647,7 @@
       </c>
       <c r="H782" t="inlineStr">
         <is>
-          <t>442074873807</t>
+          <t>+442074873807</t>
         </is>
       </c>
       <c r="I782" t="inlineStr"/>
@@ -49669,7 +49669,7 @@
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>L782</t>
+          <t>L795</t>
         </is>
       </c>
       <c r="B783" t="inlineStr">
@@ -49696,7 +49696,7 @@
       </c>
       <c r="H783" t="inlineStr">
         <is>
-          <t>447944574046</t>
+          <t>+447944574046</t>
         </is>
       </c>
       <c r="I783" t="inlineStr"/>
@@ -49722,7 +49722,7 @@
     <row r="784">
       <c r="A784" t="inlineStr">
         <is>
-          <t>L783</t>
+          <t>L796</t>
         </is>
       </c>
       <c r="B784" t="inlineStr">
@@ -49749,7 +49749,7 @@
       </c>
       <c r="H784" t="inlineStr">
         <is>
-          <t>442077293907</t>
+          <t>+442077293907</t>
         </is>
       </c>
       <c r="I784" t="inlineStr"/>
@@ -49775,7 +49775,7 @@
     <row r="785">
       <c r="A785" t="inlineStr">
         <is>
-          <t>L784</t>
+          <t>L797</t>
         </is>
       </c>
       <c r="B785" t="inlineStr">
@@ -49802,7 +49802,7 @@
       </c>
       <c r="H785" t="inlineStr">
         <is>
-          <t>447976855259</t>
+          <t>+447976855259</t>
         </is>
       </c>
       <c r="I785" t="inlineStr"/>
@@ -49824,7 +49824,7 @@
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
-          <t>L785</t>
+          <t>L798</t>
         </is>
       </c>
       <c r="B786" t="inlineStr">
@@ -49851,7 +49851,7 @@
       </c>
       <c r="H786" t="inlineStr">
         <is>
-          <t>442033369040</t>
+          <t>+442033369040</t>
         </is>
       </c>
       <c r="I786" t="inlineStr"/>
@@ -49877,7 +49877,7 @@
     <row r="787">
       <c r="A787" t="inlineStr">
         <is>
-          <t>L786</t>
+          <t>L799</t>
         </is>
       </c>
       <c r="B787" t="inlineStr">
@@ -49904,7 +49904,7 @@
       </c>
       <c r="H787" t="inlineStr">
         <is>
-          <t>442088232323</t>
+          <t>+442088232323</t>
         </is>
       </c>
       <c r="I787" t="inlineStr"/>
@@ -49930,7 +49930,7 @@
     <row r="788">
       <c r="A788" t="inlineStr">
         <is>
-          <t>L787</t>
+          <t>L800</t>
         </is>
       </c>
       <c r="B788" t="inlineStr">
@@ -49957,7 +49957,7 @@
       </c>
       <c r="H788" t="inlineStr">
         <is>
-          <t>447516916432</t>
+          <t>+447516916432</t>
         </is>
       </c>
       <c r="I788" t="inlineStr"/>
@@ -49983,7 +49983,7 @@
     <row r="789">
       <c r="A789" t="inlineStr">
         <is>
-          <t>L788</t>
+          <t>L801</t>
         </is>
       </c>
       <c r="B789" t="inlineStr">
@@ -50010,7 +50010,7 @@
       </c>
       <c r="H789" t="inlineStr">
         <is>
-          <t>447857948554</t>
+          <t>+447857948554</t>
         </is>
       </c>
       <c r="I789" t="inlineStr"/>
@@ -50036,7 +50036,7 @@
     <row r="790">
       <c r="A790" t="inlineStr">
         <is>
-          <t>L789</t>
+          <t>L802</t>
         </is>
       </c>
       <c r="B790" t="inlineStr">
@@ -50063,7 +50063,7 @@
       </c>
       <c r="H790" t="inlineStr">
         <is>
-          <t>442074035979</t>
+          <t>+442074035979</t>
         </is>
       </c>
       <c r="I790" t="inlineStr"/>
@@ -50085,7 +50085,7 @@
     <row r="791">
       <c r="A791" t="inlineStr">
         <is>
-          <t>L790</t>
+          <t>L803</t>
         </is>
       </c>
       <c r="B791" t="inlineStr">
@@ -50112,7 +50112,7 @@
       </c>
       <c r="H791" t="inlineStr">
         <is>
-          <t>442072659693</t>
+          <t>+442072659693</t>
         </is>
       </c>
       <c r="I791" t="inlineStr"/>
@@ -50138,7 +50138,7 @@
     <row r="792">
       <c r="A792" t="inlineStr">
         <is>
-          <t>L791</t>
+          <t>L804</t>
         </is>
       </c>
       <c r="B792" t="inlineStr">
@@ -50165,7 +50165,7 @@
       </c>
       <c r="H792" t="inlineStr">
         <is>
-          <t>442072540332</t>
+          <t>+442072540332</t>
         </is>
       </c>
       <c r="I792" t="inlineStr"/>
@@ -50187,7 +50187,7 @@
     <row r="793">
       <c r="A793" t="inlineStr">
         <is>
-          <t>L792</t>
+          <t>L805</t>
         </is>
       </c>
       <c r="B793" t="inlineStr">
@@ -50214,7 +50214,7 @@
       </c>
       <c r="H793" t="inlineStr">
         <is>
-          <t>447503554872</t>
+          <t>+447503554872</t>
         </is>
       </c>
       <c r="I793" t="inlineStr"/>
@@ -50236,7 +50236,7 @@
     <row r="794">
       <c r="A794" t="inlineStr">
         <is>
-          <t>L793</t>
+          <t>L806</t>
         </is>
       </c>
       <c r="B794" t="inlineStr">
@@ -50263,7 +50263,7 @@
       </c>
       <c r="H794" t="inlineStr">
         <is>
-          <t>447591492052</t>
+          <t>+447591492052</t>
         </is>
       </c>
       <c r="I794" t="inlineStr"/>
@@ -50289,7 +50289,7 @@
     <row r="795">
       <c r="A795" t="inlineStr">
         <is>
-          <t>L794</t>
+          <t>L807</t>
         </is>
       </c>
       <c r="B795" t="inlineStr">
@@ -50316,7 +50316,7 @@
       </c>
       <c r="H795" t="inlineStr">
         <is>
-          <t>442078134293</t>
+          <t>+442078134293</t>
         </is>
       </c>
       <c r="I795" t="inlineStr"/>
@@ -50338,7 +50338,7 @@
     <row r="796">
       <c r="A796" t="inlineStr">
         <is>
-          <t>L795</t>
+          <t>L808</t>
         </is>
       </c>
       <c r="B796" t="inlineStr">
@@ -50365,7 +50365,7 @@
       </c>
       <c r="H796" t="inlineStr">
         <is>
-          <t>442070436032</t>
+          <t>+442070436032</t>
         </is>
       </c>
       <c r="I796" t="inlineStr"/>
@@ -50387,7 +50387,7 @@
     <row r="797">
       <c r="A797" t="inlineStr">
         <is>
-          <t>L796</t>
+          <t>L809</t>
         </is>
       </c>
       <c r="B797" t="inlineStr">
@@ -50414,7 +50414,7 @@
       </c>
       <c r="H797" t="inlineStr">
         <is>
-          <t>442073701000</t>
+          <t>+442073701000</t>
         </is>
       </c>
       <c r="I797" t="inlineStr"/>
@@ -50440,7 +50440,7 @@
     <row r="798">
       <c r="A798" t="inlineStr">
         <is>
-          <t>L797</t>
+          <t>L810</t>
         </is>
       </c>
       <c r="B798" t="inlineStr">
@@ -50467,7 +50467,7 @@
       </c>
       <c r="H798" t="inlineStr">
         <is>
-          <t>447438308367</t>
+          <t>+447438308367</t>
         </is>
       </c>
       <c r="I798" t="inlineStr"/>
@@ -50489,7 +50489,7 @@
     <row r="799">
       <c r="A799" t="inlineStr">
         <is>
-          <t>L798</t>
+          <t>L811</t>
         </is>
       </c>
       <c r="B799" t="inlineStr">
@@ -50516,7 +50516,7 @@
       </c>
       <c r="H799" t="inlineStr">
         <is>
-          <t>447910061481</t>
+          <t>+447910061481</t>
         </is>
       </c>
       <c r="I799" t="inlineStr"/>
@@ -50538,7 +50538,7 @@
     <row r="800">
       <c r="A800" t="inlineStr">
         <is>
-          <t>L799</t>
+          <t>L812</t>
         </is>
       </c>
       <c r="B800" t="inlineStr">
@@ -50587,7 +50587,7 @@
     <row r="801">
       <c r="A801" t="inlineStr">
         <is>
-          <t>L800</t>
+          <t>L813</t>
         </is>
       </c>
       <c r="B801" t="inlineStr">
@@ -50614,7 +50614,7 @@
       </c>
       <c r="H801" t="inlineStr">
         <is>
-          <t>442037717955</t>
+          <t>+442037717955</t>
         </is>
       </c>
       <c r="I801" t="inlineStr"/>
@@ -50640,7 +50640,7 @@
     <row r="802">
       <c r="A802" t="inlineStr">
         <is>
-          <t>L801</t>
+          <t>L814</t>
         </is>
       </c>
       <c r="B802" t="inlineStr">
@@ -50667,7 +50667,7 @@
       </c>
       <c r="H802" t="inlineStr">
         <is>
-          <t>447360334349</t>
+          <t>+447360334349</t>
         </is>
       </c>
       <c r="I802" t="inlineStr"/>
@@ -50693,7 +50693,7 @@
     <row r="803">
       <c r="A803" t="inlineStr">
         <is>
-          <t>L802</t>
+          <t>L815</t>
         </is>
       </c>
       <c r="B803" t="inlineStr">
@@ -50720,7 +50720,7 @@
       </c>
       <c r="H803" t="inlineStr">
         <is>
-          <t>447887427765</t>
+          <t>+447887427765</t>
         </is>
       </c>
       <c r="I803" t="inlineStr"/>
@@ -50746,7 +50746,7 @@
     <row r="804">
       <c r="A804" t="inlineStr">
         <is>
-          <t>L803</t>
+          <t>L816</t>
         </is>
       </c>
       <c r="B804" t="inlineStr">
@@ -50773,7 +50773,7 @@
       </c>
       <c r="H804" t="inlineStr">
         <is>
-          <t>442075865880</t>
+          <t>+442075865880</t>
         </is>
       </c>
       <c r="I804" t="inlineStr"/>
@@ -50795,7 +50795,7 @@
     <row r="805">
       <c r="A805" t="inlineStr">
         <is>
-          <t>L804</t>
+          <t>L817</t>
         </is>
       </c>
       <c r="B805" t="inlineStr">
@@ -50822,7 +50822,7 @@
       </c>
       <c r="H805" t="inlineStr">
         <is>
-          <t>447713482314</t>
+          <t>+447713482314</t>
         </is>
       </c>
       <c r="I805" t="inlineStr"/>
@@ -50844,7 +50844,7 @@
     <row r="806">
       <c r="A806" t="inlineStr">
         <is>
-          <t>L805</t>
+          <t>L818</t>
         </is>
       </c>
       <c r="B806" t="inlineStr">
@@ -50871,7 +50871,7 @@
       </c>
       <c r="H806" t="inlineStr">
         <is>
-          <t>447765243012</t>
+          <t>+447765243012</t>
         </is>
       </c>
       <c r="I806" t="inlineStr"/>
@@ -50893,7 +50893,7 @@
     <row r="807">
       <c r="A807" t="inlineStr">
         <is>
-          <t>L806</t>
+          <t>L819</t>
         </is>
       </c>
       <c r="B807" t="inlineStr">
@@ -50920,7 +50920,7 @@
       </c>
       <c r="H807" t="inlineStr">
         <is>
-          <t>447930824601</t>
+          <t>+447930824601</t>
         </is>
       </c>
       <c r="I807" t="inlineStr"/>
@@ -50946,7 +50946,7 @@
     <row r="808">
       <c r="A808" t="inlineStr">
         <is>
-          <t>L807</t>
+          <t>L820</t>
         </is>
       </c>
       <c r="B808" t="inlineStr">
@@ -50991,7 +50991,7 @@
     <row r="809">
       <c r="A809" t="inlineStr">
         <is>
-          <t>L808</t>
+          <t>L821</t>
         </is>
       </c>
       <c r="B809" t="inlineStr">
@@ -51040,7 +51040,7 @@
     <row r="810">
       <c r="A810" t="inlineStr">
         <is>
-          <t>L809</t>
+          <t>L822</t>
         </is>
       </c>
       <c r="B810" t="inlineStr">
@@ -51067,7 +51067,7 @@
       </c>
       <c r="H810" t="inlineStr">
         <is>
-          <t>447949029157</t>
+          <t>+447949029157</t>
         </is>
       </c>
       <c r="I810" t="inlineStr"/>
@@ -51089,7 +51089,7 @@
     <row r="811">
       <c r="A811" t="inlineStr">
         <is>
-          <t>L810</t>
+          <t>L823</t>
         </is>
       </c>
       <c r="B811" t="inlineStr">
@@ -51116,7 +51116,7 @@
       </c>
       <c r="H811" t="inlineStr">
         <is>
-          <t>442077230206</t>
+          <t>+442077230206</t>
         </is>
       </c>
       <c r="I811" t="inlineStr"/>
@@ -51138,7 +51138,7 @@
     <row r="812">
       <c r="A812" t="inlineStr">
         <is>
-          <t>L811</t>
+          <t>L824</t>
         </is>
       </c>
       <c r="B812" t="inlineStr">
@@ -51165,7 +51165,7 @@
       </c>
       <c r="H812" t="inlineStr">
         <is>
-          <t>447976411901</t>
+          <t>+447976411901</t>
         </is>
       </c>
       <c r="I812" t="inlineStr"/>
@@ -51191,7 +51191,7 @@
     <row r="813">
       <c r="A813" t="inlineStr">
         <is>
-          <t>L812</t>
+          <t>L825</t>
         </is>
       </c>
       <c r="B813" t="inlineStr">
@@ -51218,7 +51218,7 @@
       </c>
       <c r="H813" t="inlineStr">
         <is>
-          <t>447920056974</t>
+          <t>+447920056974</t>
         </is>
       </c>
       <c r="I813" t="inlineStr"/>
@@ -51244,7 +51244,7 @@
     <row r="814">
       <c r="A814" t="inlineStr">
         <is>
-          <t>L813</t>
+          <t>L826</t>
         </is>
       </c>
       <c r="B814" t="inlineStr">
@@ -51271,7 +51271,7 @@
       </c>
       <c r="H814" t="inlineStr">
         <is>
-          <t>447737825087</t>
+          <t>+447737825087</t>
         </is>
       </c>
       <c r="I814" t="inlineStr"/>
@@ -51297,7 +51297,7 @@
     <row r="815">
       <c r="A815" t="inlineStr">
         <is>
-          <t>L814</t>
+          <t>L827</t>
         </is>
       </c>
       <c r="B815" t="inlineStr">
@@ -51342,7 +51342,7 @@
     <row r="816">
       <c r="A816" t="inlineStr">
         <is>
-          <t>L815</t>
+          <t>L828</t>
         </is>
       </c>
       <c r="B816" t="inlineStr">
@@ -51369,7 +51369,7 @@
       </c>
       <c r="H816" t="inlineStr">
         <is>
-          <t>447903570600</t>
+          <t>+447903570600</t>
         </is>
       </c>
       <c r="I816" t="inlineStr"/>
@@ -51391,7 +51391,7 @@
     <row r="817">
       <c r="A817" t="inlineStr">
         <is>
-          <t>L816</t>
+          <t>L829</t>
         </is>
       </c>
       <c r="B817" t="inlineStr">
@@ -51418,7 +51418,7 @@
       </c>
       <c r="H817" t="inlineStr">
         <is>
-          <t>447564434982</t>
+          <t>+447564434982</t>
         </is>
       </c>
       <c r="I817" t="inlineStr"/>
@@ -51444,7 +51444,7 @@
     <row r="818">
       <c r="A818" t="inlineStr">
         <is>
-          <t>L817</t>
+          <t>L830</t>
         </is>
       </c>
       <c r="B818" t="inlineStr">
@@ -51471,7 +51471,7 @@
       </c>
       <c r="H818" t="inlineStr">
         <is>
-          <t>447857967855</t>
+          <t>+447857967855</t>
         </is>
       </c>
       <c r="I818" t="inlineStr"/>
@@ -51489,7 +51489,7 @@
     <row r="819">
       <c r="A819" t="inlineStr">
         <is>
-          <t>L818</t>
+          <t>L831</t>
         </is>
       </c>
       <c r="B819" t="inlineStr">
@@ -51516,7 +51516,7 @@
       </c>
       <c r="H819" t="inlineStr">
         <is>
-          <t>447821679058</t>
+          <t>+447821679058</t>
         </is>
       </c>
       <c r="I819" t="inlineStr"/>
@@ -51542,7 +51542,7 @@
     <row r="820">
       <c r="A820" t="inlineStr">
         <is>
-          <t>L819</t>
+          <t>L832</t>
         </is>
       </c>
       <c r="B820" t="inlineStr">
@@ -51569,7 +51569,7 @@
       </c>
       <c r="H820" t="inlineStr">
         <is>
-          <t>447931709140</t>
+          <t>+447931709140</t>
         </is>
       </c>
       <c r="I820" t="inlineStr"/>
@@ -51591,7 +51591,7 @@
     <row r="821">
       <c r="A821" t="inlineStr">
         <is>
-          <t>L820</t>
+          <t>L833</t>
         </is>
       </c>
       <c r="B821" t="inlineStr">
@@ -51618,7 +51618,7 @@
       </c>
       <c r="H821" t="inlineStr">
         <is>
-          <t>447720218455</t>
+          <t>+447720218455</t>
         </is>
       </c>
       <c r="I821" t="inlineStr"/>
@@ -51640,7 +51640,7 @@
     <row r="822">
       <c r="A822" t="inlineStr">
         <is>
-          <t>L821</t>
+          <t>L834</t>
         </is>
       </c>
       <c r="B822" t="inlineStr">
@@ -51667,7 +51667,7 @@
       </c>
       <c r="H822" t="inlineStr">
         <is>
-          <t>442076878333</t>
+          <t>+442076878333</t>
         </is>
       </c>
       <c r="I822" t="inlineStr"/>
@@ -51693,7 +51693,7 @@
     <row r="823">
       <c r="A823" t="inlineStr">
         <is>
-          <t>L822</t>
+          <t>L835</t>
         </is>
       </c>
       <c r="B823" t="inlineStr">
@@ -51742,7 +51742,7 @@
     <row r="824">
       <c r="A824" t="inlineStr">
         <is>
-          <t>L823</t>
+          <t>L836</t>
         </is>
       </c>
       <c r="B824" t="inlineStr">
@@ -51769,7 +51769,7 @@
       </c>
       <c r="H824" t="inlineStr">
         <is>
-          <t>447723009164</t>
+          <t>+447723009164</t>
         </is>
       </c>
       <c r="I824" t="inlineStr"/>
@@ -51791,7 +51791,7 @@
     <row r="825">
       <c r="A825" t="inlineStr">
         <is>
-          <t>L824</t>
+          <t>L837</t>
         </is>
       </c>
       <c r="B825" t="inlineStr">
@@ -51818,7 +51818,7 @@
       </c>
       <c r="H825" t="inlineStr">
         <is>
-          <t>442081232824</t>
+          <t>+442081232824</t>
         </is>
       </c>
       <c r="I825" t="inlineStr"/>
@@ -51840,7 +51840,7 @@
     <row r="826">
       <c r="A826" t="inlineStr">
         <is>
-          <t>L825</t>
+          <t>L838</t>
         </is>
       </c>
       <c r="B826" t="inlineStr">
@@ -51867,7 +51867,7 @@
       </c>
       <c r="H826" t="inlineStr">
         <is>
-          <t>447751813956</t>
+          <t>+447751813956</t>
         </is>
       </c>
       <c r="I826" t="inlineStr"/>
@@ -51893,7 +51893,7 @@
     <row r="827">
       <c r="A827" t="inlineStr">
         <is>
-          <t>L826</t>
+          <t>L839</t>
         </is>
       </c>
       <c r="B827" t="inlineStr">
@@ -51920,7 +51920,7 @@
       </c>
       <c r="H827" t="inlineStr">
         <is>
-          <t>447961534525</t>
+          <t>+447961534525</t>
         </is>
       </c>
       <c r="I827" t="inlineStr"/>
@@ -51946,7 +51946,7 @@
     <row r="828">
       <c r="A828" t="inlineStr">
         <is>
-          <t>L827</t>
+          <t>L840</t>
         </is>
       </c>
       <c r="B828" t="inlineStr">
@@ -51973,7 +51973,7 @@
       </c>
       <c r="H828" t="inlineStr">
         <is>
-          <t>447909914567</t>
+          <t>+447909914567</t>
         </is>
       </c>
       <c r="I828" t="inlineStr"/>
@@ -51995,7 +51995,7 @@
     <row r="829">
       <c r="A829" t="inlineStr">
         <is>
-          <t>L828</t>
+          <t>L841</t>
         </is>
       </c>
       <c r="B829" t="inlineStr">
@@ -52022,7 +52022,7 @@
       </c>
       <c r="H829" t="inlineStr">
         <is>
-          <t>447956593184</t>
+          <t>+447956593184</t>
         </is>
       </c>
       <c r="I829" t="inlineStr"/>
@@ -52044,7 +52044,7 @@
     <row r="830">
       <c r="A830" t="inlineStr">
         <is>
-          <t>L829</t>
+          <t>L842</t>
         </is>
       </c>
       <c r="B830" t="inlineStr">
@@ -52071,7 +52071,7 @@
       </c>
       <c r="H830" t="inlineStr">
         <is>
-          <t>447779249469</t>
+          <t>+447779249469</t>
         </is>
       </c>
       <c r="I830" t="inlineStr"/>
@@ -52097,7 +52097,7 @@
     <row r="831">
       <c r="A831" t="inlineStr">
         <is>
-          <t>L830</t>
+          <t>L843</t>
         </is>
       </c>
       <c r="B831" t="inlineStr">
@@ -52124,7 +52124,7 @@
       </c>
       <c r="H831" t="inlineStr">
         <is>
-          <t>447801406639</t>
+          <t>+447801406639</t>
         </is>
       </c>
       <c r="I831" t="inlineStr"/>
@@ -52150,7 +52150,7 @@
     <row r="832">
       <c r="A832" t="inlineStr">
         <is>
-          <t>L831</t>
+          <t>L844</t>
         </is>
       </c>
       <c r="B832" t="inlineStr">
@@ -52177,7 +52177,7 @@
       </c>
       <c r="H832" t="inlineStr">
         <is>
-          <t>447960599125</t>
+          <t>+447960599125</t>
         </is>
       </c>
       <c r="I832" t="inlineStr"/>
@@ -52203,7 +52203,7 @@
     <row r="833">
       <c r="A833" t="inlineStr">
         <is>
-          <t>L832</t>
+          <t>L845</t>
         </is>
       </c>
       <c r="B833" t="inlineStr">
@@ -52230,7 +52230,7 @@
       </c>
       <c r="H833" t="inlineStr">
         <is>
-          <t>447837643316</t>
+          <t>+447837643316</t>
         </is>
       </c>
       <c r="I833" t="inlineStr"/>
@@ -52252,7 +52252,7 @@
     <row r="834">
       <c r="A834" t="inlineStr">
         <is>
-          <t>L833</t>
+          <t>L846</t>
         </is>
       </c>
       <c r="B834" t="inlineStr">
@@ -52279,7 +52279,7 @@
       </c>
       <c r="H834" t="inlineStr">
         <is>
-          <t>447540841820</t>
+          <t>+447540841820</t>
         </is>
       </c>
       <c r="I834" t="inlineStr"/>
@@ -52305,7 +52305,7 @@
     <row r="835">
       <c r="A835" t="inlineStr">
         <is>
-          <t>L834</t>
+          <t>L847</t>
         </is>
       </c>
       <c r="B835" t="inlineStr">
@@ -52332,7 +52332,7 @@
       </c>
       <c r="H835" t="inlineStr">
         <is>
-          <t>442087410231</t>
+          <t>+442087410231</t>
         </is>
       </c>
       <c r="I835" t="inlineStr"/>
@@ -52358,7 +52358,7 @@
     <row r="836">
       <c r="A836" t="inlineStr">
         <is>
-          <t>L835</t>
+          <t>L848</t>
         </is>
       </c>
       <c r="B836" t="inlineStr">
@@ -52385,7 +52385,7 @@
       </c>
       <c r="H836" t="inlineStr">
         <is>
-          <t>447365331358</t>
+          <t>+447365331358</t>
         </is>
       </c>
       <c r="I836" t="inlineStr"/>
@@ -52411,7 +52411,7 @@
     <row r="837">
       <c r="A837" t="inlineStr">
         <is>
-          <t>L836</t>
+          <t>L849</t>
         </is>
       </c>
       <c r="B837" t="inlineStr">
@@ -52438,7 +52438,7 @@
       </c>
       <c r="H837" t="inlineStr">
         <is>
-          <t>447518111170</t>
+          <t>+447518111170</t>
         </is>
       </c>
       <c r="I837" t="inlineStr"/>
@@ -52464,7 +52464,7 @@
     <row r="838">
       <c r="A838" t="inlineStr">
         <is>
-          <t>L837</t>
+          <t>L850</t>
         </is>
       </c>
       <c r="B838" t="inlineStr">
@@ -52491,7 +52491,7 @@
       </c>
       <c r="H838" t="inlineStr">
         <is>
-          <t>447360542667</t>
+          <t>+447360542667</t>
         </is>
       </c>
       <c r="I838" t="inlineStr"/>
@@ -52517,7 +52517,7 @@
     <row r="839">
       <c r="A839" t="inlineStr">
         <is>
-          <t>L838</t>
+          <t>L851</t>
         </is>
       </c>
       <c r="B839" t="inlineStr">
@@ -52544,7 +52544,7 @@
       </c>
       <c r="H839" t="inlineStr">
         <is>
-          <t>442080791044</t>
+          <t>+442080791044</t>
         </is>
       </c>
       <c r="I839" t="inlineStr"/>
@@ -52570,7 +52570,7 @@
     <row r="840">
       <c r="A840" t="inlineStr">
         <is>
-          <t>L839</t>
+          <t>L852</t>
         </is>
       </c>
       <c r="B840" t="inlineStr">
@@ -52597,7 +52597,7 @@
       </c>
       <c r="H840" t="inlineStr">
         <is>
-          <t>447834230066</t>
+          <t>+447834230066</t>
         </is>
       </c>
       <c r="I840" t="inlineStr"/>
@@ -52623,7 +52623,7 @@
     <row r="841">
       <c r="A841" t="inlineStr">
         <is>
-          <t>L840</t>
+          <t>L853</t>
         </is>
       </c>
       <c r="B841" t="inlineStr">
@@ -52650,7 +52650,7 @@
       </c>
       <c r="H841" t="inlineStr">
         <is>
-          <t>447565132401</t>
+          <t>+447565132401</t>
         </is>
       </c>
       <c r="I841" t="inlineStr"/>
@@ -52676,7 +52676,7 @@
     <row r="842">
       <c r="A842" t="inlineStr">
         <is>
-          <t>L841</t>
+          <t>L854</t>
         </is>
       </c>
       <c r="B842" t="inlineStr">
@@ -52703,7 +52703,7 @@
       </c>
       <c r="H842" t="inlineStr">
         <is>
-          <t>447716222602</t>
+          <t>+447716222602</t>
         </is>
       </c>
       <c r="I842" t="inlineStr"/>
@@ -52729,7 +52729,7 @@
     <row r="843">
       <c r="A843" t="inlineStr">
         <is>
-          <t>L842</t>
+          <t>L855</t>
         </is>
       </c>
       <c r="B843" t="inlineStr">
@@ -52756,7 +52756,7 @@
       </c>
       <c r="H843" t="inlineStr">
         <is>
-          <t>447841764210</t>
+          <t>+447841764210</t>
         </is>
       </c>
       <c r="I843" t="inlineStr"/>
@@ -52782,7 +52782,7 @@
     <row r="844">
       <c r="A844" t="inlineStr">
         <is>
-          <t>L843</t>
+          <t>L856</t>
         </is>
       </c>
       <c r="B844" t="inlineStr">
@@ -52809,7 +52809,7 @@
       </c>
       <c r="H844" t="inlineStr">
         <is>
-          <t>447498471113</t>
+          <t>+447498471113</t>
         </is>
       </c>
       <c r="I844" t="inlineStr"/>
@@ -52831,7 +52831,7 @@
     <row r="845">
       <c r="A845" t="inlineStr">
         <is>
-          <t>L844</t>
+          <t>L857</t>
         </is>
       </c>
       <c r="B845" t="inlineStr">
@@ -52858,7 +52858,7 @@
       </c>
       <c r="H845" t="inlineStr">
         <is>
-          <t>447734463932</t>
+          <t>+447734463932</t>
         </is>
       </c>
       <c r="I845" t="inlineStr"/>
@@ -52884,7 +52884,7 @@
     <row r="846">
       <c r="A846" t="inlineStr">
         <is>
-          <t>L845</t>
+          <t>L858</t>
         </is>
       </c>
       <c r="B846" t="inlineStr">
@@ -52933,7 +52933,7 @@
     <row r="847">
       <c r="A847" t="inlineStr">
         <is>
-          <t>L846</t>
+          <t>L859</t>
         </is>
       </c>
       <c r="B847" t="inlineStr">
@@ -52960,7 +52960,7 @@
       </c>
       <c r="H847" t="inlineStr">
         <is>
-          <t>442081290847</t>
+          <t>+442081290847</t>
         </is>
       </c>
       <c r="I847" t="inlineStr"/>
@@ -52986,7 +52986,7 @@
     <row r="848">
       <c r="A848" t="inlineStr">
         <is>
-          <t>L847</t>
+          <t>L860</t>
         </is>
       </c>
       <c r="B848" t="inlineStr">
@@ -53013,7 +53013,7 @@
       </c>
       <c r="H848" t="inlineStr">
         <is>
-          <t>447902491656</t>
+          <t>+447902491656</t>
         </is>
       </c>
       <c r="I848" t="inlineStr"/>
@@ -53039,7 +53039,7 @@
     <row r="849">
       <c r="A849" t="inlineStr">
         <is>
-          <t>L848</t>
+          <t>L861</t>
         </is>
       </c>
       <c r="B849" t="inlineStr">
@@ -53066,7 +53066,7 @@
       </c>
       <c r="H849" t="inlineStr">
         <is>
-          <t>447496636266</t>
+          <t>+447496636266</t>
         </is>
       </c>
       <c r="I849" t="inlineStr"/>
@@ -53092,7 +53092,7 @@
     <row r="850">
       <c r="A850" t="inlineStr">
         <is>
-          <t>L849</t>
+          <t>L862</t>
         </is>
       </c>
       <c r="B850" t="inlineStr">
@@ -53119,7 +53119,7 @@
       </c>
       <c r="H850" t="inlineStr">
         <is>
-          <t>447984973337</t>
+          <t>+447984973337</t>
         </is>
       </c>
       <c r="I850" t="inlineStr"/>
@@ -53141,7 +53141,7 @@
     <row r="851">
       <c r="A851" t="inlineStr">
         <is>
-          <t>L850</t>
+          <t>L863</t>
         </is>
       </c>
       <c r="B851" t="inlineStr">
@@ -53168,7 +53168,7 @@
       </c>
       <c r="H851" t="inlineStr">
         <is>
-          <t>442080128355</t>
+          <t>+442080128355</t>
         </is>
       </c>
       <c r="I851" t="inlineStr"/>
@@ -53194,7 +53194,7 @@
     <row r="852">
       <c r="A852" t="inlineStr">
         <is>
-          <t>L851</t>
+          <t>L864</t>
         </is>
       </c>
       <c r="B852" t="inlineStr">
@@ -53239,7 +53239,7 @@
     <row r="853">
       <c r="A853" t="inlineStr">
         <is>
-          <t>L852</t>
+          <t>L865</t>
         </is>
       </c>
       <c r="B853" t="inlineStr">
@@ -53266,7 +53266,7 @@
       </c>
       <c r="H853" t="inlineStr">
         <is>
-          <t>447521420733</t>
+          <t>+447521420733</t>
         </is>
       </c>
       <c r="I853" t="inlineStr"/>
@@ -53292,7 +53292,7 @@
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>L853</t>
+          <t>L866</t>
         </is>
       </c>
       <c r="B854" t="inlineStr">
@@ -53319,7 +53319,7 @@
       </c>
       <c r="H854" t="inlineStr">
         <is>
-          <t>447903190978</t>
+          <t>+447903190978</t>
         </is>
       </c>
       <c r="I854" t="inlineStr"/>
@@ -53345,7 +53345,7 @@
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
-          <t>L854</t>
+          <t>L867</t>
         </is>
       </c>
       <c r="B855" t="inlineStr">
@@ -53372,7 +53372,7 @@
       </c>
       <c r="H855" t="inlineStr">
         <is>
-          <t>447539946777</t>
+          <t>+447539946777</t>
         </is>
       </c>
       <c r="I855" t="inlineStr"/>
@@ -53398,7 +53398,7 @@
     <row r="856">
       <c r="A856" t="inlineStr">
         <is>
-          <t>L855</t>
+          <t>L868</t>
         </is>
       </c>
       <c r="B856" t="inlineStr">
@@ -53447,7 +53447,7 @@
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t>L856</t>
+          <t>L869</t>
         </is>
       </c>
       <c r="B857" t="inlineStr">
@@ -53474,7 +53474,7 @@
       </c>
       <c r="H857" t="inlineStr">
         <is>
-          <t>447385187483</t>
+          <t>+447385187483</t>
         </is>
       </c>
       <c r="I857" t="inlineStr"/>
@@ -53500,7 +53500,7 @@
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
-          <t>L857</t>
+          <t>L870</t>
         </is>
       </c>
       <c r="B858" t="inlineStr">
@@ -53527,7 +53527,7 @@
       </c>
       <c r="H858" t="inlineStr">
         <is>
-          <t>447887776132</t>
+          <t>+447887776132</t>
         </is>
       </c>
       <c r="I858" t="inlineStr"/>
@@ -53553,7 +53553,7 @@
     <row r="859">
       <c r="A859" t="inlineStr">
         <is>
-          <t>L858</t>
+          <t>L871</t>
         </is>
       </c>
       <c r="B859" t="inlineStr">
@@ -53580,7 +53580,7 @@
       </c>
       <c r="H859" t="inlineStr">
         <is>
-          <t>441614457733</t>
+          <t>+441614457733</t>
         </is>
       </c>
       <c r="I859" t="inlineStr"/>
@@ -53602,7 +53602,7 @@
     <row r="860">
       <c r="A860" t="inlineStr">
         <is>
-          <t>L859</t>
+          <t>L872</t>
         </is>
       </c>
       <c r="B860" t="inlineStr">
@@ -53629,7 +53629,7 @@
       </c>
       <c r="H860" t="inlineStr">
         <is>
-          <t>442088168382</t>
+          <t>+442088168382</t>
         </is>
       </c>
       <c r="I860" t="inlineStr"/>
@@ -53651,7 +53651,7 @@
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t>L860</t>
+          <t>L873</t>
         </is>
       </c>
       <c r="B861" t="inlineStr">
@@ -53678,7 +53678,7 @@
       </c>
       <c r="H861" t="inlineStr">
         <is>
-          <t>447543619474</t>
+          <t>+447543619474</t>
         </is>
       </c>
       <c r="I861" t="inlineStr"/>
@@ -53704,7 +53704,7 @@
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
-          <t>L861</t>
+          <t>L874</t>
         </is>
       </c>
       <c r="B862" t="inlineStr">
@@ -53731,7 +53731,7 @@
       </c>
       <c r="H862" t="inlineStr">
         <is>
-          <t>447961914054</t>
+          <t>+447961914054</t>
         </is>
       </c>
       <c r="I862" t="inlineStr"/>
@@ -53757,7 +53757,7 @@
     <row r="863">
       <c r="A863" t="inlineStr">
         <is>
-          <t>L862</t>
+          <t>L875</t>
         </is>
       </c>
       <c r="B863" t="inlineStr">
@@ -53784,7 +53784,7 @@
       </c>
       <c r="H863" t="inlineStr">
         <is>
-          <t>447897313488</t>
+          <t>+447897313488</t>
         </is>
       </c>
       <c r="I863" t="inlineStr"/>
@@ -53810,7 +53810,7 @@
     <row r="864">
       <c r="A864" t="inlineStr">
         <is>
-          <t>L863</t>
+          <t>L876</t>
         </is>
       </c>
       <c r="B864" t="inlineStr">
@@ -53837,7 +53837,7 @@
       </c>
       <c r="H864" t="inlineStr">
         <is>
-          <t>447593913883</t>
+          <t>+447593913883</t>
         </is>
       </c>
       <c r="I864" t="inlineStr"/>
@@ -53859,7 +53859,7 @@
     <row r="865">
       <c r="A865" t="inlineStr">
         <is>
-          <t>L864</t>
+          <t>L877</t>
         </is>
       </c>
       <c r="B865" t="inlineStr">
@@ -53886,7 +53886,7 @@
       </c>
       <c r="H865" t="inlineStr">
         <is>
-          <t>447856969170</t>
+          <t>+447856969170</t>
         </is>
       </c>
       <c r="I865" t="inlineStr"/>
@@ -53908,7 +53908,7 @@
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t>L865</t>
+          <t>L878</t>
         </is>
       </c>
       <c r="B866" t="inlineStr">
@@ -53935,7 +53935,7 @@
       </c>
       <c r="H866" t="inlineStr">
         <is>
-          <t>447475938425</t>
+          <t>+447475938425</t>
         </is>
       </c>
       <c r="I866" t="inlineStr"/>
@@ -53957,7 +53957,7 @@
     <row r="867">
       <c r="A867" t="inlineStr">
         <is>
-          <t>L866</t>
+          <t>L879</t>
         </is>
       </c>
       <c r="B867" t="inlineStr">
@@ -53984,7 +53984,7 @@
       </c>
       <c r="H867" t="inlineStr">
         <is>
-          <t>447811575614</t>
+          <t>+447811575614</t>
         </is>
       </c>
       <c r="I867" t="inlineStr"/>
@@ -54002,7 +54002,7 @@
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t>L867</t>
+          <t>L880</t>
         </is>
       </c>
       <c r="B868" t="inlineStr">
@@ -54029,7 +54029,7 @@
       </c>
       <c r="H868" t="inlineStr">
         <is>
-          <t>447811006469</t>
+          <t>+447811006469</t>
         </is>
       </c>
       <c r="I868" t="inlineStr"/>
@@ -54055,7 +54055,7 @@
     <row r="869">
       <c r="A869" t="inlineStr">
         <is>
-          <t>L868</t>
+          <t>L881</t>
         </is>
       </c>
       <c r="B869" t="inlineStr">
@@ -54082,7 +54082,7 @@
       </c>
       <c r="H869" t="inlineStr">
         <is>
-          <t>447591214756</t>
+          <t>+447591214756</t>
         </is>
       </c>
       <c r="I869" t="inlineStr"/>
@@ -54108,7 +54108,7 @@
     <row r="870">
       <c r="A870" t="inlineStr">
         <is>
-          <t>L869</t>
+          <t>L882</t>
         </is>
       </c>
       <c r="B870" t="inlineStr">
@@ -54135,7 +54135,7 @@
       </c>
       <c r="H870" t="inlineStr">
         <is>
-          <t>447519038169</t>
+          <t>+447519038169</t>
         </is>
       </c>
       <c r="I870" t="inlineStr"/>
@@ -54157,7 +54157,7 @@
     <row r="871">
       <c r="A871" t="inlineStr">
         <is>
-          <t>L870</t>
+          <t>L883</t>
         </is>
       </c>
       <c r="B871" t="inlineStr">
@@ -54184,7 +54184,7 @@
       </c>
       <c r="H871" t="inlineStr">
         <is>
-          <t>447713499484</t>
+          <t>+447713499484</t>
         </is>
       </c>
       <c r="I871" t="inlineStr"/>
@@ -54206,7 +54206,7 @@
     <row r="872">
       <c r="A872" t="inlineStr">
         <is>
-          <t>L871</t>
+          <t>L884</t>
         </is>
       </c>
       <c r="B872" t="inlineStr">
@@ -54255,7 +54255,7 @@
     <row r="873">
       <c r="A873" t="inlineStr">
         <is>
-          <t>L872</t>
+          <t>L885</t>
         </is>
       </c>
       <c r="B873" t="inlineStr">
@@ -54282,7 +54282,7 @@
       </c>
       <c r="H873" t="inlineStr">
         <is>
-          <t>447700148142</t>
+          <t>+447700148142</t>
         </is>
       </c>
       <c r="I873" t="inlineStr"/>
@@ -54304,7 +54304,7 @@
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>L873</t>
+          <t>L886</t>
         </is>
       </c>
       <c r="B874" t="inlineStr">
@@ -54331,7 +54331,7 @@
       </c>
       <c r="H874" t="inlineStr">
         <is>
-          <t>447946650820</t>
+          <t>+447946650820</t>
         </is>
       </c>
       <c r="I874" t="inlineStr"/>
@@ -54357,7 +54357,7 @@
     <row r="875">
       <c r="A875" t="inlineStr">
         <is>
-          <t>L874</t>
+          <t>L887</t>
         </is>
       </c>
       <c r="B875" t="inlineStr">
@@ -54384,7 +54384,7 @@
       </c>
       <c r="H875" t="inlineStr">
         <is>
-          <t>441617430028</t>
+          <t>+441617430028</t>
         </is>
       </c>
       <c r="I875" t="inlineStr"/>
@@ -54406,7 +54406,7 @@
     <row r="876">
       <c r="A876" t="inlineStr">
         <is>
-          <t>L875</t>
+          <t>L888</t>
         </is>
       </c>
       <c r="B876" t="inlineStr">
@@ -54433,7 +54433,7 @@
       </c>
       <c r="H876" t="inlineStr">
         <is>
-          <t>447847888828</t>
+          <t>+447847888828</t>
         </is>
       </c>
       <c r="I876" t="inlineStr"/>
@@ -54455,7 +54455,7 @@
     <row r="877">
       <c r="A877" t="inlineStr">
         <is>
-          <t>L876</t>
+          <t>L889</t>
         </is>
       </c>
       <c r="B877" t="inlineStr">
@@ -54482,7 +54482,7 @@
       </c>
       <c r="H877" t="inlineStr">
         <is>
-          <t>447932592556</t>
+          <t>+447932592556</t>
         </is>
       </c>
       <c r="I877" t="inlineStr"/>
@@ -54504,7 +54504,7 @@
     <row r="878">
       <c r="A878" t="inlineStr">
         <is>
-          <t>L877</t>
+          <t>L890</t>
         </is>
       </c>
       <c r="B878" t="inlineStr">
@@ -54549,7 +54549,7 @@
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>L878</t>
+          <t>L891</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
@@ -54576,7 +54576,7 @@
       </c>
       <c r="H879" t="inlineStr">
         <is>
-          <t>447791040637</t>
+          <t>+447791040637</t>
         </is>
       </c>
       <c r="I879" t="inlineStr"/>
@@ -54598,7 +54598,7 @@
     <row r="880">
       <c r="A880" t="inlineStr">
         <is>
-          <t>L879</t>
+          <t>L892</t>
         </is>
       </c>
       <c r="B880" t="inlineStr">
@@ -54625,7 +54625,7 @@
       </c>
       <c r="H880" t="inlineStr">
         <is>
-          <t>447506746662</t>
+          <t>+447506746662</t>
         </is>
       </c>
       <c r="I880" t="inlineStr"/>
@@ -54651,7 +54651,7 @@
     <row r="881">
       <c r="A881" t="inlineStr">
         <is>
-          <t>L880</t>
+          <t>L893</t>
         </is>
       </c>
       <c r="B881" t="inlineStr">
@@ -54678,7 +54678,7 @@
       </c>
       <c r="H881" t="inlineStr">
         <is>
-          <t>447743991146</t>
+          <t>+447743991146</t>
         </is>
       </c>
       <c r="I881" t="inlineStr"/>
@@ -54700,7 +54700,7 @@
     <row r="882">
       <c r="A882" t="inlineStr">
         <is>
-          <t>L881</t>
+          <t>L894</t>
         </is>
       </c>
       <c r="B882" t="inlineStr">
@@ -54745,7 +54745,7 @@
     <row r="883">
       <c r="A883" t="inlineStr">
         <is>
-          <t>L882</t>
+          <t>L895</t>
         </is>
       </c>
       <c r="B883" t="inlineStr">
@@ -54772,7 +54772,7 @@
       </c>
       <c r="H883" t="inlineStr">
         <is>
-          <t>441612476447</t>
+          <t>+441612476447</t>
         </is>
       </c>
       <c r="I883" t="inlineStr"/>
@@ -54794,7 +54794,7 @@
     <row r="884">
       <c r="A884" t="inlineStr">
         <is>
-          <t>L883</t>
+          <t>L896</t>
         </is>
       </c>
       <c r="B884" t="inlineStr">
@@ -54821,7 +54821,7 @@
       </c>
       <c r="H884" t="inlineStr">
         <is>
-          <t>447525441949</t>
+          <t>+447525441949</t>
         </is>
       </c>
       <c r="I884" t="inlineStr"/>
@@ -54847,7 +54847,7 @@
     <row r="885">
       <c r="A885" t="inlineStr">
         <is>
-          <t>L884</t>
+          <t>L897</t>
         </is>
       </c>
       <c r="B885" t="inlineStr">
@@ -54874,7 +54874,7 @@
       </c>
       <c r="H885" t="inlineStr">
         <is>
-          <t>447825446825</t>
+          <t>+447825446825</t>
         </is>
       </c>
       <c r="I885" t="inlineStr"/>
@@ -54900,7 +54900,7 @@
     <row r="886">
       <c r="A886" t="inlineStr">
         <is>
-          <t>L885</t>
+          <t>L898</t>
         </is>
       </c>
       <c r="B886" t="inlineStr">
@@ -54927,7 +54927,7 @@
       </c>
       <c r="H886" t="inlineStr">
         <is>
-          <t>447838355221</t>
+          <t>+447838355221</t>
         </is>
       </c>
       <c r="I886" t="inlineStr"/>
@@ -54949,7 +54949,7 @@
     <row r="887">
       <c r="A887" t="inlineStr">
         <is>
-          <t>L886</t>
+          <t>L899</t>
         </is>
       </c>
       <c r="B887" t="inlineStr">
@@ -54976,7 +54976,7 @@
       </c>
       <c r="H887" t="inlineStr">
         <is>
-          <t>447903644928</t>
+          <t>+447903644928</t>
         </is>
       </c>
       <c r="I887" t="inlineStr"/>
@@ -55002,7 +55002,7 @@
     <row r="888">
       <c r="A888" t="inlineStr">
         <is>
-          <t>L887</t>
+          <t>L900</t>
         </is>
       </c>
       <c r="B888" t="inlineStr">
@@ -55051,7 +55051,7 @@
     <row r="889">
       <c r="A889" t="inlineStr">
         <is>
-          <t>L888</t>
+          <t>L901</t>
         </is>
       </c>
       <c r="B889" t="inlineStr">
@@ -55078,7 +55078,7 @@
       </c>
       <c r="H889" t="inlineStr">
         <is>
-          <t>447738497319</t>
+          <t>+447738497319</t>
         </is>
       </c>
       <c r="I889" t="inlineStr"/>
@@ -55104,7 +55104,7 @@
     <row r="890">
       <c r="A890" t="inlineStr">
         <is>
-          <t>L889</t>
+          <t>L902</t>
         </is>
       </c>
       <c r="B890" t="inlineStr">
@@ -55131,7 +55131,7 @@
       </c>
       <c r="H890" t="inlineStr">
         <is>
-          <t>447511767186</t>
+          <t>+447511767186</t>
         </is>
       </c>
       <c r="I890" t="inlineStr"/>
@@ -55157,7 +55157,7 @@
     <row r="891">
       <c r="A891" t="inlineStr">
         <is>
-          <t>L890</t>
+          <t>L903</t>
         </is>
       </c>
       <c r="B891" t="inlineStr">
@@ -55206,7 +55206,7 @@
     <row r="892">
       <c r="A892" t="inlineStr">
         <is>
-          <t>L891</t>
+          <t>L904</t>
         </is>
       </c>
       <c r="B892" t="inlineStr">
@@ -55233,7 +55233,7 @@
       </c>
       <c r="H892" t="inlineStr">
         <is>
-          <t>447765922725</t>
+          <t>+447765922725</t>
         </is>
       </c>
       <c r="I892" t="inlineStr"/>
@@ -55259,7 +55259,7 @@
     <row r="893">
       <c r="A893" t="inlineStr">
         <is>
-          <t>L892</t>
+          <t>L905</t>
         </is>
       </c>
       <c r="B893" t="inlineStr">
@@ -55286,7 +55286,7 @@
       </c>
       <c r="H893" t="inlineStr">
         <is>
-          <t>447761882289</t>
+          <t>+447761882289</t>
         </is>
       </c>
       <c r="I893" t="inlineStr"/>
@@ -55308,7 +55308,7 @@
     <row r="894">
       <c r="A894" t="inlineStr">
         <is>
-          <t>L893</t>
+          <t>L906</t>
         </is>
       </c>
       <c r="B894" t="inlineStr">
@@ -55335,7 +55335,7 @@
       </c>
       <c r="H894" t="inlineStr">
         <is>
-          <t>441616975330</t>
+          <t>+441616975330</t>
         </is>
       </c>
       <c r="I894" t="inlineStr"/>
@@ -55361,7 +55361,7 @@
     <row r="895">
       <c r="A895" t="inlineStr">
         <is>
-          <t>L894</t>
+          <t>L907</t>
         </is>
       </c>
       <c r="B895" t="inlineStr">
@@ -55388,7 +55388,7 @@
       </c>
       <c r="H895" t="inlineStr">
         <is>
-          <t>447799424337</t>
+          <t>+447799424337</t>
         </is>
       </c>
       <c r="I895" t="inlineStr"/>
@@ -55410,7 +55410,7 @@
     <row r="896">
       <c r="A896" t="inlineStr">
         <is>
-          <t>L895</t>
+          <t>L908</t>
         </is>
       </c>
       <c r="B896" t="inlineStr">
@@ -55437,7 +55437,7 @@
       </c>
       <c r="H896" t="inlineStr">
         <is>
-          <t>447949066244</t>
+          <t>+447949066244</t>
         </is>
       </c>
       <c r="I896" t="inlineStr"/>
@@ -55459,7 +55459,7 @@
     <row r="897">
       <c r="A897" t="inlineStr">
         <is>
-          <t>L896</t>
+          <t>L909</t>
         </is>
       </c>
       <c r="B897" t="inlineStr">
@@ -55486,7 +55486,7 @@
       </c>
       <c r="H897" t="inlineStr">
         <is>
-          <t>447974649015</t>
+          <t>+447974649015</t>
         </is>
       </c>
       <c r="I897" t="inlineStr"/>
@@ -55512,7 +55512,7 @@
     <row r="898">
       <c r="A898" t="inlineStr">
         <is>
-          <t>L897</t>
+          <t>L910</t>
         </is>
       </c>
       <c r="B898" t="inlineStr">
@@ -55539,7 +55539,7 @@
       </c>
       <c r="H898" t="inlineStr">
         <is>
-          <t>447799827017</t>
+          <t>+447799827017</t>
         </is>
       </c>
       <c r="I898" t="inlineStr"/>
@@ -55561,7 +55561,7 @@
     <row r="899">
       <c r="A899" t="inlineStr">
         <is>
-          <t>L898</t>
+          <t>L911</t>
         </is>
       </c>
       <c r="B899" t="inlineStr">
@@ -55588,7 +55588,7 @@
       </c>
       <c r="H899" t="inlineStr">
         <is>
-          <t>447909673894</t>
+          <t>+447909673894</t>
         </is>
       </c>
       <c r="I899" t="inlineStr"/>
@@ -55614,7 +55614,7 @@
     <row r="900">
       <c r="A900" t="inlineStr">
         <is>
-          <t>L899</t>
+          <t>L912</t>
         </is>
       </c>
       <c r="B900" t="inlineStr">
@@ -55641,7 +55641,7 @@
       </c>
       <c r="H900" t="inlineStr">
         <is>
-          <t>447801498677</t>
+          <t>+447801498677</t>
         </is>
       </c>
       <c r="I900" t="inlineStr"/>
@@ -55667,7 +55667,7 @@
     <row r="901">
       <c r="A901" t="inlineStr">
         <is>
-          <t>L900</t>
+          <t>L913</t>
         </is>
       </c>
       <c r="B901" t="inlineStr">
@@ -55694,7 +55694,7 @@
       </c>
       <c r="H901" t="inlineStr">
         <is>
-          <t>447843304308</t>
+          <t>+447843304308</t>
         </is>
       </c>
       <c r="I901" t="inlineStr"/>
@@ -55720,7 +55720,7 @@
     <row r="902">
       <c r="A902" t="inlineStr">
         <is>
-          <t>L901</t>
+          <t>L914</t>
         </is>
       </c>
       <c r="B902" t="inlineStr">
@@ -55747,7 +55747,7 @@
       </c>
       <c r="H902" t="inlineStr">
         <is>
-          <t>441617284449</t>
+          <t>+441617284449</t>
         </is>
       </c>
       <c r="I902" t="inlineStr"/>
@@ -55773,7 +55773,7 @@
     <row r="903">
       <c r="A903" t="inlineStr">
         <is>
-          <t>L902</t>
+          <t>L915</t>
         </is>
       </c>
       <c r="B903" t="inlineStr">
@@ -55818,7 +55818,7 @@
     <row r="904">
       <c r="A904" t="inlineStr">
         <is>
-          <t>L903</t>
+          <t>L916</t>
         </is>
       </c>
       <c r="B904" t="inlineStr">
@@ -55845,7 +55845,7 @@
       </c>
       <c r="H904" t="inlineStr">
         <is>
-          <t>447930511659</t>
+          <t>+447930511659</t>
         </is>
       </c>
       <c r="I904" t="inlineStr"/>
@@ -55871,7 +55871,7 @@
     <row r="905">
       <c r="A905" t="inlineStr">
         <is>
-          <t>L904</t>
+          <t>L917</t>
         </is>
       </c>
       <c r="B905" t="inlineStr">
@@ -55898,7 +55898,7 @@
       </c>
       <c r="H905" t="inlineStr">
         <is>
-          <t>441612360686</t>
+          <t>+441612360686</t>
         </is>
       </c>
       <c r="I905" t="inlineStr"/>
@@ -55924,7 +55924,7 @@
     <row r="906">
       <c r="A906" t="inlineStr">
         <is>
-          <t>L905</t>
+          <t>L918</t>
         </is>
       </c>
       <c r="B906" t="inlineStr">
@@ -55951,7 +55951,7 @@
       </c>
       <c r="H906" t="inlineStr">
         <is>
-          <t>447746661931</t>
+          <t>+447746661931</t>
         </is>
       </c>
       <c r="I906" t="inlineStr"/>
@@ -55977,7 +55977,7 @@
     <row r="907">
       <c r="A907" t="inlineStr">
         <is>
-          <t>L906</t>
+          <t>L919</t>
         </is>
       </c>
       <c r="B907" t="inlineStr">
@@ -56004,7 +56004,7 @@
       </c>
       <c r="H907" t="inlineStr">
         <is>
-          <t>447776437440</t>
+          <t>+447776437440</t>
         </is>
       </c>
       <c r="I907" t="inlineStr"/>
@@ -56022,7 +56022,7 @@
     <row r="908">
       <c r="A908" t="inlineStr">
         <is>
-          <t>L907</t>
+          <t>L920</t>
         </is>
       </c>
       <c r="B908" t="inlineStr">
@@ -56049,7 +56049,7 @@
       </c>
       <c r="H908" t="inlineStr">
         <is>
-          <t>441612278708</t>
+          <t>+441612278708</t>
         </is>
       </c>
       <c r="I908" t="inlineStr"/>
@@ -56071,7 +56071,7 @@
     <row r="909">
       <c r="A909" t="inlineStr">
         <is>
-          <t>L908</t>
+          <t>L921</t>
         </is>
       </c>
       <c r="B909" t="inlineStr">
@@ -56120,7 +56120,7 @@
     <row r="910">
       <c r="A910" t="inlineStr">
         <is>
-          <t>L909</t>
+          <t>L922</t>
         </is>
       </c>
       <c r="B910" t="inlineStr">
@@ -56147,7 +56147,7 @@
       </c>
       <c r="H910" t="inlineStr">
         <is>
-          <t>447951246860</t>
+          <t>+447951246860</t>
         </is>
       </c>
       <c r="I910" t="inlineStr"/>
@@ -56169,7 +56169,7 @@
     <row r="911">
       <c r="A911" t="inlineStr">
         <is>
-          <t>L910</t>
+          <t>L923</t>
         </is>
       </c>
       <c r="B911" t="inlineStr">
@@ -56196,7 +56196,7 @@
       </c>
       <c r="H911" t="inlineStr">
         <is>
-          <t>443300888974</t>
+          <t>+443300888974</t>
         </is>
       </c>
       <c r="I911" t="inlineStr"/>
@@ -56222,7 +56222,7 @@
     <row r="912">
       <c r="A912" t="inlineStr">
         <is>
-          <t>L911</t>
+          <t>L924</t>
         </is>
       </c>
       <c r="B912" t="inlineStr">
@@ -56249,7 +56249,7 @@
       </c>
       <c r="H912" t="inlineStr">
         <is>
-          <t>441616835046</t>
+          <t>+441616835046</t>
         </is>
       </c>
       <c r="I912" t="inlineStr"/>
@@ -56267,7 +56267,7 @@
     <row r="913">
       <c r="A913" t="inlineStr">
         <is>
-          <t>L912</t>
+          <t>L925</t>
         </is>
       </c>
       <c r="B913" t="inlineStr">
@@ -56294,7 +56294,7 @@
       </c>
       <c r="H913" t="inlineStr">
         <is>
-          <t>447832983843</t>
+          <t>+447832983843</t>
         </is>
       </c>
       <c r="I913" t="inlineStr"/>
@@ -56316,7 +56316,7 @@
     <row r="914">
       <c r="A914" t="inlineStr">
         <is>
-          <t>L913</t>
+          <t>L926</t>
         </is>
       </c>
       <c r="B914" t="inlineStr">
@@ -56343,7 +56343,7 @@
       </c>
       <c r="H914" t="inlineStr">
         <is>
-          <t>447510947761</t>
+          <t>+447510947761</t>
         </is>
       </c>
       <c r="I914" t="inlineStr"/>
@@ -56365,7 +56365,7 @@
     <row r="915">
       <c r="A915" t="inlineStr">
         <is>
-          <t>L914</t>
+          <t>L927</t>
         </is>
       </c>
       <c r="B915" t="inlineStr">
@@ -56392,7 +56392,7 @@
       </c>
       <c r="H915" t="inlineStr">
         <is>
-          <t>447467435330</t>
+          <t>+447467435330</t>
         </is>
       </c>
       <c r="I915" t="inlineStr"/>
@@ -56418,7 +56418,7 @@
     <row r="916">
       <c r="A916" t="inlineStr">
         <is>
-          <t>L915</t>
+          <t>L928</t>
         </is>
       </c>
       <c r="B916" t="inlineStr">
@@ -56445,7 +56445,7 @@
       </c>
       <c r="H916" t="inlineStr">
         <is>
-          <t>441616085215</t>
+          <t>+441616085215</t>
         </is>
       </c>
       <c r="I916" t="inlineStr"/>
@@ -56471,7 +56471,7 @@
     <row r="917">
       <c r="A917" t="inlineStr">
         <is>
-          <t>L916</t>
+          <t>L929</t>
         </is>
       </c>
       <c r="B917" t="inlineStr">
@@ -56498,7 +56498,7 @@
       </c>
       <c r="H917" t="inlineStr">
         <is>
-          <t>447944838529</t>
+          <t>+447944838529</t>
         </is>
       </c>
       <c r="I917" t="inlineStr"/>
@@ -56516,7 +56516,7 @@
     <row r="918">
       <c r="A918" t="inlineStr">
         <is>
-          <t>L917</t>
+          <t>L930</t>
         </is>
       </c>
       <c r="B918" t="inlineStr">
@@ -56543,7 +56543,7 @@
       </c>
       <c r="H918" t="inlineStr">
         <is>
-          <t>447757623229</t>
+          <t>+447757623229</t>
         </is>
       </c>
       <c r="I918" t="inlineStr"/>
@@ -56561,7 +56561,7 @@
     <row r="919">
       <c r="A919" t="inlineStr">
         <is>
-          <t>L918</t>
+          <t>L931</t>
         </is>
       </c>
       <c r="B919" t="inlineStr">
@@ -56606,7 +56606,7 @@
     <row r="920">
       <c r="A920" t="inlineStr">
         <is>
-          <t>L919</t>
+          <t>L932</t>
         </is>
       </c>
       <c r="B920" t="inlineStr">
@@ -56633,7 +56633,7 @@
       </c>
       <c r="H920" t="inlineStr">
         <is>
-          <t>447774723839</t>
+          <t>+447774723839</t>
         </is>
       </c>
       <c r="I920" t="inlineStr"/>
@@ -56659,7 +56659,7 @@
     <row r="921">
       <c r="A921" t="inlineStr">
         <is>
-          <t>L920</t>
+          <t>L933</t>
         </is>
       </c>
       <c r="B921" t="inlineStr">
@@ -56686,7 +56686,7 @@
       </c>
       <c r="H921" t="inlineStr">
         <is>
-          <t>447951219442</t>
+          <t>+447951219442</t>
         </is>
       </c>
       <c r="I921" t="inlineStr"/>
@@ -56708,7 +56708,7 @@
     <row r="922">
       <c r="A922" t="inlineStr">
         <is>
-          <t>L921</t>
+          <t>L934</t>
         </is>
       </c>
       <c r="B922" t="inlineStr">
@@ -56735,7 +56735,7 @@
       </c>
       <c r="H922" t="inlineStr">
         <is>
-          <t>447886035030</t>
+          <t>+447886035030</t>
         </is>
       </c>
       <c r="I922" t="inlineStr"/>
@@ -56761,7 +56761,7 @@
     <row r="923">
       <c r="A923" t="inlineStr">
         <is>
-          <t>L922</t>
+          <t>L935</t>
         </is>
       </c>
       <c r="B923" t="inlineStr">
@@ -56788,7 +56788,7 @@
       </c>
       <c r="H923" t="inlineStr">
         <is>
-          <t>441615665798</t>
+          <t>+441615665798</t>
         </is>
       </c>
       <c r="I923" t="inlineStr"/>
@@ -56810,7 +56810,7 @@
     <row r="924">
       <c r="A924" t="inlineStr">
         <is>
-          <t>L923</t>
+          <t>L936</t>
         </is>
       </c>
       <c r="B924" t="inlineStr">
@@ -56837,7 +56837,7 @@
       </c>
       <c r="H924" t="inlineStr">
         <is>
-          <t>441617078124</t>
+          <t>+441617078124</t>
         </is>
       </c>
       <c r="I924" t="inlineStr"/>
@@ -56855,7 +56855,7 @@
     <row r="925">
       <c r="A925" t="inlineStr">
         <is>
-          <t>L924</t>
+          <t>L937</t>
         </is>
       </c>
       <c r="B925" t="inlineStr">
@@ -56882,7 +56882,7 @@
       </c>
       <c r="H925" t="inlineStr">
         <is>
-          <t>447854868113</t>
+          <t>+447854868113</t>
         </is>
       </c>
       <c r="I925" t="inlineStr"/>
@@ -56908,7 +56908,7 @@
     <row r="926">
       <c r="A926" t="inlineStr">
         <is>
-          <t>L925</t>
+          <t>L938</t>
         </is>
       </c>
       <c r="B926" t="inlineStr">
@@ -56935,7 +56935,7 @@
       </c>
       <c r="H926" t="inlineStr">
         <is>
-          <t>447562648802</t>
+          <t>+447562648802</t>
         </is>
       </c>
       <c r="I926" t="inlineStr"/>
@@ -56953,7 +56953,7 @@
     <row r="927">
       <c r="A927" t="inlineStr">
         <is>
-          <t>L926</t>
+          <t>L939</t>
         </is>
       </c>
       <c r="B927" t="inlineStr">
@@ -56980,7 +56980,7 @@
       </c>
       <c r="H927" t="inlineStr">
         <is>
-          <t>447863877959</t>
+          <t>+447863877959</t>
         </is>
       </c>
       <c r="I927" t="inlineStr"/>
@@ -57006,7 +57006,7 @@
     <row r="928">
       <c r="A928" t="inlineStr">
         <is>
-          <t>L927</t>
+          <t>L940</t>
         </is>
       </c>
       <c r="B928" t="inlineStr">
@@ -57033,7 +57033,7 @@
       </c>
       <c r="H928" t="inlineStr">
         <is>
-          <t>447748567595</t>
+          <t>+447748567595</t>
         </is>
       </c>
       <c r="I928" t="inlineStr"/>
@@ -57055,7 +57055,7 @@
     <row r="929">
       <c r="A929" t="inlineStr">
         <is>
-          <t>L928</t>
+          <t>L941</t>
         </is>
       </c>
       <c r="B929" t="inlineStr">
@@ -57082,7 +57082,7 @@
       </c>
       <c r="H929" t="inlineStr">
         <is>
-          <t>441615472679</t>
+          <t>+441615472679</t>
         </is>
       </c>
       <c r="I929" t="inlineStr"/>
@@ -57108,7 +57108,7 @@
     <row r="930">
       <c r="A930" t="inlineStr">
         <is>
-          <t>L929</t>
+          <t>L942</t>
         </is>
       </c>
       <c r="B930" t="inlineStr">
@@ -57135,7 +57135,7 @@
       </c>
       <c r="H930" t="inlineStr">
         <is>
-          <t>447554299598</t>
+          <t>+447554299598</t>
         </is>
       </c>
       <c r="I930" t="inlineStr"/>
@@ -57153,7 +57153,7 @@
     <row r="931">
       <c r="A931" t="inlineStr">
         <is>
-          <t>L930</t>
+          <t>L943</t>
         </is>
       </c>
       <c r="B931" t="inlineStr">
@@ -57202,7 +57202,7 @@
     <row r="932">
       <c r="A932" t="inlineStr">
         <is>
-          <t>L931</t>
+          <t>L944</t>
         </is>
       </c>
       <c r="B932" t="inlineStr">
@@ -57229,7 +57229,7 @@
       </c>
       <c r="H932" t="inlineStr">
         <is>
-          <t>447890869960</t>
+          <t>+447890869960</t>
         </is>
       </c>
       <c r="I932" t="inlineStr"/>
@@ -57251,7 +57251,7 @@
     <row r="933">
       <c r="A933" t="inlineStr">
         <is>
-          <t>L932</t>
+          <t>L945</t>
         </is>
       </c>
       <c r="B933" t="inlineStr">
@@ -57278,7 +57278,7 @@
       </c>
       <c r="H933" t="inlineStr">
         <is>
-          <t>447759383081</t>
+          <t>+447759383081</t>
         </is>
       </c>
       <c r="I933" t="inlineStr"/>
@@ -57296,7 +57296,7 @@
     <row r="934">
       <c r="A934" t="inlineStr">
         <is>
-          <t>L933</t>
+          <t>L946</t>
         </is>
       </c>
       <c r="B934" t="inlineStr">
@@ -57323,7 +57323,7 @@
       </c>
       <c r="H934" t="inlineStr">
         <is>
-          <t>447927127256</t>
+          <t>+447927127256</t>
         </is>
       </c>
       <c r="I934" t="inlineStr"/>
@@ -57341,7 +57341,7 @@
     <row r="935">
       <c r="A935" t="inlineStr">
         <is>
-          <t>L934</t>
+          <t>L947</t>
         </is>
       </c>
       <c r="B935" t="inlineStr">
@@ -57372,7 +57372,7 @@
       </c>
       <c r="H935" t="inlineStr">
         <is>
-          <t>447833257747</t>
+          <t>+447833257747</t>
         </is>
       </c>
       <c r="I935" t="inlineStr"/>
@@ -57394,7 +57394,7 @@
     <row r="936">
       <c r="A936" t="inlineStr">
         <is>
-          <t>L935</t>
+          <t>L948</t>
         </is>
       </c>
       <c r="B936" t="inlineStr">
@@ -57421,7 +57421,7 @@
       </c>
       <c r="H936" t="inlineStr">
         <is>
-          <t>447770583190</t>
+          <t>+447770583190</t>
         </is>
       </c>
       <c r="I936" t="inlineStr"/>
@@ -57443,7 +57443,7 @@
     <row r="937">
       <c r="A937" t="inlineStr">
         <is>
-          <t>L936</t>
+          <t>L949</t>
         </is>
       </c>
       <c r="B937" t="inlineStr">
@@ -57470,7 +57470,7 @@
       </c>
       <c r="H937" t="inlineStr">
         <is>
-          <t>447500584846</t>
+          <t>+447500584846</t>
         </is>
       </c>
       <c r="I937" t="inlineStr"/>
@@ -57488,7 +57488,7 @@
     <row r="938">
       <c r="A938" t="inlineStr">
         <is>
-          <t>L937</t>
+          <t>L950</t>
         </is>
       </c>
       <c r="B938" t="inlineStr">
@@ -57537,7 +57537,7 @@
     <row r="939">
       <c r="A939" t="inlineStr">
         <is>
-          <t>L938</t>
+          <t>L951</t>
         </is>
       </c>
       <c r="B939" t="inlineStr">
@@ -57564,7 +57564,7 @@
       </c>
       <c r="H939" t="inlineStr">
         <is>
-          <t>447476927426</t>
+          <t>+447476927426</t>
         </is>
       </c>
       <c r="I939" t="inlineStr"/>
@@ -57586,7 +57586,7 @@
     <row r="940">
       <c r="A940" t="inlineStr">
         <is>
-          <t>L939</t>
+          <t>L952</t>
         </is>
       </c>
       <c r="B940" t="inlineStr">
@@ -57613,7 +57613,7 @@
       </c>
       <c r="H940" t="inlineStr">
         <is>
-          <t>447496555708</t>
+          <t>+447496555708</t>
         </is>
       </c>
       <c r="I940" t="inlineStr"/>
@@ -57639,7 +57639,7 @@
     <row r="941">
       <c r="A941" t="inlineStr">
         <is>
-          <t>L940</t>
+          <t>L953</t>
         </is>
       </c>
       <c r="B941" t="inlineStr">
@@ -57666,7 +57666,7 @@
       </c>
       <c r="H941" t="inlineStr">
         <is>
-          <t>447398896732</t>
+          <t>+447398896732</t>
         </is>
       </c>
       <c r="I941" t="inlineStr"/>
@@ -57688,7 +57688,7 @@
     <row r="942">
       <c r="A942" t="inlineStr">
         <is>
-          <t>L941</t>
+          <t>L954</t>
         </is>
       </c>
       <c r="B942" t="inlineStr">
@@ -57715,7 +57715,7 @@
       </c>
       <c r="H942" t="inlineStr">
         <is>
-          <t>447448573150</t>
+          <t>+447448573150</t>
         </is>
       </c>
       <c r="I942" t="inlineStr"/>
@@ -57741,7 +57741,7 @@
     <row r="943">
       <c r="A943" t="inlineStr">
         <is>
-          <t>L942</t>
+          <t>L955</t>
         </is>
       </c>
       <c r="B943" t="inlineStr">
@@ -57768,7 +57768,7 @@
       </c>
       <c r="H943" t="inlineStr">
         <is>
-          <t>441613123100</t>
+          <t>+441613123100</t>
         </is>
       </c>
       <c r="I943" t="inlineStr"/>
@@ -57790,7 +57790,7 @@
     <row r="944">
       <c r="A944" t="inlineStr">
         <is>
-          <t>L943</t>
+          <t>L956</t>
         </is>
       </c>
       <c r="B944" t="inlineStr">
@@ -57817,7 +57817,7 @@
       </c>
       <c r="H944" t="inlineStr">
         <is>
-          <t>447549966379</t>
+          <t>+447549966379</t>
         </is>
       </c>
       <c r="I944" t="inlineStr"/>
@@ -57839,7 +57839,7 @@
     <row r="945">
       <c r="A945" t="inlineStr">
         <is>
-          <t>L944</t>
+          <t>L957</t>
         </is>
       </c>
       <c r="B945" t="inlineStr">
@@ -57866,7 +57866,7 @@
       </c>
       <c r="H945" t="inlineStr">
         <is>
-          <t>447973697683</t>
+          <t>+447973697683</t>
         </is>
       </c>
       <c r="I945" t="inlineStr"/>
@@ -57892,7 +57892,7 @@
     <row r="946">
       <c r="A946" t="inlineStr">
         <is>
-          <t>L945</t>
+          <t>L958</t>
         </is>
       </c>
       <c r="B946" t="inlineStr">
@@ -57919,7 +57919,7 @@
       </c>
       <c r="H946" t="inlineStr">
         <is>
-          <t>441613008795</t>
+          <t>+441613008795</t>
         </is>
       </c>
       <c r="I946" t="inlineStr"/>
@@ -57945,7 +57945,7 @@
     <row r="947">
       <c r="A947" t="inlineStr">
         <is>
-          <t>L946</t>
+          <t>L959</t>
         </is>
       </c>
       <c r="B947" t="inlineStr">
@@ -57972,7 +57972,7 @@
       </c>
       <c r="H947" t="inlineStr">
         <is>
-          <t>441614949191</t>
+          <t>+441614949191</t>
         </is>
       </c>
       <c r="I947" t="inlineStr"/>
@@ -57998,7 +57998,7 @@
     <row r="948">
       <c r="A948" t="inlineStr">
         <is>
-          <t>L947</t>
+          <t>L960</t>
         </is>
       </c>
       <c r="B948" t="inlineStr">
@@ -58025,7 +58025,7 @@
       </c>
       <c r="H948" t="inlineStr">
         <is>
-          <t>447555486603</t>
+          <t>+447555486603</t>
         </is>
       </c>
       <c r="I948" t="inlineStr"/>
@@ -58047,7 +58047,7 @@
     <row r="949">
       <c r="A949" t="inlineStr">
         <is>
-          <t>L948</t>
+          <t>L961</t>
         </is>
       </c>
       <c r="B949" t="inlineStr">
@@ -58074,7 +58074,7 @@
       </c>
       <c r="H949" t="inlineStr">
         <is>
-          <t>447760543735</t>
+          <t>+447760543735</t>
         </is>
       </c>
       <c r="I949" t="inlineStr"/>
@@ -58100,7 +58100,7 @@
     <row r="950">
       <c r="A950" t="inlineStr">
         <is>
-          <t>L949</t>
+          <t>L962</t>
         </is>
       </c>
       <c r="B950" t="inlineStr">
@@ -58127,7 +58127,7 @@
       </c>
       <c r="H950" t="inlineStr">
         <is>
-          <t>441616378110</t>
+          <t>+441616378110</t>
         </is>
       </c>
       <c r="I950" t="inlineStr"/>
@@ -58149,7 +58149,7 @@
     <row r="951">
       <c r="A951" t="inlineStr">
         <is>
-          <t>L950</t>
+          <t>L963</t>
         </is>
       </c>
       <c r="B951" t="inlineStr">
@@ -58176,7 +58176,7 @@
       </c>
       <c r="H951" t="inlineStr">
         <is>
-          <t>447715549105</t>
+          <t>+447715549105</t>
         </is>
       </c>
       <c r="I951" t="inlineStr"/>

--- a/HWA_Lead_Tracker.xlsx
+++ b/HWA_Lead_Tracker.xlsx
@@ -8,9 +8,11 @@
   </bookViews>
   <sheets>
     <sheet name="Leads" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Scrape Report" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$O$951</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -18,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,6 +31,11 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="13"/>
     </font>
   </fonts>
   <fills count="3">
@@ -40,7 +47,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
+        <fgColor rgb="001F4E4F"/>
+        <bgColor rgb="001F4E4F"/>
       </patternFill>
     </fill>
   </fills>
@@ -56,9 +64,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -427,21 +438,21 @@
   <dimension ref="A1:O951"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
-    <col width="24" customWidth="1" min="14" max="14"/>
-    <col width="24" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="46" customWidth="1" min="12" max="12"/>
+    <col width="40" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="36" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -43482,7 +43493,7 @@
       </c>
       <c r="L681" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M681" t="inlineStr">
@@ -43543,7 +43554,7 @@
       </c>
       <c r="L682" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M682" t="inlineStr">
@@ -43604,7 +43615,7 @@
       </c>
       <c r="L683" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M683" t="inlineStr">
@@ -43665,7 +43676,7 @@
       </c>
       <c r="L684" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M684" t="inlineStr">
@@ -43726,7 +43737,7 @@
       </c>
       <c r="L685" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M685" t="inlineStr">
@@ -43753,7 +43764,7 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>Unknown Gym</t>
+          <t>Kodokan 01</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
@@ -43787,7 +43798,7 @@
       </c>
       <c r="L686" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M686" t="inlineStr">
@@ -43848,7 +43859,7 @@
       </c>
       <c r="L687" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M687" t="inlineStr">
@@ -43909,7 +43920,7 @@
       </c>
       <c r="L688" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | EXCLUDED (Day 9 QA): constructed PEC address + website mismatch - contamination</t>
         </is>
       </c>
       <c r="M688" t="inlineStr">
@@ -43970,7 +43981,7 @@
       </c>
       <c r="L689" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M689" t="inlineStr">
@@ -44031,7 +44042,7 @@
       </c>
       <c r="L690" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | EXCLUDED (Day 9 QA): placeholder email esempio@ilmiosito.com</t>
         </is>
       </c>
       <c r="M690" t="inlineStr">
@@ -44092,7 +44103,7 @@
       </c>
       <c r="L691" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M691" t="inlineStr">
@@ -44153,7 +44164,7 @@
       </c>
       <c r="L692" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | EXCLUDED (Day 9 QA): parked domain ssdmtt.it</t>
         </is>
       </c>
       <c r="M692" t="inlineStr">
@@ -44180,7 +44191,7 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>Unknown Gym</t>
+          <t>KBC Boxe Genova</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
@@ -44214,7 +44225,7 @@
       </c>
       <c r="L693" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M693" t="inlineStr">
@@ -44275,7 +44286,7 @@
       </c>
       <c r="L694" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M694" t="inlineStr">
@@ -44302,7 +44313,7 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>Accademia Pugilistica Portoghese, Bari, Pugil</t>
+          <t>Accademia Pugilistica Portoghese</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
@@ -44336,7 +44347,7 @@
       </c>
       <c r="L695" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M695" t="inlineStr">
@@ -44405,7 +44416,7 @@
       </c>
       <c r="L696" t="inlineStr">
         <is>
-          <t>HUNTED Day 8 | IG profile not found (Day 8 batch)</t>
+          <t>HUNTED Day 8 | IG profile not found (Day 8 batch) | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M696" t="inlineStr">
@@ -44466,7 +44477,7 @@
       </c>
       <c r="L697" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | EXCLUDED (Day 9 QA): federation fpi.it - not a buyer</t>
         </is>
       </c>
       <c r="M697" t="inlineStr">
@@ -44527,7 +44538,7 @@
       </c>
       <c r="L698" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | EXCLUDED (Day 9 QA): constructed PEC address + website mismatch - contamination</t>
         </is>
       </c>
       <c r="M698" t="inlineStr">
@@ -44554,7 +44565,7 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>Kick Boxing Bari: scopri i corsi Gotham</t>
+          <t>Gotham Gym Bari</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
@@ -44588,7 +44599,7 @@
       </c>
       <c r="L699" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M699" t="inlineStr">
@@ -44649,7 +44660,7 @@
       </c>
       <c r="L700" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M700" t="inlineStr">
@@ -44676,7 +44687,7 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>Kickboxing</t>
+          <t>CFC Padova</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
@@ -44710,7 +44721,7 @@
       </c>
       <c r="L701" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M701" t="inlineStr">
@@ -44737,7 +44748,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>Corsi di KickBoxing</t>
+          <t>SDM Team</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
@@ -44771,7 +44782,7 @@
       </c>
       <c r="L702" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M702" t="inlineStr">
@@ -44832,7 +44843,7 @@
       </c>
       <c r="L703" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M703" t="inlineStr">
@@ -44859,7 +44870,7 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>Padova Top Team: La Palestra ad Abano Terme d</t>
+          <t>Padova Top Team</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
@@ -44893,7 +44904,7 @@
       </c>
       <c r="L704" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M704" t="inlineStr">
@@ -44920,7 +44931,7 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>Unknown Gym</t>
+          <t>MyClub Padova</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
@@ -44954,7 +44965,7 @@
       </c>
       <c r="L705" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M705" t="inlineStr">
@@ -45015,7 +45026,7 @@
       </c>
       <c r="L706" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | EXCLUDED (Day 9 QA): no live site gymup-city.it</t>
         </is>
       </c>
       <c r="M706" t="inlineStr">
@@ -45042,7 +45053,7 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>Info</t>
+          <t>Drago Blu</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
@@ -45076,7 +45087,7 @@
       </c>
       <c r="L707" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M707" t="inlineStr">
@@ -45103,7 +45114,7 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>Palestra di boxe a Verona</t>
+          <t>Speri Fight Club</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
@@ -45137,7 +45148,7 @@
       </c>
       <c r="L708" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M708" t="inlineStr">
@@ -45164,7 +45175,7 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>Unknown Gym</t>
+          <t>Verona Boxing Fighters</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
@@ -45198,7 +45209,7 @@
       </c>
       <c r="L709" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M709" t="inlineStr">
@@ -45259,7 +45270,7 @@
       </c>
       <c r="L710" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M710" t="inlineStr">
@@ -45286,7 +45297,7 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>Gym Boxe</t>
+          <t>Tempio degli Elfi</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
@@ -45320,7 +45331,7 @@
       </c>
       <c r="L711" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M711" t="inlineStr">
@@ -45347,7 +45358,7 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>Sport da combattimento Centro Forma Evolution</t>
+          <t>Centro Forma Evolution</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
@@ -45381,7 +45392,7 @@
       </c>
       <c r="L712" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M712" t="inlineStr">
@@ -45442,7 +45453,7 @@
       </c>
       <c r="L713" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M713" t="inlineStr">
@@ -45469,7 +45480,7 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>Nr.1 für Fitnessboxen</t>
+          <t>Box Academy Stuttgart</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
@@ -45503,7 +45514,7 @@
       </c>
       <c r="L714" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M714" t="inlineStr">
@@ -45564,7 +45575,7 @@
       </c>
       <c r="L715" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M715" t="inlineStr">
@@ -45625,7 +45636,7 @@
       </c>
       <c r="L716" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M716" t="inlineStr">
@@ -45652,7 +45663,7 @@
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>Unknown Gym</t>
+          <t>Sturm Boxing</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
@@ -45686,7 +45697,7 @@
       </c>
       <c r="L717" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M717" t="inlineStr">
@@ -45713,7 +45724,7 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>Boxing: Im Boxring Stuttgart</t>
+          <t>Uni Sport Hohenheim Boxen</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
@@ -45747,7 +45758,7 @@
       </c>
       <c r="L718" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M718" t="inlineStr">
@@ -45774,7 +45785,7 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>Dragon Gym Kampfkunstschule in Stuttgart</t>
+          <t>Dragon Gym Stuttgart</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
@@ -45808,7 +45819,7 @@
       </c>
       <c r="L719" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M719" t="inlineStr">
@@ -45869,7 +45880,7 @@
       </c>
       <c r="L720" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M720" t="inlineStr">
@@ -45896,7 +45907,7 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>Unknown Gym</t>
+          <t>MFA Gym</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
@@ -45930,7 +45941,7 @@
       </c>
       <c r="L721" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M721" t="inlineStr">
@@ -45957,7 +45968,7 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>MMA</t>
+          <t>Red Tiger Club Duesseldorf</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
@@ -45991,7 +46002,7 @@
       </c>
       <c r="L722" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M722" t="inlineStr">
@@ -46018,7 +46029,7 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>Unknown Gym</t>
+          <t>Boxklub Dresden</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
@@ -46052,7 +46063,7 @@
       </c>
       <c r="L723" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M723" t="inlineStr">
@@ -46113,7 +46124,7 @@
       </c>
       <c r="L724" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | EXCLUDED (Day 9 QA): email/site mismatch (taofit.de vs kampfsport-akademie.de)</t>
         </is>
       </c>
       <c r="M724" t="inlineStr">
@@ -46140,7 +46151,7 @@
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>Kampfsportzentrum Dresden: Kontakt und FAQ</t>
+          <t>Kampfsportzentrum Dresden</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
@@ -46174,7 +46185,7 @@
       </c>
       <c r="L725" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M725" t="inlineStr">
@@ -46235,7 +46246,7 @@
       </c>
       <c r="L726" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M726" t="inlineStr">
@@ -46262,7 +46273,7 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>Boxring Dresden e.V. in Dresden</t>
+          <t>Boxring Dresden</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
@@ -46296,7 +46307,7 @@
       </c>
       <c r="L727" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M727" t="inlineStr">
@@ -46357,7 +46368,7 @@
       </c>
       <c r="L728" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M728" t="inlineStr">
@@ -46384,7 +46395,7 @@
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>Kampfsport &amp; Selbstverteidigung in Dresden</t>
+          <t>Training Hoch 3 Kampfsport</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
@@ -46418,7 +46429,7 @@
       </c>
       <c r="L729" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M729" t="inlineStr">
@@ -46445,7 +46456,7 @@
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>I.S- Double Touch GYM Dresden e.V.</t>
+          <t>IS Double Touch Gym Dresden</t>
         </is>
       </c>
       <c r="C730" t="inlineStr">
@@ -46479,7 +46490,7 @@
       </c>
       <c r="L730" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M730" t="inlineStr">
@@ -46506,7 +46517,7 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>Unknown Gym</t>
+          <t>Kick-Box Verein Leipzig</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
@@ -46540,7 +46551,7 @@
       </c>
       <c r="L731" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M731" t="inlineStr">
@@ -46567,7 +46578,7 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>Kickboxen Training</t>
+          <t>Boxring Atlas</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
@@ -46601,7 +46612,7 @@
       </c>
       <c r="L732" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M732" t="inlineStr">
@@ -46628,7 +46639,7 @@
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>Kickboxen</t>
+          <t>Seiwakai Leipzig</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
@@ -46662,7 +46673,7 @@
       </c>
       <c r="L733" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M733" t="inlineStr">
@@ -46689,7 +46700,7 @@
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>Effektives Kickboxen in Leipzig</t>
+          <t>Prisma Empowerment</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
@@ -46731,7 +46742,7 @@
       </c>
       <c r="L734" t="inlineStr">
         <is>
-          <t>HUNTED Day 8 | IG profile not found (Day 8 batch)</t>
+          <t>HUNTED Day 8 | IG profile not found (Day 8 batch) | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M734" t="inlineStr">
@@ -46792,7 +46803,7 @@
       </c>
       <c r="L735" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M735" t="inlineStr">
@@ -46819,7 +46830,7 @@
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>Boxzentrum-Nuernberg</t>
+          <t>Boxzentrum Nuernberg</t>
         </is>
       </c>
       <c r="C736" t="inlineStr">
@@ -46853,7 +46864,7 @@
       </c>
       <c r="L736" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M736" t="inlineStr">
@@ -46880,7 +46891,7 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>Kontakt Boxclub Almaz Nürnberg</t>
+          <t>Boxclub Almaz Nuernberg</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
@@ -46914,7 +46925,7 @@
       </c>
       <c r="L737" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M737" t="inlineStr">
@@ -46975,7 +46986,7 @@
       </c>
       <c r="L738" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M738" t="inlineStr">
@@ -47036,7 +47047,7 @@
       </c>
       <c r="L739" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M739" t="inlineStr">
@@ -47063,7 +47074,7 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>The Gym Nuernberg</t>
         </is>
       </c>
       <c r="C740" t="inlineStr">
@@ -47097,7 +47108,7 @@
       </c>
       <c r="L740" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M740" t="inlineStr">
@@ -47124,7 +47135,7 @@
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>Unknown Gym</t>
+          <t>Boxenstop Nuernberg</t>
         </is>
       </c>
       <c r="C741" t="inlineStr">
@@ -47158,7 +47169,7 @@
       </c>
       <c r="L741" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M741" t="inlineStr">
@@ -47185,7 +47196,7 @@
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>Unknown Gym</t>
+          <t>Box-Club FCN</t>
         </is>
       </c>
       <c r="C742" t="inlineStr">
@@ -47219,7 +47230,7 @@
       </c>
       <c r="L742" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M742" t="inlineStr">
@@ -47246,7 +47257,7 @@
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>Unknown Gym</t>
+          <t>Kings Gym Hannover</t>
         </is>
       </c>
       <c r="C743" t="inlineStr">
@@ -47280,7 +47291,7 @@
       </c>
       <c r="L743" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | EMAIL FAILED (Day 9): recipient-not-registered</t>
         </is>
       </c>
       <c r="M743" t="inlineStr">
@@ -47341,7 +47352,7 @@
       </c>
       <c r="L744" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M744" t="inlineStr">
@@ -47368,7 +47379,7 @@
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>Mixed Martial Arts</t>
+          <t>Sticks and Stones</t>
         </is>
       </c>
       <c r="C745" t="inlineStr">
@@ -47402,7 +47413,7 @@
       </c>
       <c r="L745" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M745" t="inlineStr">
@@ -47429,7 +47440,7 @@
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>Kickboxen, Thaiboxen, Boxen, Karate, MMA, Rin</t>
+          <t>UFA Kampfsport</t>
         </is>
       </c>
       <c r="C746" t="inlineStr">
@@ -47463,7 +47474,7 @@
       </c>
       <c r="L746" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M746" t="inlineStr">
@@ -47490,7 +47501,7 @@
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>Unknown Gym</t>
+          <t>Fight Academy Groningen</t>
         </is>
       </c>
       <c r="C747" t="inlineStr">
@@ -47524,7 +47535,7 @@
       </c>
       <c r="L747" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M747" t="inlineStr">
@@ -47551,7 +47562,7 @@
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>Muay Thai Groningen, Assen &amp; Veendam</t>
+          <t>Paulo Boer Muay Thai</t>
         </is>
       </c>
       <c r="C748" t="inlineStr">
@@ -47585,7 +47596,7 @@
       </c>
       <c r="L748" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M748" t="inlineStr">
@@ -47612,7 +47623,7 @@
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>Unknown Gym</t>
+          <t>Kickboxing Groningen</t>
         </is>
       </c>
       <c r="C749" t="inlineStr">
@@ -47646,7 +47657,7 @@
       </c>
       <c r="L749" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M749" t="inlineStr">
@@ -47673,7 +47684,7 @@
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>Kung Fu / Wushu vereniging Bao Trieu / Blijd</t>
+          <t>Bao Trieu Kung Fu</t>
         </is>
       </c>
       <c r="C750" t="inlineStr">
@@ -47707,7 +47718,7 @@
       </c>
       <c r="L750" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M750" t="inlineStr">
@@ -47734,7 +47745,7 @@
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>Unknown Gym</t>
+          <t>Renshu Fights</t>
         </is>
       </c>
       <c r="C751" t="inlineStr">
@@ -47768,7 +47779,7 @@
       </c>
       <c r="L751" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M751" t="inlineStr">
@@ -47829,7 +47840,7 @@
       </c>
       <c r="L752" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M752" t="inlineStr">
@@ -47856,7 +47867,7 @@
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>Contact Muay-Thai Gym Enschede</t>
+          <t>Muay Thai Gym Enschede</t>
         </is>
       </c>
       <c r="C753" t="inlineStr">
@@ -47890,7 +47901,7 @@
       </c>
       <c r="L753" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M753" t="inlineStr">
@@ -47951,7 +47962,7 @@
       </c>
       <c r="L754" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M754" t="inlineStr">
@@ -47978,7 +47989,7 @@
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>Boxeo: clases en Zaragoza</t>
+          <t>Sabah Boxeo Zaragoza</t>
         </is>
       </c>
       <c r="C755" t="inlineStr">
@@ -48012,7 +48023,7 @@
       </c>
       <c r="L755" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M755" t="inlineStr">
@@ -48039,7 +48050,7 @@
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>Unknown Gym</t>
+          <t>Gallar Box</t>
         </is>
       </c>
       <c r="C756" t="inlineStr">
@@ -48073,7 +48084,7 @@
       </c>
       <c r="L756" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M756" t="inlineStr">
@@ -48100,7 +48111,7 @@
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>Boxeo en Zaragoza</t>
+          <t>Stadium Venecia</t>
         </is>
       </c>
       <c r="C757" t="inlineStr">
@@ -48134,7 +48145,7 @@
       </c>
       <c r="L757" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M757" t="inlineStr">
@@ -48161,7 +48172,7 @@
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>Boxeo Zaragoza</t>
+          <t>Karate Kan Zaragoza</t>
         </is>
       </c>
       <c r="C758" t="inlineStr">
@@ -48195,7 +48206,7 @@
       </c>
       <c r="L758" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M758" t="inlineStr">
@@ -48222,7 +48233,7 @@
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>Gimasio Almozara Zaragoza Kyokushin Mantente</t>
+          <t>Gimnasio Almozara</t>
         </is>
       </c>
       <c r="C759" t="inlineStr">
@@ -48256,7 +48267,7 @@
       </c>
       <c r="L759" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M759" t="inlineStr">
@@ -48283,7 +48294,7 @@
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>Academias de BJJ y MMA en Malaga</t>
+          <t>Arte Suave</t>
         </is>
       </c>
       <c r="C760" t="inlineStr">
@@ -48317,7 +48328,7 @@
       </c>
       <c r="L760" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M760" t="inlineStr">
@@ -48378,7 +48389,7 @@
       </c>
       <c r="L761" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M761" t="inlineStr">
@@ -48405,7 +48416,7 @@
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>Gimnasio de Muay Thai y MMA en Marbella</t>
+          <t>Baan Kai Muay</t>
         </is>
       </c>
       <c r="C762" t="inlineStr">
@@ -48439,7 +48450,7 @@
       </c>
       <c r="L762" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M762" t="inlineStr">
@@ -48500,7 +48511,7 @@
       </c>
       <c r="L763" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M763" t="inlineStr">
@@ -48561,7 +48572,7 @@
       </c>
       <c r="L764" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M764" t="inlineStr">
@@ -48588,7 +48599,7 @@
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>Artes Marciales</t>
+          <t>Dragons Club</t>
         </is>
       </c>
       <c r="C765" t="inlineStr">
@@ -48622,7 +48633,7 @@
       </c>
       <c r="L765" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M765" t="inlineStr">
@@ -48649,7 +48660,7 @@
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>Contacto Alicante</t>
+          <t>Fightland Alicante</t>
         </is>
       </c>
       <c r="C766" t="inlineStr">
@@ -48683,7 +48694,7 @@
       </c>
       <c r="L766" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M766" t="inlineStr">
@@ -48744,7 +48755,7 @@
       </c>
       <c r="L767" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M767" t="inlineStr">
@@ -48771,7 +48782,7 @@
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>Boxing Box</t>
+          <t>Arena Alicante Boxing</t>
         </is>
       </c>
       <c r="C768" t="inlineStr">
@@ -48805,7 +48816,7 @@
       </c>
       <c r="L768" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M768" t="inlineStr">
@@ -48874,7 +48885,7 @@
       </c>
       <c r="L769" t="inlineStr">
         <is>
-          <t>HUNTED Day 8 | IG profile not found (Day 8 batch)</t>
+          <t>HUNTED Day 8 | IG profile not found (Day 8 batch) | EXCLUDED (Day 9 QA): dead domain academinalegiovii.com</t>
         </is>
       </c>
       <c r="M769" t="inlineStr">
@@ -48901,7 +48912,7 @@
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>Club de Boxeo, Alicante: Horario, Precio y Op</t>
+          <t>SGO Wellness</t>
         </is>
       </c>
       <c r="C770" t="inlineStr">
@@ -48935,7 +48946,7 @@
       </c>
       <c r="L770" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M770" t="inlineStr">
@@ -48996,7 +49007,7 @@
       </c>
       <c r="L771" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M771" t="inlineStr">
@@ -49057,7 +49068,7 @@
       </c>
       <c r="L772" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | EXCLUDED (Day 9 QA): federation fboxcv.com - not a buyer</t>
         </is>
       </c>
       <c r="M772" t="inlineStr">
@@ -49118,7 +49129,7 @@
       </c>
       <c r="L773" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M773" t="inlineStr">
@@ -49145,7 +49156,7 @@
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>Clases De Boxeo, Taekwondo Y Entrenamiento Pe</t>
+          <t>In Legatum Vigo</t>
         </is>
       </c>
       <c r="C774" t="inlineStr">
@@ -49179,7 +49190,7 @@
       </c>
       <c r="L774" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M774" t="inlineStr">
@@ -49206,7 +49217,7 @@
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>Club de boxeo</t>
+          <t>Gimnasio Arena Vigo</t>
         </is>
       </c>
       <c r="C775" t="inlineStr">
@@ -49240,7 +49251,7 @@
       </c>
       <c r="L775" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M775" t="inlineStr">
@@ -49267,7 +49278,7 @@
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>Boxeo</t>
+          <t>Coliseum Vigo</t>
         </is>
       </c>
       <c r="C776" t="inlineStr">
@@ -49301,7 +49312,7 @@
       </c>
       <c r="L776" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M776" t="inlineStr">
@@ -49328,7 +49339,7 @@
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>Florida Gym, Vigo: Horario, Precio y Opinione</t>
+          <t>Florida Gym Vigo</t>
         </is>
       </c>
       <c r="C777" t="inlineStr">
@@ -49362,7 +49373,7 @@
       </c>
       <c r="L777" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M777" t="inlineStr">
@@ -49389,7 +49400,7 @@
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>¿Dónde boxeo?</t>
+          <t>La Vieja Escuela Gym</t>
         </is>
       </c>
       <c r="C778" t="inlineStr">
@@ -49423,7 +49434,7 @@
       </c>
       <c r="L778" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M778" t="inlineStr">
@@ -49450,7 +49461,7 @@
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>Contactos</t>
+          <t>Braga Open Boxing</t>
         </is>
       </c>
       <c r="C779" t="inlineStr">
@@ -49484,7 +49495,7 @@
       </c>
       <c r="L779" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M779" t="inlineStr">
@@ -49545,7 +49556,7 @@
       </c>
       <c r="L780" t="inlineStr">
         <is>
-          <t>HUNTED Day 8</t>
+          <t>HUNTED Day 8 | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M780" t="inlineStr">
@@ -49610,7 +49621,7 @@
       </c>
       <c r="L781" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-21) | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M781" t="inlineStr"/>
@@ -49712,7 +49723,7 @@
       </c>
       <c r="L783" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-21) | WA sent (Day 8 manual wave, 2026-10-21) | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M783" t="inlineStr"/>
@@ -49765,7 +49776,7 @@
       </c>
       <c r="L784" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-21) | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M784" t="inlineStr"/>
@@ -49814,7 +49825,7 @@
       </c>
       <c r="L785" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-21) | WA sent (Day 9) - verified transcript</t>
         </is>
       </c>
       <c r="M785" t="inlineStr"/>
@@ -49867,7 +49878,7 @@
       </c>
       <c r="L786" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-21) | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M786" t="inlineStr"/>
@@ -49920,7 +49931,7 @@
       </c>
       <c r="L787" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-21) | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M787" t="inlineStr"/>
@@ -49973,7 +49984,7 @@
       </c>
       <c r="L788" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-21) | COMPLETE: email sent (Day 9, 2026-10-21) | WA retry-queued (Day 9: WA session died before attempt)</t>
         </is>
       </c>
       <c r="M788" t="inlineStr"/>
@@ -50026,7 +50037,7 @@
       </c>
       <c r="L789" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-21) | WA sent (Day 8 manual wave, 2026-10-21) | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M789" t="inlineStr"/>
@@ -50128,7 +50139,7 @@
       </c>
       <c r="L791" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-21) | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M791" t="inlineStr"/>
@@ -50226,7 +50237,7 @@
       </c>
       <c r="L793" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-21) | WA retry-queued (Day 9: WA session died before attempt)</t>
         </is>
       </c>
       <c r="M793" t="inlineStr"/>
@@ -50279,7 +50290,7 @@
       </c>
       <c r="L794" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-21) | WA sent (Day 8 manual wave, 2026-10-21) | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M794" t="inlineStr"/>
@@ -50430,7 +50441,7 @@
       </c>
       <c r="L797" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-21) | COMPLETE: email sent (Day 9, 2026-10-21)</t>
         </is>
       </c>
       <c r="M797" t="inlineStr"/>
@@ -50479,7 +50490,7 @@
       </c>
       <c r="L798" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-21) | WA retry-queued (Day 9: WA session died before attempt)</t>
         </is>
       </c>
       <c r="M798" t="inlineStr"/>
@@ -50528,7 +50539,7 @@
       </c>
       <c r="L799" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-21) | WA retry-queued (Day 9: WA session died before attempt)</t>
         </is>
       </c>
       <c r="M799" t="inlineStr"/>
@@ -50683,7 +50694,7 @@
       </c>
       <c r="L802" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-21) | WA sent (Day 8 manual wave, 2026-10-21)</t>
         </is>
       </c>
       <c r="M802" t="inlineStr"/>
@@ -50736,7 +50747,7 @@
       </c>
       <c r="L803" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-21) | WA sent (Day 8 manual wave, 2026-10-21)</t>
         </is>
       </c>
       <c r="M803" t="inlineStr"/>
@@ -50834,7 +50845,7 @@
       </c>
       <c r="L805" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-21) | WA retry-queued (Day 9: WA session died before attempt)</t>
         </is>
       </c>
       <c r="M805" t="inlineStr"/>
@@ -50883,7 +50894,7 @@
       </c>
       <c r="L806" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-21) | WA retry-queued (Day 9: WA session died before attempt)</t>
         </is>
       </c>
       <c r="M806" t="inlineStr"/>
@@ -50936,7 +50947,7 @@
       </c>
       <c r="L807" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-21) | WA sent (Day 8 manual wave, 2026-10-21)</t>
         </is>
       </c>
       <c r="M807" t="inlineStr"/>
@@ -51079,7 +51090,7 @@
       </c>
       <c r="L810" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-21) | WA retry-queued (Day 9: WA session died before attempt)</t>
         </is>
       </c>
       <c r="M810" t="inlineStr"/>
@@ -51181,7 +51192,7 @@
       </c>
       <c r="L812" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-21) | WA sent (Day 8 manual wave, 2026-10-21)</t>
         </is>
       </c>
       <c r="M812" t="inlineStr"/>
@@ -51234,7 +51245,7 @@
       </c>
       <c r="L813" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-21) | WA sent (Day 8 manual wave, 2026-10-21)</t>
         </is>
       </c>
       <c r="M813" t="inlineStr"/>
@@ -51287,7 +51298,7 @@
       </c>
       <c r="L814" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-21) | WA sent (Day 8 manual wave, 2026-10-21)</t>
         </is>
       </c>
       <c r="M814" t="inlineStr"/>
@@ -51381,7 +51392,7 @@
       </c>
       <c r="L816" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-21) | WA retry-queued (Day 9: WA session died before attempt)</t>
         </is>
       </c>
       <c r="M816" t="inlineStr"/>
@@ -51434,7 +51445,7 @@
       </c>
       <c r="L817" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-21) | WA retry-queued (Day 9: WA session died before attempt)</t>
         </is>
       </c>
       <c r="M817" t="inlineStr"/>
@@ -51532,7 +51543,7 @@
       </c>
       <c r="L819" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-21) | WA sent (Day 8 manual wave, 2026-10-21)</t>
         </is>
       </c>
       <c r="M819" t="inlineStr"/>
@@ -57384,7 +57395,7 @@
       </c>
       <c r="L935" t="inlineStr">
         <is>
-          <t>HUNTED (gmaps 2PM 2026-10-21)</t>
+          <t>HUNTED (gmaps 2PM 2026-10-21) | IG follow=ok dm=sent (Day 9)</t>
         </is>
       </c>
       <c r="M935" t="inlineStr"/>
@@ -58200,6 +58211,7 @@
       <c r="O951" t="inlineStr"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:O951"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -58210,34 +58222,76 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>gmaps daily scrape - 2026-10-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>New leads today</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>171</v>
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>HSN Warrior Apparels — Lead Tracker Summary</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+          <t>Generated (UTC):</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-10-21 23:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Total leads:</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>950</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>USA batch:</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>USA emails sent:</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>USA IG follow/DM done:</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>HOT leads:</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
